--- a/app/templates/informes/Humedad ASTM D2216-19/1-INF.-N-000-26-SU20-HM-V07.XLSX
+++ b/app/templates/informes/Humedad ASTM D2216-19/1-INF.-N-000-26-SU20-HM-V07.XLSX
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="24332"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="27928"/>
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Mi unidad\3.0 Formatos e informes\2026\1.0 Informe de ensayo\1.1 Informe Suelo\INFORME ACREDITADO-E ISO\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Lenovo\Documents\crmnew\api-geofal-crm\app\templates\informes\Humedad ASTM D2216-19\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{83CB10A4-D8C2-4A78-8CE2-3645BCB75D3E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8F49AAB9-6E69-47CF-A2F2-0E0EDDA7C8E0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="723" firstSheet="1" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="723" firstSheet="1" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="informe NTP" sheetId="91" state="hidden" r:id="rId1"/>
@@ -1259,7 +1259,7 @@
     <numFmt numFmtId="186" formatCode="000\-\ &quot;26&quot;"/>
     <numFmt numFmtId="187" formatCode="&quot;FORMATO F-LEM-P-SU-11.01&quot;"/>
   </numFmts>
-  <fonts count="82" x14ac:knownFonts="1">
+  <fonts count="82">
     <font>
       <sz val="10"/>
       <name val="Arial"/>
@@ -4226,44 +4226,100 @@
     <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="3" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="4" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="3" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="6" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="38" fillId="8" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="38" fillId="8" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="38" fillId="8" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="38" fillId="8" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="42" fillId="8" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="42" fillId="8" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="166" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="169" fontId="20" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="176" fontId="25" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" xfId="4" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="7" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
       <protection hidden="1"/>
     </xf>
     <xf numFmtId="0" fontId="42" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="55" fillId="4" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="55" fillId="4" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="55" fillId="4" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="55" fillId="4" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="14" fontId="8" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" xfId="4" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="7" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
       <protection hidden="1"/>
     </xf>
     <xf numFmtId="0" fontId="16" fillId="9" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
@@ -4315,88 +4371,66 @@
       <alignment horizontal="left" vertical="center" wrapText="1"/>
       <protection hidden="1"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="4" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="55" fillId="4" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="55" fillId="4" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="55" fillId="4" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="55" fillId="4" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="8" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="3" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="48" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="6" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="48" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="38" fillId="8" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="25" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="187" fontId="25" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection hidden="1"/>
     </xf>
-    <xf numFmtId="0" fontId="38" fillId="8" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection hidden="1"/>
     </xf>
-    <xf numFmtId="0" fontId="38" fillId="8" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection hidden="1"/>
     </xf>
-    <xf numFmtId="0" fontId="38" fillId="8" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection hidden="1"/>
     </xf>
-    <xf numFmtId="0" fontId="42" fillId="8" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection hidden="1"/>
     </xf>
-    <xf numFmtId="0" fontId="42" fillId="8" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="166" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="3" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="169" fontId="20" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="176" fontId="25" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="2" borderId="0" xfId="9" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="16" fillId="2" borderId="1" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="1"/>
@@ -4405,28 +4439,33 @@
       <alignment horizontal="center" vertical="center"/>
       <protection hidden="1"/>
     </xf>
-    <xf numFmtId="16" fontId="16" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="2" borderId="0" xfId="2" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="29" fillId="2" borderId="10" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="2" borderId="11" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="2" borderId="12" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="2" borderId="1" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="16" fillId="2" borderId="10" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="16" fillId="2" borderId="11" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="16" fillId="2" borderId="12" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="38" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="38" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="16" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
@@ -4452,15 +4491,6 @@
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="167" fontId="16" fillId="2" borderId="10" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="167" fontId="16" fillId="2" borderId="11" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="167" fontId="16" fillId="2" borderId="12" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="38" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection hidden="1"/>
@@ -4481,61 +4511,54 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="38" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="38" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="16" fillId="2" borderId="0" xfId="9" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="29" fillId="2" borderId="10" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="2" borderId="11" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="2" borderId="12" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="2" borderId="1" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="48" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="16" fontId="16" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="2" borderId="0" xfId="2" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="4" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="48" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="187" fontId="25" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="42" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" xfId="4" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="4" quotePrefix="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="58" fillId="0" borderId="0" xfId="4" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" xfId="4" quotePrefix="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="184" fontId="25" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
@@ -4558,9 +4581,6 @@
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="4" quotePrefix="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="3" fontId="16" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -4578,19 +4598,6 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="42" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" xfId="4" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="58" fillId="0" borderId="0" xfId="4" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" xfId="4" quotePrefix="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center"/>
       <protection locked="0"/>
@@ -4599,12 +4606,14 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="4" quotePrefix="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" xfId="3" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="169" fontId="5" fillId="0" borderId="1" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="10" xfId="3" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -4642,13 +4651,28 @@
     <xf numFmtId="167" fontId="5" fillId="0" borderId="12" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" xfId="3" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="169" fontId="5" fillId="0" borderId="1" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="59" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="59" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="62" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="181" fontId="59" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="181" fontId="59" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="181" fontId="4" fillId="2" borderId="10" xfId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="181" fontId="4" fillId="2" borderId="12" xfId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="3" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="64" fillId="2" borderId="4" xfId="6" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -4735,30 +4759,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="2" fontId="16" fillId="2" borderId="40" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="59" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="59" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="62" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="181" fontId="59" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="181" fontId="59" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="181" fontId="4" fillId="2" borderId="10" xfId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="181" fontId="4" fillId="2" borderId="12" xfId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="3" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="65" fillId="2" borderId="1" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -6173,15 +6173,15 @@
       <xdr:twoCellAnchor editAs="oneCell">
         <xdr:from>
           <xdr:col>4</xdr:col>
-          <xdr:colOff>771525</xdr:colOff>
+          <xdr:colOff>769620</xdr:colOff>
           <xdr:row>11</xdr:row>
-          <xdr:rowOff>85725</xdr:rowOff>
+          <xdr:rowOff>83820</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>6</xdr:col>
-          <xdr:colOff>476250</xdr:colOff>
+          <xdr:colOff>480060</xdr:colOff>
           <xdr:row>15</xdr:row>
-          <xdr:rowOff>57150</xdr:rowOff>
+          <xdr:rowOff>60960</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
@@ -6523,7 +6523,7 @@
 </file>
 
 <file path=xl/externalLinks/externalLink1.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <sheetNames>
       <sheetName val="-------"/>
@@ -6582,7 +6582,7 @@
 </file>
 
 <file path=xl/externalLinks/externalLink2.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <sheetNames>
       <sheetName val="datos de ecuacion del anillo"/>
@@ -6701,7 +6701,7 @@
 </file>
 
 <file path=xl/externalLinks/externalLink3.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <sheetNames>
       <sheetName val="-------"/>
@@ -6752,7 +6752,7 @@
 </file>
 
 <file path=xl/externalLinks/externalLink4.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <sheetNames>
       <sheetName val="-------"/>
@@ -6804,7 +6804,7 @@
 </file>
 
 <file path=xl/externalLinks/externalLink5.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <sheetNames>
       <sheetName val="BGA"/>
@@ -6836,7 +6836,7 @@
 </file>
 
 <file path=xl/externalLinks/externalLink6.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <sheetNames>
       <sheetName val="-------"/>
@@ -7542,29 +7542,29 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr codeName="Hoja2"/>
   <dimension ref="A1:Z101"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="10.28515625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="10.33203125" defaultRowHeight="13.8"/>
   <cols>
-    <col min="1" max="1" width="16.28515625" style="15" customWidth="1"/>
+    <col min="1" max="1" width="16.33203125" style="15" customWidth="1"/>
     <col min="2" max="2" width="2" style="15" customWidth="1"/>
-    <col min="3" max="5" width="9.7109375" style="15" customWidth="1"/>
-    <col min="6" max="6" width="6.7109375" style="15" customWidth="1"/>
-    <col min="7" max="8" width="9.7109375" style="15" customWidth="1"/>
-    <col min="9" max="9" width="8.85546875" style="15" customWidth="1"/>
-    <col min="10" max="10" width="1.5703125" style="15" customWidth="1"/>
-    <col min="11" max="11" width="13.5703125" style="15" customWidth="1"/>
-    <col min="12" max="13" width="6.42578125" style="15" customWidth="1"/>
+    <col min="3" max="5" width="9.6640625" style="15" customWidth="1"/>
+    <col min="6" max="6" width="6.6640625" style="15" customWidth="1"/>
+    <col min="7" max="8" width="9.6640625" style="15" customWidth="1"/>
+    <col min="9" max="9" width="8.88671875" style="15" customWidth="1"/>
+    <col min="10" max="10" width="1.5546875" style="15" customWidth="1"/>
+    <col min="11" max="11" width="13.5546875" style="15" customWidth="1"/>
+    <col min="12" max="13" width="6.44140625" style="15" customWidth="1"/>
     <col min="14" max="14" width="8" style="15" customWidth="1"/>
-    <col min="15" max="15" width="10.28515625" style="15"/>
-    <col min="16" max="16" width="18.28515625" style="15" customWidth="1"/>
-    <col min="17" max="17" width="10.28515625" style="15"/>
+    <col min="15" max="15" width="10.33203125" style="15"/>
+    <col min="16" max="16" width="18.33203125" style="15" customWidth="1"/>
+    <col min="17" max="17" width="10.33203125" style="15"/>
     <col min="18" max="18" width="12" style="15" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="11.42578125" style="15" customWidth="1"/>
-    <col min="20" max="21" width="10.28515625" style="15"/>
-    <col min="22" max="22" width="12.42578125" style="15" customWidth="1"/>
-    <col min="23" max="16384" width="10.28515625" style="15"/>
+    <col min="19" max="19" width="11.44140625" style="15" customWidth="1"/>
+    <col min="20" max="21" width="10.33203125" style="15"/>
+    <col min="22" max="22" width="12.44140625" style="15" customWidth="1"/>
+    <col min="23" max="16384" width="10.33203125" style="15"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:18" ht="15.75" customHeight="1">
       <c r="A1" s="13"/>
       <c r="B1" s="13"/>
       <c r="C1" s="13"/>
@@ -7574,7 +7574,7 @@
       <c r="G1" s="14"/>
       <c r="H1" s="14"/>
     </row>
-    <row r="2" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:18" ht="15.75" customHeight="1">
       <c r="A2" s="13"/>
       <c r="B2" s="13"/>
       <c r="C2" s="13"/>
@@ -7584,7 +7584,7 @@
       <c r="G2" s="14"/>
       <c r="H2" s="14"/>
     </row>
-    <row r="3" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:18" ht="15.75" customHeight="1">
       <c r="A3" s="13"/>
       <c r="B3" s="13"/>
       <c r="C3" s="13"/>
@@ -7594,7 +7594,7 @@
       <c r="G3" s="14"/>
       <c r="H3" s="14"/>
     </row>
-    <row r="4" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:18" ht="15.75" customHeight="1">
       <c r="A4" s="13"/>
       <c r="B4" s="13"/>
       <c r="C4" s="13"/>
@@ -7604,7 +7604,7 @@
       <c r="G4" s="14"/>
       <c r="H4" s="14"/>
     </row>
-    <row r="5" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:18" ht="15.75" customHeight="1">
       <c r="A5" s="16"/>
       <c r="B5" s="16"/>
       <c r="C5" s="16"/>
@@ -7617,7 +7617,7 @@
       <c r="J5" s="16"/>
       <c r="K5" s="16"/>
     </row>
-    <row r="6" spans="1:18" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:18" ht="15.9" customHeight="1">
       <c r="A6" s="16"/>
       <c r="B6" s="16"/>
       <c r="C6" s="16"/>
@@ -7630,41 +7630,41 @@
       <c r="J6" s="16"/>
       <c r="K6" s="16"/>
     </row>
-    <row r="7" spans="1:18" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="567" t="s">
+    <row r="7" spans="1:18" ht="15.9" customHeight="1">
+      <c r="A7" s="544" t="s">
         <v>0</v>
       </c>
-      <c r="B7" s="567"/>
-      <c r="C7" s="567"/>
-      <c r="D7" s="567"/>
-      <c r="E7" s="567"/>
-      <c r="F7" s="567"/>
-      <c r="G7" s="567"/>
-      <c r="H7" s="567"/>
-      <c r="I7" s="567"/>
-      <c r="J7" s="567"/>
-      <c r="K7" s="567"/>
-    </row>
-    <row r="8" spans="1:18" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="587">
+      <c r="B7" s="544"/>
+      <c r="C7" s="544"/>
+      <c r="D7" s="544"/>
+      <c r="E7" s="544"/>
+      <c r="F7" s="544"/>
+      <c r="G7" s="544"/>
+      <c r="H7" s="544"/>
+      <c r="I7" s="544"/>
+      <c r="J7" s="544"/>
+      <c r="K7" s="544"/>
+    </row>
+    <row r="8" spans="1:18" ht="15.9" customHeight="1">
+      <c r="A8" s="565">
         <f>K13</f>
         <v>15</v>
       </c>
-      <c r="B8" s="587"/>
-      <c r="C8" s="587"/>
-      <c r="D8" s="587"/>
-      <c r="E8" s="587"/>
-      <c r="F8" s="587"/>
-      <c r="G8" s="587"/>
-      <c r="H8" s="587"/>
-      <c r="I8" s="587"/>
-      <c r="J8" s="587"/>
-      <c r="K8" s="587"/>
-    </row>
-    <row r="9" spans="1:18" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B8" s="565"/>
+      <c r="C8" s="565"/>
+      <c r="D8" s="565"/>
+      <c r="E8" s="565"/>
+      <c r="F8" s="565"/>
+      <c r="G8" s="565"/>
+      <c r="H8" s="565"/>
+      <c r="I8" s="565"/>
+      <c r="J8" s="565"/>
+      <c r="K8" s="565"/>
+    </row>
+    <row r="9" spans="1:18" ht="15.9" customHeight="1">
       <c r="P9" s="17"/>
     </row>
-    <row r="10" spans="1:18" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:18" ht="15.9" customHeight="1">
       <c r="A10" s="19" t="s">
         <v>1</v>
       </c>
@@ -7683,7 +7683,7 @@
       <c r="J10" s="18"/>
       <c r="K10" s="18"/>
     </row>
-    <row r="11" spans="1:18" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:18" ht="15.9" customHeight="1">
       <c r="A11" s="19" t="s">
         <v>4</v>
       </c>
@@ -7712,7 +7712,7 @@
       <c r="N11" s="25"/>
       <c r="P11" s="26"/>
     </row>
-    <row r="12" spans="1:18" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:18" ht="15.9" customHeight="1">
       <c r="A12" s="19" t="s">
         <v>8</v>
       </c>
@@ -7743,7 +7743,7 @@
       <c r="Q12" s="30"/>
       <c r="R12" s="31"/>
     </row>
-    <row r="13" spans="1:18" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:18" ht="15.9" customHeight="1">
       <c r="A13" s="19" t="s">
         <v>11</v>
       </c>
@@ -7770,10 +7770,10 @@
       <c r="L13" s="25"/>
       <c r="M13" s="25"/>
       <c r="N13" s="25"/>
-      <c r="Q13" s="578"/>
-      <c r="R13" s="578"/>
-    </row>
-    <row r="14" spans="1:18" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="Q13" s="556"/>
+      <c r="R13" s="556"/>
+    </row>
+    <row r="14" spans="1:18" ht="15.9" customHeight="1">
       <c r="A14" s="167" t="s">
         <v>14</v>
       </c>
@@ -7793,51 +7793,51 @@
       <c r="Q14" s="304"/>
       <c r="R14" s="304"/>
     </row>
-    <row r="15" spans="1:18" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="579" t="s">
+    <row r="15" spans="1:18" ht="18" customHeight="1">
+      <c r="A15" s="557" t="s">
         <v>15</v>
       </c>
-      <c r="B15" s="580"/>
-      <c r="C15" s="580"/>
-      <c r="D15" s="580"/>
-      <c r="E15" s="580"/>
-      <c r="F15" s="580"/>
-      <c r="G15" s="580"/>
-      <c r="H15" s="580"/>
-      <c r="I15" s="580"/>
-      <c r="J15" s="580"/>
-      <c r="K15" s="581"/>
+      <c r="B15" s="558"/>
+      <c r="C15" s="558"/>
+      <c r="D15" s="558"/>
+      <c r="E15" s="558"/>
+      <c r="F15" s="558"/>
+      <c r="G15" s="558"/>
+      <c r="H15" s="558"/>
+      <c r="I15" s="558"/>
+      <c r="J15" s="558"/>
+      <c r="K15" s="559"/>
       <c r="L15" s="25"/>
       <c r="M15" s="25"/>
       <c r="N15" s="25"/>
       <c r="Q15" s="304"/>
       <c r="R15" s="304"/>
     </row>
-    <row r="16" spans="1:18" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="584" t="s">
+    <row r="16" spans="1:18" ht="18" customHeight="1">
+      <c r="A16" s="562" t="s">
         <v>16</v>
       </c>
-      <c r="B16" s="585"/>
-      <c r="C16" s="585"/>
-      <c r="D16" s="585"/>
-      <c r="E16" s="585"/>
-      <c r="F16" s="585"/>
-      <c r="G16" s="585"/>
-      <c r="H16" s="585"/>
-      <c r="I16" s="585"/>
-      <c r="J16" s="585"/>
-      <c r="K16" s="586"/>
+      <c r="B16" s="563"/>
+      <c r="C16" s="563"/>
+      <c r="D16" s="563"/>
+      <c r="E16" s="563"/>
+      <c r="F16" s="563"/>
+      <c r="G16" s="563"/>
+      <c r="H16" s="563"/>
+      <c r="I16" s="563"/>
+      <c r="J16" s="563"/>
+      <c r="K16" s="564"/>
       <c r="L16" s="25"/>
       <c r="M16" s="25"/>
       <c r="N16" s="25"/>
       <c r="Q16" s="304"/>
       <c r="R16" s="304"/>
     </row>
-    <row r="17" spans="1:26" ht="11.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="568" t="s">
+    <row r="17" spans="1:26" ht="11.25" customHeight="1">
+      <c r="A17" s="545" t="s">
         <v>17</v>
       </c>
-      <c r="B17" s="569"/>
+      <c r="B17" s="546"/>
       <c r="C17" s="36"/>
       <c r="D17" s="36"/>
       <c r="E17" s="36"/>
@@ -7853,9 +7853,9 @@
       <c r="Q17" s="304"/>
       <c r="R17" s="304"/>
     </row>
-    <row r="18" spans="1:26" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="570"/>
-      <c r="B18" s="571"/>
+    <row r="18" spans="1:26" ht="15.9" customHeight="1">
+      <c r="A18" s="547"/>
+      <c r="B18" s="548"/>
       <c r="C18" s="39"/>
       <c r="D18" s="39"/>
       <c r="E18" s="39"/>
@@ -7887,7 +7887,7 @@
       <c r="Y18" s="83"/>
       <c r="Z18" s="84"/>
     </row>
-    <row r="19" spans="1:26" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:26" ht="15.9" customHeight="1">
       <c r="A19" s="40" t="s">
         <v>20</v>
       </c>
@@ -7929,7 +7929,7 @@
       <c r="Y19" s="89"/>
       <c r="Z19" s="90"/>
     </row>
-    <row r="20" spans="1:26" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:26" ht="15.9" customHeight="1">
       <c r="A20" s="40" t="s">
         <v>25</v>
       </c>
@@ -7971,7 +7971,7 @@
       <c r="Y20" s="89"/>
       <c r="Z20" s="90"/>
     </row>
-    <row r="21" spans="1:26" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:26" ht="15.9" customHeight="1">
       <c r="A21" s="40" t="s">
         <v>29</v>
       </c>
@@ -8000,10 +8000,10 @@
       <c r="P21" s="93" t="s">
         <v>32</v>
       </c>
-      <c r="Q21" s="550">
+      <c r="Q21" s="588">
         <v>44090</v>
       </c>
-      <c r="R21" s="550"/>
+      <c r="R21" s="588"/>
       <c r="S21" s="94"/>
       <c r="T21" s="95"/>
       <c r="U21" s="94"/>
@@ -8013,7 +8013,7 @@
       <c r="Y21" s="96"/>
       <c r="Z21" s="97"/>
     </row>
-    <row r="22" spans="1:26" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:26" ht="15" customHeight="1">
       <c r="A22" s="155" t="s">
         <v>33</v>
       </c>
@@ -8044,23 +8044,23 @@
       <c r="Y22"/>
       <c r="Z22"/>
     </row>
-    <row r="23" spans="1:26" ht="13.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:26" ht="13.5" customHeight="1" thickBot="1">
       <c r="A23" s="168"/>
-      <c r="B23" s="588"/>
-      <c r="C23" s="588"/>
+      <c r="B23" s="566"/>
+      <c r="C23" s="566"/>
       <c r="D23" s="306"/>
       <c r="E23" s="306"/>
       <c r="F23" s="306"/>
       <c r="G23" s="306"/>
       <c r="H23" s="306"/>
-      <c r="I23" s="588"/>
-      <c r="J23" s="588"/>
+      <c r="I23" s="566"/>
+      <c r="J23" s="566"/>
       <c r="K23" s="168"/>
       <c r="L23" s="25"/>
       <c r="M23" s="49"/>
       <c r="N23" s="49"/>
     </row>
-    <row r="24" spans="1:26" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:26" ht="17.25" customHeight="1">
       <c r="A24" s="171"/>
       <c r="B24" s="50" t="s">
         <v>35</v>
@@ -8076,8 +8076,8 @@
         <f>+R24</f>
         <v>1</v>
       </c>
-      <c r="I24" s="582"/>
-      <c r="J24" s="582"/>
+      <c r="I24" s="560"/>
+      <c r="J24" s="560"/>
       <c r="K24" s="305"/>
       <c r="L24" s="25"/>
       <c r="M24" s="54"/>
@@ -8091,23 +8091,23 @@
       <c r="R24" s="56">
         <v>1</v>
       </c>
-      <c r="S24" s="551" t="s">
+      <c r="S24" s="549" t="s">
         <v>37</v>
       </c>
       <c r="U24" s="56">
         <v>2</v>
       </c>
-      <c r="V24" s="551" t="s">
+      <c r="V24" s="549" t="s">
         <v>37</v>
       </c>
-      <c r="W24" s="546" t="s">
+      <c r="W24" s="584" t="s">
         <v>38</v>
       </c>
-      <c r="X24" s="546"/>
-      <c r="Y24" s="546"/>
-      <c r="Z24" s="547"/>
-    </row>
-    <row r="25" spans="1:26" ht="17.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="X24" s="584"/>
+      <c r="Y24" s="584"/>
+      <c r="Z24" s="585"/>
+    </row>
+    <row r="25" spans="1:26" ht="17.25" customHeight="1" thickBot="1">
       <c r="A25" s="171"/>
       <c r="B25" s="50" t="s">
         <v>39</v>
@@ -8123,8 +8123,8 @@
         <f>+R25</f>
         <v>1</v>
       </c>
-      <c r="I25" s="582"/>
-      <c r="J25" s="582"/>
+      <c r="I25" s="560"/>
+      <c r="J25" s="560"/>
       <c r="K25" s="305"/>
       <c r="L25" s="25"/>
       <c r="M25" s="54"/>
@@ -8138,17 +8138,17 @@
       <c r="R25" s="59">
         <v>1</v>
       </c>
-      <c r="S25" s="551"/>
+      <c r="S25" s="549"/>
       <c r="U25" s="59">
         <v>2</v>
       </c>
-      <c r="V25" s="551"/>
-      <c r="W25" s="548"/>
-      <c r="X25" s="548"/>
-      <c r="Y25" s="548"/>
-      <c r="Z25" s="549"/>
-    </row>
-    <row r="26" spans="1:26" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="V25" s="549"/>
+      <c r="W25" s="586"/>
+      <c r="X25" s="586"/>
+      <c r="Y25" s="586"/>
+      <c r="Z25" s="587"/>
+    </row>
+    <row r="26" spans="1:26" ht="17.25" customHeight="1">
       <c r="A26" s="171"/>
       <c r="B26" s="50" t="s">
         <v>40</v>
@@ -8164,8 +8164,8 @@
         <f>S26</f>
         <v>794.6995891401001</v>
       </c>
-      <c r="I26" s="583"/>
-      <c r="J26" s="583"/>
+      <c r="I26" s="561"/>
+      <c r="J26" s="561"/>
       <c r="K26" s="169"/>
       <c r="L26" s="60"/>
       <c r="M26" s="54"/>
@@ -8191,7 +8191,7 @@
         <v>793.69958965710009</v>
       </c>
     </row>
-    <row r="27" spans="1:26" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:26" ht="17.25" customHeight="1">
       <c r="A27" s="171"/>
       <c r="B27" s="50" t="s">
         <v>43</v>
@@ -8234,7 +8234,7 @@
         <v>775.79959891139993</v>
       </c>
     </row>
-    <row r="28" spans="1:26" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:26" ht="17.25" customHeight="1">
       <c r="A28" s="171"/>
       <c r="B28" s="50" t="s">
         <v>45</v>
@@ -8277,7 +8277,7 @@
         <v>775.79959891139993</v>
       </c>
     </row>
-    <row r="29" spans="1:26" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:26" ht="17.25" customHeight="1">
       <c r="A29" s="171"/>
       <c r="B29" s="50" t="s">
         <v>47</v>
@@ -8320,7 +8320,7 @@
         <v>775.79959891139993</v>
       </c>
     </row>
-    <row r="30" spans="1:26" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:26" ht="17.25" customHeight="1">
       <c r="A30" s="171"/>
       <c r="B30" s="50" t="s">
         <v>49</v>
@@ -8365,7 +8365,7 @@
         <v>17.899990745700165</v>
       </c>
     </row>
-    <row r="31" spans="1:26" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:26" ht="17.25" customHeight="1">
       <c r="A31" s="171"/>
       <c r="B31" s="50" t="s">
         <v>51</v>
@@ -8408,7 +8408,7 @@
         <v>163.1999156256</v>
       </c>
     </row>
-    <row r="32" spans="1:26" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:26" ht="17.25" customHeight="1">
       <c r="A32" s="62"/>
       <c r="B32" s="50" t="s">
         <v>53</v>
@@ -8453,7 +8453,7 @@
         <v>612.59968328579998</v>
       </c>
     </row>
-    <row r="33" spans="1:22" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:22" ht="17.25" customHeight="1">
       <c r="A33" s="171"/>
       <c r="B33" s="142" t="s">
         <v>55</v>
@@ -8498,7 +8498,7 @@
         <v>2.9219719229513821</v>
       </c>
     </row>
-    <row r="34" spans="1:22" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:22" ht="15.9" customHeight="1">
       <c r="B34" s="68" t="s">
         <v>58</v>
       </c>
@@ -8507,35 +8507,35 @@
       <c r="L34" s="25"/>
       <c r="M34" s="25"/>
       <c r="N34" s="25"/>
-      <c r="P34" s="572" t="s">
+      <c r="P34" s="550" t="s">
         <v>59</v>
       </c>
-      <c r="Q34" s="573"/>
-      <c r="R34" s="576" t="s">
+      <c r="Q34" s="551"/>
+      <c r="R34" s="554" t="s">
         <v>60</v>
       </c>
-      <c r="S34" s="576" t="s">
+      <c r="S34" s="554" t="s">
         <v>61</v>
       </c>
       <c r="T34" s="132"/>
       <c r="U34" s="132"/>
       <c r="V34" s="132"/>
     </row>
-    <row r="35" spans="1:22" ht="2.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:22" ht="2.25" customHeight="1">
       <c r="J35" s="61"/>
       <c r="K35" s="61"/>
       <c r="L35" s="25"/>
       <c r="M35" s="25"/>
       <c r="N35" s="25"/>
-      <c r="P35" s="574"/>
-      <c r="Q35" s="575"/>
-      <c r="R35" s="577"/>
-      <c r="S35" s="577"/>
+      <c r="P35" s="552"/>
+      <c r="Q35" s="553"/>
+      <c r="R35" s="555"/>
+      <c r="S35" s="555"/>
       <c r="T35" s="133"/>
       <c r="U35" s="132"/>
       <c r="V35" s="132"/>
     </row>
-    <row r="36" spans="1:22" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:22" ht="15.9" customHeight="1">
       <c r="A36" s="170" t="s">
         <v>62</v>
       </c>
@@ -8566,7 +8566,7 @@
       <c r="U36"/>
       <c r="V36" s="98"/>
     </row>
-    <row r="37" spans="1:22" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:22" ht="15.9" customHeight="1">
       <c r="A37" s="164" t="s">
         <v>66</v>
       </c>
@@ -8599,7 +8599,7 @@
       <c r="U37" s="135"/>
       <c r="V37" s="135"/>
     </row>
-    <row r="38" spans="1:22" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:22" ht="14.25" customHeight="1">
       <c r="A38" s="164" t="s">
         <v>71</v>
       </c>
@@ -8618,7 +8618,7 @@
       <c r="L38" s="25"/>
       <c r="M38" s="25"/>
       <c r="N38" s="25"/>
-      <c r="P38" s="554" t="s">
+      <c r="P38" s="570" t="s">
         <v>72</v>
       </c>
       <c r="Q38" s="108">
@@ -8634,17 +8634,17 @@
       <c r="U38" s="135"/>
       <c r="V38" s="135"/>
     </row>
-    <row r="39" spans="1:22" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A39" s="552" t="s">
+    <row r="39" spans="1:22" ht="14.25" customHeight="1">
+      <c r="A39" s="567" t="s">
         <v>75</v>
       </c>
-      <c r="B39" s="552"/>
-      <c r="C39" s="552"/>
-      <c r="D39" s="552"/>
-      <c r="E39" s="552"/>
-      <c r="F39" s="552"/>
-      <c r="G39" s="552"/>
-      <c r="H39" s="553"/>
+      <c r="B39" s="567"/>
+      <c r="C39" s="567"/>
+      <c r="D39" s="567"/>
+      <c r="E39" s="567"/>
+      <c r="F39" s="567"/>
+      <c r="G39" s="567"/>
+      <c r="H39" s="568"/>
       <c r="I39" s="166" t="s">
         <v>67</v>
       </c>
@@ -8653,7 +8653,7 @@
       <c r="L39" s="25"/>
       <c r="M39" s="25"/>
       <c r="N39" s="25"/>
-      <c r="P39" s="555"/>
+      <c r="P39" s="571"/>
       <c r="Q39" s="108">
         <v>0.75</v>
       </c>
@@ -8665,7 +8665,7 @@
       <c r="U39" s="135"/>
       <c r="V39" s="135"/>
     </row>
-    <row r="40" spans="1:22" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:22" ht="8.25" customHeight="1">
       <c r="A40" s="125"/>
       <c r="B40" s="126"/>
       <c r="C40" s="126"/>
@@ -8678,7 +8678,7 @@
       <c r="L40" s="25"/>
       <c r="M40" s="25"/>
       <c r="N40" s="25"/>
-      <c r="P40" s="555"/>
+      <c r="P40" s="571"/>
       <c r="Q40" s="108">
         <v>1.5</v>
       </c>
@@ -8690,7 +8690,7 @@
       <c r="U40" s="135"/>
       <c r="V40" s="135"/>
     </row>
-    <row r="41" spans="1:22" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:22" ht="15.9" customHeight="1">
       <c r="A41" s="69" t="s">
         <v>78</v>
       </c>
@@ -8705,7 +8705,7 @@
       <c r="L41" s="25"/>
       <c r="M41" s="25"/>
       <c r="N41" s="25"/>
-      <c r="P41" s="556"/>
+      <c r="P41" s="572"/>
       <c r="Q41" s="104">
         <v>3</v>
       </c>
@@ -8717,7 +8717,7 @@
       <c r="U41" s="135"/>
       <c r="V41" s="135"/>
     </row>
-    <row r="42" spans="1:22" ht="12" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:22" ht="12" customHeight="1">
       <c r="A42" s="153" t="s">
         <v>80</v>
       </c>
@@ -8746,7 +8746,7 @@
       <c r="U42" s="137"/>
       <c r="V42" s="137"/>
     </row>
-    <row r="43" spans="1:22" ht="12" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:22" ht="12" customHeight="1">
       <c r="A43" s="153" t="s">
         <v>82</v>
       </c>
@@ -8776,7 +8776,7 @@
       <c r="U43" s="99"/>
       <c r="V43" s="98"/>
     </row>
-    <row r="44" spans="1:22" ht="12" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:22" ht="12" customHeight="1">
       <c r="A44" s="153" t="s">
         <v>85</v>
       </c>
@@ -8808,7 +8808,7 @@
       <c r="U44" s="100"/>
       <c r="V44" s="101"/>
     </row>
-    <row r="45" spans="1:22" ht="12" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:22" ht="12" customHeight="1">
       <c r="A45" s="153" t="s">
         <v>87</v>
       </c>
@@ -8836,9 +8836,9 @@
       </c>
       <c r="T45" s="86"/>
       <c r="U45" s="102"/>
-      <c r="V45" s="545"/>
-    </row>
-    <row r="46" spans="1:22" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="V45" s="569"/>
+    </row>
+    <row r="46" spans="1:22" ht="15.9" customHeight="1">
       <c r="C46" s="42"/>
       <c r="D46" s="67"/>
       <c r="E46" s="67"/>
@@ -8862,9 +8862,9 @@
       </c>
       <c r="T46" s="86"/>
       <c r="U46" s="106"/>
-      <c r="V46" s="545"/>
-    </row>
-    <row r="47" spans="1:22" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="V46" s="569"/>
+    </row>
+    <row r="47" spans="1:22" ht="12.75" customHeight="1">
       <c r="A47" s="154" t="s">
         <v>91</v>
       </c>
@@ -8894,7 +8894,7 @@
       <c r="U47" s="106"/>
       <c r="V47" s="107"/>
     </row>
-    <row r="48" spans="1:22" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:22" ht="12.75" customHeight="1">
       <c r="A48" s="154" t="s">
         <v>93</v>
       </c>
@@ -8915,7 +8915,7 @@
       <c r="U48" s="109"/>
       <c r="V48" s="107"/>
     </row>
-    <row r="49" spans="1:22" ht="10.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:22" ht="10.5" customHeight="1">
       <c r="A49" s="77" t="s">
         <v>94</v>
       </c>
@@ -8932,7 +8932,7 @@
       <c r="U49" s="109"/>
       <c r="V49" s="107"/>
     </row>
-    <row r="50" spans="1:22" ht="10.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:22" ht="10.5" customHeight="1">
       <c r="A50" s="77" t="s">
         <v>95</v>
       </c>
@@ -8950,64 +8950,64 @@
       <c r="U50" s="110"/>
       <c r="V50" s="107"/>
     </row>
-    <row r="51" spans="1:22" ht="33" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A51" s="566" t="s">
+    <row r="51" spans="1:22" ht="33" customHeight="1">
+      <c r="A51" s="582" t="s">
         <v>96</v>
       </c>
-      <c r="B51" s="566"/>
-      <c r="C51" s="566"/>
-      <c r="D51" s="566"/>
-      <c r="E51" s="566"/>
-      <c r="F51" s="566"/>
-      <c r="G51" s="566"/>
-      <c r="H51" s="566"/>
-      <c r="I51" s="566"/>
-      <c r="J51" s="566"/>
-      <c r="K51" s="566"/>
+      <c r="B51" s="582"/>
+      <c r="C51" s="582"/>
+      <c r="D51" s="582"/>
+      <c r="E51" s="582"/>
+      <c r="F51" s="582"/>
+      <c r="G51" s="582"/>
+      <c r="H51" s="582"/>
+      <c r="I51" s="582"/>
+      <c r="J51" s="582"/>
+      <c r="K51" s="582"/>
       <c r="T51" s="86"/>
       <c r="U51" s="109"/>
       <c r="V51" s="107"/>
     </row>
-    <row r="52" spans="1:22" ht="11.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="H52" s="565" t="s">
+    <row r="52" spans="1:22" ht="11.25" customHeight="1">
+      <c r="H52" s="581" t="s">
         <v>97</v>
       </c>
-      <c r="I52" s="565"/>
-      <c r="J52" s="565"/>
-      <c r="K52" s="565"/>
+      <c r="I52" s="581"/>
+      <c r="J52" s="581"/>
+      <c r="K52" s="581"/>
       <c r="T52" s="86"/>
       <c r="U52" s="109"/>
       <c r="V52" s="107"/>
     </row>
-    <row r="53" spans="1:22" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:22" ht="15.9" customHeight="1">
       <c r="J53" s="70"/>
       <c r="K53" s="71"/>
       <c r="T53" s="117"/>
       <c r="U53" s="109"/>
       <c r="V53" s="107"/>
     </row>
-    <row r="54" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:22">
       <c r="J54" s="72"/>
       <c r="K54" s="71"/>
-      <c r="T54" s="544"/>
+      <c r="T54" s="583"/>
       <c r="U54" s="109"/>
       <c r="V54" s="107"/>
     </row>
-    <row r="55" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:22">
       <c r="J55"/>
       <c r="K55" s="71"/>
-      <c r="T55" s="544"/>
+      <c r="T55" s="583"/>
       <c r="U55" s="109"/>
       <c r="V55" s="107"/>
     </row>
-    <row r="56" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:22">
       <c r="J56"/>
       <c r="K56" s="71"/>
       <c r="T56" s="122"/>
       <c r="U56" s="109"/>
       <c r="V56" s="107"/>
     </row>
-    <row r="57" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:22">
       <c r="A57"/>
       <c r="B57"/>
       <c r="C57"/>
@@ -9022,7 +9022,7 @@
       <c r="U57" s="109"/>
       <c r="V57" s="107"/>
     </row>
-    <row r="58" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:22">
       <c r="A58" s="73"/>
       <c r="B58" s="73"/>
       <c r="C58" s="73"/>
@@ -9035,61 +9035,61 @@
       <c r="J58" s="73"/>
       <c r="K58" s="73"/>
     </row>
-    <row r="59" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A59" s="557" t="s">
+    <row r="59" spans="1:22">
+      <c r="A59" s="573" t="s">
         <v>98</v>
       </c>
-      <c r="B59" s="559"/>
-      <c r="C59" s="559"/>
-      <c r="D59" s="559"/>
-      <c r="E59" s="559"/>
-      <c r="F59" s="559"/>
-      <c r="G59" s="559"/>
-      <c r="H59" s="559"/>
-      <c r="I59" s="559"/>
-      <c r="J59" s="559"/>
-      <c r="K59" s="560"/>
-    </row>
-    <row r="60" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A60" s="558"/>
-      <c r="B60" s="561"/>
-      <c r="C60" s="561"/>
-      <c r="D60" s="561"/>
-      <c r="E60" s="561"/>
-      <c r="F60" s="561"/>
-      <c r="G60" s="561"/>
-      <c r="H60" s="561"/>
-      <c r="I60" s="561"/>
-      <c r="J60" s="561"/>
-      <c r="K60" s="562"/>
-    </row>
-    <row r="61" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="B59" s="575"/>
+      <c r="C59" s="575"/>
+      <c r="D59" s="575"/>
+      <c r="E59" s="575"/>
+      <c r="F59" s="575"/>
+      <c r="G59" s="575"/>
+      <c r="H59" s="575"/>
+      <c r="I59" s="575"/>
+      <c r="J59" s="575"/>
+      <c r="K59" s="576"/>
+    </row>
+    <row r="60" spans="1:22">
+      <c r="A60" s="574"/>
+      <c r="B60" s="577"/>
+      <c r="C60" s="577"/>
+      <c r="D60" s="577"/>
+      <c r="E60" s="577"/>
+      <c r="F60" s="577"/>
+      <c r="G60" s="577"/>
+      <c r="H60" s="577"/>
+      <c r="I60" s="577"/>
+      <c r="J60" s="577"/>
+      <c r="K60" s="578"/>
+    </row>
+    <row r="61" spans="1:22">
       <c r="A61" s="74"/>
-      <c r="B61" s="561"/>
-      <c r="C61" s="561"/>
-      <c r="D61" s="561"/>
-      <c r="E61" s="561"/>
-      <c r="F61" s="561"/>
-      <c r="G61" s="561"/>
-      <c r="H61" s="561"/>
-      <c r="I61" s="561"/>
-      <c r="J61" s="561"/>
-      <c r="K61" s="562"/>
-    </row>
-    <row r="62" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="B61" s="577"/>
+      <c r="C61" s="577"/>
+      <c r="D61" s="577"/>
+      <c r="E61" s="577"/>
+      <c r="F61" s="577"/>
+      <c r="G61" s="577"/>
+      <c r="H61" s="577"/>
+      <c r="I61" s="577"/>
+      <c r="J61" s="577"/>
+      <c r="K61" s="578"/>
+    </row>
+    <row r="62" spans="1:22">
       <c r="A62" s="75"/>
-      <c r="B62" s="563"/>
-      <c r="C62" s="563"/>
-      <c r="D62" s="563"/>
-      <c r="E62" s="563"/>
-      <c r="F62" s="563"/>
-      <c r="G62" s="563"/>
-      <c r="H62" s="563"/>
-      <c r="I62" s="563"/>
-      <c r="J62" s="563"/>
-      <c r="K62" s="564"/>
-    </row>
-    <row r="63" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="B62" s="579"/>
+      <c r="C62" s="579"/>
+      <c r="D62" s="579"/>
+      <c r="E62" s="579"/>
+      <c r="F62" s="579"/>
+      <c r="G62" s="579"/>
+      <c r="H62" s="579"/>
+      <c r="I62" s="579"/>
+      <c r="J62" s="579"/>
+      <c r="K62" s="580"/>
+    </row>
+    <row r="63" spans="1:22">
       <c r="A63" s="76"/>
       <c r="B63" s="76"/>
       <c r="C63" s="76"/>
@@ -9102,7 +9102,7 @@
       <c r="J63" s="76"/>
       <c r="K63" s="76"/>
     </row>
-    <row r="68" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:11">
       <c r="A68"/>
       <c r="B68"/>
       <c r="C68"/>
@@ -9115,7 +9115,7 @@
       <c r="J68"/>
       <c r="K68"/>
     </row>
-    <row r="69" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:11">
       <c r="A69"/>
       <c r="B69"/>
       <c r="C69"/>
@@ -9128,139 +9128,139 @@
       <c r="J69"/>
       <c r="K69"/>
     </row>
-    <row r="77" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:11">
       <c r="H77" s="98"/>
       <c r="I77" s="98"/>
       <c r="J77" s="98"/>
       <c r="K77"/>
     </row>
-    <row r="78" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:11">
       <c r="H78"/>
       <c r="I78"/>
       <c r="J78"/>
       <c r="K78"/>
     </row>
-    <row r="79" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:11">
       <c r="H79"/>
       <c r="I79"/>
       <c r="J79"/>
       <c r="K79"/>
     </row>
-    <row r="80" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:11">
       <c r="H80"/>
       <c r="I80"/>
       <c r="J80"/>
       <c r="K80"/>
     </row>
-    <row r="81" spans="8:11" x14ac:dyDescent="0.25">
+    <row r="81" spans="8:11">
       <c r="H81"/>
       <c r="I81"/>
       <c r="J81"/>
       <c r="K81"/>
     </row>
-    <row r="82" spans="8:11" x14ac:dyDescent="0.25">
+    <row r="82" spans="8:11">
       <c r="H82" s="98"/>
       <c r="I82" s="98"/>
       <c r="J82" s="98"/>
       <c r="K82"/>
     </row>
-    <row r="83" spans="8:11" x14ac:dyDescent="0.25">
+    <row r="83" spans="8:11">
       <c r="H83" s="98"/>
       <c r="I83" s="98"/>
       <c r="J83" s="98"/>
       <c r="K83"/>
     </row>
-    <row r="84" spans="8:11" x14ac:dyDescent="0.25">
+    <row r="84" spans="8:11">
       <c r="H84" s="98"/>
       <c r="I84" s="98"/>
       <c r="J84" s="98"/>
       <c r="K84"/>
     </row>
-    <row r="85" spans="8:11" x14ac:dyDescent="0.25">
+    <row r="85" spans="8:11">
       <c r="H85" s="101"/>
       <c r="I85" s="101"/>
       <c r="J85" s="101"/>
       <c r="K85"/>
     </row>
-    <row r="86" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H86" s="545"/>
-      <c r="I86" s="545"/>
-      <c r="J86" s="545"/>
+    <row r="86" spans="8:11">
+      <c r="H86" s="569"/>
+      <c r="I86" s="569"/>
+      <c r="J86" s="569"/>
       <c r="K86"/>
     </row>
-    <row r="87" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H87" s="545"/>
-      <c r="I87" s="545"/>
-      <c r="J87" s="545"/>
+    <row r="87" spans="8:11">
+      <c r="H87" s="569"/>
+      <c r="I87" s="569"/>
+      <c r="J87" s="569"/>
       <c r="K87"/>
     </row>
-    <row r="88" spans="8:11" x14ac:dyDescent="0.25">
+    <row r="88" spans="8:11">
       <c r="H88" s="107"/>
       <c r="I88" s="107"/>
       <c r="J88" s="107"/>
       <c r="K88"/>
     </row>
-    <row r="89" spans="8:11" x14ac:dyDescent="0.25">
+    <row r="89" spans="8:11">
       <c r="H89" s="107"/>
       <c r="I89" s="107"/>
       <c r="J89" s="107"/>
       <c r="K89"/>
     </row>
-    <row r="90" spans="8:11" x14ac:dyDescent="0.25">
+    <row r="90" spans="8:11">
       <c r="H90" s="107"/>
       <c r="I90" s="107"/>
       <c r="J90" s="107"/>
       <c r="K90"/>
     </row>
-    <row r="91" spans="8:11" x14ac:dyDescent="0.25">
+    <row r="91" spans="8:11">
       <c r="H91" s="107"/>
       <c r="I91" s="107"/>
       <c r="J91" s="107"/>
       <c r="K91"/>
     </row>
-    <row r="92" spans="8:11" x14ac:dyDescent="0.25">
+    <row r="92" spans="8:11">
       <c r="H92" s="107"/>
       <c r="I92" s="107"/>
       <c r="J92" s="107"/>
       <c r="K92"/>
     </row>
-    <row r="93" spans="8:11" x14ac:dyDescent="0.25">
+    <row r="93" spans="8:11">
       <c r="H93" s="107"/>
       <c r="I93" s="107"/>
       <c r="J93" s="107"/>
       <c r="K93"/>
     </row>
-    <row r="94" spans="8:11" x14ac:dyDescent="0.25">
+    <row r="94" spans="8:11">
       <c r="H94" s="107"/>
       <c r="I94" s="107"/>
       <c r="J94" s="107"/>
       <c r="K94"/>
     </row>
-    <row r="95" spans="8:11" x14ac:dyDescent="0.25">
+    <row r="95" spans="8:11">
       <c r="H95" s="107"/>
       <c r="I95" s="107"/>
       <c r="J95" s="107"/>
       <c r="K95"/>
     </row>
-    <row r="96" spans="8:11" x14ac:dyDescent="0.25">
+    <row r="96" spans="8:11">
       <c r="H96" s="107"/>
       <c r="I96" s="107"/>
       <c r="J96" s="107"/>
       <c r="K96"/>
     </row>
-    <row r="97" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:11">
       <c r="H97" s="107"/>
       <c r="I97" s="107"/>
       <c r="J97" s="107"/>
       <c r="K97"/>
     </row>
-    <row r="98" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:11">
       <c r="H98" s="107"/>
       <c r="I98" s="107"/>
       <c r="J98" s="107"/>
       <c r="K98"/>
     </row>
-    <row r="99" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:11">
       <c r="A99"/>
       <c r="B99"/>
       <c r="C99"/>
@@ -9273,7 +9273,7 @@
       <c r="J99"/>
       <c r="K99"/>
     </row>
-    <row r="100" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:11">
       <c r="A100"/>
       <c r="B100"/>
       <c r="C100"/>
@@ -9286,7 +9286,7 @@
       <c r="J100"/>
       <c r="K100"/>
     </row>
-    <row r="101" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:11">
       <c r="A101"/>
       <c r="B101"/>
       <c r="C101"/>
@@ -9305,6 +9305,20 @@
     <protectedRange sqref="C10:C11" name="Rango3_3_1_1_1_1_1_2_1"/>
   </protectedRanges>
   <mergeCells count="29">
+    <mergeCell ref="T54:T55"/>
+    <mergeCell ref="V45:V46"/>
+    <mergeCell ref="W24:Z25"/>
+    <mergeCell ref="Q21:R21"/>
+    <mergeCell ref="S24:S25"/>
+    <mergeCell ref="A39:H39"/>
+    <mergeCell ref="H86:H87"/>
+    <mergeCell ref="I86:I87"/>
+    <mergeCell ref="J86:J87"/>
+    <mergeCell ref="P38:P41"/>
+    <mergeCell ref="A59:A60"/>
+    <mergeCell ref="B59:K62"/>
+    <mergeCell ref="H52:K52"/>
+    <mergeCell ref="A51:K51"/>
     <mergeCell ref="A7:K7"/>
     <mergeCell ref="A17:B18"/>
     <mergeCell ref="V24:V25"/>
@@ -9320,20 +9334,6 @@
     <mergeCell ref="B23:C23"/>
     <mergeCell ref="I23:J23"/>
     <mergeCell ref="I24:J24"/>
-    <mergeCell ref="A39:H39"/>
-    <mergeCell ref="H86:H87"/>
-    <mergeCell ref="I86:I87"/>
-    <mergeCell ref="J86:J87"/>
-    <mergeCell ref="P38:P41"/>
-    <mergeCell ref="A59:A60"/>
-    <mergeCell ref="B59:K62"/>
-    <mergeCell ref="H52:K52"/>
-    <mergeCell ref="A51:K51"/>
-    <mergeCell ref="T54:T55"/>
-    <mergeCell ref="V45:V46"/>
-    <mergeCell ref="W24:Z25"/>
-    <mergeCell ref="Q21:R21"/>
-    <mergeCell ref="S24:S25"/>
   </mergeCells>
   <conditionalFormatting sqref="A39">
     <cfRule type="cellIs" priority="1" stopIfTrue="1" operator="between">
@@ -9355,27 +9355,27 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B701DF6C-5F27-49B6-872C-8C68C4082771}">
   <dimension ref="A1:W63"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="10.28515625" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="10.33203125" defaultRowHeight="13.8"/>
   <cols>
-    <col min="1" max="1" width="8.7109375" style="430" customWidth="1"/>
-    <col min="2" max="2" width="3.140625" style="430" customWidth="1"/>
-    <col min="3" max="3" width="10.85546875" style="430" customWidth="1"/>
-    <col min="4" max="4" width="14.42578125" style="430" customWidth="1"/>
-    <col min="5" max="5" width="10.85546875" style="430" customWidth="1"/>
-    <col min="6" max="6" width="11.28515625" style="430" customWidth="1"/>
+    <col min="1" max="1" width="8.6640625" style="430" customWidth="1"/>
+    <col min="2" max="2" width="3.109375" style="430" customWidth="1"/>
+    <col min="3" max="3" width="10.88671875" style="430" customWidth="1"/>
+    <col min="4" max="4" width="14.44140625" style="430" customWidth="1"/>
+    <col min="5" max="5" width="10.88671875" style="430" customWidth="1"/>
+    <col min="6" max="6" width="11.33203125" style="430" customWidth="1"/>
     <col min="7" max="7" width="3" style="430" customWidth="1"/>
-    <col min="8" max="8" width="9.28515625" style="430" customWidth="1"/>
-    <col min="9" max="9" width="16.85546875" style="430" customWidth="1"/>
-    <col min="10" max="10" width="6.7109375" style="430" customWidth="1"/>
-    <col min="11" max="11" width="8.42578125" style="430" customWidth="1"/>
-    <col min="12" max="12" width="2.140625" style="430" customWidth="1"/>
-    <col min="13" max="13" width="6.42578125" style="430" customWidth="1"/>
-    <col min="14" max="14" width="9.28515625" style="430" customWidth="1"/>
-    <col min="15" max="15" width="12.42578125" style="430" customWidth="1"/>
-    <col min="16" max="16384" width="10.28515625" style="430"/>
+    <col min="8" max="8" width="9.33203125" style="430" customWidth="1"/>
+    <col min="9" max="9" width="16.88671875" style="430" customWidth="1"/>
+    <col min="10" max="10" width="6.6640625" style="430" customWidth="1"/>
+    <col min="11" max="11" width="8.44140625" style="430" customWidth="1"/>
+    <col min="12" max="12" width="2.109375" style="430" customWidth="1"/>
+    <col min="13" max="13" width="6.44140625" style="430" customWidth="1"/>
+    <col min="14" max="14" width="9.33203125" style="430" customWidth="1"/>
+    <col min="15" max="15" width="12.44140625" style="430" customWidth="1"/>
+    <col min="16" max="16384" width="10.33203125" style="430"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16" ht="12.75" customHeight="1" thickTop="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:16" ht="12.75" customHeight="1" thickTop="1">
       <c r="A1" s="461"/>
       <c r="B1" s="462"/>
       <c r="C1" s="462"/>
@@ -9389,7 +9389,7 @@
       <c r="K1" s="464"/>
       <c r="L1" s="465"/>
     </row>
-    <row r="2" spans="1:16" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:16" ht="12.75" customHeight="1">
       <c r="A2" s="466"/>
       <c r="B2" s="467"/>
       <c r="C2" s="467"/>
@@ -9405,7 +9405,7 @@
       </c>
       <c r="P2" s="451"/>
     </row>
-    <row r="3" spans="1:16" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:16" ht="12.75" customHeight="1">
       <c r="A3" s="466"/>
       <c r="B3" s="467"/>
       <c r="C3" s="467"/>
@@ -9421,7 +9421,7 @@
       </c>
       <c r="P3" s="452"/>
     </row>
-    <row r="4" spans="1:16" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:16" ht="12.75" customHeight="1">
       <c r="A4" s="466"/>
       <c r="B4" s="467"/>
       <c r="C4" s="467"/>
@@ -9437,7 +9437,7 @@
       </c>
       <c r="P4" s="452"/>
     </row>
-    <row r="5" spans="1:16" ht="12.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:16" ht="12.75" customHeight="1" thickBot="1">
       <c r="A5" s="470"/>
       <c r="B5" s="471"/>
       <c r="C5" s="471"/>
@@ -9455,7 +9455,7 @@
       </c>
       <c r="P5" s="452"/>
     </row>
-    <row r="6" spans="1:16" ht="6.75" customHeight="1" thickTop="1" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:16" ht="6.75" customHeight="1" thickTop="1">
       <c r="A6" s="473"/>
       <c r="B6" s="473"/>
       <c r="C6" s="473"/>
@@ -9471,47 +9471,47 @@
       <c r="O6" s="453"/>
       <c r="P6" s="454"/>
     </row>
-    <row r="7" spans="1:16" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A7" s="620" t="s">
+    <row r="7" spans="1:16" ht="15.9" customHeight="1">
+      <c r="A7" s="591" t="s">
         <v>0</v>
       </c>
-      <c r="B7" s="620"/>
-      <c r="C7" s="620"/>
-      <c r="D7" s="620"/>
-      <c r="E7" s="620"/>
-      <c r="F7" s="620"/>
-      <c r="G7" s="620"/>
-      <c r="H7" s="620"/>
-      <c r="I7" s="620"/>
-      <c r="J7" s="620"/>
-      <c r="K7" s="620"/>
-      <c r="L7" s="620"/>
+      <c r="B7" s="591"/>
+      <c r="C7" s="591"/>
+      <c r="D7" s="591"/>
+      <c r="E7" s="591"/>
+      <c r="F7" s="591"/>
+      <c r="G7" s="591"/>
+      <c r="H7" s="591"/>
+      <c r="I7" s="591"/>
+      <c r="J7" s="591"/>
+      <c r="K7" s="591"/>
+      <c r="L7" s="591"/>
       <c r="O7" s="450" t="s">
         <v>233</v>
       </c>
       <c r="P7" s="454"/>
     </row>
-    <row r="8" spans="1:16" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="621" t="s">
+    <row r="8" spans="1:16" ht="15.9" customHeight="1">
+      <c r="A8" s="592" t="s">
         <v>250</v>
       </c>
-      <c r="B8" s="621"/>
-      <c r="C8" s="621"/>
-      <c r="D8" s="621"/>
-      <c r="E8" s="621"/>
-      <c r="F8" s="621"/>
-      <c r="G8" s="621"/>
-      <c r="H8" s="621"/>
-      <c r="I8" s="621"/>
-      <c r="J8" s="621"/>
-      <c r="K8" s="621"/>
-      <c r="L8" s="621"/>
+      <c r="B8" s="592"/>
+      <c r="C8" s="592"/>
+      <c r="D8" s="592"/>
+      <c r="E8" s="592"/>
+      <c r="F8" s="592"/>
+      <c r="G8" s="592"/>
+      <c r="H8" s="592"/>
+      <c r="I8" s="592"/>
+      <c r="J8" s="592"/>
+      <c r="K8" s="592"/>
+      <c r="L8" s="592"/>
       <c r="O8" s="450" t="s">
         <v>296</v>
       </c>
       <c r="P8" s="455"/>
     </row>
-    <row r="9" spans="1:16" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:16" ht="8.25" customHeight="1">
       <c r="A9" s="474"/>
       <c r="B9" s="474"/>
       <c r="C9" s="474"/>
@@ -9529,7 +9529,7 @@
       </c>
       <c r="P9" s="454"/>
     </row>
-    <row r="10" spans="1:16" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:16" ht="15.9" customHeight="1">
       <c r="A10" s="474"/>
       <c r="B10" s="474"/>
       <c r="D10" s="475" t="s">
@@ -9552,7 +9552,7 @@
       <c r="O10" s="453"/>
       <c r="P10" s="454"/>
     </row>
-    <row r="11" spans="1:16" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:16" ht="15.9" customHeight="1">
       <c r="A11" s="474"/>
       <c r="B11" s="474"/>
       <c r="C11" s="474"/>
@@ -9570,7 +9570,7 @@
       </c>
       <c r="P11" s="454"/>
     </row>
-    <row r="12" spans="1:16" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:16" ht="15.9" customHeight="1">
       <c r="A12" s="474"/>
       <c r="B12" s="474"/>
       <c r="C12" s="474"/>
@@ -9584,7 +9584,7 @@
       </c>
       <c r="P12" s="455"/>
     </row>
-    <row r="13" spans="1:16" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:16" ht="7.5" customHeight="1">
       <c r="A13" s="479"/>
       <c r="B13" s="480"/>
       <c r="C13" s="481"/>
@@ -9603,47 +9603,47 @@
       </c>
       <c r="P13" s="455"/>
     </row>
-    <row r="14" spans="1:16" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A14" s="622" t="s">
+    <row r="14" spans="1:16" ht="17.25" customHeight="1">
+      <c r="A14" s="593" t="s">
         <v>102</v>
       </c>
-      <c r="B14" s="623"/>
-      <c r="C14" s="623"/>
-      <c r="D14" s="623"/>
-      <c r="E14" s="623"/>
-      <c r="F14" s="623"/>
-      <c r="G14" s="623"/>
-      <c r="H14" s="623"/>
-      <c r="I14" s="623"/>
-      <c r="J14" s="623"/>
-      <c r="K14" s="623"/>
-      <c r="L14" s="624"/>
+      <c r="B14" s="594"/>
+      <c r="C14" s="594"/>
+      <c r="D14" s="594"/>
+      <c r="E14" s="594"/>
+      <c r="F14" s="594"/>
+      <c r="G14" s="594"/>
+      <c r="H14" s="594"/>
+      <c r="I14" s="594"/>
+      <c r="J14" s="594"/>
+      <c r="K14" s="594"/>
+      <c r="L14" s="595"/>
       <c r="M14" s="87"/>
       <c r="O14" s="453"/>
       <c r="P14" s="454"/>
     </row>
-    <row r="15" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A15" s="625" t="s">
+    <row r="15" spans="1:16" ht="15" customHeight="1">
+      <c r="A15" s="596" t="s">
         <v>103</v>
       </c>
-      <c r="B15" s="626"/>
-      <c r="C15" s="626"/>
-      <c r="D15" s="626"/>
-      <c r="E15" s="626"/>
-      <c r="F15" s="626"/>
-      <c r="G15" s="626"/>
-      <c r="H15" s="626"/>
-      <c r="I15" s="626"/>
-      <c r="J15" s="626"/>
-      <c r="K15" s="626"/>
-      <c r="L15" s="627"/>
+      <c r="B15" s="597"/>
+      <c r="C15" s="597"/>
+      <c r="D15" s="597"/>
+      <c r="E15" s="597"/>
+      <c r="F15" s="597"/>
+      <c r="G15" s="597"/>
+      <c r="H15" s="597"/>
+      <c r="I15" s="597"/>
+      <c r="J15" s="597"/>
+      <c r="K15" s="597"/>
+      <c r="L15" s="598"/>
       <c r="M15" s="87"/>
       <c r="O15" s="450" t="s">
         <v>104</v>
       </c>
       <c r="P15" s="456"/>
     </row>
-    <row r="16" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:16" ht="18" customHeight="1">
       <c r="A16" s="483"/>
       <c r="B16" s="484"/>
       <c r="C16" s="485"/>
@@ -9662,18 +9662,18 @@
       </c>
       <c r="P16" s="456"/>
     </row>
-    <row r="17" spans="1:19" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A17" s="618" t="s">
+    <row r="17" spans="1:19" ht="15.9" customHeight="1">
+      <c r="A17" s="589" t="s">
         <v>254</v>
       </c>
-      <c r="B17" s="619"/>
-      <c r="C17" s="619"/>
-      <c r="D17" s="619"/>
-      <c r="E17" s="619"/>
-      <c r="F17" s="619"/>
-      <c r="G17" s="619"/>
-      <c r="H17" s="619"/>
-      <c r="I17" s="619"/>
+      <c r="B17" s="590"/>
+      <c r="C17" s="590"/>
+      <c r="D17" s="590"/>
+      <c r="E17" s="590"/>
+      <c r="F17" s="590"/>
+      <c r="G17" s="590"/>
+      <c r="H17" s="590"/>
+      <c r="I17" s="590"/>
       <c r="J17" s="431"/>
       <c r="K17" s="431"/>
       <c r="L17" s="487"/>
@@ -9682,7 +9682,7 @@
       </c>
       <c r="P17" s="457"/>
     </row>
-    <row r="18" spans="1:19" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:19" ht="18" customHeight="1">
       <c r="A18" s="488" t="s">
         <v>120</v>
       </c>
@@ -9698,7 +9698,7 @@
       <c r="K18" s="431"/>
       <c r="L18" s="487"/>
     </row>
-    <row r="19" spans="1:19" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:19" ht="18" customHeight="1">
       <c r="A19" s="488" t="s">
         <v>255</v>
       </c>
@@ -9714,7 +9714,7 @@
       <c r="K19" s="431"/>
       <c r="L19" s="487"/>
     </row>
-    <row r="20" spans="1:19" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:19" ht="18" customHeight="1">
       <c r="A20" s="488" t="s">
         <v>122</v>
       </c>
@@ -9730,7 +9730,7 @@
       <c r="K20" s="431"/>
       <c r="L20" s="487"/>
     </row>
-    <row r="21" spans="1:19" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:19" ht="18" customHeight="1">
       <c r="A21" s="488" t="s">
         <v>123</v>
       </c>
@@ -9746,7 +9746,7 @@
       <c r="K21" s="431"/>
       <c r="L21" s="487"/>
     </row>
-    <row r="22" spans="1:19" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:19" ht="18" customHeight="1">
       <c r="A22" s="491" t="s">
         <v>293</v>
       </c>
@@ -9762,7 +9762,7 @@
       <c r="K22" s="431"/>
       <c r="L22" s="487"/>
     </row>
-    <row r="23" spans="1:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:19" ht="14.4" customHeight="1">
       <c r="A23" s="492"/>
       <c r="B23" s="432"/>
       <c r="C23" s="432"/>
@@ -9776,13 +9776,13 @@
       <c r="K23" s="431"/>
       <c r="L23" s="487"/>
     </row>
-    <row r="24" spans="1:19" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A24" s="618" t="s">
+    <row r="24" spans="1:19" ht="15.9" customHeight="1">
+      <c r="A24" s="589" t="s">
         <v>256</v>
       </c>
-      <c r="B24" s="619"/>
-      <c r="C24" s="619"/>
-      <c r="D24" s="619"/>
+      <c r="B24" s="590"/>
+      <c r="C24" s="590"/>
+      <c r="D24" s="590"/>
       <c r="E24" s="432"/>
       <c r="F24" s="432"/>
       <c r="G24" s="432"/>
@@ -9792,51 +9792,51 @@
       <c r="K24" s="431"/>
       <c r="L24" s="487"/>
     </row>
-    <row r="25" spans="1:19" ht="19.149999999999999" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A25" s="590" t="s">
+    <row r="25" spans="1:19" ht="19.2" customHeight="1">
+      <c r="A25" s="599" t="s">
         <v>257</v>
       </c>
-      <c r="B25" s="590"/>
-      <c r="C25" s="590"/>
-      <c r="D25" s="590"/>
-      <c r="E25" s="591"/>
-      <c r="F25" s="591"/>
+      <c r="B25" s="599"/>
+      <c r="C25" s="599"/>
+      <c r="D25" s="599"/>
+      <c r="E25" s="600"/>
+      <c r="F25" s="600"/>
       <c r="G25" s="433"/>
-      <c r="H25" s="614" t="s">
+      <c r="H25" s="601" t="s">
         <v>286</v>
       </c>
-      <c r="I25" s="615"/>
-      <c r="J25" s="616"/>
+      <c r="I25" s="602"/>
+      <c r="J25" s="603"/>
       <c r="K25" s="493"/>
       <c r="L25" s="487"/>
     </row>
-    <row r="26" spans="1:19" ht="19.149999999999999" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A26" s="590" t="s">
+    <row r="26" spans="1:19" ht="19.2" customHeight="1">
+      <c r="A26" s="599" t="s">
         <v>258</v>
       </c>
-      <c r="B26" s="590"/>
-      <c r="C26" s="590"/>
-      <c r="D26" s="590"/>
-      <c r="E26" s="591"/>
-      <c r="F26" s="591"/>
+      <c r="B26" s="599"/>
+      <c r="C26" s="599"/>
+      <c r="D26" s="599"/>
+      <c r="E26" s="600"/>
+      <c r="F26" s="600"/>
       <c r="G26" s="433"/>
-      <c r="H26" s="617" t="s">
+      <c r="H26" s="604" t="s">
         <v>287</v>
       </c>
-      <c r="I26" s="617"/>
+      <c r="I26" s="604"/>
       <c r="J26" s="434"/>
       <c r="K26" s="494"/>
       <c r="L26" s="487"/>
     </row>
-    <row r="27" spans="1:19" ht="19.149999999999999" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A27" s="590" t="s">
+    <row r="27" spans="1:19" ht="19.2" customHeight="1">
+      <c r="A27" s="599" t="s">
         <v>259</v>
       </c>
-      <c r="B27" s="590"/>
-      <c r="C27" s="590"/>
-      <c r="D27" s="590"/>
-      <c r="E27" s="591"/>
-      <c r="F27" s="591"/>
+      <c r="B27" s="599"/>
+      <c r="C27" s="599"/>
+      <c r="D27" s="599"/>
+      <c r="E27" s="600"/>
+      <c r="F27" s="600"/>
       <c r="G27" s="433"/>
       <c r="H27" s="446"/>
       <c r="I27" s="447"/>
@@ -9845,19 +9845,19 @@
       <c r="L27" s="487"/>
       <c r="M27" s="87"/>
     </row>
-    <row r="28" spans="1:19" ht="19.149999999999999" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A28" s="590" t="s">
+    <row r="28" spans="1:19" ht="19.2" customHeight="1">
+      <c r="A28" s="599" t="s">
         <v>288</v>
       </c>
-      <c r="B28" s="590"/>
-      <c r="C28" s="590"/>
-      <c r="D28" s="590"/>
-      <c r="E28" s="591"/>
-      <c r="F28" s="591"/>
+      <c r="B28" s="599"/>
+      <c r="C28" s="599"/>
+      <c r="D28" s="599"/>
+      <c r="E28" s="600"/>
+      <c r="F28" s="600"/>
       <c r="L28" s="495"/>
       <c r="M28" s="87"/>
     </row>
-    <row r="29" spans="1:19" ht="22.15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:19" ht="22.2" customHeight="1">
       <c r="A29" s="496"/>
       <c r="B29" s="497"/>
       <c r="C29" s="497"/>
@@ -9872,39 +9872,39 @@
       <c r="L29" s="500"/>
       <c r="M29" s="87"/>
     </row>
-    <row r="30" spans="1:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:19" ht="15.75" customHeight="1">
       <c r="A30" s="501"/>
-      <c r="B30" s="612" t="s">
+      <c r="B30" s="608" t="s">
         <v>261</v>
       </c>
-      <c r="C30" s="612"/>
-      <c r="D30" s="612"/>
-      <c r="E30" s="612"/>
-      <c r="F30" s="612"/>
-      <c r="G30" s="612"/>
+      <c r="C30" s="608"/>
+      <c r="D30" s="608"/>
+      <c r="E30" s="608"/>
+      <c r="F30" s="608"/>
+      <c r="G30" s="608"/>
       <c r="H30" s="502" t="s">
         <v>262</v>
       </c>
       <c r="I30" s="502" t="s">
         <v>263</v>
       </c>
-      <c r="J30" s="613"/>
-      <c r="K30" s="613"/>
+      <c r="J30" s="609"/>
+      <c r="K30" s="609"/>
       <c r="L30" s="503"/>
       <c r="M30" s="87"/>
     </row>
-    <row r="31" spans="1:19" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:19" ht="21.75" customHeight="1">
       <c r="A31" s="504"/>
       <c r="B31" s="505">
         <v>1</v>
       </c>
-      <c r="C31" s="604" t="s">
+      <c r="C31" s="605" t="s">
         <v>35</v>
       </c>
-      <c r="D31" s="605"/>
-      <c r="E31" s="605"/>
-      <c r="F31" s="605"/>
-      <c r="G31" s="606"/>
+      <c r="D31" s="606"/>
+      <c r="E31" s="606"/>
+      <c r="F31" s="606"/>
+      <c r="G31" s="607"/>
       <c r="H31" s="506" t="s">
         <v>36</v>
       </c>
@@ -9914,18 +9914,18 @@
       <c r="L31" s="509"/>
       <c r="M31" s="87"/>
     </row>
-    <row r="32" spans="1:19" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:19" ht="21.75" customHeight="1">
       <c r="A32" s="504"/>
       <c r="B32" s="510">
         <v>2</v>
       </c>
-      <c r="C32" s="604" t="s">
+      <c r="C32" s="605" t="s">
         <v>111</v>
       </c>
-      <c r="D32" s="605"/>
-      <c r="E32" s="605"/>
-      <c r="F32" s="605"/>
-      <c r="G32" s="606"/>
+      <c r="D32" s="606"/>
+      <c r="E32" s="606"/>
+      <c r="F32" s="606"/>
+      <c r="G32" s="607"/>
       <c r="H32" s="506" t="s">
         <v>36</v>
       </c>
@@ -9936,18 +9936,18 @@
       <c r="M32" s="87"/>
       <c r="S32" s="435"/>
     </row>
-    <row r="33" spans="1:23" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:23" ht="21.75" customHeight="1">
       <c r="A33" s="504"/>
       <c r="B33" s="510">
         <v>3</v>
       </c>
-      <c r="C33" s="604" t="s">
+      <c r="C33" s="605" t="s">
         <v>112</v>
       </c>
-      <c r="D33" s="605"/>
-      <c r="E33" s="605"/>
-      <c r="F33" s="605"/>
-      <c r="G33" s="606"/>
+      <c r="D33" s="606"/>
+      <c r="E33" s="606"/>
+      <c r="F33" s="606"/>
+      <c r="G33" s="607"/>
       <c r="H33" s="506" t="s">
         <v>184</v>
       </c>
@@ -9958,18 +9958,18 @@
       <c r="M33" s="436"/>
       <c r="W33" s="435"/>
     </row>
-    <row r="34" spans="1:23" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:23" ht="21.75" customHeight="1">
       <c r="A34" s="504"/>
       <c r="B34" s="505">
         <v>4</v>
       </c>
-      <c r="C34" s="604" t="s">
+      <c r="C34" s="605" t="s">
         <v>113</v>
       </c>
-      <c r="D34" s="605"/>
-      <c r="E34" s="605"/>
-      <c r="F34" s="605"/>
-      <c r="G34" s="606"/>
+      <c r="D34" s="606"/>
+      <c r="E34" s="606"/>
+      <c r="F34" s="606"/>
+      <c r="G34" s="607"/>
       <c r="H34" s="506" t="s">
         <v>184</v>
       </c>
@@ -9982,18 +9982,18 @@
       <c r="P34" s="437"/>
       <c r="W34" s="435"/>
     </row>
-    <row r="35" spans="1:23" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:23" ht="21.75" customHeight="1">
       <c r="A35" s="504"/>
       <c r="B35" s="510">
         <v>5</v>
       </c>
-      <c r="C35" s="604" t="s">
+      <c r="C35" s="605" t="s">
         <v>265</v>
       </c>
-      <c r="D35" s="605"/>
-      <c r="E35" s="605"/>
-      <c r="F35" s="605"/>
-      <c r="G35" s="606"/>
+      <c r="D35" s="606"/>
+      <c r="E35" s="606"/>
+      <c r="F35" s="606"/>
+      <c r="G35" s="607"/>
       <c r="H35" s="506" t="s">
         <v>184</v>
       </c>
@@ -10006,18 +10006,18 @@
       <c r="P35" s="437"/>
       <c r="W35" s="435"/>
     </row>
-    <row r="36" spans="1:23" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:23" ht="21.75" customHeight="1">
       <c r="A36" s="504"/>
       <c r="B36" s="505">
         <v>6</v>
       </c>
-      <c r="C36" s="604" t="s">
+      <c r="C36" s="605" t="s">
         <v>114</v>
       </c>
-      <c r="D36" s="605"/>
-      <c r="E36" s="605"/>
-      <c r="F36" s="605"/>
-      <c r="G36" s="606"/>
+      <c r="D36" s="606"/>
+      <c r="E36" s="606"/>
+      <c r="F36" s="606"/>
+      <c r="G36" s="607"/>
       <c r="H36" s="506" t="s">
         <v>184</v>
       </c>
@@ -10030,18 +10030,18 @@
       <c r="P36" s="437"/>
       <c r="W36" s="435"/>
     </row>
-    <row r="37" spans="1:23" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:23" ht="21.75" customHeight="1">
       <c r="A37" s="504"/>
       <c r="B37" s="510">
         <v>7</v>
       </c>
-      <c r="C37" s="604" t="s">
+      <c r="C37" s="605" t="s">
         <v>294</v>
       </c>
-      <c r="D37" s="605"/>
-      <c r="E37" s="605"/>
-      <c r="F37" s="605"/>
-      <c r="G37" s="606"/>
+      <c r="D37" s="606"/>
+      <c r="E37" s="606"/>
+      <c r="F37" s="606"/>
+      <c r="G37" s="607"/>
       <c r="H37" s="506" t="s">
         <v>184</v>
       </c>
@@ -10054,18 +10054,18 @@
       <c r="O37" s="437"/>
       <c r="P37" s="437"/>
     </row>
-    <row r="38" spans="1:23" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:23" ht="21.75" customHeight="1">
       <c r="A38" s="504"/>
       <c r="B38" s="510">
         <v>8</v>
       </c>
-      <c r="C38" s="604" t="s">
+      <c r="C38" s="605" t="s">
         <v>266</v>
       </c>
-      <c r="D38" s="605"/>
-      <c r="E38" s="605"/>
-      <c r="F38" s="605"/>
-      <c r="G38" s="606"/>
+      <c r="D38" s="606"/>
+      <c r="E38" s="606"/>
+      <c r="F38" s="606"/>
+      <c r="G38" s="607"/>
       <c r="H38" s="506" t="s">
         <v>184</v>
       </c>
@@ -10078,18 +10078,18 @@
       <c r="O38" s="440"/>
       <c r="P38" s="440"/>
     </row>
-    <row r="39" spans="1:23" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:23" ht="21.75" customHeight="1">
       <c r="A39" s="504"/>
       <c r="B39" s="505">
         <v>9</v>
       </c>
-      <c r="C39" s="604" t="s">
+      <c r="C39" s="605" t="s">
         <v>267</v>
       </c>
-      <c r="D39" s="605"/>
-      <c r="E39" s="605"/>
-      <c r="F39" s="605"/>
-      <c r="G39" s="606"/>
+      <c r="D39" s="606"/>
+      <c r="E39" s="606"/>
+      <c r="F39" s="606"/>
+      <c r="G39" s="607"/>
       <c r="H39" s="506" t="s">
         <v>56</v>
       </c>
@@ -10101,7 +10101,7 @@
       <c r="N39" s="441"/>
       <c r="O39" s="201"/>
     </row>
-    <row r="40" spans="1:23" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:23" ht="6.75" customHeight="1">
       <c r="A40" s="504"/>
       <c r="B40" s="498"/>
       <c r="C40" s="498"/>
@@ -10117,33 +10117,33 @@
       <c r="O40" s="201"/>
       <c r="W40" s="435"/>
     </row>
-    <row r="41" spans="1:23" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:23" ht="17.25" customHeight="1">
       <c r="A41" s="504"/>
-      <c r="B41" s="603" t="s">
+      <c r="B41" s="615" t="s">
         <v>268</v>
       </c>
-      <c r="C41" s="603"/>
-      <c r="D41" s="603"/>
-      <c r="E41" s="603"/>
-      <c r="F41" s="603"/>
+      <c r="C41" s="615"/>
+      <c r="D41" s="615"/>
+      <c r="E41" s="615"/>
+      <c r="F41" s="615"/>
       <c r="G41" s="515"/>
-      <c r="H41" s="607" t="s">
+      <c r="H41" s="616" t="s">
         <v>269</v>
       </c>
-      <c r="I41" s="608"/>
-      <c r="J41" s="609"/>
-      <c r="K41" s="609"/>
-      <c r="L41" s="608"/>
+      <c r="I41" s="617"/>
+      <c r="J41" s="618"/>
+      <c r="K41" s="618"/>
+      <c r="L41" s="617"/>
       <c r="M41" s="87"/>
       <c r="W41" s="435"/>
     </row>
-    <row r="42" spans="1:23" ht="26.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:23" ht="26.25" customHeight="1">
       <c r="A42" s="504"/>
-      <c r="B42" s="610" t="s">
+      <c r="B42" s="619" t="s">
         <v>270</v>
       </c>
-      <c r="C42" s="610"/>
-      <c r="D42" s="610"/>
+      <c r="C42" s="619"/>
+      <c r="D42" s="619"/>
       <c r="E42" s="516" t="s">
         <v>271</v>
       </c>
@@ -10151,23 +10151,23 @@
         <v>272</v>
       </c>
       <c r="G42" s="515"/>
-      <c r="H42" s="598" t="s">
+      <c r="H42" s="610" t="s">
         <v>273</v>
       </c>
-      <c r="I42" s="598"/>
-      <c r="J42" s="611"/>
-      <c r="K42" s="611"/>
-      <c r="L42" s="611"/>
+      <c r="I42" s="610"/>
+      <c r="J42" s="620"/>
+      <c r="K42" s="620"/>
+      <c r="L42" s="620"/>
       <c r="M42" s="87"/>
       <c r="W42" s="435"/>
     </row>
-    <row r="43" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:23" ht="15" customHeight="1">
       <c r="A43" s="504"/>
-      <c r="B43" s="596" t="s">
+      <c r="B43" s="626" t="s">
         <v>274</v>
       </c>
-      <c r="C43" s="596"/>
-      <c r="D43" s="596"/>
+      <c r="C43" s="626"/>
+      <c r="D43" s="626"/>
       <c r="E43" s="517" t="s">
         <v>142</v>
       </c>
@@ -10175,23 +10175,23 @@
         <v>275</v>
       </c>
       <c r="G43" s="515"/>
-      <c r="H43" s="598" t="s">
+      <c r="H43" s="610" t="s">
         <v>276</v>
       </c>
-      <c r="I43" s="598"/>
-      <c r="J43" s="599"/>
-      <c r="K43" s="599"/>
-      <c r="L43" s="600"/>
+      <c r="I43" s="610"/>
+      <c r="J43" s="611"/>
+      <c r="K43" s="611"/>
+      <c r="L43" s="612"/>
       <c r="M43" s="87"/>
       <c r="W43" s="435"/>
     </row>
-    <row r="44" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="44" spans="1:23" ht="15" customHeight="1">
       <c r="A44" s="504"/>
-      <c r="B44" s="596" t="s">
+      <c r="B44" s="626" t="s">
         <v>277</v>
       </c>
-      <c r="C44" s="596"/>
-      <c r="D44" s="596"/>
+      <c r="C44" s="626"/>
+      <c r="D44" s="626"/>
       <c r="E44" s="517" t="s">
         <v>144</v>
       </c>
@@ -10199,20 +10199,20 @@
         <v>275</v>
       </c>
       <c r="G44" s="515"/>
-      <c r="H44" s="598"/>
-      <c r="I44" s="598"/>
-      <c r="J44" s="601"/>
-      <c r="K44" s="601"/>
-      <c r="L44" s="602"/>
+      <c r="H44" s="610"/>
+      <c r="I44" s="610"/>
+      <c r="J44" s="613"/>
+      <c r="K44" s="613"/>
+      <c r="L44" s="614"/>
       <c r="M44" s="87"/>
     </row>
-    <row r="45" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="45" spans="1:23" ht="15" customHeight="1">
       <c r="A45" s="504"/>
-      <c r="B45" s="592" t="s">
+      <c r="B45" s="622" t="s">
         <v>278</v>
       </c>
-      <c r="C45" s="592"/>
-      <c r="D45" s="592"/>
+      <c r="C45" s="622"/>
+      <c r="D45" s="622"/>
       <c r="E45" s="517" t="s">
         <v>146</v>
       </c>
@@ -10220,39 +10220,39 @@
         <v>275</v>
       </c>
       <c r="G45" s="515"/>
-      <c r="H45" s="598" t="s">
+      <c r="H45" s="610" t="s">
         <v>279</v>
       </c>
-      <c r="I45" s="598"/>
-      <c r="J45" s="599"/>
-      <c r="K45" s="599"/>
-      <c r="L45" s="600"/>
+      <c r="I45" s="610"/>
+      <c r="J45" s="611"/>
+      <c r="K45" s="611"/>
+      <c r="L45" s="612"/>
       <c r="M45" s="87"/>
     </row>
-    <row r="46" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="46" spans="1:23" ht="15" customHeight="1">
       <c r="A46" s="504"/>
-      <c r="B46" s="603" t="s">
+      <c r="B46" s="615" t="s">
         <v>280</v>
       </c>
-      <c r="C46" s="603"/>
-      <c r="D46" s="603"/>
-      <c r="E46" s="603"/>
-      <c r="F46" s="603"/>
+      <c r="C46" s="615"/>
+      <c r="D46" s="615"/>
+      <c r="E46" s="615"/>
+      <c r="F46" s="615"/>
       <c r="G46" s="515"/>
-      <c r="H46" s="598"/>
-      <c r="I46" s="598"/>
-      <c r="J46" s="601"/>
-      <c r="K46" s="601"/>
-      <c r="L46" s="602"/>
+      <c r="H46" s="610"/>
+      <c r="I46" s="610"/>
+      <c r="J46" s="613"/>
+      <c r="K46" s="613"/>
+      <c r="L46" s="614"/>
       <c r="M46" s="87"/>
     </row>
-    <row r="47" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="47" spans="1:23" ht="15" customHeight="1">
       <c r="A47" s="504"/>
-      <c r="B47" s="592" t="s">
+      <c r="B47" s="622" t="s">
         <v>281</v>
       </c>
-      <c r="C47" s="592"/>
-      <c r="D47" s="592"/>
+      <c r="C47" s="622"/>
+      <c r="D47" s="622"/>
       <c r="E47" s="517" t="s">
         <v>148</v>
       </c>
@@ -10260,20 +10260,20 @@
         <v>282</v>
       </c>
       <c r="G47" s="515"/>
-      <c r="H47" s="593"/>
-      <c r="I47" s="593"/>
-      <c r="J47" s="594"/>
-      <c r="K47" s="594"/>
-      <c r="L47" s="595"/>
+      <c r="H47" s="623"/>
+      <c r="I47" s="623"/>
+      <c r="J47" s="624"/>
+      <c r="K47" s="624"/>
+      <c r="L47" s="625"/>
       <c r="M47" s="87"/>
     </row>
-    <row r="48" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="48" spans="1:23" ht="15" customHeight="1">
       <c r="A48" s="504"/>
-      <c r="B48" s="596" t="s">
+      <c r="B48" s="626" t="s">
         <v>149</v>
       </c>
-      <c r="C48" s="596"/>
-      <c r="D48" s="596"/>
+      <c r="C48" s="626"/>
+      <c r="D48" s="626"/>
       <c r="E48" s="517" t="s">
         <v>146</v>
       </c>
@@ -10281,20 +10281,20 @@
         <v>282</v>
       </c>
       <c r="G48" s="515"/>
-      <c r="H48" s="593"/>
-      <c r="I48" s="593"/>
-      <c r="J48" s="594"/>
-      <c r="K48" s="594"/>
-      <c r="L48" s="595"/>
+      <c r="H48" s="623"/>
+      <c r="I48" s="623"/>
+      <c r="J48" s="624"/>
+      <c r="K48" s="624"/>
+      <c r="L48" s="625"/>
       <c r="M48" s="87"/>
     </row>
-    <row r="49" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="49" spans="1:13" ht="15" customHeight="1">
       <c r="A49" s="504"/>
-      <c r="B49" s="596" t="s">
+      <c r="B49" s="626" t="s">
         <v>151</v>
       </c>
-      <c r="C49" s="596"/>
-      <c r="D49" s="596"/>
+      <c r="C49" s="626"/>
+      <c r="D49" s="626"/>
       <c r="E49" s="517" t="s">
         <v>146</v>
       </c>
@@ -10309,7 +10309,7 @@
       <c r="L49" s="520"/>
       <c r="M49" s="87"/>
     </row>
-    <row r="50" spans="1:13" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="50" spans="1:13" ht="18.75" customHeight="1">
       <c r="A50" s="521"/>
       <c r="B50" s="522" t="s">
         <v>283</v>
@@ -10326,7 +10326,7 @@
       <c r="L50" s="528"/>
       <c r="M50" s="87"/>
     </row>
-    <row r="51" spans="1:13" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="51" spans="1:13" ht="7.5" customHeight="1">
       <c r="A51" s="529"/>
       <c r="B51" s="435"/>
       <c r="C51" s="435"/>
@@ -10341,7 +10341,7 @@
       <c r="L51" s="435"/>
       <c r="M51" s="87"/>
     </row>
-    <row r="52" spans="1:13" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="52" spans="1:13" ht="22.5" customHeight="1">
       <c r="A52" s="532" t="s">
         <v>98</v>
       </c>
@@ -10358,7 +10358,7 @@
       <c r="L52" s="526"/>
       <c r="M52" s="87"/>
     </row>
-    <row r="53" spans="1:13" ht="25.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="53" spans="1:13" ht="25.5" customHeight="1">
       <c r="A53" s="533"/>
       <c r="B53" s="527"/>
       <c r="C53" s="527"/>
@@ -10373,7 +10373,7 @@
       <c r="L53" s="526"/>
       <c r="M53" s="87"/>
     </row>
-    <row r="54" spans="1:13" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="54" spans="1:13" ht="6.75" customHeight="1">
       <c r="A54" s="534"/>
       <c r="B54" s="435"/>
       <c r="C54" s="435"/>
@@ -10388,7 +10388,7 @@
       <c r="L54" s="536"/>
       <c r="M54" s="87"/>
     </row>
-    <row r="55" spans="1:13" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="55" spans="1:13" ht="30" customHeight="1">
       <c r="A55" s="534"/>
       <c r="B55" s="435"/>
       <c r="C55" s="435"/>
@@ -10403,7 +10403,7 @@
       <c r="L55" s="435"/>
       <c r="M55" s="87"/>
     </row>
-    <row r="56" spans="1:13" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="56" spans="1:13" ht="15.9" customHeight="1">
       <c r="A56" s="537"/>
       <c r="B56" s="435"/>
       <c r="J56" s="435"/>
@@ -10411,21 +10411,21 @@
       <c r="L56" s="435"/>
       <c r="M56" s="87"/>
     </row>
-    <row r="57" spans="1:13" ht="4.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B57" s="597"/>
-      <c r="C57" s="597"/>
-      <c r="D57" s="597"/>
-      <c r="E57" s="597"/>
-      <c r="F57" s="597"/>
-      <c r="G57" s="597"/>
-      <c r="H57" s="597"/>
-      <c r="I57" s="597"/>
-      <c r="J57" s="597"/>
+    <row r="57" spans="1:13" ht="4.5" customHeight="1">
+      <c r="B57" s="627"/>
+      <c r="C57" s="627"/>
+      <c r="D57" s="627"/>
+      <c r="E57" s="627"/>
+      <c r="F57" s="627"/>
+      <c r="G57" s="627"/>
+      <c r="H57" s="627"/>
+      <c r="I57" s="627"/>
+      <c r="J57" s="627"/>
       <c r="K57" s="480"/>
       <c r="L57" s="435"/>
       <c r="M57" s="87"/>
     </row>
-    <row r="58" spans="1:13" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="58" spans="1:13" ht="15.9" customHeight="1">
       <c r="A58" s="538" t="s">
         <v>91</v>
       </c>
@@ -10442,7 +10442,7 @@
       <c r="L58" s="435"/>
       <c r="M58" s="87"/>
     </row>
-    <row r="59" spans="1:13" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="59" spans="1:13" ht="15.9" customHeight="1">
       <c r="A59" s="538" t="s">
         <v>295</v>
       </c>
@@ -10461,25 +10461,25 @@
       <c r="L59" s="435"/>
       <c r="M59" s="87"/>
     </row>
-    <row r="60" spans="1:13" ht="3.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="61" spans="1:13" ht="30.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A61" s="589" t="s">
+    <row r="60" spans="1:13" ht="3.75" customHeight="1"/>
+    <row r="61" spans="1:13" ht="30.75" customHeight="1">
+      <c r="A61" s="621" t="s">
         <v>285</v>
       </c>
-      <c r="B61" s="589"/>
-      <c r="C61" s="589"/>
-      <c r="D61" s="589"/>
-      <c r="E61" s="589"/>
-      <c r="F61" s="589"/>
-      <c r="G61" s="589"/>
-      <c r="H61" s="589"/>
-      <c r="I61" s="589"/>
-      <c r="J61" s="589"/>
-      <c r="K61" s="589"/>
-      <c r="L61" s="589"/>
-    </row>
-    <row r="62" spans="1:13" ht="15.95" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="63" spans="1:13" ht="15.95" customHeight="1" x14ac:dyDescent="0.2"/>
+      <c r="B61" s="621"/>
+      <c r="C61" s="621"/>
+      <c r="D61" s="621"/>
+      <c r="E61" s="621"/>
+      <c r="F61" s="621"/>
+      <c r="G61" s="621"/>
+      <c r="H61" s="621"/>
+      <c r="I61" s="621"/>
+      <c r="J61" s="621"/>
+      <c r="K61" s="621"/>
+      <c r="L61" s="621"/>
+    </row>
+    <row r="62" spans="1:13" ht="15.9" customHeight="1"/>
+    <row r="63" spans="1:13" ht="15.9" customHeight="1"/>
   </sheetData>
   <sheetProtection algorithmName="SHA-512" hashValue="zFaKPAn6ViOpya0rqSfRP+lf5nP0Stsd4GeHYr5E3M4pf5abxDHp7CyitZu3QfPbBPFWYk0mv07jVBjbhu2ckg==" saltValue="VTj2SwRAYFQHMWaCbVSW8A==" spinCount="100000" sheet="1" objects="1" scenarios="1"/>
   <protectedRanges>
@@ -10487,40 +10487,6 @@
     <protectedRange sqref="C57" name="Rango3_3_1_1_1_1_1_2_1"/>
   </protectedRanges>
   <mergeCells count="50">
-    <mergeCell ref="A24:D24"/>
-    <mergeCell ref="A7:L7"/>
-    <mergeCell ref="A8:L8"/>
-    <mergeCell ref="A14:L14"/>
-    <mergeCell ref="A15:L15"/>
-    <mergeCell ref="A17:I17"/>
-    <mergeCell ref="A25:D25"/>
-    <mergeCell ref="E25:F25"/>
-    <mergeCell ref="H25:J25"/>
-    <mergeCell ref="A26:D26"/>
-    <mergeCell ref="E26:F26"/>
-    <mergeCell ref="H26:I26"/>
-    <mergeCell ref="C37:G37"/>
-    <mergeCell ref="A27:D27"/>
-    <mergeCell ref="E27:F27"/>
-    <mergeCell ref="B30:G30"/>
-    <mergeCell ref="J30:K30"/>
-    <mergeCell ref="C31:G31"/>
-    <mergeCell ref="C32:G32"/>
-    <mergeCell ref="C33:G33"/>
-    <mergeCell ref="C34:G34"/>
-    <mergeCell ref="C35:G35"/>
-    <mergeCell ref="C36:G36"/>
-    <mergeCell ref="H45:I46"/>
-    <mergeCell ref="J45:L46"/>
-    <mergeCell ref="B46:F46"/>
-    <mergeCell ref="C38:G38"/>
-    <mergeCell ref="C39:G39"/>
-    <mergeCell ref="B41:F41"/>
-    <mergeCell ref="H41:I41"/>
-    <mergeCell ref="J41:L41"/>
-    <mergeCell ref="B42:D42"/>
-    <mergeCell ref="H42:I42"/>
-    <mergeCell ref="J42:L42"/>
     <mergeCell ref="A61:L61"/>
     <mergeCell ref="A28:D28"/>
     <mergeCell ref="E28:F28"/>
@@ -10537,6 +10503,40 @@
     <mergeCell ref="J43:L44"/>
     <mergeCell ref="B44:D44"/>
     <mergeCell ref="B45:D45"/>
+    <mergeCell ref="H45:I46"/>
+    <mergeCell ref="J45:L46"/>
+    <mergeCell ref="B46:F46"/>
+    <mergeCell ref="C38:G38"/>
+    <mergeCell ref="C39:G39"/>
+    <mergeCell ref="B41:F41"/>
+    <mergeCell ref="H41:I41"/>
+    <mergeCell ref="J41:L41"/>
+    <mergeCell ref="B42:D42"/>
+    <mergeCell ref="H42:I42"/>
+    <mergeCell ref="J42:L42"/>
+    <mergeCell ref="C37:G37"/>
+    <mergeCell ref="A27:D27"/>
+    <mergeCell ref="E27:F27"/>
+    <mergeCell ref="B30:G30"/>
+    <mergeCell ref="J30:K30"/>
+    <mergeCell ref="C31:G31"/>
+    <mergeCell ref="C32:G32"/>
+    <mergeCell ref="C33:G33"/>
+    <mergeCell ref="C34:G34"/>
+    <mergeCell ref="C35:G35"/>
+    <mergeCell ref="C36:G36"/>
+    <mergeCell ref="A25:D25"/>
+    <mergeCell ref="E25:F25"/>
+    <mergeCell ref="H25:J25"/>
+    <mergeCell ref="A26:D26"/>
+    <mergeCell ref="E26:F26"/>
+    <mergeCell ref="H26:I26"/>
+    <mergeCell ref="A24:D24"/>
+    <mergeCell ref="A7:L7"/>
+    <mergeCell ref="A8:L8"/>
+    <mergeCell ref="A14:L14"/>
+    <mergeCell ref="A15:L15"/>
+    <mergeCell ref="A17:I17"/>
   </mergeCells>
   <conditionalFormatting sqref="A18:A22">
     <cfRule type="cellIs" priority="1" stopIfTrue="1" operator="between">
@@ -10553,27 +10553,27 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:Q94"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="10.28515625" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="10.33203125" defaultRowHeight="13.8"/>
   <cols>
-    <col min="1" max="1" width="10.42578125" style="316" customWidth="1"/>
+    <col min="1" max="1" width="10.44140625" style="316" customWidth="1"/>
     <col min="2" max="2" width="3" style="316" customWidth="1"/>
-    <col min="3" max="3" width="4.42578125" style="316" customWidth="1"/>
-    <col min="4" max="4" width="1.5703125" style="316" customWidth="1"/>
-    <col min="5" max="5" width="5.42578125" style="316" customWidth="1"/>
-    <col min="6" max="8" width="9.7109375" style="316" customWidth="1"/>
-    <col min="9" max="9" width="4.5703125" style="316" customWidth="1"/>
-    <col min="10" max="10" width="6.42578125" style="316" customWidth="1"/>
-    <col min="11" max="11" width="11.7109375" style="316" customWidth="1"/>
+    <col min="3" max="3" width="4.44140625" style="316" customWidth="1"/>
+    <col min="4" max="4" width="1.5546875" style="316" customWidth="1"/>
+    <col min="5" max="5" width="5.44140625" style="316" customWidth="1"/>
+    <col min="6" max="8" width="9.6640625" style="316" customWidth="1"/>
+    <col min="9" max="9" width="4.5546875" style="316" customWidth="1"/>
+    <col min="10" max="10" width="6.44140625" style="316" customWidth="1"/>
+    <col min="11" max="11" width="11.6640625" style="316" customWidth="1"/>
     <col min="12" max="12" width="10" style="316" customWidth="1"/>
-    <col min="13" max="13" width="1.28515625" style="316" customWidth="1"/>
-    <col min="14" max="14" width="13.5703125" style="316" customWidth="1"/>
-    <col min="15" max="15" width="6.42578125" style="316" customWidth="1"/>
+    <col min="13" max="13" width="1.33203125" style="316" customWidth="1"/>
+    <col min="14" max="14" width="13.5546875" style="316" customWidth="1"/>
+    <col min="15" max="15" width="6.44140625" style="316" customWidth="1"/>
     <col min="16" max="16" width="1" style="316" customWidth="1"/>
-    <col min="17" max="17" width="6.42578125" style="316" customWidth="1"/>
-    <col min="18" max="16384" width="10.28515625" style="316"/>
+    <col min="17" max="17" width="6.44140625" style="316" customWidth="1"/>
+    <col min="18" max="16384" width="10.33203125" style="316"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:17" ht="28.5" customHeight="1">
       <c r="A1" s="309"/>
       <c r="B1" s="309"/>
       <c r="C1" s="309"/>
@@ -10589,62 +10589,62 @@
       <c r="M1" s="309"/>
       <c r="N1" s="309"/>
     </row>
-    <row r="2" spans="1:17" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="567" t="s">
+    <row r="2" spans="1:17" ht="15.9" customHeight="1">
+      <c r="A2" s="544" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="567"/>
-      <c r="C2" s="567"/>
-      <c r="D2" s="567"/>
-      <c r="E2" s="567"/>
-      <c r="F2" s="567"/>
-      <c r="G2" s="567"/>
-      <c r="H2" s="567"/>
-      <c r="I2" s="567"/>
-      <c r="J2" s="567"/>
-      <c r="K2" s="567"/>
-      <c r="L2" s="567"/>
-      <c r="M2" s="567"/>
-      <c r="N2" s="567"/>
-    </row>
-    <row r="3" spans="1:17" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="628">
+      <c r="B2" s="544"/>
+      <c r="C2" s="544"/>
+      <c r="D2" s="544"/>
+      <c r="E2" s="544"/>
+      <c r="F2" s="544"/>
+      <c r="G2" s="544"/>
+      <c r="H2" s="544"/>
+      <c r="I2" s="544"/>
+      <c r="J2" s="544"/>
+      <c r="K2" s="544"/>
+      <c r="L2" s="544"/>
+      <c r="M2" s="544"/>
+      <c r="N2" s="544"/>
+    </row>
+    <row r="3" spans="1:17" ht="15.9" customHeight="1">
+      <c r="A3" s="635">
         <v>0</v>
       </c>
-      <c r="B3" s="628"/>
-      <c r="C3" s="628"/>
-      <c r="D3" s="628"/>
-      <c r="E3" s="628"/>
-      <c r="F3" s="628"/>
-      <c r="G3" s="628"/>
-      <c r="H3" s="628"/>
-      <c r="I3" s="628"/>
-      <c r="J3" s="628"/>
-      <c r="K3" s="628"/>
-      <c r="L3" s="628"/>
-      <c r="M3" s="628"/>
-      <c r="N3" s="628"/>
-    </row>
-    <row r="4" spans="1:17" ht="15.95" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="5" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B3" s="635"/>
+      <c r="C3" s="635"/>
+      <c r="D3" s="635"/>
+      <c r="E3" s="635"/>
+      <c r="F3" s="635"/>
+      <c r="G3" s="635"/>
+      <c r="H3" s="635"/>
+      <c r="I3" s="635"/>
+      <c r="J3" s="635"/>
+      <c r="K3" s="635"/>
+      <c r="L3" s="635"/>
+      <c r="M3" s="635"/>
+      <c r="N3" s="635"/>
+    </row>
+    <row r="4" spans="1:17" ht="15.9" customHeight="1"/>
+    <row r="5" spans="1:17" ht="15" customHeight="1">
       <c r="A5" s="297" t="s">
         <v>1</v>
       </c>
       <c r="B5" s="177" t="s">
         <v>2</v>
       </c>
-      <c r="C5" s="645">
+      <c r="C5" s="647">
         <f>+Resumen!P2</f>
         <v>0</v>
       </c>
-      <c r="D5" s="645"/>
-      <c r="E5" s="645"/>
-      <c r="F5" s="645"/>
-      <c r="G5" s="645"/>
-      <c r="H5" s="645"/>
-      <c r="I5" s="645"/>
-      <c r="J5" s="645"/>
-      <c r="K5" s="645"/>
+      <c r="D5" s="647"/>
+      <c r="E5" s="647"/>
+      <c r="F5" s="647"/>
+      <c r="G5" s="647"/>
+      <c r="H5" s="647"/>
+      <c r="I5" s="647"/>
+      <c r="J5" s="647"/>
+      <c r="K5" s="647"/>
       <c r="L5" s="27" t="s">
         <v>6</v>
       </c>
@@ -10656,25 +10656,25 @@
       </c>
       <c r="Q5" s="317"/>
     </row>
-    <row r="6" spans="1:17" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:17" ht="21" customHeight="1">
       <c r="A6" s="297" t="s">
         <v>100</v>
       </c>
       <c r="B6" s="177" t="s">
         <v>2</v>
       </c>
-      <c r="C6" s="647">
+      <c r="C6" s="628">
         <f>+Resumen!P3</f>
         <v>0</v>
       </c>
-      <c r="D6" s="647"/>
-      <c r="E6" s="647"/>
-      <c r="F6" s="647"/>
-      <c r="G6" s="647"/>
-      <c r="H6" s="647"/>
-      <c r="I6" s="647"/>
-      <c r="J6" s="647"/>
-      <c r="K6" s="647"/>
+      <c r="D6" s="628"/>
+      <c r="E6" s="628"/>
+      <c r="F6" s="628"/>
+      <c r="G6" s="628"/>
+      <c r="H6" s="628"/>
+      <c r="I6" s="628"/>
+      <c r="J6" s="628"/>
+      <c r="K6" s="628"/>
       <c r="L6" s="458" t="s">
         <v>233</v>
       </c>
@@ -10689,25 +10689,25 @@
       <c r="P6" s="317"/>
       <c r="Q6" s="317"/>
     </row>
-    <row r="7" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:17" ht="15" customHeight="1">
       <c r="A7" s="297" t="s">
         <v>8</v>
       </c>
       <c r="B7" s="177" t="s">
         <v>2</v>
       </c>
-      <c r="C7" s="645">
+      <c r="C7" s="647">
         <f>+Resumen!P4</f>
         <v>0</v>
       </c>
-      <c r="D7" s="645"/>
-      <c r="E7" s="645"/>
-      <c r="F7" s="645"/>
-      <c r="G7" s="645"/>
-      <c r="H7" s="645"/>
-      <c r="I7" s="645"/>
-      <c r="J7" s="645"/>
-      <c r="K7" s="645"/>
+      <c r="D7" s="647"/>
+      <c r="E7" s="647"/>
+      <c r="F7" s="647"/>
+      <c r="G7" s="647"/>
+      <c r="H7" s="647"/>
+      <c r="I7" s="647"/>
+      <c r="J7" s="647"/>
+      <c r="K7" s="647"/>
       <c r="L7" s="458" t="s">
         <v>297</v>
       </c>
@@ -10722,25 +10722,25 @@
       <c r="P7" s="317"/>
       <c r="Q7" s="317"/>
     </row>
-    <row r="8" spans="1:17" ht="17.45" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:17" ht="17.399999999999999" customHeight="1">
       <c r="A8" s="297" t="s">
         <v>11</v>
       </c>
       <c r="B8" s="177" t="s">
         <v>2</v>
       </c>
-      <c r="C8" s="647">
+      <c r="C8" s="628">
         <f>+Resumen!P5</f>
         <v>0</v>
       </c>
-      <c r="D8" s="647"/>
-      <c r="E8" s="647"/>
-      <c r="F8" s="647"/>
-      <c r="G8" s="647"/>
-      <c r="H8" s="647"/>
-      <c r="I8" s="647"/>
-      <c r="J8" s="647"/>
-      <c r="K8" s="647"/>
+      <c r="D8" s="628"/>
+      <c r="E8" s="628"/>
+      <c r="F8" s="628"/>
+      <c r="G8" s="628"/>
+      <c r="H8" s="628"/>
+      <c r="I8" s="628"/>
+      <c r="J8" s="628"/>
+      <c r="K8" s="628"/>
       <c r="L8" s="458" t="s">
         <v>101</v>
       </c>
@@ -10748,14 +10748,14 @@
         <v>2</v>
       </c>
       <c r="N8" s="361">
-        <f>+Resumen!P9</f>
+        <f>+Resumen!P8</f>
         <v>0</v>
       </c>
       <c r="O8" s="317"/>
       <c r="P8" s="317"/>
       <c r="Q8" s="317"/>
     </row>
-    <row r="9" spans="1:17" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:17" ht="14.25" customHeight="1">
       <c r="A9" s="291" t="s">
         <v>14</v>
       </c>
@@ -10776,49 +10776,49 @@
       <c r="P9" s="317"/>
       <c r="Q9" s="317"/>
     </row>
-    <row r="10" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="A10" s="629" t="s">
+    <row r="10" spans="1:17">
+      <c r="A10" s="636" t="s">
         <v>102</v>
       </c>
-      <c r="B10" s="630"/>
-      <c r="C10" s="630"/>
-      <c r="D10" s="630"/>
-      <c r="E10" s="630"/>
-      <c r="F10" s="630"/>
-      <c r="G10" s="630"/>
-      <c r="H10" s="630"/>
-      <c r="I10" s="630"/>
-      <c r="J10" s="630"/>
-      <c r="K10" s="630"/>
-      <c r="L10" s="630"/>
-      <c r="M10" s="630"/>
-      <c r="N10" s="631"/>
+      <c r="B10" s="637"/>
+      <c r="C10" s="637"/>
+      <c r="D10" s="637"/>
+      <c r="E10" s="637"/>
+      <c r="F10" s="637"/>
+      <c r="G10" s="637"/>
+      <c r="H10" s="637"/>
+      <c r="I10" s="637"/>
+      <c r="J10" s="637"/>
+      <c r="K10" s="637"/>
+      <c r="L10" s="637"/>
+      <c r="M10" s="637"/>
+      <c r="N10" s="638"/>
       <c r="O10" s="317"/>
       <c r="P10" s="317"/>
       <c r="Q10" s="317"/>
     </row>
-    <row r="11" spans="1:17" ht="12" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A11" s="632" t="s">
+    <row r="11" spans="1:17" ht="12" customHeight="1">
+      <c r="A11" s="639" t="s">
         <v>103</v>
       </c>
-      <c r="B11" s="633"/>
-      <c r="C11" s="633"/>
-      <c r="D11" s="633"/>
-      <c r="E11" s="633"/>
-      <c r="F11" s="633"/>
-      <c r="G11" s="633"/>
-      <c r="H11" s="633"/>
-      <c r="I11" s="633"/>
-      <c r="J11" s="633"/>
-      <c r="K11" s="633"/>
-      <c r="L11" s="633"/>
-      <c r="M11" s="633"/>
-      <c r="N11" s="634"/>
+      <c r="B11" s="640"/>
+      <c r="C11" s="640"/>
+      <c r="D11" s="640"/>
+      <c r="E11" s="640"/>
+      <c r="F11" s="640"/>
+      <c r="G11" s="640"/>
+      <c r="H11" s="640"/>
+      <c r="I11" s="640"/>
+      <c r="J11" s="640"/>
+      <c r="K11" s="640"/>
+      <c r="L11" s="640"/>
+      <c r="M11" s="640"/>
+      <c r="N11" s="641"/>
       <c r="O11" s="317"/>
       <c r="P11" s="317"/>
       <c r="Q11" s="317"/>
     </row>
-    <row r="12" spans="1:17" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:17" ht="6" customHeight="1">
       <c r="A12" s="189"/>
       <c r="B12" s="190"/>
       <c r="C12" s="190"/>
@@ -10837,7 +10837,7 @@
       <c r="P12" s="317"/>
       <c r="Q12" s="317"/>
     </row>
-    <row r="13" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:17" ht="15" customHeight="1">
       <c r="A13" s="362" t="s">
         <v>17</v>
       </c>
@@ -10856,7 +10856,7 @@
       <c r="N13" s="182"/>
       <c r="Q13" s="317"/>
     </row>
-    <row r="14" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:17" ht="15" customHeight="1">
       <c r="A14" s="40" t="s">
         <v>104</v>
       </c>
@@ -10886,7 +10886,7 @@
       </c>
       <c r="Q14" s="317"/>
     </row>
-    <row r="15" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:17" ht="15" customHeight="1">
       <c r="A15" s="40" t="s">
         <v>25</v>
       </c>
@@ -10916,7 +10916,7 @@
       </c>
       <c r="Q15" s="317"/>
     </row>
-    <row r="16" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:17" ht="15" customHeight="1">
       <c r="A16" s="40" t="s">
         <v>232</v>
       </c>
@@ -10949,7 +10949,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:17" ht="15" customHeight="1">
       <c r="A17" s="155" t="s">
         <v>33</v>
       </c>
@@ -10979,37 +10979,37 @@
       </c>
       <c r="Q17" s="317"/>
     </row>
-    <row r="18" spans="1:17" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:17" ht="6.75" customHeight="1">
       <c r="A18" s="310"/>
       <c r="B18" s="310"/>
       <c r="C18" s="310"/>
-      <c r="D18" s="638"/>
-      <c r="E18" s="638"/>
+      <c r="D18" s="644"/>
+      <c r="E18" s="644"/>
       <c r="F18" s="310"/>
       <c r="G18" s="310"/>
       <c r="H18" s="310"/>
       <c r="I18" s="310"/>
       <c r="J18" s="310"/>
       <c r="K18" s="310"/>
-      <c r="L18" s="638"/>
-      <c r="M18" s="638"/>
+      <c r="L18" s="644"/>
+      <c r="M18" s="644"/>
       <c r="N18" s="310"/>
       <c r="O18" s="317"/>
       <c r="P18" s="317"/>
       <c r="Q18" s="317"/>
     </row>
-    <row r="19" spans="1:17" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:17" ht="18" customHeight="1">
       <c r="A19" s="310"/>
       <c r="B19" s="310"/>
       <c r="C19" s="310"/>
-      <c r="D19" s="639" t="s">
+      <c r="D19" s="645" t="s">
         <v>108</v>
       </c>
-      <c r="E19" s="639"/>
-      <c r="F19" s="639"/>
-      <c r="G19" s="639"/>
-      <c r="H19" s="639"/>
-      <c r="I19" s="639"/>
+      <c r="E19" s="645"/>
+      <c r="F19" s="645"/>
+      <c r="G19" s="645"/>
+      <c r="H19" s="645"/>
+      <c r="I19" s="645"/>
       <c r="J19" s="311" t="s">
         <v>109</v>
       </c>
@@ -11023,7 +11023,7 @@
       <c r="P19" s="317"/>
       <c r="Q19" s="317"/>
     </row>
-    <row r="20" spans="1:17" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:17" ht="17.25" customHeight="1">
       <c r="A20" s="188"/>
       <c r="B20" s="188"/>
       <c r="C20" s="320"/>
@@ -11042,14 +11042,14 @@
         <f>+'Datos ensayo'!G17</f>
         <v>1</v>
       </c>
-      <c r="L20" s="636"/>
-      <c r="M20" s="636"/>
+      <c r="L20" s="642"/>
+      <c r="M20" s="642"/>
       <c r="N20" s="312"/>
       <c r="O20" s="317"/>
       <c r="P20" s="317"/>
       <c r="Q20" s="317"/>
     </row>
-    <row r="21" spans="1:17" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:17" ht="17.25" customHeight="1">
       <c r="A21" s="188"/>
       <c r="B21" s="188"/>
       <c r="C21" s="320"/>
@@ -11068,14 +11068,14 @@
         <f>+'Datos ensayo'!G18</f>
         <v>0</v>
       </c>
-      <c r="L21" s="636"/>
-      <c r="M21" s="636"/>
+      <c r="L21" s="642"/>
+      <c r="M21" s="642"/>
       <c r="N21" s="312"/>
       <c r="O21" s="317"/>
       <c r="P21" s="317"/>
       <c r="Q21" s="317"/>
     </row>
-    <row r="22" spans="1:17" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:17" ht="17.25" customHeight="1">
       <c r="A22" s="188"/>
       <c r="B22" s="188"/>
       <c r="C22" s="320"/>
@@ -11094,14 +11094,14 @@
         <f>+'Datos ensayo'!H19</f>
         <v>0,00</v>
       </c>
-      <c r="L22" s="637"/>
-      <c r="M22" s="637"/>
+      <c r="L22" s="643"/>
+      <c r="M22" s="643"/>
       <c r="N22" s="313"/>
       <c r="O22" s="323"/>
       <c r="P22" s="323"/>
       <c r="Q22" s="317"/>
     </row>
-    <row r="23" spans="1:17" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:17" ht="17.25" customHeight="1">
       <c r="A23" s="188"/>
       <c r="B23" s="188"/>
       <c r="C23" s="320"/>
@@ -11127,7 +11127,7 @@
       <c r="P23" s="317"/>
       <c r="Q23" s="317"/>
     </row>
-    <row r="24" spans="1:17" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:17" ht="17.25" customHeight="1">
       <c r="A24" s="188"/>
       <c r="B24" s="188"/>
       <c r="C24" s="320"/>
@@ -11153,7 +11153,7 @@
       <c r="P24" s="317"/>
       <c r="Q24" s="317"/>
     </row>
-    <row r="25" spans="1:17" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:17" ht="17.25" customHeight="1">
       <c r="A25" s="188"/>
       <c r="B25" s="188"/>
       <c r="C25" s="320"/>
@@ -11179,7 +11179,7 @@
       <c r="P25" s="317"/>
       <c r="Q25" s="317"/>
     </row>
-    <row r="26" spans="1:17" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:17" ht="17.25" customHeight="1">
       <c r="A26" s="13"/>
       <c r="B26" s="13"/>
       <c r="C26" s="314"/>
@@ -11205,7 +11205,7 @@
       <c r="P26" s="317"/>
       <c r="Q26" s="317"/>
     </row>
-    <row r="27" spans="1:17" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:17" ht="17.25" customHeight="1">
       <c r="A27" s="188"/>
       <c r="B27" s="188"/>
       <c r="C27" s="320"/>
@@ -11231,7 +11231,7 @@
       <c r="P27" s="317"/>
       <c r="Q27" s="317"/>
     </row>
-    <row r="28" spans="1:17" ht="4.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:17" ht="4.5" customHeight="1">
       <c r="A28" s="188"/>
       <c r="B28" s="188"/>
       <c r="C28" s="188"/>
@@ -11250,7 +11250,7 @@
       <c r="P28" s="317"/>
       <c r="Q28" s="317"/>
     </row>
-    <row r="29" spans="1:17" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:17" ht="15.9" customHeight="1">
       <c r="A29" s="170" t="s">
         <v>118</v>
       </c>
@@ -11271,7 +11271,7 @@
       <c r="P29" s="317"/>
       <c r="Q29" s="317"/>
     </row>
-    <row r="30" spans="1:17" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:17" ht="15.9" customHeight="1">
       <c r="A30" s="356" t="s">
         <v>119</v>
       </c>
@@ -11295,7 +11295,7 @@
       <c r="P30" s="317"/>
       <c r="Q30" s="317"/>
     </row>
-    <row r="31" spans="1:17" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:17" ht="15.9" customHeight="1">
       <c r="A31" s="356" t="s">
         <v>120</v>
       </c>
@@ -11319,7 +11319,7 @@
       <c r="P31" s="317"/>
       <c r="Q31" s="317"/>
     </row>
-    <row r="32" spans="1:17" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:17" ht="15.9" customHeight="1">
       <c r="A32" s="356" t="s">
         <v>121</v>
       </c>
@@ -11343,7 +11343,7 @@
       <c r="P32" s="317"/>
       <c r="Q32" s="317"/>
     </row>
-    <row r="33" spans="1:17" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:17" ht="15.9" customHeight="1">
       <c r="A33" s="356" t="s">
         <v>122</v>
       </c>
@@ -11367,7 +11367,7 @@
       <c r="P33" s="317"/>
       <c r="Q33" s="317"/>
     </row>
-    <row r="34" spans="1:17" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:17" ht="14.25" customHeight="1">
       <c r="A34" s="356" t="s">
         <v>123</v>
       </c>
@@ -11391,7 +11391,7 @@
       <c r="P34" s="317"/>
       <c r="Q34" s="317"/>
     </row>
-    <row r="35" spans="1:17" ht="5.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:17" ht="5.25" customHeight="1">
       <c r="A35" s="356"/>
       <c r="B35" s="193"/>
       <c r="C35" s="193"/>
@@ -11410,7 +11410,7 @@
       <c r="P35" s="317"/>
       <c r="Q35" s="317"/>
     </row>
-    <row r="36" spans="1:17" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:17" ht="14.25" customHeight="1">
       <c r="A36" s="170" t="s">
         <v>228</v>
       </c>
@@ -11431,7 +11431,7 @@
       <c r="P36" s="317"/>
       <c r="Q36" s="317"/>
     </row>
-    <row r="37" spans="1:17" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:17" ht="14.25" customHeight="1">
       <c r="A37" s="357" t="s">
         <v>230</v>
       </c>
@@ -11444,18 +11444,18 @@
       <c r="H37" s="193"/>
       <c r="I37" s="195"/>
       <c r="J37" s="195"/>
-      <c r="K37" s="646">
+      <c r="K37" s="648">
         <f>+Resumen!E27</f>
         <v>0</v>
       </c>
-      <c r="L37" s="646"/>
+      <c r="L37" s="648"/>
       <c r="M37" s="159"/>
       <c r="N37" s="159"/>
       <c r="O37" s="317"/>
       <c r="P37" s="317"/>
       <c r="Q37" s="317"/>
     </row>
-    <row r="38" spans="1:17" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:17" ht="14.25" customHeight="1">
       <c r="A38" s="357" t="s">
         <v>229</v>
       </c>
@@ -11468,25 +11468,25 @@
       <c r="H38" s="193"/>
       <c r="I38" s="195"/>
       <c r="J38" s="195"/>
-      <c r="K38" s="640">
+      <c r="K38" s="646">
         <f>+Resumen!E28</f>
         <v>0</v>
       </c>
-      <c r="L38" s="640"/>
+      <c r="L38" s="646"/>
       <c r="M38" s="159"/>
       <c r="N38" s="159"/>
       <c r="O38" s="317"/>
       <c r="P38" s="317"/>
       <c r="Q38" s="317"/>
     </row>
-    <row r="39" spans="1:17" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:17" ht="6" customHeight="1">
       <c r="M39" s="159"/>
       <c r="N39" s="159"/>
       <c r="O39" s="317"/>
       <c r="P39" s="317"/>
       <c r="Q39" s="317"/>
     </row>
-    <row r="40" spans="1:17" ht="10.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:17" ht="10.5" customHeight="1">
       <c r="A40" s="170" t="s">
         <v>124</v>
       </c>
@@ -11507,112 +11507,112 @@
       <c r="P40" s="317"/>
       <c r="Q40" s="317"/>
     </row>
-    <row r="41" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A41" s="648" t="s">
+    <row r="41" spans="1:17" ht="15" customHeight="1">
+      <c r="A41" s="629" t="s">
         <v>312</v>
       </c>
-      <c r="B41" s="648"/>
-      <c r="C41" s="648"/>
-      <c r="D41" s="648"/>
-      <c r="E41" s="648"/>
-      <c r="F41" s="648"/>
-      <c r="G41" s="648"/>
-      <c r="H41" s="648"/>
-      <c r="I41" s="648"/>
-      <c r="J41" s="648"/>
-      <c r="K41" s="648"/>
-      <c r="L41" s="648"/>
-      <c r="M41" s="648"/>
-      <c r="N41" s="648"/>
+      <c r="B41" s="629"/>
+      <c r="C41" s="629"/>
+      <c r="D41" s="629"/>
+      <c r="E41" s="629"/>
+      <c r="F41" s="629"/>
+      <c r="G41" s="629"/>
+      <c r="H41" s="629"/>
+      <c r="I41" s="629"/>
+      <c r="J41" s="629"/>
+      <c r="K41" s="629"/>
+      <c r="L41" s="629"/>
+      <c r="M41" s="629"/>
+      <c r="N41" s="629"/>
       <c r="O41" s="317"/>
       <c r="P41" s="317"/>
       <c r="Q41" s="317"/>
     </row>
-    <row r="42" spans="1:17" ht="33" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A42" s="635" t="s">
+    <row r="42" spans="1:17" ht="33" customHeight="1">
+      <c r="A42" s="632" t="s">
         <v>313</v>
       </c>
-      <c r="B42" s="635"/>
-      <c r="C42" s="635"/>
-      <c r="D42" s="635"/>
-      <c r="E42" s="635"/>
-      <c r="F42" s="635"/>
-      <c r="G42" s="635"/>
-      <c r="H42" s="635"/>
-      <c r="I42" s="635"/>
-      <c r="J42" s="635"/>
-      <c r="K42" s="635"/>
-      <c r="L42" s="635"/>
-      <c r="M42" s="635"/>
-      <c r="N42" s="635"/>
+      <c r="B42" s="632"/>
+      <c r="C42" s="632"/>
+      <c r="D42" s="632"/>
+      <c r="E42" s="632"/>
+      <c r="F42" s="632"/>
+      <c r="G42" s="632"/>
+      <c r="H42" s="632"/>
+      <c r="I42" s="632"/>
+      <c r="J42" s="632"/>
+      <c r="K42" s="632"/>
+      <c r="L42" s="632"/>
+      <c r="M42" s="632"/>
+      <c r="N42" s="632"/>
       <c r="O42" s="317"/>
       <c r="P42" s="317"/>
       <c r="Q42" s="317"/>
     </row>
-    <row r="43" spans="1:17" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A43" s="635" t="s">
+    <row r="43" spans="1:17" ht="18.600000000000001" customHeight="1">
+      <c r="A43" s="632" t="s">
         <v>314</v>
       </c>
-      <c r="B43" s="635"/>
-      <c r="C43" s="635"/>
-      <c r="D43" s="635"/>
-      <c r="E43" s="635"/>
-      <c r="F43" s="635"/>
-      <c r="G43" s="635"/>
-      <c r="H43" s="635"/>
-      <c r="I43" s="635"/>
-      <c r="J43" s="635"/>
-      <c r="K43" s="635"/>
-      <c r="L43" s="635"/>
-      <c r="M43" s="635"/>
-      <c r="N43" s="635"/>
+      <c r="B43" s="632"/>
+      <c r="C43" s="632"/>
+      <c r="D43" s="632"/>
+      <c r="E43" s="632"/>
+      <c r="F43" s="632"/>
+      <c r="G43" s="632"/>
+      <c r="H43" s="632"/>
+      <c r="I43" s="632"/>
+      <c r="J43" s="632"/>
+      <c r="K43" s="632"/>
+      <c r="L43" s="632"/>
+      <c r="M43" s="632"/>
+      <c r="N43" s="632"/>
       <c r="O43" s="317"/>
       <c r="P43" s="317"/>
       <c r="Q43" s="317"/>
     </row>
-    <row r="44" spans="1:17" ht="23.45" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A44" s="635" t="s">
+    <row r="44" spans="1:17" ht="23.4" customHeight="1">
+      <c r="A44" s="632" t="s">
         <v>315</v>
       </c>
-      <c r="B44" s="635"/>
-      <c r="C44" s="635"/>
-      <c r="D44" s="635"/>
-      <c r="E44" s="635"/>
-      <c r="F44" s="635"/>
-      <c r="G44" s="635"/>
-      <c r="H44" s="635"/>
-      <c r="I44" s="635"/>
-      <c r="J44" s="635"/>
-      <c r="K44" s="635"/>
-      <c r="L44" s="635"/>
-      <c r="M44" s="635"/>
-      <c r="N44" s="635"/>
+      <c r="B44" s="632"/>
+      <c r="C44" s="632"/>
+      <c r="D44" s="632"/>
+      <c r="E44" s="632"/>
+      <c r="F44" s="632"/>
+      <c r="G44" s="632"/>
+      <c r="H44" s="632"/>
+      <c r="I44" s="632"/>
+      <c r="J44" s="632"/>
+      <c r="K44" s="632"/>
+      <c r="L44" s="632"/>
+      <c r="M44" s="632"/>
+      <c r="N44" s="632"/>
       <c r="O44" s="317"/>
       <c r="P44" s="317"/>
       <c r="Q44" s="317"/>
     </row>
-    <row r="45" spans="1:17" ht="23.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A45" s="644" t="s">
+    <row r="45" spans="1:17" ht="23.25" customHeight="1">
+      <c r="A45" s="634" t="s">
         <v>316</v>
       </c>
-      <c r="B45" s="644"/>
-      <c r="C45" s="644"/>
-      <c r="D45" s="644"/>
-      <c r="E45" s="644"/>
-      <c r="F45" s="644"/>
-      <c r="G45" s="644"/>
-      <c r="H45" s="644"/>
-      <c r="I45" s="644"/>
-      <c r="J45" s="644"/>
-      <c r="K45" s="644"/>
-      <c r="L45" s="644"/>
-      <c r="M45" s="644"/>
-      <c r="N45" s="644"/>
+      <c r="B45" s="634"/>
+      <c r="C45" s="634"/>
+      <c r="D45" s="634"/>
+      <c r="E45" s="634"/>
+      <c r="F45" s="634"/>
+      <c r="G45" s="634"/>
+      <c r="H45" s="634"/>
+      <c r="I45" s="634"/>
+      <c r="J45" s="634"/>
+      <c r="K45" s="634"/>
+      <c r="L45" s="634"/>
+      <c r="M45" s="634"/>
+      <c r="N45" s="634"/>
       <c r="O45" s="317"/>
       <c r="P45" s="317"/>
       <c r="Q45" s="317"/>
     </row>
-    <row r="46" spans="1:17" ht="5.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="46" spans="1:17" ht="5.25" customHeight="1">
       <c r="A46" s="193"/>
       <c r="B46" s="196"/>
       <c r="C46" s="196"/>
@@ -11620,7 +11620,7 @@
       <c r="P46" s="317"/>
       <c r="Q46" s="317"/>
     </row>
-    <row r="47" spans="1:17" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="47" spans="1:17" ht="19.5" customHeight="1">
       <c r="A47" s="170" t="s">
         <v>98</v>
       </c>
@@ -11641,19 +11641,19 @@
       <c r="P47" s="317"/>
       <c r="Q47" s="317"/>
     </row>
-    <row r="48" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="48" spans="1:17" ht="15" customHeight="1">
       <c r="A48" s="196"/>
       <c r="B48" s="196"/>
       <c r="C48" s="196"/>
-      <c r="K48" s="643"/>
-      <c r="L48" s="643"/>
-      <c r="M48" s="643"/>
-      <c r="N48" s="643"/>
+      <c r="K48" s="633"/>
+      <c r="L48" s="633"/>
+      <c r="M48" s="633"/>
+      <c r="N48" s="633"/>
       <c r="O48" s="317"/>
       <c r="P48" s="317"/>
       <c r="Q48" s="317"/>
     </row>
-    <row r="49" spans="1:17" ht="66.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="49" spans="1:17" ht="66.75" customHeight="1">
       <c r="A49" s="196"/>
       <c r="B49" s="196"/>
       <c r="C49" s="196"/>
@@ -11666,19 +11666,19 @@
       <c r="P49" s="317"/>
       <c r="Q49" s="317"/>
     </row>
-    <row r="50" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="50" spans="1:17">
       <c r="A50" s="196"/>
       <c r="B50" s="196"/>
       <c r="C50" s="196"/>
-      <c r="K50" s="643"/>
-      <c r="L50" s="643"/>
-      <c r="M50" s="643"/>
-      <c r="N50" s="643"/>
+      <c r="K50" s="633"/>
+      <c r="L50" s="633"/>
+      <c r="M50" s="633"/>
+      <c r="N50" s="633"/>
       <c r="O50" s="317"/>
       <c r="P50" s="317"/>
       <c r="Q50" s="317"/>
     </row>
-    <row r="51" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="51" spans="1:17">
       <c r="A51" s="195" t="s">
         <v>91</v>
       </c>
@@ -11691,12 +11691,12 @@
       <c r="H51" s="324"/>
       <c r="I51" s="324"/>
       <c r="J51" s="324"/>
-      <c r="K51" s="643"/>
-      <c r="L51" s="643"/>
-      <c r="M51" s="643"/>
-      <c r="N51" s="643"/>
-    </row>
-    <row r="52" spans="1:17" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="K51" s="633"/>
+      <c r="L51" s="633"/>
+      <c r="M51" s="633"/>
+      <c r="N51" s="633"/>
+    </row>
+    <row r="52" spans="1:17" ht="11.25" customHeight="1">
       <c r="A52" s="195" t="s">
         <v>317</v>
       </c>
@@ -11709,30 +11709,30 @@
       <c r="H52" s="324"/>
       <c r="I52" s="324"/>
       <c r="J52" s="324"/>
-      <c r="K52" s="643" t="s">
+      <c r="K52" s="633" t="s">
         <v>125</v>
       </c>
-      <c r="L52" s="643"/>
-      <c r="M52" s="643"/>
-      <c r="N52" s="643"/>
-    </row>
-    <row r="53" spans="1:17" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="L52" s="633"/>
+      <c r="M52" s="633"/>
+      <c r="N52" s="633"/>
+    </row>
+    <row r="53" spans="1:17" ht="15.9" customHeight="1">
       <c r="M53" s="185"/>
       <c r="N53" s="317"/>
     </row>
-    <row r="54" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="54" spans="1:17">
       <c r="M54" s="186"/>
       <c r="N54" s="317"/>
     </row>
-    <row r="55" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="55" spans="1:17">
       <c r="M55" s="317"/>
       <c r="N55" s="317"/>
     </row>
-    <row r="56" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="56" spans="1:17">
       <c r="M56" s="317"/>
       <c r="N56" s="317"/>
     </row>
-    <row r="57" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="57" spans="1:17">
       <c r="A57" s="317"/>
       <c r="B57" s="317"/>
       <c r="C57" s="317"/>
@@ -11747,7 +11747,7 @@
       <c r="L57" s="317"/>
       <c r="M57" s="317"/>
     </row>
-    <row r="58" spans="1:17" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="58" spans="1:17" ht="11.25" customHeight="1">
       <c r="A58" s="187"/>
       <c r="B58" s="187"/>
       <c r="C58" s="187"/>
@@ -11763,23 +11763,23 @@
       <c r="M58" s="187"/>
       <c r="N58" s="187"/>
     </row>
-    <row r="59" spans="1:17" ht="30" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A59" s="642"/>
-      <c r="B59" s="642"/>
-      <c r="C59" s="642"/>
-      <c r="D59" s="642"/>
-      <c r="E59" s="642"/>
-      <c r="F59" s="642"/>
-      <c r="G59" s="642"/>
-      <c r="H59" s="642"/>
-      <c r="I59" s="642"/>
-      <c r="J59" s="642"/>
-      <c r="K59" s="642"/>
-      <c r="L59" s="642"/>
-      <c r="M59" s="642"/>
-      <c r="N59" s="642"/>
-    </row>
-    <row r="60" spans="1:17" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="59" spans="1:17" ht="30" customHeight="1">
+      <c r="A59" s="631"/>
+      <c r="B59" s="631"/>
+      <c r="C59" s="631"/>
+      <c r="D59" s="631"/>
+      <c r="E59" s="631"/>
+      <c r="F59" s="631"/>
+      <c r="G59" s="631"/>
+      <c r="H59" s="631"/>
+      <c r="I59" s="631"/>
+      <c r="J59" s="631"/>
+      <c r="K59" s="631"/>
+      <c r="L59" s="631"/>
+      <c r="M59" s="631"/>
+      <c r="N59" s="631"/>
+    </row>
+    <row r="60" spans="1:17" ht="30" customHeight="1">
       <c r="A60" s="193"/>
       <c r="B60" s="193"/>
       <c r="C60" s="193"/>
@@ -11795,23 +11795,23 @@
       <c r="M60" s="324"/>
       <c r="N60" s="324"/>
     </row>
-    <row r="61" spans="1:17" ht="39.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A61" s="642"/>
-      <c r="B61" s="642"/>
-      <c r="C61" s="642"/>
-      <c r="D61" s="642"/>
-      <c r="E61" s="642"/>
-      <c r="F61" s="642"/>
-      <c r="G61" s="642"/>
-      <c r="H61" s="642"/>
-      <c r="I61" s="642"/>
-      <c r="J61" s="642"/>
-      <c r="K61" s="642"/>
-      <c r="L61" s="642"/>
-      <c r="M61" s="642"/>
-      <c r="N61" s="642"/>
-    </row>
-    <row r="62" spans="1:17" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="61" spans="1:17" ht="39.75" customHeight="1">
+      <c r="A61" s="631"/>
+      <c r="B61" s="631"/>
+      <c r="C61" s="631"/>
+      <c r="D61" s="631"/>
+      <c r="E61" s="631"/>
+      <c r="F61" s="631"/>
+      <c r="G61" s="631"/>
+      <c r="H61" s="631"/>
+      <c r="I61" s="631"/>
+      <c r="J61" s="631"/>
+      <c r="K61" s="631"/>
+      <c r="L61" s="631"/>
+      <c r="M61" s="631"/>
+      <c r="N61" s="631"/>
+    </row>
+    <row r="62" spans="1:17" ht="30" customHeight="1">
       <c r="A62" s="194"/>
       <c r="B62" s="194"/>
       <c r="C62" s="194"/>
@@ -11827,7 +11827,7 @@
       <c r="M62" s="307"/>
       <c r="N62" s="307"/>
     </row>
-    <row r="63" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="63" spans="1:17">
       <c r="A63" s="327"/>
       <c r="B63" s="327"/>
       <c r="C63" s="327"/>
@@ -11843,139 +11843,139 @@
       <c r="M63" s="327"/>
       <c r="N63" s="327"/>
     </row>
-    <row r="70" spans="11:14" x14ac:dyDescent="0.2">
+    <row r="70" spans="11:14">
       <c r="K70" s="317"/>
       <c r="L70" s="317"/>
       <c r="M70" s="317"/>
       <c r="N70" s="317"/>
     </row>
-    <row r="71" spans="11:14" x14ac:dyDescent="0.2">
+    <row r="71" spans="11:14">
       <c r="K71" s="317"/>
       <c r="L71" s="317"/>
       <c r="M71" s="317"/>
       <c r="N71" s="317"/>
     </row>
-    <row r="72" spans="11:14" x14ac:dyDescent="0.2">
+    <row r="72" spans="11:14">
       <c r="K72" s="317"/>
       <c r="L72" s="317"/>
       <c r="M72" s="317"/>
       <c r="N72" s="317"/>
     </row>
-    <row r="73" spans="11:14" x14ac:dyDescent="0.2">
+    <row r="73" spans="11:14">
       <c r="K73" s="317"/>
       <c r="L73" s="317"/>
       <c r="M73" s="317"/>
       <c r="N73" s="317"/>
     </row>
-    <row r="74" spans="11:14" x14ac:dyDescent="0.2">
+    <row r="74" spans="11:14">
       <c r="K74" s="317"/>
       <c r="L74" s="317"/>
       <c r="M74" s="317"/>
       <c r="N74" s="317"/>
     </row>
-    <row r="75" spans="11:14" x14ac:dyDescent="0.2">
+    <row r="75" spans="11:14">
       <c r="K75" s="317"/>
       <c r="L75" s="317"/>
       <c r="M75" s="317"/>
       <c r="N75" s="317"/>
     </row>
-    <row r="76" spans="11:14" x14ac:dyDescent="0.2">
+    <row r="76" spans="11:14">
       <c r="K76" s="317"/>
       <c r="L76" s="317"/>
       <c r="M76" s="317"/>
       <c r="N76" s="317"/>
     </row>
-    <row r="77" spans="11:14" x14ac:dyDescent="0.2">
+    <row r="77" spans="11:14">
       <c r="K77" s="317"/>
       <c r="L77" s="317"/>
       <c r="M77" s="317"/>
       <c r="N77" s="317"/>
     </row>
-    <row r="78" spans="11:14" x14ac:dyDescent="0.2">
+    <row r="78" spans="11:14">
       <c r="K78" s="328"/>
       <c r="L78" s="328"/>
       <c r="M78" s="328"/>
       <c r="N78" s="317"/>
     </row>
-    <row r="79" spans="11:14" x14ac:dyDescent="0.2">
-      <c r="K79" s="641"/>
-      <c r="L79" s="641"/>
-      <c r="M79" s="641"/>
+    <row r="79" spans="11:14">
+      <c r="K79" s="630"/>
+      <c r="L79" s="630"/>
+      <c r="M79" s="630"/>
       <c r="N79" s="317"/>
     </row>
-    <row r="80" spans="11:14" x14ac:dyDescent="0.2">
-      <c r="K80" s="641"/>
-      <c r="L80" s="641"/>
-      <c r="M80" s="641"/>
+    <row r="80" spans="11:14">
+      <c r="K80" s="630"/>
+      <c r="L80" s="630"/>
+      <c r="M80" s="630"/>
       <c r="N80" s="317"/>
     </row>
-    <row r="81" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="81" spans="1:14">
       <c r="K81" s="329"/>
       <c r="L81" s="329"/>
       <c r="M81" s="329"/>
       <c r="N81" s="317"/>
     </row>
-    <row r="82" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="82" spans="1:14">
       <c r="K82" s="329"/>
       <c r="L82" s="329"/>
       <c r="M82" s="329"/>
       <c r="N82" s="317"/>
     </row>
-    <row r="83" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="83" spans="1:14">
       <c r="K83" s="329"/>
       <c r="L83" s="329"/>
       <c r="M83" s="329"/>
       <c r="N83" s="317"/>
     </row>
-    <row r="84" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="84" spans="1:14">
       <c r="K84" s="329"/>
       <c r="L84" s="329"/>
       <c r="M84" s="329"/>
       <c r="N84" s="317"/>
     </row>
-    <row r="85" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="85" spans="1:14">
       <c r="K85" s="329"/>
       <c r="L85" s="329"/>
       <c r="M85" s="329"/>
       <c r="N85" s="317"/>
     </row>
-    <row r="86" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="86" spans="1:14">
       <c r="K86" s="329"/>
       <c r="L86" s="329"/>
       <c r="M86" s="329"/>
       <c r="N86" s="317"/>
     </row>
-    <row r="87" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="87" spans="1:14">
       <c r="K87" s="329"/>
       <c r="L87" s="329"/>
       <c r="M87" s="329"/>
       <c r="N87" s="317"/>
     </row>
-    <row r="88" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="88" spans="1:14">
       <c r="K88" s="329"/>
       <c r="L88" s="329"/>
       <c r="M88" s="329"/>
       <c r="N88" s="317"/>
     </row>
-    <row r="89" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="89" spans="1:14">
       <c r="K89" s="329"/>
       <c r="L89" s="329"/>
       <c r="M89" s="329"/>
       <c r="N89" s="317"/>
     </row>
-    <row r="90" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="90" spans="1:14">
       <c r="K90" s="329"/>
       <c r="L90" s="329"/>
       <c r="M90" s="329"/>
       <c r="N90" s="317"/>
     </row>
-    <row r="91" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="91" spans="1:14">
       <c r="K91" s="329"/>
       <c r="L91" s="329"/>
       <c r="M91" s="329"/>
       <c r="N91" s="317"/>
     </row>
-    <row r="92" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="92" spans="1:14">
       <c r="A92" s="317"/>
       <c r="B92" s="317"/>
       <c r="C92" s="317"/>
@@ -11991,7 +11991,7 @@
       <c r="M92" s="317"/>
       <c r="N92" s="317"/>
     </row>
-    <row r="93" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="93" spans="1:14">
       <c r="A93" s="317"/>
       <c r="B93" s="317"/>
       <c r="C93" s="317"/>
@@ -12007,7 +12007,7 @@
       <c r="M93" s="317"/>
       <c r="N93" s="317"/>
     </row>
-    <row r="94" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="94" spans="1:14">
       <c r="A94" s="317"/>
       <c r="B94" s="317"/>
       <c r="C94" s="317"/>
@@ -12030,20 +12030,6 @@
     <protectedRange sqref="E5:F6" name="Rango3_3_1_1_1_1_1_2_1"/>
   </protectedRanges>
   <mergeCells count="30">
-    <mergeCell ref="C8:K8"/>
-    <mergeCell ref="A41:N41"/>
-    <mergeCell ref="M79:M80"/>
-    <mergeCell ref="A59:N59"/>
-    <mergeCell ref="A61:N61"/>
-    <mergeCell ref="A42:N42"/>
-    <mergeCell ref="A44:N44"/>
-    <mergeCell ref="K50:N50"/>
-    <mergeCell ref="K48:N48"/>
-    <mergeCell ref="A45:N45"/>
-    <mergeCell ref="K51:N51"/>
-    <mergeCell ref="K52:N52"/>
-    <mergeCell ref="K79:K80"/>
-    <mergeCell ref="L79:L80"/>
     <mergeCell ref="A2:N2"/>
     <mergeCell ref="A3:N3"/>
     <mergeCell ref="A10:N10"/>
@@ -12060,6 +12046,20 @@
     <mergeCell ref="K37:L37"/>
     <mergeCell ref="C6:K6"/>
     <mergeCell ref="C7:K7"/>
+    <mergeCell ref="C8:K8"/>
+    <mergeCell ref="A41:N41"/>
+    <mergeCell ref="M79:M80"/>
+    <mergeCell ref="A59:N59"/>
+    <mergeCell ref="A61:N61"/>
+    <mergeCell ref="A42:N42"/>
+    <mergeCell ref="A44:N44"/>
+    <mergeCell ref="K50:N50"/>
+    <mergeCell ref="K48:N48"/>
+    <mergeCell ref="A45:N45"/>
+    <mergeCell ref="K51:N51"/>
+    <mergeCell ref="K52:N52"/>
+    <mergeCell ref="K79:K80"/>
+    <mergeCell ref="L79:L80"/>
   </mergeCells>
   <conditionalFormatting sqref="A30:A38">
     <cfRule type="cellIs" priority="1" stopIfTrue="1" operator="between">
@@ -12092,23 +12092,23 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:N53"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="10.28515625" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="10.33203125" defaultRowHeight="13.2"/>
   <cols>
-    <col min="1" max="1" width="4.7109375" style="317" customWidth="1"/>
-    <col min="2" max="2" width="11.28515625" style="317" customWidth="1"/>
-    <col min="3" max="3" width="12.28515625" style="317" customWidth="1"/>
-    <col min="4" max="5" width="11.28515625" style="317" customWidth="1"/>
-    <col min="6" max="6" width="13.28515625" style="317" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="12.140625" style="317" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.85546875" style="317" customWidth="1"/>
-    <col min="9" max="9" width="10.7109375" style="317" customWidth="1"/>
-    <col min="10" max="10" width="11.42578125" style="317" customWidth="1"/>
-    <col min="11" max="11" width="13.28515625" style="317" customWidth="1"/>
-    <col min="12" max="12" width="5.7109375" style="317" customWidth="1"/>
-    <col min="13" max="16384" width="10.28515625" style="317"/>
+    <col min="1" max="1" width="4.6640625" style="317" customWidth="1"/>
+    <col min="2" max="2" width="11.33203125" style="317" customWidth="1"/>
+    <col min="3" max="3" width="12.33203125" style="317" customWidth="1"/>
+    <col min="4" max="5" width="11.33203125" style="317" customWidth="1"/>
+    <col min="6" max="6" width="13.33203125" style="317" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="12.109375" style="317" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.88671875" style="317" customWidth="1"/>
+    <col min="9" max="9" width="10.6640625" style="317" customWidth="1"/>
+    <col min="10" max="10" width="11.44140625" style="317" customWidth="1"/>
+    <col min="11" max="11" width="13.33203125" style="317" customWidth="1"/>
+    <col min="12" max="12" width="5.6640625" style="317" customWidth="1"/>
+    <col min="13" max="16384" width="10.33203125" style="317"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" ht="5.45" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:14" ht="5.4" customHeight="1">
       <c r="A1" s="383"/>
       <c r="B1" s="384"/>
       <c r="C1" s="384"/>
@@ -12123,41 +12123,41 @@
       <c r="L1" s="385"/>
       <c r="M1" s="386"/>
     </row>
-    <row r="2" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:14" ht="15" customHeight="1">
       <c r="A2" s="387"/>
-      <c r="B2" s="661" t="s">
+      <c r="B2" s="649" t="s">
         <v>102</v>
       </c>
-      <c r="C2" s="661"/>
-      <c r="D2" s="661"/>
-      <c r="E2" s="661"/>
-      <c r="F2" s="661"/>
-      <c r="G2" s="661"/>
-      <c r="H2" s="661"/>
-      <c r="I2" s="661"/>
-      <c r="J2" s="661"/>
-      <c r="K2" s="661"/>
+      <c r="C2" s="649"/>
+      <c r="D2" s="649"/>
+      <c r="E2" s="649"/>
+      <c r="F2" s="649"/>
+      <c r="G2" s="649"/>
+      <c r="H2" s="649"/>
+      <c r="I2" s="649"/>
+      <c r="J2" s="649"/>
+      <c r="K2" s="649"/>
       <c r="L2" s="374"/>
       <c r="M2" s="386"/>
     </row>
-    <row r="3" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:14" ht="15" customHeight="1">
       <c r="A3" s="387"/>
-      <c r="B3" s="661" t="s">
+      <c r="B3" s="649" t="s">
         <v>103</v>
       </c>
-      <c r="C3" s="661"/>
-      <c r="D3" s="661"/>
-      <c r="E3" s="661"/>
-      <c r="F3" s="661"/>
-      <c r="G3" s="661"/>
-      <c r="H3" s="661"/>
-      <c r="I3" s="661"/>
-      <c r="J3" s="661"/>
-      <c r="K3" s="661"/>
+      <c r="C3" s="649"/>
+      <c r="D3" s="649"/>
+      <c r="E3" s="649"/>
+      <c r="F3" s="649"/>
+      <c r="G3" s="649"/>
+      <c r="H3" s="649"/>
+      <c r="I3" s="649"/>
+      <c r="J3" s="649"/>
+      <c r="K3" s="649"/>
       <c r="L3" s="374"/>
       <c r="M3" s="386"/>
     </row>
-    <row r="4" spans="1:14" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:14" ht="6.6" customHeight="1">
       <c r="A4" s="387"/>
       <c r="B4" s="375"/>
       <c r="C4" s="375"/>
@@ -12172,14 +12172,14 @@
       <c r="L4" s="374"/>
       <c r="M4" s="386"/>
     </row>
-    <row r="5" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:14" ht="15" customHeight="1">
       <c r="A5" s="387"/>
-      <c r="B5" s="652" t="s">
+      <c r="B5" s="655" t="s">
         <v>126</v>
       </c>
-      <c r="C5" s="653"/>
-      <c r="D5" s="653"/>
-      <c r="E5" s="654"/>
+      <c r="C5" s="656"/>
+      <c r="D5" s="656"/>
+      <c r="E5" s="657"/>
       <c r="F5" s="331">
         <f>+Resumen!J26</f>
         <v>0</v>
@@ -12194,7 +12194,7 @@
       <c r="L5" s="374"/>
       <c r="M5" s="386"/>
     </row>
-    <row r="6" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:14" ht="15" customHeight="1">
       <c r="A6" s="387"/>
       <c r="B6" s="375"/>
       <c r="C6" s="375"/>
@@ -12212,14 +12212,14 @@
       <c r="M6" s="386"/>
       <c r="N6" s="197"/>
     </row>
-    <row r="7" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:14" ht="15" customHeight="1">
       <c r="A7" s="387"/>
-      <c r="B7" s="652" t="s">
+      <c r="B7" s="655" t="s">
         <v>129</v>
       </c>
-      <c r="C7" s="653"/>
-      <c r="D7" s="653"/>
-      <c r="E7" s="654"/>
+      <c r="C7" s="656"/>
+      <c r="D7" s="656"/>
+      <c r="E7" s="657"/>
       <c r="F7" s="331">
         <f>+IF(F5="A",0.1,0.01)</f>
         <v>0.01</v>
@@ -12229,7 +12229,7 @@
       <c r="M7" s="386"/>
       <c r="N7" s="197"/>
     </row>
-    <row r="8" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:14" ht="15" customHeight="1">
       <c r="A8" s="387"/>
       <c r="B8" s="375"/>
       <c r="C8" s="375"/>
@@ -12254,7 +12254,7 @@
       <c r="L8" s="374"/>
       <c r="M8" s="386"/>
     </row>
-    <row r="9" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:14" ht="15" customHeight="1">
       <c r="A9" s="387"/>
       <c r="B9" s="372" t="s">
         <v>246</v>
@@ -12284,7 +12284,7 @@
       <c r="L9" s="377"/>
       <c r="M9" s="386"/>
     </row>
-    <row r="10" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:14" ht="15" customHeight="1">
       <c r="A10" s="387"/>
       <c r="G10" s="197"/>
       <c r="H10" s="330" t="str">
@@ -12304,7 +12304,7 @@
       </c>
       <c r="L10" s="378"/>
     </row>
-    <row r="11" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:14" ht="15" customHeight="1">
       <c r="A11" s="387"/>
       <c r="B11" s="372" t="s">
         <v>238</v>
@@ -12322,12 +12322,12 @@
       <c r="K11" s="379"/>
       <c r="L11" s="380"/>
     </row>
-    <row r="12" spans="1:14" ht="8.4499999999999993" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:14" ht="8.4" customHeight="1">
       <c r="A12" s="387"/>
       <c r="G12" s="197"/>
       <c r="L12" s="394"/>
     </row>
-    <row r="13" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:14" ht="15" customHeight="1">
       <c r="A13" s="387"/>
       <c r="B13" s="372" t="s">
         <v>245</v>
@@ -12340,12 +12340,12 @@
       <c r="G13" s="197"/>
       <c r="L13" s="394"/>
     </row>
-    <row r="14" spans="1:14" ht="7.9" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:14" ht="7.95" customHeight="1">
       <c r="A14" s="387"/>
       <c r="G14" s="197"/>
       <c r="L14" s="394"/>
     </row>
-    <row r="15" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:14" ht="15" customHeight="1">
       <c r="A15" s="387"/>
       <c r="B15" s="372" t="s">
         <v>107</v>
@@ -12361,27 +12361,27 @@
       <c r="G15" s="197"/>
       <c r="L15" s="394"/>
     </row>
-    <row r="16" spans="1:14" ht="7.9" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:14" ht="7.95" customHeight="1">
       <c r="A16" s="387"/>
       <c r="L16" s="394"/>
     </row>
-    <row r="17" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:12" ht="15" customHeight="1">
       <c r="A17" s="396">
         <v>1</v>
       </c>
-      <c r="B17" s="655" t="s">
+      <c r="B17" s="658" t="s">
         <v>35</v>
       </c>
-      <c r="C17" s="656"/>
-      <c r="D17" s="656"/>
-      <c r="E17" s="657"/>
+      <c r="C17" s="659"/>
+      <c r="D17" s="659"/>
+      <c r="E17" s="660"/>
       <c r="F17" s="397" t="s">
         <v>36</v>
       </c>
       <c r="G17" s="426">
         <v>1</v>
       </c>
-      <c r="H17" s="663" t="s">
+      <c r="H17" s="651" t="s">
         <v>37</v>
       </c>
       <c r="J17" s="4" t="s">
@@ -12392,16 +12392,16 @@
       </c>
       <c r="L17" s="394"/>
     </row>
-    <row r="18" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:12" ht="17.25" customHeight="1">
       <c r="A18" s="396">
         <v>2</v>
       </c>
-      <c r="B18" s="655" t="s">
+      <c r="B18" s="658" t="s">
         <v>111</v>
       </c>
-      <c r="C18" s="656"/>
-      <c r="D18" s="656"/>
-      <c r="E18" s="657"/>
+      <c r="C18" s="659"/>
+      <c r="D18" s="659"/>
+      <c r="E18" s="660"/>
       <c r="F18" s="397" t="s">
         <v>36</v>
       </c>
@@ -12409,7 +12409,7 @@
         <f>+Resumen!I32</f>
         <v>0</v>
       </c>
-      <c r="H18" s="663"/>
+      <c r="H18" s="651"/>
       <c r="J18" s="4" t="s">
         <v>237</v>
       </c>
@@ -12418,16 +12418,16 @@
       </c>
       <c r="L18" s="394"/>
     </row>
-    <row r="19" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:12" ht="17.25" customHeight="1">
       <c r="A19" s="396">
         <v>3</v>
       </c>
-      <c r="B19" s="655" t="s">
+      <c r="B19" s="658" t="s">
         <v>112</v>
       </c>
-      <c r="C19" s="656"/>
-      <c r="D19" s="656"/>
-      <c r="E19" s="657"/>
+      <c r="C19" s="659"/>
+      <c r="D19" s="659"/>
+      <c r="E19" s="660"/>
       <c r="F19" s="397" t="s">
         <v>41</v>
       </c>
@@ -12447,16 +12447,16 @@
       </c>
       <c r="L19" s="394"/>
     </row>
-    <row r="20" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:12" ht="17.25" customHeight="1">
       <c r="A20" s="396">
         <v>4</v>
       </c>
-      <c r="B20" s="655" t="s">
+      <c r="B20" s="658" t="s">
         <v>113</v>
       </c>
-      <c r="C20" s="656"/>
-      <c r="D20" s="656"/>
-      <c r="E20" s="657"/>
+      <c r="C20" s="659"/>
+      <c r="D20" s="659"/>
+      <c r="E20" s="660"/>
       <c r="F20" s="397" t="s">
         <v>41</v>
       </c>
@@ -12476,7 +12476,7 @@
       </c>
       <c r="L20" s="394"/>
     </row>
-    <row r="21" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:12" ht="17.25" customHeight="1">
       <c r="A21" s="396">
         <v>5</v>
       </c>
@@ -12505,16 +12505,16 @@
       </c>
       <c r="L21" s="394"/>
     </row>
-    <row r="22" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:12" ht="17.25" customHeight="1">
       <c r="A22" s="396">
         <v>6</v>
       </c>
-      <c r="B22" s="655" t="s">
+      <c r="B22" s="658" t="s">
         <v>114</v>
       </c>
-      <c r="C22" s="656"/>
-      <c r="D22" s="656"/>
-      <c r="E22" s="657"/>
+      <c r="C22" s="659"/>
+      <c r="D22" s="659"/>
+      <c r="E22" s="660"/>
       <c r="F22" s="399" t="s">
         <v>41</v>
       </c>
@@ -12534,16 +12534,16 @@
       </c>
       <c r="L22" s="394"/>
     </row>
-    <row r="23" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:12" ht="17.25" customHeight="1">
       <c r="A23" s="396">
         <v>7</v>
       </c>
-      <c r="B23" s="655" t="s">
+      <c r="B23" s="658" t="s">
         <v>115</v>
       </c>
-      <c r="C23" s="656"/>
-      <c r="D23" s="656"/>
-      <c r="E23" s="657"/>
+      <c r="C23" s="659"/>
+      <c r="D23" s="659"/>
+      <c r="E23" s="660"/>
       <c r="F23" s="397" t="s">
         <v>41</v>
       </c>
@@ -12563,16 +12563,16 @@
       </c>
       <c r="L23" s="394"/>
     </row>
-    <row r="24" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:12" ht="17.25" customHeight="1">
       <c r="A24" s="396">
         <v>8</v>
       </c>
-      <c r="B24" s="655" t="s">
+      <c r="B24" s="658" t="s">
         <v>116</v>
       </c>
-      <c r="C24" s="656"/>
-      <c r="D24" s="656"/>
-      <c r="E24" s="657"/>
+      <c r="C24" s="659"/>
+      <c r="D24" s="659"/>
+      <c r="E24" s="660"/>
       <c r="F24" s="399" t="s">
         <v>41</v>
       </c>
@@ -12592,16 +12592,16 @@
       </c>
       <c r="L24" s="394"/>
     </row>
-    <row r="25" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:12" ht="17.25" customHeight="1">
       <c r="A25" s="396">
         <v>9</v>
       </c>
-      <c r="B25" s="658" t="s">
+      <c r="B25" s="661" t="s">
         <v>117</v>
       </c>
-      <c r="C25" s="659"/>
-      <c r="D25" s="659"/>
-      <c r="E25" s="660"/>
+      <c r="C25" s="662"/>
+      <c r="D25" s="662"/>
+      <c r="E25" s="663"/>
       <c r="F25" s="399" t="s">
         <v>56</v>
       </c>
@@ -12621,7 +12621,7 @@
       </c>
       <c r="L25" s="394"/>
     </row>
-    <row r="26" spans="1:12" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:12" ht="14.25" customHeight="1">
       <c r="A26" s="387"/>
       <c r="B26" s="400"/>
       <c r="C26" s="400"/>
@@ -12642,7 +12642,7 @@
       </c>
       <c r="L26" s="394"/>
     </row>
-    <row r="27" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:12" ht="17.25" customHeight="1">
       <c r="A27" s="387"/>
       <c r="B27" s="199" t="s">
         <v>134</v>
@@ -12664,7 +12664,7 @@
       </c>
       <c r="L27" s="394"/>
     </row>
-    <row r="28" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:12" ht="17.25" customHeight="1">
       <c r="A28" s="387"/>
       <c r="B28" s="199" t="s">
         <v>135</v>
@@ -12686,7 +12686,7 @@
       </c>
       <c r="L28" s="394"/>
     </row>
-    <row r="29" spans="1:12" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:12" ht="15.9" customHeight="1">
       <c r="A29" s="387"/>
       <c r="B29" s="199" t="s">
         <v>136</v>
@@ -12708,33 +12708,33 @@
       </c>
       <c r="L29" s="394"/>
     </row>
-    <row r="30" spans="1:12" ht="5.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:12" ht="5.25" customHeight="1">
       <c r="A30" s="387"/>
       <c r="I30" s="405"/>
       <c r="J30" s="406"/>
       <c r="K30" s="406"/>
       <c r="L30" s="394"/>
     </row>
-    <row r="31" spans="1:12" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:12" ht="15.9" customHeight="1">
       <c r="A31" s="387"/>
-      <c r="B31" s="662" t="s">
+      <c r="B31" s="650" t="s">
         <v>137</v>
       </c>
-      <c r="C31" s="662"/>
-      <c r="D31" s="662"/>
-      <c r="E31" s="662"/>
-      <c r="F31" s="662"/>
-      <c r="G31" s="662"/>
+      <c r="C31" s="650"/>
+      <c r="D31" s="650"/>
+      <c r="E31" s="650"/>
+      <c r="F31" s="650"/>
+      <c r="G31" s="650"/>
       <c r="L31" s="394"/>
     </row>
-    <row r="32" spans="1:12" ht="26.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:12" ht="26.25" customHeight="1">
       <c r="A32" s="387"/>
-      <c r="B32" s="652" t="s">
+      <c r="B32" s="655" t="s">
         <v>138</v>
       </c>
-      <c r="C32" s="653"/>
-      <c r="D32" s="653"/>
-      <c r="E32" s="654"/>
+      <c r="C32" s="656"/>
+      <c r="D32" s="656"/>
+      <c r="E32" s="657"/>
       <c r="F32" s="369" t="s">
         <v>139</v>
       </c>
@@ -12743,14 +12743,14 @@
       </c>
       <c r="L32" s="394"/>
     </row>
-    <row r="33" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:12" ht="16.5" customHeight="1">
       <c r="A33" s="387"/>
-      <c r="B33" s="649" t="s">
+      <c r="B33" s="652" t="s">
         <v>141</v>
       </c>
-      <c r="C33" s="650"/>
-      <c r="D33" s="650"/>
-      <c r="E33" s="651"/>
+      <c r="C33" s="653"/>
+      <c r="D33" s="653"/>
+      <c r="E33" s="654"/>
       <c r="F33" s="330" t="s">
         <v>142</v>
       </c>
@@ -12759,14 +12759,14 @@
       </c>
       <c r="L33" s="394"/>
     </row>
-    <row r="34" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:12" ht="16.5" customHeight="1">
       <c r="A34" s="387"/>
-      <c r="B34" s="649" t="s">
+      <c r="B34" s="652" t="s">
         <v>143</v>
       </c>
-      <c r="C34" s="650"/>
-      <c r="D34" s="650"/>
-      <c r="E34" s="651"/>
+      <c r="C34" s="653"/>
+      <c r="D34" s="653"/>
+      <c r="E34" s="654"/>
       <c r="F34" s="330" t="s">
         <v>144</v>
       </c>
@@ -12775,14 +12775,14 @@
       </c>
       <c r="L34" s="394"/>
     </row>
-    <row r="35" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:12" ht="16.5" customHeight="1">
       <c r="A35" s="387"/>
-      <c r="B35" s="649" t="s">
+      <c r="B35" s="652" t="s">
         <v>145</v>
       </c>
-      <c r="C35" s="650"/>
-      <c r="D35" s="650"/>
-      <c r="E35" s="651"/>
+      <c r="C35" s="653"/>
+      <c r="D35" s="653"/>
+      <c r="E35" s="654"/>
       <c r="F35" s="330" t="s">
         <v>146</v>
       </c>
@@ -12791,26 +12791,26 @@
       </c>
       <c r="L35" s="394"/>
     </row>
-    <row r="36" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:12" ht="16.5" customHeight="1">
       <c r="A36" s="387"/>
-      <c r="B36" s="662" t="s">
+      <c r="B36" s="650" t="s">
         <v>147</v>
       </c>
-      <c r="C36" s="662"/>
-      <c r="D36" s="662"/>
-      <c r="E36" s="662"/>
-      <c r="F36" s="662"/>
-      <c r="G36" s="662"/>
+      <c r="C36" s="650"/>
+      <c r="D36" s="650"/>
+      <c r="E36" s="650"/>
+      <c r="F36" s="650"/>
+      <c r="G36" s="650"/>
       <c r="L36" s="394"/>
     </row>
-    <row r="37" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:12" ht="16.5" customHeight="1">
       <c r="A37" s="387"/>
-      <c r="B37" s="649" t="s">
+      <c r="B37" s="652" t="s">
         <v>227</v>
       </c>
-      <c r="C37" s="650"/>
-      <c r="D37" s="650"/>
-      <c r="E37" s="651"/>
+      <c r="C37" s="653"/>
+      <c r="D37" s="653"/>
+      <c r="E37" s="654"/>
       <c r="F37" s="330" t="s">
         <v>148</v>
       </c>
@@ -12819,14 +12819,14 @@
       </c>
       <c r="L37" s="394"/>
     </row>
-    <row r="38" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:12" ht="16.5" customHeight="1">
       <c r="A38" s="387"/>
-      <c r="B38" s="649" t="s">
+      <c r="B38" s="652" t="s">
         <v>149</v>
       </c>
-      <c r="C38" s="650"/>
-      <c r="D38" s="650"/>
-      <c r="E38" s="651"/>
+      <c r="C38" s="653"/>
+      <c r="D38" s="653"/>
+      <c r="E38" s="654"/>
       <c r="F38" s="330" t="s">
         <v>150</v>
       </c>
@@ -12835,14 +12835,14 @@
       </c>
       <c r="L38" s="394"/>
     </row>
-    <row r="39" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:12" ht="16.5" customHeight="1">
       <c r="A39" s="387"/>
-      <c r="B39" s="649" t="s">
+      <c r="B39" s="652" t="s">
         <v>151</v>
       </c>
-      <c r="C39" s="650"/>
-      <c r="D39" s="650"/>
-      <c r="E39" s="651"/>
+      <c r="C39" s="653"/>
+      <c r="D39" s="653"/>
+      <c r="E39" s="654"/>
       <c r="F39" s="330" t="s">
         <v>152</v>
       </c>
@@ -12851,98 +12851,98 @@
       </c>
       <c r="L39" s="394"/>
     </row>
-    <row r="40" spans="1:12" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:12" ht="13.5" customHeight="1">
       <c r="A40" s="387"/>
       <c r="I40" s="197"/>
       <c r="J40" s="381"/>
       <c r="K40" s="329"/>
       <c r="L40" s="394"/>
     </row>
-    <row r="41" spans="1:12" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:12" ht="13.5" customHeight="1">
       <c r="A41" s="387"/>
       <c r="I41" s="197"/>
       <c r="J41" s="381"/>
       <c r="K41" s="329"/>
       <c r="L41" s="394"/>
     </row>
-    <row r="42" spans="1:12" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:12" ht="13.5" customHeight="1">
       <c r="A42" s="387"/>
       <c r="I42" s="197"/>
       <c r="J42" s="381"/>
       <c r="K42" s="329"/>
       <c r="L42" s="394"/>
     </row>
-    <row r="43" spans="1:12" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:12" ht="13.5" customHeight="1">
       <c r="A43" s="387"/>
       <c r="I43" s="197"/>
       <c r="J43" s="381"/>
       <c r="K43" s="329"/>
       <c r="L43" s="394"/>
     </row>
-    <row r="44" spans="1:12" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="44" spans="1:12" ht="13.5" customHeight="1">
       <c r="A44" s="387"/>
       <c r="I44" s="197"/>
       <c r="J44" s="381"/>
       <c r="K44" s="329"/>
       <c r="L44" s="394"/>
     </row>
-    <row r="45" spans="1:12" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="45" spans="1:12" ht="13.5" customHeight="1">
       <c r="A45" s="387"/>
       <c r="I45" s="197"/>
       <c r="J45" s="381"/>
       <c r="K45" s="329"/>
       <c r="L45" s="394"/>
     </row>
-    <row r="46" spans="1:12" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="46" spans="1:12" ht="13.5" customHeight="1">
       <c r="A46" s="387"/>
       <c r="I46" s="197"/>
       <c r="J46" s="381"/>
       <c r="K46" s="329"/>
       <c r="L46" s="394"/>
     </row>
-    <row r="47" spans="1:12" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="47" spans="1:12" ht="13.5" customHeight="1">
       <c r="A47" s="387"/>
       <c r="I47" s="197"/>
       <c r="J47" s="381"/>
       <c r="K47" s="329"/>
       <c r="L47" s="394"/>
     </row>
-    <row r="48" spans="1:12" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="48" spans="1:12" ht="13.5" customHeight="1">
       <c r="A48" s="387"/>
       <c r="I48" s="197"/>
       <c r="J48" s="381"/>
       <c r="K48" s="329"/>
       <c r="L48" s="394"/>
     </row>
-    <row r="49" spans="1:12" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="49" spans="1:12" ht="13.5" customHeight="1">
       <c r="A49" s="387"/>
       <c r="I49" s="197"/>
       <c r="J49" s="381"/>
       <c r="K49" s="329"/>
       <c r="L49" s="394"/>
     </row>
-    <row r="50" spans="1:12" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="50" spans="1:12" ht="13.5" customHeight="1">
       <c r="A50" s="387"/>
       <c r="I50" s="197"/>
       <c r="J50" s="381"/>
       <c r="K50" s="329"/>
       <c r="L50" s="394"/>
     </row>
-    <row r="51" spans="1:12" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="51" spans="1:12" ht="13.5" customHeight="1">
       <c r="A51" s="387"/>
       <c r="I51" s="197"/>
       <c r="J51" s="382"/>
       <c r="K51" s="329"/>
       <c r="L51" s="394"/>
     </row>
-    <row r="52" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="52" spans="1:12">
       <c r="A52" s="387"/>
       <c r="I52" s="197"/>
       <c r="J52" s="381"/>
       <c r="K52" s="329"/>
       <c r="L52" s="394"/>
     </row>
-    <row r="53" spans="1:12" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:12" ht="13.8" thickBot="1">
       <c r="A53" s="407"/>
       <c r="B53" s="408"/>
       <c r="C53" s="408"/>
@@ -12959,15 +12959,6 @@
   </sheetData>
   <sheetProtection algorithmName="SHA-512" hashValue="xWWTH2ODRJvJuq26fz8BDBTKOyLp8SD8OPQSny0kNhk0w02O6G1TzYz/+8aUJNSNF0435K8vhuSYHksIa+3eMQ==" saltValue="O89M/G/p4V9ywCWV4cqXXA==" spinCount="100000" sheet="1" objects="1" scenarios="1"/>
   <mergeCells count="22">
-    <mergeCell ref="B2:K2"/>
-    <mergeCell ref="B3:K3"/>
-    <mergeCell ref="B31:G31"/>
-    <mergeCell ref="B36:G36"/>
-    <mergeCell ref="H17:H18"/>
-    <mergeCell ref="B33:E33"/>
-    <mergeCell ref="B34:E34"/>
-    <mergeCell ref="B35:E35"/>
-    <mergeCell ref="B32:E32"/>
     <mergeCell ref="B39:E39"/>
     <mergeCell ref="B5:E5"/>
     <mergeCell ref="B7:E7"/>
@@ -12981,6 +12972,15 @@
     <mergeCell ref="B25:E25"/>
     <mergeCell ref="B37:E37"/>
     <mergeCell ref="B38:E38"/>
+    <mergeCell ref="B2:K2"/>
+    <mergeCell ref="B3:K3"/>
+    <mergeCell ref="B31:G31"/>
+    <mergeCell ref="B36:G36"/>
+    <mergeCell ref="H17:H18"/>
+    <mergeCell ref="B33:E33"/>
+    <mergeCell ref="B34:E34"/>
+    <mergeCell ref="B35:E35"/>
+    <mergeCell ref="B32:E32"/>
   </mergeCells>
   <conditionalFormatting sqref="E11">
     <cfRule type="containsText" dxfId="0" priority="1" operator="containsText" text="no">
@@ -13009,32 +13009,32 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:K72"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11.42578125" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.44140625" defaultRowHeight="13.2"/>
   <cols>
-    <col min="1" max="1" width="21.85546875" style="339" customWidth="1"/>
-    <col min="2" max="2" width="11.5703125" style="339" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="12.5703125" style="339" customWidth="1"/>
-    <col min="4" max="4" width="11.5703125" style="339" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="21.88671875" style="339" customWidth="1"/>
+    <col min="2" max="2" width="11.5546875" style="339" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.5546875" style="339" customWidth="1"/>
+    <col min="4" max="4" width="11.5546875" style="339" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="20" style="339" customWidth="1"/>
     <col min="6" max="6" width="14" style="339" customWidth="1"/>
-    <col min="7" max="7" width="13.7109375" style="339" customWidth="1"/>
-    <col min="8" max="8" width="15.28515625" style="339" customWidth="1"/>
-    <col min="9" max="9" width="9.85546875" style="339" customWidth="1"/>
-    <col min="10" max="10" width="14.42578125" style="339" customWidth="1"/>
-    <col min="11" max="16384" width="11.42578125" style="339"/>
+    <col min="7" max="7" width="13.6640625" style="339" customWidth="1"/>
+    <col min="8" max="8" width="15.33203125" style="339" customWidth="1"/>
+    <col min="9" max="9" width="9.88671875" style="339" customWidth="1"/>
+    <col min="10" max="10" width="14.44140625" style="339" customWidth="1"/>
+    <col min="11" max="16384" width="11.44140625" style="339"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="673"/>
-      <c r="B1" s="674"/>
-      <c r="C1" s="664" t="s">
+    <row r="1" spans="1:10" ht="12.75" customHeight="1">
+      <c r="A1" s="681"/>
+      <c r="B1" s="682"/>
+      <c r="C1" s="672" t="s">
         <v>153</v>
       </c>
-      <c r="D1" s="665"/>
-      <c r="E1" s="665"/>
-      <c r="F1" s="665"/>
-      <c r="G1" s="665"/>
-      <c r="H1" s="666"/>
+      <c r="D1" s="673"/>
+      <c r="E1" s="673"/>
+      <c r="F1" s="673"/>
+      <c r="G1" s="673"/>
+      <c r="H1" s="674"/>
       <c r="I1" s="221" t="s">
         <v>154</v>
       </c>
@@ -13042,15 +13042,15 @@
         <v>155</v>
       </c>
     </row>
-    <row r="2" spans="1:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="675"/>
-      <c r="B2" s="676"/>
-      <c r="C2" s="667"/>
-      <c r="D2" s="668"/>
-      <c r="E2" s="668"/>
-      <c r="F2" s="668"/>
-      <c r="G2" s="668"/>
-      <c r="H2" s="669"/>
+    <row r="2" spans="1:10" ht="12.75" customHeight="1">
+      <c r="A2" s="683"/>
+      <c r="B2" s="684"/>
+      <c r="C2" s="675"/>
+      <c r="D2" s="676"/>
+      <c r="E2" s="676"/>
+      <c r="F2" s="676"/>
+      <c r="G2" s="676"/>
+      <c r="H2" s="677"/>
       <c r="I2" s="221" t="s">
         <v>156</v>
       </c>
@@ -13058,15 +13058,15 @@
         <v>3</v>
       </c>
     </row>
-    <row r="3" spans="1:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="675"/>
-      <c r="B3" s="676"/>
-      <c r="C3" s="667"/>
-      <c r="D3" s="668"/>
-      <c r="E3" s="668"/>
-      <c r="F3" s="668"/>
-      <c r="G3" s="668"/>
-      <c r="H3" s="669"/>
+    <row r="3" spans="1:10" ht="12.75" customHeight="1">
+      <c r="A3" s="683"/>
+      <c r="B3" s="684"/>
+      <c r="C3" s="675"/>
+      <c r="D3" s="676"/>
+      <c r="E3" s="676"/>
+      <c r="F3" s="676"/>
+      <c r="G3" s="676"/>
+      <c r="H3" s="677"/>
       <c r="I3" s="221" t="s">
         <v>157</v>
       </c>
@@ -13074,15 +13074,15 @@
         <v>46146</v>
       </c>
     </row>
-    <row r="4" spans="1:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A4" s="677"/>
-      <c r="B4" s="678"/>
-      <c r="C4" s="670"/>
-      <c r="D4" s="671"/>
-      <c r="E4" s="671"/>
-      <c r="F4" s="671"/>
-      <c r="G4" s="671"/>
-      <c r="H4" s="672"/>
+    <row r="4" spans="1:10" ht="12.75" customHeight="1">
+      <c r="A4" s="685"/>
+      <c r="B4" s="686"/>
+      <c r="C4" s="678"/>
+      <c r="D4" s="679"/>
+      <c r="E4" s="679"/>
+      <c r="F4" s="679"/>
+      <c r="G4" s="679"/>
+      <c r="H4" s="680"/>
       <c r="I4" s="221" t="s">
         <v>158</v>
       </c>
@@ -13090,7 +13090,7 @@
         <v>159</v>
       </c>
     </row>
-    <row r="6" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:10" ht="18" customHeight="1">
       <c r="A6" s="223" t="s">
         <v>160</v>
       </c>
@@ -13106,7 +13106,7 @@
       <c r="I6" s="340"/>
       <c r="J6" s="341"/>
     </row>
-    <row r="7" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:10" ht="18" customHeight="1">
       <c r="A7" s="223" t="s">
         <v>162</v>
       </c>
@@ -13122,7 +13122,7 @@
       <c r="I7" s="340"/>
       <c r="J7" s="341"/>
     </row>
-    <row r="8" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:10" ht="18" customHeight="1">
       <c r="A8" s="223" t="s">
         <v>163</v>
       </c>
@@ -13138,7 +13138,7 @@
       <c r="I8" s="340"/>
       <c r="J8" s="341"/>
     </row>
-    <row r="9" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:10" ht="18" customHeight="1">
       <c r="A9" s="224" t="s">
         <v>302</v>
       </c>
@@ -13154,13 +13154,13 @@
       <c r="I9" s="340"/>
       <c r="J9" s="341"/>
     </row>
-    <row r="11" spans="1:10" ht="12" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:10" ht="12" customHeight="1">
       <c r="A11" s="351" t="s">
         <v>303</v>
       </c>
     </row>
-    <row r="12" spans="1:10" ht="12" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="13" spans="1:10" ht="12" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:10" ht="12" customHeight="1"/>
+    <row r="13" spans="1:10" ht="12" customHeight="1">
       <c r="A13" s="353" t="s">
         <v>165</v>
       </c>
@@ -13168,81 +13168,81 @@
         <v>169</v>
       </c>
     </row>
-    <row r="14" spans="1:10" ht="12" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="15" spans="1:10" ht="12" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:10" ht="12" customHeight="1"/>
+    <row r="15" spans="1:10" ht="12" customHeight="1">
       <c r="A15" s="352" t="s">
         <v>166</v>
       </c>
       <c r="G15" s="350"/>
     </row>
-    <row r="16" spans="1:10" ht="12" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:10" ht="12" customHeight="1">
       <c r="A16" s="352" t="s">
         <v>167</v>
       </c>
     </row>
-    <row r="17" spans="1:11" ht="12" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:11" ht="12" customHeight="1">
       <c r="A17" s="352" t="s">
         <v>168</v>
       </c>
       <c r="G17" s="350"/>
     </row>
-    <row r="18" spans="1:11" ht="12" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="19" spans="1:11" ht="12" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:11" ht="12" customHeight="1"/>
+    <row r="19" spans="1:11" ht="12" customHeight="1">
       <c r="A19" s="353" t="s">
         <v>170</v>
       </c>
       <c r="G19" s="350"/>
     </row>
-    <row r="20" spans="1:11" ht="12" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="21" spans="1:11" ht="12" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:11" ht="12" customHeight="1"/>
+    <row r="21" spans="1:11" ht="12" customHeight="1">
       <c r="A21" s="352" t="s">
         <v>171</v>
       </c>
       <c r="G21" s="350"/>
     </row>
-    <row r="22" spans="1:11" ht="17.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="23" spans="1:11" ht="12" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:11" ht="17.25" customHeight="1"/>
+    <row r="23" spans="1:11" ht="12" customHeight="1">
       <c r="A23" s="351" t="s">
         <v>172</v>
       </c>
     </row>
-    <row r="24" spans="1:11" ht="12" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="25" spans="1:11" ht="12" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="26" spans="1:11" ht="12" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="27" spans="1:11" ht="12" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:11" ht="12" customHeight="1"/>
+    <row r="25" spans="1:11" ht="12" customHeight="1"/>
+    <row r="26" spans="1:11" ht="12" customHeight="1"/>
+    <row r="27" spans="1:11" ht="12" customHeight="1">
       <c r="K27" s="350"/>
     </row>
-    <row r="28" spans="1:11" ht="6" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="29" spans="1:11" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:11" ht="6" customHeight="1"/>
+    <row r="29" spans="1:11" ht="16.5" customHeight="1">
       <c r="F29" s="350"/>
     </row>
-    <row r="30" spans="1:11" ht="16.5" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="31" spans="1:11" ht="16.5" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="32" spans="1:11" ht="16.5" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="33" spans="1:10" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:11" ht="16.5" customHeight="1"/>
+    <row r="31" spans="1:11" ht="16.5" customHeight="1"/>
+    <row r="32" spans="1:11" ht="16.5" customHeight="1"/>
+    <row r="33" spans="1:10" ht="21.75" customHeight="1">
       <c r="I33" s="350"/>
     </row>
-    <row r="34" spans="1:10" ht="17.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="35" spans="1:10" ht="17.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="37" spans="1:10" ht="10.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:10" ht="17.25" customHeight="1"/>
+    <row r="35" spans="1:10" ht="17.25" customHeight="1"/>
+    <row r="37" spans="1:10" ht="10.5" customHeight="1">
       <c r="I37" s="337"/>
       <c r="J37" s="337"/>
     </row>
-    <row r="38" spans="1:10" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A38" s="683" t="s">
+    <row r="38" spans="1:10" ht="15.75" customHeight="1" thickBot="1">
+      <c r="A38" s="691" t="s">
         <v>304</v>
       </c>
-      <c r="B38" s="684"/>
-      <c r="C38" s="684"/>
-      <c r="D38" s="684"/>
-      <c r="E38" s="684"/>
-      <c r="F38" s="684"/>
-      <c r="G38" s="684"/>
-      <c r="H38" s="685"/>
+      <c r="B38" s="692"/>
+      <c r="C38" s="692"/>
+      <c r="D38" s="692"/>
+      <c r="E38" s="692"/>
+      <c r="F38" s="692"/>
+      <c r="G38" s="692"/>
+      <c r="H38" s="693"/>
       <c r="I38" s="337"/>
       <c r="J38" s="337"/>
     </row>
-    <row r="39" spans="1:10" ht="45" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:10" ht="45" customHeight="1" thickBot="1">
       <c r="A39" s="244" t="s">
         <v>173</v>
       </c>
@@ -13273,7 +13273,7 @@
       </c>
       <c r="J39" s="337"/>
     </row>
-    <row r="40" spans="1:10" s="343" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:10" s="343" customFormat="1" ht="21.75" customHeight="1">
       <c r="A40" s="234" t="s">
         <v>181</v>
       </c>
@@ -13302,7 +13302,7 @@
       <c r="I40" s="337"/>
       <c r="J40" s="342"/>
     </row>
-    <row r="41" spans="1:10" s="343" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:10" s="343" customFormat="1" ht="21.75" customHeight="1">
       <c r="A41" s="268" t="s">
         <v>183</v>
       </c>
@@ -13333,7 +13333,7 @@
       </c>
       <c r="I41" s="337"/>
     </row>
-    <row r="42" spans="1:10" s="343" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:10" s="343" customFormat="1" ht="21.75" customHeight="1">
       <c r="A42" s="235" t="s">
         <v>185</v>
       </c>
@@ -13360,7 +13360,7 @@
       </c>
       <c r="I42" s="337"/>
     </row>
-    <row r="43" spans="1:10" s="343" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:10" s="343" customFormat="1" ht="21.75" customHeight="1">
       <c r="A43" s="235" t="s">
         <v>187</v>
       </c>
@@ -13387,7 +13387,7 @@
       </c>
       <c r="I43" s="337"/>
     </row>
-    <row r="44" spans="1:10" s="343" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="44" spans="1:10" s="343" customFormat="1" ht="21.75" customHeight="1">
       <c r="A44" s="235" t="s">
         <v>189</v>
       </c>
@@ -13414,7 +13414,7 @@
       </c>
       <c r="I44" s="337"/>
     </row>
-    <row r="45" spans="1:10" s="343" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="45" spans="1:10" s="343" customFormat="1" ht="21.75" customHeight="1">
       <c r="A45" s="268" t="s">
         <v>191</v>
       </c>
@@ -13444,7 +13444,7 @@
       <c r="I45" s="337"/>
       <c r="J45" s="337"/>
     </row>
-    <row r="46" spans="1:10" s="343" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="46" spans="1:10" s="343" customFormat="1" ht="21.75" customHeight="1">
       <c r="A46" s="235" t="s">
         <v>185</v>
       </c>
@@ -13472,7 +13472,7 @@
       <c r="I46" s="337"/>
       <c r="J46" s="337"/>
     </row>
-    <row r="47" spans="1:10" s="343" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="47" spans="1:10" s="343" customFormat="1" ht="21.75" customHeight="1">
       <c r="A47" s="235" t="s">
         <v>187</v>
       </c>
@@ -13500,7 +13500,7 @@
       <c r="I47" s="337"/>
       <c r="J47" s="337"/>
     </row>
-    <row r="48" spans="1:10" s="343" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="48" spans="1:10" s="343" customFormat="1" ht="21.75" customHeight="1">
       <c r="A48" s="235" t="s">
         <v>189</v>
       </c>
@@ -13528,7 +13528,7 @@
       <c r="I48" s="337"/>
       <c r="J48" s="337"/>
     </row>
-    <row r="49" spans="1:10" s="343" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="49" spans="1:10" s="343" customFormat="1" ht="21.75" customHeight="1">
       <c r="A49" s="268" t="s">
         <v>192</v>
       </c>
@@ -13558,7 +13558,7 @@
       <c r="I49" s="337"/>
       <c r="J49" s="337"/>
     </row>
-    <row r="50" spans="1:10" s="343" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="50" spans="1:10" s="343" customFormat="1" ht="21.75" customHeight="1">
       <c r="A50" s="235" t="s">
         <v>185</v>
       </c>
@@ -13586,7 +13586,7 @@
       <c r="I50" s="337"/>
       <c r="J50" s="337"/>
     </row>
-    <row r="51" spans="1:10" s="343" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="51" spans="1:10" s="343" customFormat="1" ht="21.75" customHeight="1">
       <c r="A51" s="235" t="s">
         <v>187</v>
       </c>
@@ -13614,7 +13614,7 @@
       <c r="I51" s="337"/>
       <c r="J51" s="337"/>
     </row>
-    <row r="52" spans="1:10" s="343" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="52" spans="1:10" s="343" customFormat="1" ht="21.75" customHeight="1">
       <c r="A52" s="235" t="s">
         <v>189</v>
       </c>
@@ -13642,7 +13642,7 @@
       <c r="I52" s="337"/>
       <c r="J52" s="337"/>
     </row>
-    <row r="53" spans="1:10" s="343" customFormat="1" ht="21.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:10" s="343" customFormat="1" ht="21.75" customHeight="1" thickBot="1">
       <c r="A53" s="272" t="s">
         <v>193</v>
       </c>
@@ -13671,49 +13671,49 @@
       <c r="I53" s="337"/>
       <c r="J53" s="337"/>
     </row>
-    <row r="54" spans="1:10" s="343" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A54" s="686" t="s">
+    <row r="54" spans="1:10" s="343" customFormat="1" ht="16.5" customHeight="1">
+      <c r="A54" s="694" t="s">
         <v>195</v>
       </c>
-      <c r="B54" s="687"/>
-      <c r="C54" s="688"/>
+      <c r="B54" s="695"/>
+      <c r="C54" s="696"/>
       <c r="D54" s="280" t="s">
         <v>56</v>
       </c>
       <c r="E54" s="281"/>
-      <c r="F54" s="679" t="e">
+      <c r="F54" s="687" t="e">
         <f>SQRT((H41*H41)+(H45*H45)+(H49*H49)+(H53*H53))</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="G54" s="679"/>
-      <c r="H54" s="680"/>
+      <c r="G54" s="687"/>
+      <c r="H54" s="688"/>
       <c r="I54" s="337" t="s">
         <v>196</v>
       </c>
       <c r="J54" s="337"/>
     </row>
-    <row r="55" spans="1:10" s="343" customFormat="1" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A55" s="689" t="s">
+    <row r="55" spans="1:10" s="343" customFormat="1" ht="18" customHeight="1" thickBot="1">
+      <c r="A55" s="697" t="s">
         <v>197</v>
       </c>
-      <c r="B55" s="690"/>
-      <c r="C55" s="691"/>
+      <c r="B55" s="698"/>
+      <c r="C55" s="699"/>
       <c r="D55" s="308" t="s">
         <v>56</v>
       </c>
       <c r="E55" s="282"/>
-      <c r="F55" s="681" t="e">
+      <c r="F55" s="689" t="e">
         <f>F54*2</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="G55" s="681"/>
-      <c r="H55" s="682"/>
+      <c r="G55" s="689"/>
+      <c r="H55" s="690"/>
       <c r="I55" s="337" t="s">
         <v>198</v>
       </c>
       <c r="J55" s="337"/>
     </row>
-    <row r="56" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="56" spans="1:10" ht="15" customHeight="1">
       <c r="A56" s="337"/>
       <c r="D56" s="337"/>
       <c r="E56" s="337"/>
@@ -13723,7 +13723,7 @@
       <c r="I56" s="337"/>
       <c r="J56" s="337"/>
     </row>
-    <row r="57" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="57" spans="1:10" ht="15" customHeight="1">
       <c r="A57" s="337"/>
       <c r="D57" s="337"/>
       <c r="E57" s="337"/>
@@ -13733,7 +13733,7 @@
       <c r="I57" s="337"/>
       <c r="J57" s="337"/>
     </row>
-    <row r="58" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="58" spans="1:10" ht="15" customHeight="1">
       <c r="E58" s="337"/>
       <c r="F58" s="337"/>
       <c r="G58" s="337"/>
@@ -13741,7 +13741,7 @@
       <c r="I58" s="337"/>
       <c r="J58" s="337"/>
     </row>
-    <row r="59" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="59" spans="1:10" ht="15" customHeight="1">
       <c r="B59" s="345" t="s">
         <v>305</v>
       </c>
@@ -13752,7 +13752,7 @@
       <c r="I59" s="337"/>
       <c r="J59" s="337"/>
     </row>
-    <row r="60" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="60" spans="1:10" ht="15" customHeight="1">
       <c r="A60" s="252"/>
       <c r="B60" s="228" t="s">
         <v>199</v>
@@ -13770,7 +13770,7 @@
       <c r="I60" s="337"/>
       <c r="J60" s="337"/>
     </row>
-    <row r="61" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="61" spans="1:10" ht="15" customHeight="1">
       <c r="A61" s="253"/>
       <c r="B61" s="346" t="str">
         <f>A41</f>
@@ -13791,7 +13791,7 @@
       <c r="I61" s="337"/>
       <c r="J61" s="337"/>
     </row>
-    <row r="62" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="62" spans="1:10" ht="15" customHeight="1">
       <c r="A62" s="253"/>
       <c r="B62" s="346" t="str">
         <f>A45</f>
@@ -13812,7 +13812,7 @@
       <c r="I62" s="337"/>
       <c r="J62" s="337"/>
     </row>
-    <row r="63" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="63" spans="1:10" ht="15" customHeight="1">
       <c r="A63" s="255"/>
       <c r="B63" s="347" t="str">
         <f>A49</f>
@@ -13833,7 +13833,7 @@
       <c r="I63" s="337"/>
       <c r="J63" s="337"/>
     </row>
-    <row r="64" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="64" spans="1:10" ht="15" customHeight="1">
       <c r="A64" s="255"/>
       <c r="B64" s="347" t="str">
         <f>A53</f>
@@ -13854,7 +13854,7 @@
       <c r="I64" s="337"/>
       <c r="J64" s="337"/>
     </row>
-    <row r="65" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="65" spans="1:10" ht="15" customHeight="1">
       <c r="A65" s="257"/>
       <c r="B65" s="258"/>
       <c r="C65" s="259" t="e">
@@ -13872,54 +13872,48 @@
       <c r="I65" s="337"/>
       <c r="J65" s="337"/>
     </row>
-    <row r="66" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="67" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="68" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="69" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="70" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="66" spans="1:10" ht="15" customHeight="1"/>
+    <row r="67" spans="1:10" ht="15" customHeight="1"/>
+    <row r="68" spans="1:10" ht="15" customHeight="1"/>
+    <row r="69" spans="1:10" ht="15" customHeight="1"/>
+    <row r="70" spans="1:10">
       <c r="A70" s="541" t="s">
         <v>306</v>
       </c>
-      <c r="B70" s="692" t="s">
+      <c r="B70" s="664" t="s">
         <v>307</v>
       </c>
-      <c r="C70" s="693"/>
+      <c r="C70" s="665"/>
       <c r="D70" s="542"/>
-      <c r="E70" s="694" t="s">
+      <c r="E70" s="666" t="s">
         <v>308</v>
       </c>
-      <c r="F70" s="694"/>
-      <c r="G70" s="695" t="s">
+      <c r="F70" s="666"/>
+      <c r="G70" s="667" t="s">
         <v>309</v>
       </c>
-      <c r="H70" s="696"/>
-    </row>
-    <row r="72" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="H70" s="668"/>
+    </row>
+    <row r="72" spans="1:10">
       <c r="A72" s="543" t="s">
         <v>310</v>
       </c>
-      <c r="B72" s="697">
+      <c r="B72" s="669">
         <v>44944</v>
       </c>
-      <c r="C72" s="698"/>
-      <c r="E72" s="699" t="s">
+      <c r="C72" s="670"/>
+      <c r="E72" s="671" t="s">
         <v>311</v>
       </c>
-      <c r="F72" s="699"/>
-      <c r="G72" s="697">
+      <c r="F72" s="671"/>
+      <c r="G72" s="669">
         <v>44944</v>
       </c>
-      <c r="H72" s="698"/>
+      <c r="H72" s="670"/>
     </row>
   </sheetData>
   <sheetProtection algorithmName="SHA-512" hashValue="iLEnVB6pm8HGxp/myiIucvHcjmqcSrUFV5EFJhRy/Wl6J20Lu8rufg9gJo4vTQR/wN6I3HZ06PN9TnsphGZBRg==" saltValue="rC1uvtCaR6F4sqhd68ayKA==" spinCount="100000" sheet="1" selectLockedCells="1" selectUnlockedCells="1"/>
   <mergeCells count="13">
-    <mergeCell ref="B70:C70"/>
-    <mergeCell ref="E70:F70"/>
-    <mergeCell ref="G70:H70"/>
-    <mergeCell ref="B72:C72"/>
-    <mergeCell ref="E72:F72"/>
-    <mergeCell ref="G72:H72"/>
     <mergeCell ref="C1:H4"/>
     <mergeCell ref="A1:B4"/>
     <mergeCell ref="F54:H54"/>
@@ -13927,6 +13921,12 @@
     <mergeCell ref="A38:H38"/>
     <mergeCell ref="A54:C54"/>
     <mergeCell ref="A55:C55"/>
+    <mergeCell ref="B70:C70"/>
+    <mergeCell ref="E70:F70"/>
+    <mergeCell ref="G70:H70"/>
+    <mergeCell ref="B72:C72"/>
+    <mergeCell ref="E72:F72"/>
+    <mergeCell ref="G72:H72"/>
   </mergeCells>
   <pageMargins left="0.70866141732283472" right="0.31496062992125984" top="0.74803149606299213" bottom="0.55118110236220474" header="0.31496062992125984" footer="0.31496062992125984"/>
   <pageSetup paperSize="9" scale="70" orientation="portrait" r:id="rId1"/>
@@ -13940,15 +13940,15 @@
             <anchor moveWithCells="1">
               <from>
                 <xdr:col>4</xdr:col>
-                <xdr:colOff>771525</xdr:colOff>
+                <xdr:colOff>769620</xdr:colOff>
                 <xdr:row>11</xdr:row>
-                <xdr:rowOff>85725</xdr:rowOff>
+                <xdr:rowOff>83820</xdr:rowOff>
               </from>
               <to>
                 <xdr:col>6</xdr:col>
-                <xdr:colOff>476250</xdr:colOff>
+                <xdr:colOff>480060</xdr:colOff>
                 <xdr:row>15</xdr:row>
-                <xdr:rowOff>57150</xdr:rowOff>
+                <xdr:rowOff>60960</xdr:rowOff>
               </to>
             </anchor>
           </objectPr>
@@ -13965,22 +13965,22 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <dimension ref="B2:O26"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11.42578125" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.44140625" defaultRowHeight="13.2"/>
   <cols>
     <col min="1" max="1" width="3" style="173" customWidth="1"/>
-    <col min="2" max="2" width="11.42578125" style="173"/>
-    <col min="3" max="3" width="10.28515625" style="173" customWidth="1"/>
+    <col min="2" max="2" width="11.44140625" style="173"/>
+    <col min="3" max="3" width="10.33203125" style="173" customWidth="1"/>
     <col min="4" max="4" width="12" style="173" customWidth="1"/>
-    <col min="5" max="7" width="11.42578125" style="173"/>
-    <col min="8" max="8" width="14.42578125" style="173" customWidth="1"/>
-    <col min="9" max="9" width="11.42578125" style="173"/>
-    <col min="10" max="10" width="11.85546875" style="173" customWidth="1"/>
-    <col min="11" max="11" width="9.85546875" style="173" customWidth="1"/>
-    <col min="12" max="15" width="12.140625" style="173" customWidth="1"/>
-    <col min="16" max="16384" width="11.42578125" style="173"/>
+    <col min="5" max="7" width="11.44140625" style="173"/>
+    <col min="8" max="8" width="14.44140625" style="173" customWidth="1"/>
+    <col min="9" max="9" width="11.44140625" style="173"/>
+    <col min="10" max="10" width="11.88671875" style="173" customWidth="1"/>
+    <col min="11" max="11" width="9.88671875" style="173" customWidth="1"/>
+    <col min="12" max="15" width="12.109375" style="173" customWidth="1"/>
+    <col min="16" max="16384" width="11.44140625" style="173"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="2" spans="2:15">
       <c r="B2" s="203" t="s">
         <v>201</v>
       </c>
@@ -13992,7 +13992,7 @@
       <c r="K2" s="204"/>
       <c r="L2" s="204"/>
     </row>
-    <row r="3" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="3" spans="2:15">
       <c r="B3" s="289" t="s">
         <v>130</v>
       </c>
@@ -14007,7 +14007,7 @@
         <v>3.7900000000000001E-6</v>
       </c>
     </row>
-    <row r="4" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="4" spans="2:15">
       <c r="B4" s="173" t="s">
         <v>202</v>
       </c>
@@ -14028,7 +14028,7 @@
         <v>2.3000000000000001E-10</v>
       </c>
     </row>
-    <row r="5" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="5" spans="2:15">
       <c r="B5" s="173" t="s">
         <v>203</v>
       </c>
@@ -14045,7 +14045,7 @@
       </c>
       <c r="L5" s="289"/>
     </row>
-    <row r="6" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="6" spans="2:15">
       <c r="B6" s="173" t="s">
         <v>204</v>
       </c>
@@ -14065,7 +14065,7 @@
       </c>
       <c r="L6" s="289"/>
     </row>
-    <row r="7" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="7" spans="2:15">
       <c r="B7" s="173" t="s">
         <v>206</v>
       </c>
@@ -14081,7 +14081,7 @@
         <v>133</v>
       </c>
     </row>
-    <row r="8" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="8" spans="2:15">
       <c r="B8" s="173" t="s">
         <v>300</v>
       </c>
@@ -14098,22 +14098,22 @@
         <v>46132</v>
       </c>
     </row>
-    <row r="9" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="9" spans="2:15">
       <c r="B9" s="206"/>
       <c r="C9" s="205"/>
       <c r="J9" s="206"/>
     </row>
-    <row r="10" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="10" spans="2:15">
       <c r="B10" s="206"/>
       <c r="C10" s="205"/>
       <c r="J10" s="206"/>
     </row>
-    <row r="11" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="11" spans="2:15">
       <c r="B11" s="206"/>
       <c r="C11" s="205"/>
       <c r="J11" s="206"/>
     </row>
-    <row r="12" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="12" spans="2:15">
       <c r="B12" s="209" t="s">
         <v>249</v>
       </c>
@@ -14154,7 +14154,7 @@
         <v>1000</v>
       </c>
     </row>
-    <row r="13" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="13" spans="2:15">
       <c r="B13" s="359"/>
       <c r="C13" s="360"/>
       <c r="D13" s="299"/>
@@ -14169,7 +14169,7 @@
       <c r="N13" s="358"/>
       <c r="O13" s="358"/>
     </row>
-    <row r="14" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="14" spans="2:15">
       <c r="B14" s="359"/>
       <c r="C14" s="360"/>
       <c r="D14" s="299"/>
@@ -14184,14 +14184,14 @@
       <c r="N14" s="358"/>
       <c r="O14" s="358"/>
     </row>
-    <row r="15" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="15" spans="2:15">
       <c r="D15" s="210"/>
       <c r="E15" s="210"/>
       <c r="F15" s="210"/>
       <c r="G15" s="210"/>
       <c r="H15" s="210"/>
     </row>
-    <row r="16" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="16" spans="2:15">
       <c r="B16" s="208"/>
       <c r="C16" s="207" t="s">
         <v>208</v>
@@ -14228,7 +14228,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:15">
       <c r="C18" s="700" t="s">
         <v>209</v>
       </c>
@@ -14246,7 +14246,7 @@
       <c r="N18" s="703"/>
       <c r="O18" s="704"/>
     </row>
-    <row r="19" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:15">
       <c r="C19" s="213"/>
       <c r="D19" s="214"/>
       <c r="E19" s="214"/>
@@ -14260,7 +14260,7 @@
       <c r="N19" s="214"/>
       <c r="O19" s="215"/>
     </row>
-    <row r="20" spans="3:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="20" spans="3:15" ht="15.75" customHeight="1">
       <c r="C20" s="216"/>
       <c r="D20" s="208">
         <f>+D12</f>
@@ -14297,7 +14297,7 @@
       </c>
       <c r="O20" s="172"/>
     </row>
-    <row r="21" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:15">
       <c r="C21" s="216"/>
       <c r="D21" s="211">
         <f>D16</f>
@@ -14338,7 +14338,7 @@
       </c>
       <c r="O21" s="172"/>
     </row>
-    <row r="22" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:15">
       <c r="C22" s="216"/>
       <c r="G22" s="217"/>
       <c r="H22" s="215"/>
@@ -14349,7 +14349,7 @@
       <c r="N22" s="287"/>
       <c r="O22" s="172"/>
     </row>
-    <row r="23" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:15">
       <c r="C23" s="216"/>
       <c r="D23" s="260"/>
       <c r="E23" s="261" t="s">
@@ -14379,7 +14379,7 @@
       </c>
       <c r="O23" s="172"/>
     </row>
-    <row r="24" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:15">
       <c r="C24" s="216"/>
       <c r="D24" s="216"/>
       <c r="E24" s="262" t="s">
@@ -14409,7 +14409,7 @@
       </c>
       <c r="O24" s="172"/>
     </row>
-    <row r="25" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:15">
       <c r="C25" s="216"/>
       <c r="D25" s="260"/>
       <c r="E25" s="295" t="s">
@@ -14439,7 +14439,7 @@
       </c>
       <c r="O25" s="172"/>
     </row>
-    <row r="26" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="26" spans="3:15">
       <c r="C26" s="218"/>
       <c r="D26" s="219"/>
       <c r="E26" s="219"/>
@@ -14468,28 +14468,28 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
   <dimension ref="B2:F12"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11.42578125" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.44140625" defaultRowHeight="13.2"/>
   <cols>
-    <col min="1" max="1" width="6.7109375" style="201" customWidth="1"/>
-    <col min="2" max="2" width="38.85546875" style="201" customWidth="1"/>
-    <col min="3" max="5" width="11.42578125" style="201"/>
-    <col min="6" max="6" width="13.5703125" style="201" customWidth="1"/>
-    <col min="7" max="16384" width="11.42578125" style="201"/>
+    <col min="1" max="1" width="6.6640625" style="201" customWidth="1"/>
+    <col min="2" max="2" width="38.88671875" style="201" customWidth="1"/>
+    <col min="3" max="5" width="11.44140625" style="201"/>
+    <col min="6" max="6" width="13.5546875" style="201" customWidth="1"/>
+    <col min="7" max="16384" width="11.44140625" style="201"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:6" x14ac:dyDescent="0.2">
+    <row r="2" spans="2:6">
       <c r="B2" s="285"/>
     </row>
-    <row r="3" spans="2:6" x14ac:dyDescent="0.2">
+    <row r="3" spans="2:6">
       <c r="B3" s="284"/>
     </row>
-    <row r="4" spans="2:6" x14ac:dyDescent="0.2">
+    <row r="4" spans="2:6">
       <c r="B4" s="285" t="s">
         <v>301</v>
       </c>
       <c r="C4" s="349"/>
     </row>
-    <row r="5" spans="2:6" ht="13.9" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="5" spans="2:6" ht="13.95" customHeight="1">
       <c r="B5" s="284" t="s">
         <v>32</v>
       </c>
@@ -14497,11 +14497,11 @@
         <v>46064</v>
       </c>
     </row>
-    <row r="6" spans="2:6" x14ac:dyDescent="0.2">
+    <row r="6" spans="2:6">
       <c r="B6" s="284"/>
       <c r="E6" s="284"/>
     </row>
-    <row r="7" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="7" spans="2:6" ht="15" customHeight="1">
       <c r="B7" s="283" t="s">
         <v>210</v>
       </c>
@@ -14512,7 +14512,7 @@
       <c r="E7" s="705"/>
       <c r="F7" s="284"/>
     </row>
-    <row r="8" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="8" spans="2:6" ht="15" customHeight="1">
       <c r="B8" s="283" t="s">
         <v>211</v>
       </c>
@@ -14523,10 +14523,10 @@
       <c r="E8" s="705"/>
       <c r="F8" s="284"/>
     </row>
-    <row r="9" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="10" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="11" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="12" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="9" spans="2:6" ht="15" customHeight="1"/>
+    <row r="10" spans="2:6" ht="15" customHeight="1"/>
+    <row r="11" spans="2:6" ht="15" customHeight="1"/>
+    <row r="12" spans="2:6" ht="15" customHeight="1"/>
   </sheetData>
   <sheetProtection algorithmName="SHA-512" hashValue="fksItH3sKB6aMM9OjE11xpwc3b7QQ4B/ZgnDmR0PCCclYu+rmlI//dvWUv9w8mTKYTp/W81Rdw2DHPDsFl5ALw==" saltValue="fdRUkgooo9rZMN2n5fqfUw==" spinCount="100000" sheet="1" objects="1" scenarios="1"/>
   <mergeCells count="2">
@@ -14542,18 +14542,18 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
   <sheetPr codeName="Hoja3"/>
   <dimension ref="A2:M9"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11.42578125" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.44140625" defaultRowHeight="13.2"/>
   <cols>
-    <col min="1" max="2" width="10.42578125" customWidth="1"/>
-    <col min="3" max="3" width="18.28515625" customWidth="1"/>
+    <col min="1" max="2" width="10.44140625" customWidth="1"/>
+    <col min="3" max="3" width="18.33203125" customWidth="1"/>
     <col min="4" max="4" width="20" customWidth="1"/>
-    <col min="6" max="6" width="12.42578125" customWidth="1"/>
-    <col min="11" max="11" width="17.7109375" customWidth="1"/>
-    <col min="12" max="12" width="12.42578125" customWidth="1"/>
-    <col min="13" max="13" width="15.42578125" customWidth="1"/>
+    <col min="6" max="6" width="12.44140625" customWidth="1"/>
+    <col min="11" max="11" width="17.6640625" customWidth="1"/>
+    <col min="12" max="12" width="12.44140625" customWidth="1"/>
+    <col min="13" max="13" width="15.44140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:13" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:13" ht="18.75" customHeight="1">
       <c r="A2" s="706" t="s">
         <v>212</v>
       </c>
@@ -14592,7 +14592,7 @@
         <v>223</v>
       </c>
     </row>
-    <row r="3" spans="1:13" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:13" ht="18.75" customHeight="1">
       <c r="A3" s="7">
         <v>4400</v>
       </c>
@@ -14638,7 +14638,7 @@
         <v>225</v>
       </c>
     </row>
-    <row r="4" spans="1:13" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:13" ht="18.75" customHeight="1">
       <c r="A4" s="1"/>
       <c r="B4" s="1"/>
       <c r="C4" s="6" t="str">
@@ -14675,7 +14675,7 @@
         <v>226</v>
       </c>
     </row>
-    <row r="5" spans="1:13" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:13" ht="18.75" customHeight="1">
       <c r="A5" s="1">
         <f>+B3+1</f>
         <v>4402</v>
@@ -14718,7 +14718,7 @@
         <v>226</v>
       </c>
     </row>
-    <row r="6" spans="1:13" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:13" ht="18.75" customHeight="1">
       <c r="A6" s="1"/>
       <c r="B6" s="1"/>
       <c r="C6" s="6" t="str">
@@ -14755,7 +14755,7 @@
         <v>226</v>
       </c>
     </row>
-    <row r="7" spans="1:13" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:13" ht="18.75" customHeight="1">
       <c r="A7" s="1">
         <f>+B5+1</f>
         <v>4404</v>
@@ -14798,7 +14798,7 @@
         <v>226</v>
       </c>
     </row>
-    <row r="8" spans="1:13" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:13" ht="18.75" customHeight="1">
       <c r="A8" s="1"/>
       <c r="B8" s="1"/>
       <c r="C8" s="6" t="str">
@@ -14835,7 +14835,7 @@
         <v>225</v>
       </c>
     </row>
-    <row r="9" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="9" spans="1:13" ht="15" customHeight="1"/>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A2:B2"/>

--- a/app/templates/informes/Humedad ASTM D2216-19/1-INF.-N-000-26-SU20-HM-V07.XLSX
+++ b/app/templates/informes/Humedad ASTM D2216-19/1-INF.-N-000-26-SU20-HM-V07.XLSX
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="27928"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="24332"/>
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Lenovo\Documents\crmnew\api-geofal-crm\app\templates\informes\Humedad ASTM D2216-19\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Mi unidad\3.0 Formatos e informes\2026\1.0 Informe de ensayo\1.1 Informe Suelo\INFORME ACREDITADO-E ISO\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8F49AAB9-6E69-47CF-A2F2-0E0EDDA7C8E0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{83CB10A4-D8C2-4A78-8CE2-3645BCB75D3E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="723" firstSheet="1" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="723" firstSheet="1" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="informe NTP" sheetId="91" state="hidden" r:id="rId1"/>
@@ -1259,7 +1259,7 @@
     <numFmt numFmtId="186" formatCode="000\-\ &quot;26&quot;"/>
     <numFmt numFmtId="187" formatCode="&quot;FORMATO F-LEM-P-SU-11.01&quot;"/>
   </numFmts>
-  <fonts count="82">
+  <fonts count="82" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
       <name val="Arial"/>
@@ -4226,100 +4226,44 @@
     <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="3" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="4" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="42" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="55" fillId="4" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="55" fillId="4" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="55" fillId="4" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="55" fillId="4" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="8" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="3" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="6" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
+      <protection hidden="1"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection hidden="1"/>
     </xf>
-    <xf numFmtId="0" fontId="38" fillId="8" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="38" fillId="8" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="38" fillId="8" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="38" fillId="8" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="42" fillId="8" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="42" fillId="8" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="166" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="3" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="169" fontId="20" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="176" fontId="25" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="23" fillId="0" borderId="0" xfId="4" applyFont="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
       <protection hidden="1"/>
     </xf>
     <xf numFmtId="0" fontId="23" fillId="0" borderId="7" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="42" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection hidden="1"/>
     </xf>
     <xf numFmtId="0" fontId="16" fillId="9" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
@@ -4371,66 +4315,88 @@
       <alignment horizontal="left" vertical="center" wrapText="1"/>
       <protection hidden="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="4" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="3" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="6" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="38" fillId="8" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection hidden="1"/>
     </xf>
-    <xf numFmtId="0" fontId="55" fillId="4" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="38" fillId="8" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection hidden="1"/>
     </xf>
-    <xf numFmtId="0" fontId="55" fillId="4" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="38" fillId="8" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection hidden="1"/>
     </xf>
-    <xf numFmtId="0" fontId="55" fillId="4" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="38" fillId="8" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection hidden="1"/>
     </xf>
-    <xf numFmtId="0" fontId="55" fillId="4" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="42" fillId="8" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection hidden="1"/>
     </xf>
-    <xf numFmtId="14" fontId="8" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="48" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="48" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="187" fontId="25" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="42" fillId="8" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="166" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="169" fontId="20" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="176" fontId="25" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center"/>
       <protection hidden="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="2" borderId="0" xfId="9" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
     </xf>
     <xf numFmtId="0" fontId="16" fillId="2" borderId="1" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="1"/>
@@ -4439,33 +4405,28 @@
       <alignment horizontal="center" vertical="center"/>
       <protection hidden="1"/>
     </xf>
-    <xf numFmtId="0" fontId="29" fillId="2" borderId="10" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="2" borderId="11" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="2" borderId="12" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="2" borderId="1" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="167" fontId="16" fillId="2" borderId="10" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="167" fontId="16" fillId="2" borderId="11" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="167" fontId="16" fillId="2" borderId="12" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="38" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="38" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="16" fontId="16" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="2" borderId="0" xfId="2" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="16" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
@@ -4491,6 +4452,15 @@
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
+    <xf numFmtId="167" fontId="16" fillId="2" borderId="10" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="16" fillId="2" borderId="11" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="16" fillId="2" borderId="12" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="38" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection hidden="1"/>
@@ -4511,31 +4481,123 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="2" borderId="0" xfId="9" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="38" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="38" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="16" fontId="16" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="29" fillId="2" borderId="10" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="2" borderId="11" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="2" borderId="12" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="2" borderId="1" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="48" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="48" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="187" fontId="25" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="184" fontId="25" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="4" quotePrefix="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="16" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="169" fontId="23" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="38" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="38" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="71" fillId="0" borderId="1" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="42" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" xfId="4" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="58" fillId="0" borderId="0" xfId="4" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" xfId="4" quotePrefix="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="2" borderId="0" xfId="2" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="12" fontId="23" fillId="0" borderId="1" xfId="4" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -4544,77 +4606,6 @@
     <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="4" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="42" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" xfId="4" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="4" quotePrefix="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="58" fillId="0" borderId="0" xfId="4" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" xfId="4" quotePrefix="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="184" fontId="25" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="3" fontId="16" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="169" fontId="23" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="38" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="38" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="71" fillId="0" borderId="1" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="12" fontId="23" fillId="0" borderId="1" xfId="4" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" xfId="3" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="169" fontId="5" fillId="0" borderId="1" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="10" xfId="3" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -4651,28 +4642,13 @@
     <xf numFmtId="167" fontId="5" fillId="0" borderId="12" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="59" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="59" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="62" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="181" fontId="59" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="181" fontId="59" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="181" fontId="4" fillId="2" borderId="10" xfId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="181" fontId="4" fillId="2" borderId="12" xfId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="3" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" xfId="3" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="169" fontId="5" fillId="0" borderId="1" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="64" fillId="2" borderId="4" xfId="6" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -4759,6 +4735,30 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="2" fontId="16" fillId="2" borderId="40" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="59" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="59" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="62" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="181" fontId="59" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="181" fontId="59" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="181" fontId="4" fillId="2" borderId="10" xfId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="181" fontId="4" fillId="2" borderId="12" xfId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="3" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="65" fillId="2" borderId="1" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -6173,15 +6173,15 @@
       <xdr:twoCellAnchor editAs="oneCell">
         <xdr:from>
           <xdr:col>4</xdr:col>
-          <xdr:colOff>769620</xdr:colOff>
+          <xdr:colOff>771525</xdr:colOff>
           <xdr:row>11</xdr:row>
-          <xdr:rowOff>83820</xdr:rowOff>
+          <xdr:rowOff>85725</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>6</xdr:col>
-          <xdr:colOff>480060</xdr:colOff>
+          <xdr:colOff>476250</xdr:colOff>
           <xdr:row>15</xdr:row>
-          <xdr:rowOff>60960</xdr:rowOff>
+          <xdr:rowOff>57150</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
@@ -6523,7 +6523,7 @@
 </file>
 
 <file path=xl/externalLinks/externalLink1.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <sheetNames>
       <sheetName val="-------"/>
@@ -6582,7 +6582,7 @@
 </file>
 
 <file path=xl/externalLinks/externalLink2.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <sheetNames>
       <sheetName val="datos de ecuacion del anillo"/>
@@ -6701,7 +6701,7 @@
 </file>
 
 <file path=xl/externalLinks/externalLink3.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <sheetNames>
       <sheetName val="-------"/>
@@ -6752,7 +6752,7 @@
 </file>
 
 <file path=xl/externalLinks/externalLink4.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <sheetNames>
       <sheetName val="-------"/>
@@ -6804,7 +6804,7 @@
 </file>
 
 <file path=xl/externalLinks/externalLink5.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <sheetNames>
       <sheetName val="BGA"/>
@@ -6836,7 +6836,7 @@
 </file>
 
 <file path=xl/externalLinks/externalLink6.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <sheetNames>
       <sheetName val="-------"/>
@@ -7542,29 +7542,29 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr codeName="Hoja2"/>
   <dimension ref="A1:Z101"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="10.33203125" defaultRowHeight="13.8"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="10.28515625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="16.33203125" style="15" customWidth="1"/>
+    <col min="1" max="1" width="16.28515625" style="15" customWidth="1"/>
     <col min="2" max="2" width="2" style="15" customWidth="1"/>
-    <col min="3" max="5" width="9.6640625" style="15" customWidth="1"/>
-    <col min="6" max="6" width="6.6640625" style="15" customWidth="1"/>
-    <col min="7" max="8" width="9.6640625" style="15" customWidth="1"/>
-    <col min="9" max="9" width="8.88671875" style="15" customWidth="1"/>
-    <col min="10" max="10" width="1.5546875" style="15" customWidth="1"/>
-    <col min="11" max="11" width="13.5546875" style="15" customWidth="1"/>
-    <col min="12" max="13" width="6.44140625" style="15" customWidth="1"/>
+    <col min="3" max="5" width="9.7109375" style="15" customWidth="1"/>
+    <col min="6" max="6" width="6.7109375" style="15" customWidth="1"/>
+    <col min="7" max="8" width="9.7109375" style="15" customWidth="1"/>
+    <col min="9" max="9" width="8.85546875" style="15" customWidth="1"/>
+    <col min="10" max="10" width="1.5703125" style="15" customWidth="1"/>
+    <col min="11" max="11" width="13.5703125" style="15" customWidth="1"/>
+    <col min="12" max="13" width="6.42578125" style="15" customWidth="1"/>
     <col min="14" max="14" width="8" style="15" customWidth="1"/>
-    <col min="15" max="15" width="10.33203125" style="15"/>
-    <col min="16" max="16" width="18.33203125" style="15" customWidth="1"/>
-    <col min="17" max="17" width="10.33203125" style="15"/>
+    <col min="15" max="15" width="10.28515625" style="15"/>
+    <col min="16" max="16" width="18.28515625" style="15" customWidth="1"/>
+    <col min="17" max="17" width="10.28515625" style="15"/>
     <col min="18" max="18" width="12" style="15" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="11.44140625" style="15" customWidth="1"/>
-    <col min="20" max="21" width="10.33203125" style="15"/>
-    <col min="22" max="22" width="12.44140625" style="15" customWidth="1"/>
-    <col min="23" max="16384" width="10.33203125" style="15"/>
+    <col min="19" max="19" width="11.42578125" style="15" customWidth="1"/>
+    <col min="20" max="21" width="10.28515625" style="15"/>
+    <col min="22" max="22" width="12.42578125" style="15" customWidth="1"/>
+    <col min="23" max="16384" width="10.28515625" style="15"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:18" ht="15.75" customHeight="1">
+    <row r="1" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="13"/>
       <c r="B1" s="13"/>
       <c r="C1" s="13"/>
@@ -7574,7 +7574,7 @@
       <c r="G1" s="14"/>
       <c r="H1" s="14"/>
     </row>
-    <row r="2" spans="1:18" ht="15.75" customHeight="1">
+    <row r="2" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="13"/>
       <c r="B2" s="13"/>
       <c r="C2" s="13"/>
@@ -7584,7 +7584,7 @@
       <c r="G2" s="14"/>
       <c r="H2" s="14"/>
     </row>
-    <row r="3" spans="1:18" ht="15.75" customHeight="1">
+    <row r="3" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="13"/>
       <c r="B3" s="13"/>
       <c r="C3" s="13"/>
@@ -7594,7 +7594,7 @@
       <c r="G3" s="14"/>
       <c r="H3" s="14"/>
     </row>
-    <row r="4" spans="1:18" ht="15.75" customHeight="1">
+    <row r="4" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="13"/>
       <c r="B4" s="13"/>
       <c r="C4" s="13"/>
@@ -7604,7 +7604,7 @@
       <c r="G4" s="14"/>
       <c r="H4" s="14"/>
     </row>
-    <row r="5" spans="1:18" ht="15.75" customHeight="1">
+    <row r="5" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="16"/>
       <c r="B5" s="16"/>
       <c r="C5" s="16"/>
@@ -7617,7 +7617,7 @@
       <c r="J5" s="16"/>
       <c r="K5" s="16"/>
     </row>
-    <row r="6" spans="1:18" ht="15.9" customHeight="1">
+    <row r="6" spans="1:18" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="16"/>
       <c r="B6" s="16"/>
       <c r="C6" s="16"/>
@@ -7630,41 +7630,41 @@
       <c r="J6" s="16"/>
       <c r="K6" s="16"/>
     </row>
-    <row r="7" spans="1:18" ht="15.9" customHeight="1">
-      <c r="A7" s="544" t="s">
+    <row r="7" spans="1:18" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="567" t="s">
         <v>0</v>
       </c>
-      <c r="B7" s="544"/>
-      <c r="C7" s="544"/>
-      <c r="D7" s="544"/>
-      <c r="E7" s="544"/>
-      <c r="F7" s="544"/>
-      <c r="G7" s="544"/>
-      <c r="H7" s="544"/>
-      <c r="I7" s="544"/>
-      <c r="J7" s="544"/>
-      <c r="K7" s="544"/>
-    </row>
-    <row r="8" spans="1:18" ht="15.9" customHeight="1">
-      <c r="A8" s="565">
+      <c r="B7" s="567"/>
+      <c r="C7" s="567"/>
+      <c r="D7" s="567"/>
+      <c r="E7" s="567"/>
+      <c r="F7" s="567"/>
+      <c r="G7" s="567"/>
+      <c r="H7" s="567"/>
+      <c r="I7" s="567"/>
+      <c r="J7" s="567"/>
+      <c r="K7" s="567"/>
+    </row>
+    <row r="8" spans="1:18" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="587">
         <f>K13</f>
         <v>15</v>
       </c>
-      <c r="B8" s="565"/>
-      <c r="C8" s="565"/>
-      <c r="D8" s="565"/>
-      <c r="E8" s="565"/>
-      <c r="F8" s="565"/>
-      <c r="G8" s="565"/>
-      <c r="H8" s="565"/>
-      <c r="I8" s="565"/>
-      <c r="J8" s="565"/>
-      <c r="K8" s="565"/>
-    </row>
-    <row r="9" spans="1:18" ht="15.9" customHeight="1">
+      <c r="B8" s="587"/>
+      <c r="C8" s="587"/>
+      <c r="D8" s="587"/>
+      <c r="E8" s="587"/>
+      <c r="F8" s="587"/>
+      <c r="G8" s="587"/>
+      <c r="H8" s="587"/>
+      <c r="I8" s="587"/>
+      <c r="J8" s="587"/>
+      <c r="K8" s="587"/>
+    </row>
+    <row r="9" spans="1:18" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="P9" s="17"/>
     </row>
-    <row r="10" spans="1:18" ht="15.9" customHeight="1">
+    <row r="10" spans="1:18" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="19" t="s">
         <v>1</v>
       </c>
@@ -7683,7 +7683,7 @@
       <c r="J10" s="18"/>
       <c r="K10" s="18"/>
     </row>
-    <row r="11" spans="1:18" ht="15.9" customHeight="1">
+    <row r="11" spans="1:18" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="19" t="s">
         <v>4</v>
       </c>
@@ -7712,7 +7712,7 @@
       <c r="N11" s="25"/>
       <c r="P11" s="26"/>
     </row>
-    <row r="12" spans="1:18" ht="15.9" customHeight="1">
+    <row r="12" spans="1:18" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="19" t="s">
         <v>8</v>
       </c>
@@ -7743,7 +7743,7 @@
       <c r="Q12" s="30"/>
       <c r="R12" s="31"/>
     </row>
-    <row r="13" spans="1:18" ht="15.9" customHeight="1">
+    <row r="13" spans="1:18" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="19" t="s">
         <v>11</v>
       </c>
@@ -7770,10 +7770,10 @@
       <c r="L13" s="25"/>
       <c r="M13" s="25"/>
       <c r="N13" s="25"/>
-      <c r="Q13" s="556"/>
-      <c r="R13" s="556"/>
-    </row>
-    <row r="14" spans="1:18" ht="15.9" customHeight="1">
+      <c r="Q13" s="578"/>
+      <c r="R13" s="578"/>
+    </row>
+    <row r="14" spans="1:18" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="167" t="s">
         <v>14</v>
       </c>
@@ -7793,51 +7793,51 @@
       <c r="Q14" s="304"/>
       <c r="R14" s="304"/>
     </row>
-    <row r="15" spans="1:18" ht="18" customHeight="1">
-      <c r="A15" s="557" t="s">
+    <row r="15" spans="1:18" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A15" s="579" t="s">
         <v>15</v>
       </c>
-      <c r="B15" s="558"/>
-      <c r="C15" s="558"/>
-      <c r="D15" s="558"/>
-      <c r="E15" s="558"/>
-      <c r="F15" s="558"/>
-      <c r="G15" s="558"/>
-      <c r="H15" s="558"/>
-      <c r="I15" s="558"/>
-      <c r="J15" s="558"/>
-      <c r="K15" s="559"/>
+      <c r="B15" s="580"/>
+      <c r="C15" s="580"/>
+      <c r="D15" s="580"/>
+      <c r="E15" s="580"/>
+      <c r="F15" s="580"/>
+      <c r="G15" s="580"/>
+      <c r="H15" s="580"/>
+      <c r="I15" s="580"/>
+      <c r="J15" s="580"/>
+      <c r="K15" s="581"/>
       <c r="L15" s="25"/>
       <c r="M15" s="25"/>
       <c r="N15" s="25"/>
       <c r="Q15" s="304"/>
       <c r="R15" s="304"/>
     </row>
-    <row r="16" spans="1:18" ht="18" customHeight="1">
-      <c r="A16" s="562" t="s">
+    <row r="16" spans="1:18" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A16" s="584" t="s">
         <v>16</v>
       </c>
-      <c r="B16" s="563"/>
-      <c r="C16" s="563"/>
-      <c r="D16" s="563"/>
-      <c r="E16" s="563"/>
-      <c r="F16" s="563"/>
-      <c r="G16" s="563"/>
-      <c r="H16" s="563"/>
-      <c r="I16" s="563"/>
-      <c r="J16" s="563"/>
-      <c r="K16" s="564"/>
+      <c r="B16" s="585"/>
+      <c r="C16" s="585"/>
+      <c r="D16" s="585"/>
+      <c r="E16" s="585"/>
+      <c r="F16" s="585"/>
+      <c r="G16" s="585"/>
+      <c r="H16" s="585"/>
+      <c r="I16" s="585"/>
+      <c r="J16" s="585"/>
+      <c r="K16" s="586"/>
       <c r="L16" s="25"/>
       <c r="M16" s="25"/>
       <c r="N16" s="25"/>
       <c r="Q16" s="304"/>
       <c r="R16" s="304"/>
     </row>
-    <row r="17" spans="1:26" ht="11.25" customHeight="1">
-      <c r="A17" s="545" t="s">
+    <row r="17" spans="1:26" ht="11.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A17" s="568" t="s">
         <v>17</v>
       </c>
-      <c r="B17" s="546"/>
+      <c r="B17" s="569"/>
       <c r="C17" s="36"/>
       <c r="D17" s="36"/>
       <c r="E17" s="36"/>
@@ -7853,9 +7853,9 @@
       <c r="Q17" s="304"/>
       <c r="R17" s="304"/>
     </row>
-    <row r="18" spans="1:26" ht="15.9" customHeight="1">
-      <c r="A18" s="547"/>
-      <c r="B18" s="548"/>
+    <row r="18" spans="1:26" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A18" s="570"/>
+      <c r="B18" s="571"/>
       <c r="C18" s="39"/>
       <c r="D18" s="39"/>
       <c r="E18" s="39"/>
@@ -7887,7 +7887,7 @@
       <c r="Y18" s="83"/>
       <c r="Z18" s="84"/>
     </row>
-    <row r="19" spans="1:26" ht="15.9" customHeight="1">
+    <row r="19" spans="1:26" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="40" t="s">
         <v>20</v>
       </c>
@@ -7929,7 +7929,7 @@
       <c r="Y19" s="89"/>
       <c r="Z19" s="90"/>
     </row>
-    <row r="20" spans="1:26" ht="15.9" customHeight="1">
+    <row r="20" spans="1:26" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="40" t="s">
         <v>25</v>
       </c>
@@ -7971,7 +7971,7 @@
       <c r="Y20" s="89"/>
       <c r="Z20" s="90"/>
     </row>
-    <row r="21" spans="1:26" ht="15.9" customHeight="1">
+    <row r="21" spans="1:26" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="40" t="s">
         <v>29</v>
       </c>
@@ -8000,10 +8000,10 @@
       <c r="P21" s="93" t="s">
         <v>32</v>
       </c>
-      <c r="Q21" s="588">
+      <c r="Q21" s="550">
         <v>44090</v>
       </c>
-      <c r="R21" s="588"/>
+      <c r="R21" s="550"/>
       <c r="S21" s="94"/>
       <c r="T21" s="95"/>
       <c r="U21" s="94"/>
@@ -8013,7 +8013,7 @@
       <c r="Y21" s="96"/>
       <c r="Z21" s="97"/>
     </row>
-    <row r="22" spans="1:26" ht="15" customHeight="1">
+    <row r="22" spans="1:26" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="155" t="s">
         <v>33</v>
       </c>
@@ -8044,23 +8044,23 @@
       <c r="Y22"/>
       <c r="Z22"/>
     </row>
-    <row r="23" spans="1:26" ht="13.5" customHeight="1" thickBot="1">
+    <row r="23" spans="1:26" ht="13.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A23" s="168"/>
-      <c r="B23" s="566"/>
-      <c r="C23" s="566"/>
+      <c r="B23" s="588"/>
+      <c r="C23" s="588"/>
       <c r="D23" s="306"/>
       <c r="E23" s="306"/>
       <c r="F23" s="306"/>
       <c r="G23" s="306"/>
       <c r="H23" s="306"/>
-      <c r="I23" s="566"/>
-      <c r="J23" s="566"/>
+      <c r="I23" s="588"/>
+      <c r="J23" s="588"/>
       <c r="K23" s="168"/>
       <c r="L23" s="25"/>
       <c r="M23" s="49"/>
       <c r="N23" s="49"/>
     </row>
-    <row r="24" spans="1:26" ht="17.25" customHeight="1">
+    <row r="24" spans="1:26" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="171"/>
       <c r="B24" s="50" t="s">
         <v>35</v>
@@ -8076,8 +8076,8 @@
         <f>+R24</f>
         <v>1</v>
       </c>
-      <c r="I24" s="560"/>
-      <c r="J24" s="560"/>
+      <c r="I24" s="582"/>
+      <c r="J24" s="582"/>
       <c r="K24" s="305"/>
       <c r="L24" s="25"/>
       <c r="M24" s="54"/>
@@ -8091,23 +8091,23 @@
       <c r="R24" s="56">
         <v>1</v>
       </c>
-      <c r="S24" s="549" t="s">
+      <c r="S24" s="551" t="s">
         <v>37</v>
       </c>
       <c r="U24" s="56">
         <v>2</v>
       </c>
-      <c r="V24" s="549" t="s">
+      <c r="V24" s="551" t="s">
         <v>37</v>
       </c>
-      <c r="W24" s="584" t="s">
+      <c r="W24" s="546" t="s">
         <v>38</v>
       </c>
-      <c r="X24" s="584"/>
-      <c r="Y24" s="584"/>
-      <c r="Z24" s="585"/>
-    </row>
-    <row r="25" spans="1:26" ht="17.25" customHeight="1" thickBot="1">
+      <c r="X24" s="546"/>
+      <c r="Y24" s="546"/>
+      <c r="Z24" s="547"/>
+    </row>
+    <row r="25" spans="1:26" ht="17.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A25" s="171"/>
       <c r="B25" s="50" t="s">
         <v>39</v>
@@ -8123,8 +8123,8 @@
         <f>+R25</f>
         <v>1</v>
       </c>
-      <c r="I25" s="560"/>
-      <c r="J25" s="560"/>
+      <c r="I25" s="582"/>
+      <c r="J25" s="582"/>
       <c r="K25" s="305"/>
       <c r="L25" s="25"/>
       <c r="M25" s="54"/>
@@ -8138,17 +8138,17 @@
       <c r="R25" s="59">
         <v>1</v>
       </c>
-      <c r="S25" s="549"/>
+      <c r="S25" s="551"/>
       <c r="U25" s="59">
         <v>2</v>
       </c>
-      <c r="V25" s="549"/>
-      <c r="W25" s="586"/>
-      <c r="X25" s="586"/>
-      <c r="Y25" s="586"/>
-      <c r="Z25" s="587"/>
-    </row>
-    <row r="26" spans="1:26" ht="17.25" customHeight="1">
+      <c r="V25" s="551"/>
+      <c r="W25" s="548"/>
+      <c r="X25" s="548"/>
+      <c r="Y25" s="548"/>
+      <c r="Z25" s="549"/>
+    </row>
+    <row r="26" spans="1:26" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="171"/>
       <c r="B26" s="50" t="s">
         <v>40</v>
@@ -8164,8 +8164,8 @@
         <f>S26</f>
         <v>794.6995891401001</v>
       </c>
-      <c r="I26" s="561"/>
-      <c r="J26" s="561"/>
+      <c r="I26" s="583"/>
+      <c r="J26" s="583"/>
       <c r="K26" s="169"/>
       <c r="L26" s="60"/>
       <c r="M26" s="54"/>
@@ -8191,7 +8191,7 @@
         <v>793.69958965710009</v>
       </c>
     </row>
-    <row r="27" spans="1:26" ht="17.25" customHeight="1">
+    <row r="27" spans="1:26" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="171"/>
       <c r="B27" s="50" t="s">
         <v>43</v>
@@ -8234,7 +8234,7 @@
         <v>775.79959891139993</v>
       </c>
     </row>
-    <row r="28" spans="1:26" ht="17.25" customHeight="1">
+    <row r="28" spans="1:26" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="171"/>
       <c r="B28" s="50" t="s">
         <v>45</v>
@@ -8277,7 +8277,7 @@
         <v>775.79959891139993</v>
       </c>
     </row>
-    <row r="29" spans="1:26" ht="17.25" customHeight="1">
+    <row r="29" spans="1:26" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="171"/>
       <c r="B29" s="50" t="s">
         <v>47</v>
@@ -8320,7 +8320,7 @@
         <v>775.79959891139993</v>
       </c>
     </row>
-    <row r="30" spans="1:26" ht="17.25" customHeight="1">
+    <row r="30" spans="1:26" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="171"/>
       <c r="B30" s="50" t="s">
         <v>49</v>
@@ -8365,7 +8365,7 @@
         <v>17.899990745700165</v>
       </c>
     </row>
-    <row r="31" spans="1:26" ht="17.25" customHeight="1">
+    <row r="31" spans="1:26" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" s="171"/>
       <c r="B31" s="50" t="s">
         <v>51</v>
@@ -8408,7 +8408,7 @@
         <v>163.1999156256</v>
       </c>
     </row>
-    <row r="32" spans="1:26" ht="17.25" customHeight="1">
+    <row r="32" spans="1:26" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" s="62"/>
       <c r="B32" s="50" t="s">
         <v>53</v>
@@ -8453,7 +8453,7 @@
         <v>612.59968328579998</v>
       </c>
     </row>
-    <row r="33" spans="1:22" ht="17.25" customHeight="1">
+    <row r="33" spans="1:22" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A33" s="171"/>
       <c r="B33" s="142" t="s">
         <v>55</v>
@@ -8498,7 +8498,7 @@
         <v>2.9219719229513821</v>
       </c>
     </row>
-    <row r="34" spans="1:22" ht="15.9" customHeight="1">
+    <row r="34" spans="1:22" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B34" s="68" t="s">
         <v>58</v>
       </c>
@@ -8507,35 +8507,35 @@
       <c r="L34" s="25"/>
       <c r="M34" s="25"/>
       <c r="N34" s="25"/>
-      <c r="P34" s="550" t="s">
+      <c r="P34" s="572" t="s">
         <v>59</v>
       </c>
-      <c r="Q34" s="551"/>
-      <c r="R34" s="554" t="s">
+      <c r="Q34" s="573"/>
+      <c r="R34" s="576" t="s">
         <v>60</v>
       </c>
-      <c r="S34" s="554" t="s">
+      <c r="S34" s="576" t="s">
         <v>61</v>
       </c>
       <c r="T34" s="132"/>
       <c r="U34" s="132"/>
       <c r="V34" s="132"/>
     </row>
-    <row r="35" spans="1:22" ht="2.25" customHeight="1">
+    <row r="35" spans="1:22" ht="2.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="J35" s="61"/>
       <c r="K35" s="61"/>
       <c r="L35" s="25"/>
       <c r="M35" s="25"/>
       <c r="N35" s="25"/>
-      <c r="P35" s="552"/>
-      <c r="Q35" s="553"/>
-      <c r="R35" s="555"/>
-      <c r="S35" s="555"/>
+      <c r="P35" s="574"/>
+      <c r="Q35" s="575"/>
+      <c r="R35" s="577"/>
+      <c r="S35" s="577"/>
       <c r="T35" s="133"/>
       <c r="U35" s="132"/>
       <c r="V35" s="132"/>
     </row>
-    <row r="36" spans="1:22" ht="15.9" customHeight="1">
+    <row r="36" spans="1:22" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A36" s="170" t="s">
         <v>62</v>
       </c>
@@ -8566,7 +8566,7 @@
       <c r="U36"/>
       <c r="V36" s="98"/>
     </row>
-    <row r="37" spans="1:22" ht="15.9" customHeight="1">
+    <row r="37" spans="1:22" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A37" s="164" t="s">
         <v>66</v>
       </c>
@@ -8599,7 +8599,7 @@
       <c r="U37" s="135"/>
       <c r="V37" s="135"/>
     </row>
-    <row r="38" spans="1:22" ht="14.25" customHeight="1">
+    <row r="38" spans="1:22" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A38" s="164" t="s">
         <v>71</v>
       </c>
@@ -8618,7 +8618,7 @@
       <c r="L38" s="25"/>
       <c r="M38" s="25"/>
       <c r="N38" s="25"/>
-      <c r="P38" s="570" t="s">
+      <c r="P38" s="554" t="s">
         <v>72</v>
       </c>
       <c r="Q38" s="108">
@@ -8634,17 +8634,17 @@
       <c r="U38" s="135"/>
       <c r="V38" s="135"/>
     </row>
-    <row r="39" spans="1:22" ht="14.25" customHeight="1">
-      <c r="A39" s="567" t="s">
+    <row r="39" spans="1:22" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A39" s="552" t="s">
         <v>75</v>
       </c>
-      <c r="B39" s="567"/>
-      <c r="C39" s="567"/>
-      <c r="D39" s="567"/>
-      <c r="E39" s="567"/>
-      <c r="F39" s="567"/>
-      <c r="G39" s="567"/>
-      <c r="H39" s="568"/>
+      <c r="B39" s="552"/>
+      <c r="C39" s="552"/>
+      <c r="D39" s="552"/>
+      <c r="E39" s="552"/>
+      <c r="F39" s="552"/>
+      <c r="G39" s="552"/>
+      <c r="H39" s="553"/>
       <c r="I39" s="166" t="s">
         <v>67</v>
       </c>
@@ -8653,7 +8653,7 @@
       <c r="L39" s="25"/>
       <c r="M39" s="25"/>
       <c r="N39" s="25"/>
-      <c r="P39" s="571"/>
+      <c r="P39" s="555"/>
       <c r="Q39" s="108">
         <v>0.75</v>
       </c>
@@ -8665,7 +8665,7 @@
       <c r="U39" s="135"/>
       <c r="V39" s="135"/>
     </row>
-    <row r="40" spans="1:22" ht="8.25" customHeight="1">
+    <row r="40" spans="1:22" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A40" s="125"/>
       <c r="B40" s="126"/>
       <c r="C40" s="126"/>
@@ -8678,7 +8678,7 @@
       <c r="L40" s="25"/>
       <c r="M40" s="25"/>
       <c r="N40" s="25"/>
-      <c r="P40" s="571"/>
+      <c r="P40" s="555"/>
       <c r="Q40" s="108">
         <v>1.5</v>
       </c>
@@ -8690,7 +8690,7 @@
       <c r="U40" s="135"/>
       <c r="V40" s="135"/>
     </row>
-    <row r="41" spans="1:22" ht="15.9" customHeight="1">
+    <row r="41" spans="1:22" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A41" s="69" t="s">
         <v>78</v>
       </c>
@@ -8705,7 +8705,7 @@
       <c r="L41" s="25"/>
       <c r="M41" s="25"/>
       <c r="N41" s="25"/>
-      <c r="P41" s="572"/>
+      <c r="P41" s="556"/>
       <c r="Q41" s="104">
         <v>3</v>
       </c>
@@ -8717,7 +8717,7 @@
       <c r="U41" s="135"/>
       <c r="V41" s="135"/>
     </row>
-    <row r="42" spans="1:22" ht="12" customHeight="1">
+    <row r="42" spans="1:22" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A42" s="153" t="s">
         <v>80</v>
       </c>
@@ -8746,7 +8746,7 @@
       <c r="U42" s="137"/>
       <c r="V42" s="137"/>
     </row>
-    <row r="43" spans="1:22" ht="12" customHeight="1">
+    <row r="43" spans="1:22" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A43" s="153" t="s">
         <v>82</v>
       </c>
@@ -8776,7 +8776,7 @@
       <c r="U43" s="99"/>
       <c r="V43" s="98"/>
     </row>
-    <row r="44" spans="1:22" ht="12" customHeight="1">
+    <row r="44" spans="1:22" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A44" s="153" t="s">
         <v>85</v>
       </c>
@@ -8808,7 +8808,7 @@
       <c r="U44" s="100"/>
       <c r="V44" s="101"/>
     </row>
-    <row r="45" spans="1:22" ht="12" customHeight="1">
+    <row r="45" spans="1:22" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A45" s="153" t="s">
         <v>87</v>
       </c>
@@ -8836,9 +8836,9 @@
       </c>
       <c r="T45" s="86"/>
       <c r="U45" s="102"/>
-      <c r="V45" s="569"/>
-    </row>
-    <row r="46" spans="1:22" ht="15.9" customHeight="1">
+      <c r="V45" s="545"/>
+    </row>
+    <row r="46" spans="1:22" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C46" s="42"/>
       <c r="D46" s="67"/>
       <c r="E46" s="67"/>
@@ -8862,9 +8862,9 @@
       </c>
       <c r="T46" s="86"/>
       <c r="U46" s="106"/>
-      <c r="V46" s="569"/>
-    </row>
-    <row r="47" spans="1:22" ht="12.75" customHeight="1">
+      <c r="V46" s="545"/>
+    </row>
+    <row r="47" spans="1:22" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A47" s="154" t="s">
         <v>91</v>
       </c>
@@ -8894,7 +8894,7 @@
       <c r="U47" s="106"/>
       <c r="V47" s="107"/>
     </row>
-    <row r="48" spans="1:22" ht="12.75" customHeight="1">
+    <row r="48" spans="1:22" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A48" s="154" t="s">
         <v>93</v>
       </c>
@@ -8915,7 +8915,7 @@
       <c r="U48" s="109"/>
       <c r="V48" s="107"/>
     </row>
-    <row r="49" spans="1:22" ht="10.5" customHeight="1">
+    <row r="49" spans="1:22" ht="10.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A49" s="77" t="s">
         <v>94</v>
       </c>
@@ -8932,7 +8932,7 @@
       <c r="U49" s="109"/>
       <c r="V49" s="107"/>
     </row>
-    <row r="50" spans="1:22" ht="10.5" customHeight="1">
+    <row r="50" spans="1:22" ht="10.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A50" s="77" t="s">
         <v>95</v>
       </c>
@@ -8950,64 +8950,64 @@
       <c r="U50" s="110"/>
       <c r="V50" s="107"/>
     </row>
-    <row r="51" spans="1:22" ht="33" customHeight="1">
-      <c r="A51" s="582" t="s">
+    <row r="51" spans="1:22" ht="33" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A51" s="566" t="s">
         <v>96</v>
       </c>
-      <c r="B51" s="582"/>
-      <c r="C51" s="582"/>
-      <c r="D51" s="582"/>
-      <c r="E51" s="582"/>
-      <c r="F51" s="582"/>
-      <c r="G51" s="582"/>
-      <c r="H51" s="582"/>
-      <c r="I51" s="582"/>
-      <c r="J51" s="582"/>
-      <c r="K51" s="582"/>
+      <c r="B51" s="566"/>
+      <c r="C51" s="566"/>
+      <c r="D51" s="566"/>
+      <c r="E51" s="566"/>
+      <c r="F51" s="566"/>
+      <c r="G51" s="566"/>
+      <c r="H51" s="566"/>
+      <c r="I51" s="566"/>
+      <c r="J51" s="566"/>
+      <c r="K51" s="566"/>
       <c r="T51" s="86"/>
       <c r="U51" s="109"/>
       <c r="V51" s="107"/>
     </row>
-    <row r="52" spans="1:22" ht="11.25" customHeight="1">
-      <c r="H52" s="581" t="s">
+    <row r="52" spans="1:22" ht="11.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H52" s="565" t="s">
         <v>97</v>
       </c>
-      <c r="I52" s="581"/>
-      <c r="J52" s="581"/>
-      <c r="K52" s="581"/>
+      <c r="I52" s="565"/>
+      <c r="J52" s="565"/>
+      <c r="K52" s="565"/>
       <c r="T52" s="86"/>
       <c r="U52" s="109"/>
       <c r="V52" s="107"/>
     </row>
-    <row r="53" spans="1:22" ht="15.9" customHeight="1">
+    <row r="53" spans="1:22" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="J53" s="70"/>
       <c r="K53" s="71"/>
       <c r="T53" s="117"/>
       <c r="U53" s="109"/>
       <c r="V53" s="107"/>
     </row>
-    <row r="54" spans="1:22">
+    <row r="54" spans="1:22" x14ac:dyDescent="0.25">
       <c r="J54" s="72"/>
       <c r="K54" s="71"/>
-      <c r="T54" s="583"/>
+      <c r="T54" s="544"/>
       <c r="U54" s="109"/>
       <c r="V54" s="107"/>
     </row>
-    <row r="55" spans="1:22">
+    <row r="55" spans="1:22" x14ac:dyDescent="0.25">
       <c r="J55"/>
       <c r="K55" s="71"/>
-      <c r="T55" s="583"/>
+      <c r="T55" s="544"/>
       <c r="U55" s="109"/>
       <c r="V55" s="107"/>
     </row>
-    <row r="56" spans="1:22">
+    <row r="56" spans="1:22" x14ac:dyDescent="0.25">
       <c r="J56"/>
       <c r="K56" s="71"/>
       <c r="T56" s="122"/>
       <c r="U56" s="109"/>
       <c r="V56" s="107"/>
     </row>
-    <row r="57" spans="1:22">
+    <row r="57" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A57"/>
       <c r="B57"/>
       <c r="C57"/>
@@ -9022,7 +9022,7 @@
       <c r="U57" s="109"/>
       <c r="V57" s="107"/>
     </row>
-    <row r="58" spans="1:22">
+    <row r="58" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A58" s="73"/>
       <c r="B58" s="73"/>
       <c r="C58" s="73"/>
@@ -9035,61 +9035,61 @@
       <c r="J58" s="73"/>
       <c r="K58" s="73"/>
     </row>
-    <row r="59" spans="1:22">
-      <c r="A59" s="573" t="s">
+    <row r="59" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A59" s="557" t="s">
         <v>98</v>
       </c>
-      <c r="B59" s="575"/>
-      <c r="C59" s="575"/>
-      <c r="D59" s="575"/>
-      <c r="E59" s="575"/>
-      <c r="F59" s="575"/>
-      <c r="G59" s="575"/>
-      <c r="H59" s="575"/>
-      <c r="I59" s="575"/>
-      <c r="J59" s="575"/>
-      <c r="K59" s="576"/>
-    </row>
-    <row r="60" spans="1:22">
-      <c r="A60" s="574"/>
-      <c r="B60" s="577"/>
-      <c r="C60" s="577"/>
-      <c r="D60" s="577"/>
-      <c r="E60" s="577"/>
-      <c r="F60" s="577"/>
-      <c r="G60" s="577"/>
-      <c r="H60" s="577"/>
-      <c r="I60" s="577"/>
-      <c r="J60" s="577"/>
-      <c r="K60" s="578"/>
-    </row>
-    <row r="61" spans="1:22">
+      <c r="B59" s="559"/>
+      <c r="C59" s="559"/>
+      <c r="D59" s="559"/>
+      <c r="E59" s="559"/>
+      <c r="F59" s="559"/>
+      <c r="G59" s="559"/>
+      <c r="H59" s="559"/>
+      <c r="I59" s="559"/>
+      <c r="J59" s="559"/>
+      <c r="K59" s="560"/>
+    </row>
+    <row r="60" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A60" s="558"/>
+      <c r="B60" s="561"/>
+      <c r="C60" s="561"/>
+      <c r="D60" s="561"/>
+      <c r="E60" s="561"/>
+      <c r="F60" s="561"/>
+      <c r="G60" s="561"/>
+      <c r="H60" s="561"/>
+      <c r="I60" s="561"/>
+      <c r="J60" s="561"/>
+      <c r="K60" s="562"/>
+    </row>
+    <row r="61" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A61" s="74"/>
-      <c r="B61" s="577"/>
-      <c r="C61" s="577"/>
-      <c r="D61" s="577"/>
-      <c r="E61" s="577"/>
-      <c r="F61" s="577"/>
-      <c r="G61" s="577"/>
-      <c r="H61" s="577"/>
-      <c r="I61" s="577"/>
-      <c r="J61" s="577"/>
-      <c r="K61" s="578"/>
-    </row>
-    <row r="62" spans="1:22">
+      <c r="B61" s="561"/>
+      <c r="C61" s="561"/>
+      <c r="D61" s="561"/>
+      <c r="E61" s="561"/>
+      <c r="F61" s="561"/>
+      <c r="G61" s="561"/>
+      <c r="H61" s="561"/>
+      <c r="I61" s="561"/>
+      <c r="J61" s="561"/>
+      <c r="K61" s="562"/>
+    </row>
+    <row r="62" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A62" s="75"/>
-      <c r="B62" s="579"/>
-      <c r="C62" s="579"/>
-      <c r="D62" s="579"/>
-      <c r="E62" s="579"/>
-      <c r="F62" s="579"/>
-      <c r="G62" s="579"/>
-      <c r="H62" s="579"/>
-      <c r="I62" s="579"/>
-      <c r="J62" s="579"/>
-      <c r="K62" s="580"/>
-    </row>
-    <row r="63" spans="1:22">
+      <c r="B62" s="563"/>
+      <c r="C62" s="563"/>
+      <c r="D62" s="563"/>
+      <c r="E62" s="563"/>
+      <c r="F62" s="563"/>
+      <c r="G62" s="563"/>
+      <c r="H62" s="563"/>
+      <c r="I62" s="563"/>
+      <c r="J62" s="563"/>
+      <c r="K62" s="564"/>
+    </row>
+    <row r="63" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A63" s="76"/>
       <c r="B63" s="76"/>
       <c r="C63" s="76"/>
@@ -9102,7 +9102,7 @@
       <c r="J63" s="76"/>
       <c r="K63" s="76"/>
     </row>
-    <row r="68" spans="1:11">
+    <row r="68" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A68"/>
       <c r="B68"/>
       <c r="C68"/>
@@ -9115,7 +9115,7 @@
       <c r="J68"/>
       <c r="K68"/>
     </row>
-    <row r="69" spans="1:11">
+    <row r="69" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A69"/>
       <c r="B69"/>
       <c r="C69"/>
@@ -9128,139 +9128,139 @@
       <c r="J69"/>
       <c r="K69"/>
     </row>
-    <row r="77" spans="1:11">
+    <row r="77" spans="1:11" x14ac:dyDescent="0.25">
       <c r="H77" s="98"/>
       <c r="I77" s="98"/>
       <c r="J77" s="98"/>
       <c r="K77"/>
     </row>
-    <row r="78" spans="1:11">
+    <row r="78" spans="1:11" x14ac:dyDescent="0.25">
       <c r="H78"/>
       <c r="I78"/>
       <c r="J78"/>
       <c r="K78"/>
     </row>
-    <row r="79" spans="1:11">
+    <row r="79" spans="1:11" x14ac:dyDescent="0.25">
       <c r="H79"/>
       <c r="I79"/>
       <c r="J79"/>
       <c r="K79"/>
     </row>
-    <row r="80" spans="1:11">
+    <row r="80" spans="1:11" x14ac:dyDescent="0.25">
       <c r="H80"/>
       <c r="I80"/>
       <c r="J80"/>
       <c r="K80"/>
     </row>
-    <row r="81" spans="8:11">
+    <row r="81" spans="8:11" x14ac:dyDescent="0.25">
       <c r="H81"/>
       <c r="I81"/>
       <c r="J81"/>
       <c r="K81"/>
     </row>
-    <row r="82" spans="8:11">
+    <row r="82" spans="8:11" x14ac:dyDescent="0.25">
       <c r="H82" s="98"/>
       <c r="I82" s="98"/>
       <c r="J82" s="98"/>
       <c r="K82"/>
     </row>
-    <row r="83" spans="8:11">
+    <row r="83" spans="8:11" x14ac:dyDescent="0.25">
       <c r="H83" s="98"/>
       <c r="I83" s="98"/>
       <c r="J83" s="98"/>
       <c r="K83"/>
     </row>
-    <row r="84" spans="8:11">
+    <row r="84" spans="8:11" x14ac:dyDescent="0.25">
       <c r="H84" s="98"/>
       <c r="I84" s="98"/>
       <c r="J84" s="98"/>
       <c r="K84"/>
     </row>
-    <row r="85" spans="8:11">
+    <row r="85" spans="8:11" x14ac:dyDescent="0.25">
       <c r="H85" s="101"/>
       <c r="I85" s="101"/>
       <c r="J85" s="101"/>
       <c r="K85"/>
     </row>
-    <row r="86" spans="8:11">
-      <c r="H86" s="569"/>
-      <c r="I86" s="569"/>
-      <c r="J86" s="569"/>
+    <row r="86" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H86" s="545"/>
+      <c r="I86" s="545"/>
+      <c r="J86" s="545"/>
       <c r="K86"/>
     </row>
-    <row r="87" spans="8:11">
-      <c r="H87" s="569"/>
-      <c r="I87" s="569"/>
-      <c r="J87" s="569"/>
+    <row r="87" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H87" s="545"/>
+      <c r="I87" s="545"/>
+      <c r="J87" s="545"/>
       <c r="K87"/>
     </row>
-    <row r="88" spans="8:11">
+    <row r="88" spans="8:11" x14ac:dyDescent="0.25">
       <c r="H88" s="107"/>
       <c r="I88" s="107"/>
       <c r="J88" s="107"/>
       <c r="K88"/>
     </row>
-    <row r="89" spans="8:11">
+    <row r="89" spans="8:11" x14ac:dyDescent="0.25">
       <c r="H89" s="107"/>
       <c r="I89" s="107"/>
       <c r="J89" s="107"/>
       <c r="K89"/>
     </row>
-    <row r="90" spans="8:11">
+    <row r="90" spans="8:11" x14ac:dyDescent="0.25">
       <c r="H90" s="107"/>
       <c r="I90" s="107"/>
       <c r="J90" s="107"/>
       <c r="K90"/>
     </row>
-    <row r="91" spans="8:11">
+    <row r="91" spans="8:11" x14ac:dyDescent="0.25">
       <c r="H91" s="107"/>
       <c r="I91" s="107"/>
       <c r="J91" s="107"/>
       <c r="K91"/>
     </row>
-    <row r="92" spans="8:11">
+    <row r="92" spans="8:11" x14ac:dyDescent="0.25">
       <c r="H92" s="107"/>
       <c r="I92" s="107"/>
       <c r="J92" s="107"/>
       <c r="K92"/>
     </row>
-    <row r="93" spans="8:11">
+    <row r="93" spans="8:11" x14ac:dyDescent="0.25">
       <c r="H93" s="107"/>
       <c r="I93" s="107"/>
       <c r="J93" s="107"/>
       <c r="K93"/>
     </row>
-    <row r="94" spans="8:11">
+    <row r="94" spans="8:11" x14ac:dyDescent="0.25">
       <c r="H94" s="107"/>
       <c r="I94" s="107"/>
       <c r="J94" s="107"/>
       <c r="K94"/>
     </row>
-    <row r="95" spans="8:11">
+    <row r="95" spans="8:11" x14ac:dyDescent="0.25">
       <c r="H95" s="107"/>
       <c r="I95" s="107"/>
       <c r="J95" s="107"/>
       <c r="K95"/>
     </row>
-    <row r="96" spans="8:11">
+    <row r="96" spans="8:11" x14ac:dyDescent="0.25">
       <c r="H96" s="107"/>
       <c r="I96" s="107"/>
       <c r="J96" s="107"/>
       <c r="K96"/>
     </row>
-    <row r="97" spans="1:11">
+    <row r="97" spans="1:11" x14ac:dyDescent="0.25">
       <c r="H97" s="107"/>
       <c r="I97" s="107"/>
       <c r="J97" s="107"/>
       <c r="K97"/>
     </row>
-    <row r="98" spans="1:11">
+    <row r="98" spans="1:11" x14ac:dyDescent="0.25">
       <c r="H98" s="107"/>
       <c r="I98" s="107"/>
       <c r="J98" s="107"/>
       <c r="K98"/>
     </row>
-    <row r="99" spans="1:11">
+    <row r="99" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A99"/>
       <c r="B99"/>
       <c r="C99"/>
@@ -9273,7 +9273,7 @@
       <c r="J99"/>
       <c r="K99"/>
     </row>
-    <row r="100" spans="1:11">
+    <row r="100" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A100"/>
       <c r="B100"/>
       <c r="C100"/>
@@ -9286,7 +9286,7 @@
       <c r="J100"/>
       <c r="K100"/>
     </row>
-    <row r="101" spans="1:11">
+    <row r="101" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A101"/>
       <c r="B101"/>
       <c r="C101"/>
@@ -9305,20 +9305,6 @@
     <protectedRange sqref="C10:C11" name="Rango3_3_1_1_1_1_1_2_1"/>
   </protectedRanges>
   <mergeCells count="29">
-    <mergeCell ref="T54:T55"/>
-    <mergeCell ref="V45:V46"/>
-    <mergeCell ref="W24:Z25"/>
-    <mergeCell ref="Q21:R21"/>
-    <mergeCell ref="S24:S25"/>
-    <mergeCell ref="A39:H39"/>
-    <mergeCell ref="H86:H87"/>
-    <mergeCell ref="I86:I87"/>
-    <mergeCell ref="J86:J87"/>
-    <mergeCell ref="P38:P41"/>
-    <mergeCell ref="A59:A60"/>
-    <mergeCell ref="B59:K62"/>
-    <mergeCell ref="H52:K52"/>
-    <mergeCell ref="A51:K51"/>
     <mergeCell ref="A7:K7"/>
     <mergeCell ref="A17:B18"/>
     <mergeCell ref="V24:V25"/>
@@ -9334,6 +9320,20 @@
     <mergeCell ref="B23:C23"/>
     <mergeCell ref="I23:J23"/>
     <mergeCell ref="I24:J24"/>
+    <mergeCell ref="A39:H39"/>
+    <mergeCell ref="H86:H87"/>
+    <mergeCell ref="I86:I87"/>
+    <mergeCell ref="J86:J87"/>
+    <mergeCell ref="P38:P41"/>
+    <mergeCell ref="A59:A60"/>
+    <mergeCell ref="B59:K62"/>
+    <mergeCell ref="H52:K52"/>
+    <mergeCell ref="A51:K51"/>
+    <mergeCell ref="T54:T55"/>
+    <mergeCell ref="V45:V46"/>
+    <mergeCell ref="W24:Z25"/>
+    <mergeCell ref="Q21:R21"/>
+    <mergeCell ref="S24:S25"/>
   </mergeCells>
   <conditionalFormatting sqref="A39">
     <cfRule type="cellIs" priority="1" stopIfTrue="1" operator="between">
@@ -9355,27 +9355,27 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B701DF6C-5F27-49B6-872C-8C68C4082771}">
   <dimension ref="A1:W63"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="10.33203125" defaultRowHeight="13.8"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="10.28515625" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="8.6640625" style="430" customWidth="1"/>
-    <col min="2" max="2" width="3.109375" style="430" customWidth="1"/>
-    <col min="3" max="3" width="10.88671875" style="430" customWidth="1"/>
-    <col min="4" max="4" width="14.44140625" style="430" customWidth="1"/>
-    <col min="5" max="5" width="10.88671875" style="430" customWidth="1"/>
-    <col min="6" max="6" width="11.33203125" style="430" customWidth="1"/>
+    <col min="1" max="1" width="8.7109375" style="430" customWidth="1"/>
+    <col min="2" max="2" width="3.140625" style="430" customWidth="1"/>
+    <col min="3" max="3" width="10.85546875" style="430" customWidth="1"/>
+    <col min="4" max="4" width="14.42578125" style="430" customWidth="1"/>
+    <col min="5" max="5" width="10.85546875" style="430" customWidth="1"/>
+    <col min="6" max="6" width="11.28515625" style="430" customWidth="1"/>
     <col min="7" max="7" width="3" style="430" customWidth="1"/>
-    <col min="8" max="8" width="9.33203125" style="430" customWidth="1"/>
-    <col min="9" max="9" width="16.88671875" style="430" customWidth="1"/>
-    <col min="10" max="10" width="6.6640625" style="430" customWidth="1"/>
-    <col min="11" max="11" width="8.44140625" style="430" customWidth="1"/>
-    <col min="12" max="12" width="2.109375" style="430" customWidth="1"/>
-    <col min="13" max="13" width="6.44140625" style="430" customWidth="1"/>
-    <col min="14" max="14" width="9.33203125" style="430" customWidth="1"/>
-    <col min="15" max="15" width="12.44140625" style="430" customWidth="1"/>
-    <col min="16" max="16384" width="10.33203125" style="430"/>
+    <col min="8" max="8" width="9.28515625" style="430" customWidth="1"/>
+    <col min="9" max="9" width="16.85546875" style="430" customWidth="1"/>
+    <col min="10" max="10" width="6.7109375" style="430" customWidth="1"/>
+    <col min="11" max="11" width="8.42578125" style="430" customWidth="1"/>
+    <col min="12" max="12" width="2.140625" style="430" customWidth="1"/>
+    <col min="13" max="13" width="6.42578125" style="430" customWidth="1"/>
+    <col min="14" max="14" width="9.28515625" style="430" customWidth="1"/>
+    <col min="15" max="15" width="12.42578125" style="430" customWidth="1"/>
+    <col min="16" max="16384" width="10.28515625" style="430"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16" ht="12.75" customHeight="1" thickTop="1">
+    <row r="1" spans="1:16" ht="12.75" customHeight="1" thickTop="1" x14ac:dyDescent="0.2">
       <c r="A1" s="461"/>
       <c r="B1" s="462"/>
       <c r="C1" s="462"/>
@@ -9389,7 +9389,7 @@
       <c r="K1" s="464"/>
       <c r="L1" s="465"/>
     </row>
-    <row r="2" spans="1:16" ht="12.75" customHeight="1">
+    <row r="2" spans="1:16" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="466"/>
       <c r="B2" s="467"/>
       <c r="C2" s="467"/>
@@ -9405,7 +9405,7 @@
       </c>
       <c r="P2" s="451"/>
     </row>
-    <row r="3" spans="1:16" ht="12.75" customHeight="1">
+    <row r="3" spans="1:16" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="466"/>
       <c r="B3" s="467"/>
       <c r="C3" s="467"/>
@@ -9421,7 +9421,7 @@
       </c>
       <c r="P3" s="452"/>
     </row>
-    <row r="4" spans="1:16" ht="12.75" customHeight="1">
+    <row r="4" spans="1:16" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="466"/>
       <c r="B4" s="467"/>
       <c r="C4" s="467"/>
@@ -9437,7 +9437,7 @@
       </c>
       <c r="P4" s="452"/>
     </row>
-    <row r="5" spans="1:16" ht="12.75" customHeight="1" thickBot="1">
+    <row r="5" spans="1:16" ht="12.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A5" s="470"/>
       <c r="B5" s="471"/>
       <c r="C5" s="471"/>
@@ -9455,7 +9455,7 @@
       </c>
       <c r="P5" s="452"/>
     </row>
-    <row r="6" spans="1:16" ht="6.75" customHeight="1" thickTop="1">
+    <row r="6" spans="1:16" ht="6.75" customHeight="1" thickTop="1" x14ac:dyDescent="0.2">
       <c r="A6" s="473"/>
       <c r="B6" s="473"/>
       <c r="C6" s="473"/>
@@ -9471,47 +9471,47 @@
       <c r="O6" s="453"/>
       <c r="P6" s="454"/>
     </row>
-    <row r="7" spans="1:16" ht="15.9" customHeight="1">
-      <c r="A7" s="591" t="s">
+    <row r="7" spans="1:16" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A7" s="620" t="s">
         <v>0</v>
       </c>
-      <c r="B7" s="591"/>
-      <c r="C7" s="591"/>
-      <c r="D7" s="591"/>
-      <c r="E7" s="591"/>
-      <c r="F7" s="591"/>
-      <c r="G7" s="591"/>
-      <c r="H7" s="591"/>
-      <c r="I7" s="591"/>
-      <c r="J7" s="591"/>
-      <c r="K7" s="591"/>
-      <c r="L7" s="591"/>
+      <c r="B7" s="620"/>
+      <c r="C7" s="620"/>
+      <c r="D7" s="620"/>
+      <c r="E7" s="620"/>
+      <c r="F7" s="620"/>
+      <c r="G7" s="620"/>
+      <c r="H7" s="620"/>
+      <c r="I7" s="620"/>
+      <c r="J7" s="620"/>
+      <c r="K7" s="620"/>
+      <c r="L7" s="620"/>
       <c r="O7" s="450" t="s">
         <v>233</v>
       </c>
       <c r="P7" s="454"/>
     </row>
-    <row r="8" spans="1:16" ht="15.9" customHeight="1">
-      <c r="A8" s="592" t="s">
+    <row r="8" spans="1:16" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="621" t="s">
         <v>250</v>
       </c>
-      <c r="B8" s="592"/>
-      <c r="C8" s="592"/>
-      <c r="D8" s="592"/>
-      <c r="E8" s="592"/>
-      <c r="F8" s="592"/>
-      <c r="G8" s="592"/>
-      <c r="H8" s="592"/>
-      <c r="I8" s="592"/>
-      <c r="J8" s="592"/>
-      <c r="K8" s="592"/>
-      <c r="L8" s="592"/>
+      <c r="B8" s="621"/>
+      <c r="C8" s="621"/>
+      <c r="D8" s="621"/>
+      <c r="E8" s="621"/>
+      <c r="F8" s="621"/>
+      <c r="G8" s="621"/>
+      <c r="H8" s="621"/>
+      <c r="I8" s="621"/>
+      <c r="J8" s="621"/>
+      <c r="K8" s="621"/>
+      <c r="L8" s="621"/>
       <c r="O8" s="450" t="s">
         <v>296</v>
       </c>
       <c r="P8" s="455"/>
     </row>
-    <row r="9" spans="1:16" ht="8.25" customHeight="1">
+    <row r="9" spans="1:16" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="474"/>
       <c r="B9" s="474"/>
       <c r="C9" s="474"/>
@@ -9529,7 +9529,7 @@
       </c>
       <c r="P9" s="454"/>
     </row>
-    <row r="10" spans="1:16" ht="15.9" customHeight="1">
+    <row r="10" spans="1:16" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="474"/>
       <c r="B10" s="474"/>
       <c r="D10" s="475" t="s">
@@ -9552,7 +9552,7 @@
       <c r="O10" s="453"/>
       <c r="P10" s="454"/>
     </row>
-    <row r="11" spans="1:16" ht="15.9" customHeight="1">
+    <row r="11" spans="1:16" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="474"/>
       <c r="B11" s="474"/>
       <c r="C11" s="474"/>
@@ -9570,7 +9570,7 @@
       </c>
       <c r="P11" s="454"/>
     </row>
-    <row r="12" spans="1:16" ht="15.9" customHeight="1">
+    <row r="12" spans="1:16" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="474"/>
       <c r="B12" s="474"/>
       <c r="C12" s="474"/>
@@ -9584,7 +9584,7 @@
       </c>
       <c r="P12" s="455"/>
     </row>
-    <row r="13" spans="1:16" ht="7.5" customHeight="1">
+    <row r="13" spans="1:16" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" s="479"/>
       <c r="B13" s="480"/>
       <c r="C13" s="481"/>
@@ -9603,47 +9603,47 @@
       </c>
       <c r="P13" s="455"/>
     </row>
-    <row r="14" spans="1:16" ht="17.25" customHeight="1">
-      <c r="A14" s="593" t="s">
+    <row r="14" spans="1:16" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A14" s="622" t="s">
         <v>102</v>
       </c>
-      <c r="B14" s="594"/>
-      <c r="C14" s="594"/>
-      <c r="D14" s="594"/>
-      <c r="E14" s="594"/>
-      <c r="F14" s="594"/>
-      <c r="G14" s="594"/>
-      <c r="H14" s="594"/>
-      <c r="I14" s="594"/>
-      <c r="J14" s="594"/>
-      <c r="K14" s="594"/>
-      <c r="L14" s="595"/>
+      <c r="B14" s="623"/>
+      <c r="C14" s="623"/>
+      <c r="D14" s="623"/>
+      <c r="E14" s="623"/>
+      <c r="F14" s="623"/>
+      <c r="G14" s="623"/>
+      <c r="H14" s="623"/>
+      <c r="I14" s="623"/>
+      <c r="J14" s="623"/>
+      <c r="K14" s="623"/>
+      <c r="L14" s="624"/>
       <c r="M14" s="87"/>
       <c r="O14" s="453"/>
       <c r="P14" s="454"/>
     </row>
-    <row r="15" spans="1:16" ht="15" customHeight="1">
-      <c r="A15" s="596" t="s">
+    <row r="15" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A15" s="625" t="s">
         <v>103</v>
       </c>
-      <c r="B15" s="597"/>
-      <c r="C15" s="597"/>
-      <c r="D15" s="597"/>
-      <c r="E15" s="597"/>
-      <c r="F15" s="597"/>
-      <c r="G15" s="597"/>
-      <c r="H15" s="597"/>
-      <c r="I15" s="597"/>
-      <c r="J15" s="597"/>
-      <c r="K15" s="597"/>
-      <c r="L15" s="598"/>
+      <c r="B15" s="626"/>
+      <c r="C15" s="626"/>
+      <c r="D15" s="626"/>
+      <c r="E15" s="626"/>
+      <c r="F15" s="626"/>
+      <c r="G15" s="626"/>
+      <c r="H15" s="626"/>
+      <c r="I15" s="626"/>
+      <c r="J15" s="626"/>
+      <c r="K15" s="626"/>
+      <c r="L15" s="627"/>
       <c r="M15" s="87"/>
       <c r="O15" s="450" t="s">
         <v>104</v>
       </c>
       <c r="P15" s="456"/>
     </row>
-    <row r="16" spans="1:16" ht="18" customHeight="1">
+    <row r="16" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A16" s="483"/>
       <c r="B16" s="484"/>
       <c r="C16" s="485"/>
@@ -9662,18 +9662,18 @@
       </c>
       <c r="P16" s="456"/>
     </row>
-    <row r="17" spans="1:19" ht="15.9" customHeight="1">
-      <c r="A17" s="589" t="s">
+    <row r="17" spans="1:19" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A17" s="618" t="s">
         <v>254</v>
       </c>
-      <c r="B17" s="590"/>
-      <c r="C17" s="590"/>
-      <c r="D17" s="590"/>
-      <c r="E17" s="590"/>
-      <c r="F17" s="590"/>
-      <c r="G17" s="590"/>
-      <c r="H17" s="590"/>
-      <c r="I17" s="590"/>
+      <c r="B17" s="619"/>
+      <c r="C17" s="619"/>
+      <c r="D17" s="619"/>
+      <c r="E17" s="619"/>
+      <c r="F17" s="619"/>
+      <c r="G17" s="619"/>
+      <c r="H17" s="619"/>
+      <c r="I17" s="619"/>
       <c r="J17" s="431"/>
       <c r="K17" s="431"/>
       <c r="L17" s="487"/>
@@ -9682,7 +9682,7 @@
       </c>
       <c r="P17" s="457"/>
     </row>
-    <row r="18" spans="1:19" ht="18" customHeight="1">
+    <row r="18" spans="1:19" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A18" s="488" t="s">
         <v>120</v>
       </c>
@@ -9698,7 +9698,7 @@
       <c r="K18" s="431"/>
       <c r="L18" s="487"/>
     </row>
-    <row r="19" spans="1:19" ht="18" customHeight="1">
+    <row r="19" spans="1:19" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A19" s="488" t="s">
         <v>255</v>
       </c>
@@ -9714,7 +9714,7 @@
       <c r="K19" s="431"/>
       <c r="L19" s="487"/>
     </row>
-    <row r="20" spans="1:19" ht="18" customHeight="1">
+    <row r="20" spans="1:19" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A20" s="488" t="s">
         <v>122</v>
       </c>
@@ -9730,7 +9730,7 @@
       <c r="K20" s="431"/>
       <c r="L20" s="487"/>
     </row>
-    <row r="21" spans="1:19" ht="18" customHeight="1">
+    <row r="21" spans="1:19" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A21" s="488" t="s">
         <v>123</v>
       </c>
@@ -9746,7 +9746,7 @@
       <c r="K21" s="431"/>
       <c r="L21" s="487"/>
     </row>
-    <row r="22" spans="1:19" ht="18" customHeight="1">
+    <row r="22" spans="1:19" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A22" s="491" t="s">
         <v>293</v>
       </c>
@@ -9762,7 +9762,7 @@
       <c r="K22" s="431"/>
       <c r="L22" s="487"/>
     </row>
-    <row r="23" spans="1:19" ht="14.4" customHeight="1">
+    <row r="23" spans="1:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A23" s="492"/>
       <c r="B23" s="432"/>
       <c r="C23" s="432"/>
@@ -9776,13 +9776,13 @@
       <c r="K23" s="431"/>
       <c r="L23" s="487"/>
     </row>
-    <row r="24" spans="1:19" ht="15.9" customHeight="1">
-      <c r="A24" s="589" t="s">
+    <row r="24" spans="1:19" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A24" s="618" t="s">
         <v>256</v>
       </c>
-      <c r="B24" s="590"/>
-      <c r="C24" s="590"/>
-      <c r="D24" s="590"/>
+      <c r="B24" s="619"/>
+      <c r="C24" s="619"/>
+      <c r="D24" s="619"/>
       <c r="E24" s="432"/>
       <c r="F24" s="432"/>
       <c r="G24" s="432"/>
@@ -9792,51 +9792,51 @@
       <c r="K24" s="431"/>
       <c r="L24" s="487"/>
     </row>
-    <row r="25" spans="1:19" ht="19.2" customHeight="1">
-      <c r="A25" s="599" t="s">
+    <row r="25" spans="1:19" ht="19.149999999999999" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A25" s="590" t="s">
         <v>257</v>
       </c>
-      <c r="B25" s="599"/>
-      <c r="C25" s="599"/>
-      <c r="D25" s="599"/>
-      <c r="E25" s="600"/>
-      <c r="F25" s="600"/>
+      <c r="B25" s="590"/>
+      <c r="C25" s="590"/>
+      <c r="D25" s="590"/>
+      <c r="E25" s="591"/>
+      <c r="F25" s="591"/>
       <c r="G25" s="433"/>
-      <c r="H25" s="601" t="s">
+      <c r="H25" s="614" t="s">
         <v>286</v>
       </c>
-      <c r="I25" s="602"/>
-      <c r="J25" s="603"/>
+      <c r="I25" s="615"/>
+      <c r="J25" s="616"/>
       <c r="K25" s="493"/>
       <c r="L25" s="487"/>
     </row>
-    <row r="26" spans="1:19" ht="19.2" customHeight="1">
-      <c r="A26" s="599" t="s">
+    <row r="26" spans="1:19" ht="19.149999999999999" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A26" s="590" t="s">
         <v>258</v>
       </c>
-      <c r="B26" s="599"/>
-      <c r="C26" s="599"/>
-      <c r="D26" s="599"/>
-      <c r="E26" s="600"/>
-      <c r="F26" s="600"/>
+      <c r="B26" s="590"/>
+      <c r="C26" s="590"/>
+      <c r="D26" s="590"/>
+      <c r="E26" s="591"/>
+      <c r="F26" s="591"/>
       <c r="G26" s="433"/>
-      <c r="H26" s="604" t="s">
+      <c r="H26" s="617" t="s">
         <v>287</v>
       </c>
-      <c r="I26" s="604"/>
+      <c r="I26" s="617"/>
       <c r="J26" s="434"/>
       <c r="K26" s="494"/>
       <c r="L26" s="487"/>
     </row>
-    <row r="27" spans="1:19" ht="19.2" customHeight="1">
-      <c r="A27" s="599" t="s">
+    <row r="27" spans="1:19" ht="19.149999999999999" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A27" s="590" t="s">
         <v>259</v>
       </c>
-      <c r="B27" s="599"/>
-      <c r="C27" s="599"/>
-      <c r="D27" s="599"/>
-      <c r="E27" s="600"/>
-      <c r="F27" s="600"/>
+      <c r="B27" s="590"/>
+      <c r="C27" s="590"/>
+      <c r="D27" s="590"/>
+      <c r="E27" s="591"/>
+      <c r="F27" s="591"/>
       <c r="G27" s="433"/>
       <c r="H27" s="446"/>
       <c r="I27" s="447"/>
@@ -9845,19 +9845,19 @@
       <c r="L27" s="487"/>
       <c r="M27" s="87"/>
     </row>
-    <row r="28" spans="1:19" ht="19.2" customHeight="1">
-      <c r="A28" s="599" t="s">
+    <row r="28" spans="1:19" ht="19.149999999999999" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A28" s="590" t="s">
         <v>288</v>
       </c>
-      <c r="B28" s="599"/>
-      <c r="C28" s="599"/>
-      <c r="D28" s="599"/>
-      <c r="E28" s="600"/>
-      <c r="F28" s="600"/>
+      <c r="B28" s="590"/>
+      <c r="C28" s="590"/>
+      <c r="D28" s="590"/>
+      <c r="E28" s="591"/>
+      <c r="F28" s="591"/>
       <c r="L28" s="495"/>
       <c r="M28" s="87"/>
     </row>
-    <row r="29" spans="1:19" ht="22.2" customHeight="1">
+    <row r="29" spans="1:19" ht="22.15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A29" s="496"/>
       <c r="B29" s="497"/>
       <c r="C29" s="497"/>
@@ -9872,39 +9872,39 @@
       <c r="L29" s="500"/>
       <c r="M29" s="87"/>
     </row>
-    <row r="30" spans="1:19" ht="15.75" customHeight="1">
+    <row r="30" spans="1:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A30" s="501"/>
-      <c r="B30" s="608" t="s">
+      <c r="B30" s="612" t="s">
         <v>261</v>
       </c>
-      <c r="C30" s="608"/>
-      <c r="D30" s="608"/>
-      <c r="E30" s="608"/>
-      <c r="F30" s="608"/>
-      <c r="G30" s="608"/>
+      <c r="C30" s="612"/>
+      <c r="D30" s="612"/>
+      <c r="E30" s="612"/>
+      <c r="F30" s="612"/>
+      <c r="G30" s="612"/>
       <c r="H30" s="502" t="s">
         <v>262</v>
       </c>
       <c r="I30" s="502" t="s">
         <v>263</v>
       </c>
-      <c r="J30" s="609"/>
-      <c r="K30" s="609"/>
+      <c r="J30" s="613"/>
+      <c r="K30" s="613"/>
       <c r="L30" s="503"/>
       <c r="M30" s="87"/>
     </row>
-    <row r="31" spans="1:19" ht="21.75" customHeight="1">
+    <row r="31" spans="1:19" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A31" s="504"/>
       <c r="B31" s="505">
         <v>1</v>
       </c>
-      <c r="C31" s="605" t="s">
+      <c r="C31" s="604" t="s">
         <v>35</v>
       </c>
-      <c r="D31" s="606"/>
-      <c r="E31" s="606"/>
-      <c r="F31" s="606"/>
-      <c r="G31" s="607"/>
+      <c r="D31" s="605"/>
+      <c r="E31" s="605"/>
+      <c r="F31" s="605"/>
+      <c r="G31" s="606"/>
       <c r="H31" s="506" t="s">
         <v>36</v>
       </c>
@@ -9914,18 +9914,18 @@
       <c r="L31" s="509"/>
       <c r="M31" s="87"/>
     </row>
-    <row r="32" spans="1:19" ht="21.75" customHeight="1">
+    <row r="32" spans="1:19" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A32" s="504"/>
       <c r="B32" s="510">
         <v>2</v>
       </c>
-      <c r="C32" s="605" t="s">
+      <c r="C32" s="604" t="s">
         <v>111</v>
       </c>
-      <c r="D32" s="606"/>
-      <c r="E32" s="606"/>
-      <c r="F32" s="606"/>
-      <c r="G32" s="607"/>
+      <c r="D32" s="605"/>
+      <c r="E32" s="605"/>
+      <c r="F32" s="605"/>
+      <c r="G32" s="606"/>
       <c r="H32" s="506" t="s">
         <v>36</v>
       </c>
@@ -9936,18 +9936,18 @@
       <c r="M32" s="87"/>
       <c r="S32" s="435"/>
     </row>
-    <row r="33" spans="1:23" ht="21.75" customHeight="1">
+    <row r="33" spans="1:23" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A33" s="504"/>
       <c r="B33" s="510">
         <v>3</v>
       </c>
-      <c r="C33" s="605" t="s">
+      <c r="C33" s="604" t="s">
         <v>112</v>
       </c>
-      <c r="D33" s="606"/>
-      <c r="E33" s="606"/>
-      <c r="F33" s="606"/>
-      <c r="G33" s="607"/>
+      <c r="D33" s="605"/>
+      <c r="E33" s="605"/>
+      <c r="F33" s="605"/>
+      <c r="G33" s="606"/>
       <c r="H33" s="506" t="s">
         <v>184</v>
       </c>
@@ -9958,18 +9958,18 @@
       <c r="M33" s="436"/>
       <c r="W33" s="435"/>
     </row>
-    <row r="34" spans="1:23" ht="21.75" customHeight="1">
+    <row r="34" spans="1:23" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A34" s="504"/>
       <c r="B34" s="505">
         <v>4</v>
       </c>
-      <c r="C34" s="605" t="s">
+      <c r="C34" s="604" t="s">
         <v>113</v>
       </c>
-      <c r="D34" s="606"/>
-      <c r="E34" s="606"/>
-      <c r="F34" s="606"/>
-      <c r="G34" s="607"/>
+      <c r="D34" s="605"/>
+      <c r="E34" s="605"/>
+      <c r="F34" s="605"/>
+      <c r="G34" s="606"/>
       <c r="H34" s="506" t="s">
         <v>184</v>
       </c>
@@ -9982,18 +9982,18 @@
       <c r="P34" s="437"/>
       <c r="W34" s="435"/>
     </row>
-    <row r="35" spans="1:23" ht="21.75" customHeight="1">
+    <row r="35" spans="1:23" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A35" s="504"/>
       <c r="B35" s="510">
         <v>5</v>
       </c>
-      <c r="C35" s="605" t="s">
+      <c r="C35" s="604" t="s">
         <v>265</v>
       </c>
-      <c r="D35" s="606"/>
-      <c r="E35" s="606"/>
-      <c r="F35" s="606"/>
-      <c r="G35" s="607"/>
+      <c r="D35" s="605"/>
+      <c r="E35" s="605"/>
+      <c r="F35" s="605"/>
+      <c r="G35" s="606"/>
       <c r="H35" s="506" t="s">
         <v>184</v>
       </c>
@@ -10006,18 +10006,18 @@
       <c r="P35" s="437"/>
       <c r="W35" s="435"/>
     </row>
-    <row r="36" spans="1:23" ht="21.75" customHeight="1">
+    <row r="36" spans="1:23" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A36" s="504"/>
       <c r="B36" s="505">
         <v>6</v>
       </c>
-      <c r="C36" s="605" t="s">
+      <c r="C36" s="604" t="s">
         <v>114</v>
       </c>
-      <c r="D36" s="606"/>
-      <c r="E36" s="606"/>
-      <c r="F36" s="606"/>
-      <c r="G36" s="607"/>
+      <c r="D36" s="605"/>
+      <c r="E36" s="605"/>
+      <c r="F36" s="605"/>
+      <c r="G36" s="606"/>
       <c r="H36" s="506" t="s">
         <v>184</v>
       </c>
@@ -10030,18 +10030,18 @@
       <c r="P36" s="437"/>
       <c r="W36" s="435"/>
     </row>
-    <row r="37" spans="1:23" ht="21.75" customHeight="1">
+    <row r="37" spans="1:23" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A37" s="504"/>
       <c r="B37" s="510">
         <v>7</v>
       </c>
-      <c r="C37" s="605" t="s">
+      <c r="C37" s="604" t="s">
         <v>294</v>
       </c>
-      <c r="D37" s="606"/>
-      <c r="E37" s="606"/>
-      <c r="F37" s="606"/>
-      <c r="G37" s="607"/>
+      <c r="D37" s="605"/>
+      <c r="E37" s="605"/>
+      <c r="F37" s="605"/>
+      <c r="G37" s="606"/>
       <c r="H37" s="506" t="s">
         <v>184</v>
       </c>
@@ -10054,18 +10054,18 @@
       <c r="O37" s="437"/>
       <c r="P37" s="437"/>
     </row>
-    <row r="38" spans="1:23" ht="21.75" customHeight="1">
+    <row r="38" spans="1:23" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A38" s="504"/>
       <c r="B38" s="510">
         <v>8</v>
       </c>
-      <c r="C38" s="605" t="s">
+      <c r="C38" s="604" t="s">
         <v>266</v>
       </c>
-      <c r="D38" s="606"/>
-      <c r="E38" s="606"/>
-      <c r="F38" s="606"/>
-      <c r="G38" s="607"/>
+      <c r="D38" s="605"/>
+      <c r="E38" s="605"/>
+      <c r="F38" s="605"/>
+      <c r="G38" s="606"/>
       <c r="H38" s="506" t="s">
         <v>184</v>
       </c>
@@ -10078,18 +10078,18 @@
       <c r="O38" s="440"/>
       <c r="P38" s="440"/>
     </row>
-    <row r="39" spans="1:23" ht="21.75" customHeight="1">
+    <row r="39" spans="1:23" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A39" s="504"/>
       <c r="B39" s="505">
         <v>9</v>
       </c>
-      <c r="C39" s="605" t="s">
+      <c r="C39" s="604" t="s">
         <v>267</v>
       </c>
-      <c r="D39" s="606"/>
-      <c r="E39" s="606"/>
-      <c r="F39" s="606"/>
-      <c r="G39" s="607"/>
+      <c r="D39" s="605"/>
+      <c r="E39" s="605"/>
+      <c r="F39" s="605"/>
+      <c r="G39" s="606"/>
       <c r="H39" s="506" t="s">
         <v>56</v>
       </c>
@@ -10101,7 +10101,7 @@
       <c r="N39" s="441"/>
       <c r="O39" s="201"/>
     </row>
-    <row r="40" spans="1:23" ht="6.75" customHeight="1">
+    <row r="40" spans="1:23" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A40" s="504"/>
       <c r="B40" s="498"/>
       <c r="C40" s="498"/>
@@ -10117,33 +10117,33 @@
       <c r="O40" s="201"/>
       <c r="W40" s="435"/>
     </row>
-    <row r="41" spans="1:23" ht="17.25" customHeight="1">
+    <row r="41" spans="1:23" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A41" s="504"/>
-      <c r="B41" s="615" t="s">
+      <c r="B41" s="603" t="s">
         <v>268</v>
       </c>
-      <c r="C41" s="615"/>
-      <c r="D41" s="615"/>
-      <c r="E41" s="615"/>
-      <c r="F41" s="615"/>
+      <c r="C41" s="603"/>
+      <c r="D41" s="603"/>
+      <c r="E41" s="603"/>
+      <c r="F41" s="603"/>
       <c r="G41" s="515"/>
-      <c r="H41" s="616" t="s">
+      <c r="H41" s="607" t="s">
         <v>269</v>
       </c>
-      <c r="I41" s="617"/>
-      <c r="J41" s="618"/>
-      <c r="K41" s="618"/>
-      <c r="L41" s="617"/>
+      <c r="I41" s="608"/>
+      <c r="J41" s="609"/>
+      <c r="K41" s="609"/>
+      <c r="L41" s="608"/>
       <c r="M41" s="87"/>
       <c r="W41" s="435"/>
     </row>
-    <row r="42" spans="1:23" ht="26.25" customHeight="1">
+    <row r="42" spans="1:23" ht="26.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A42" s="504"/>
-      <c r="B42" s="619" t="s">
+      <c r="B42" s="610" t="s">
         <v>270</v>
       </c>
-      <c r="C42" s="619"/>
-      <c r="D42" s="619"/>
+      <c r="C42" s="610"/>
+      <c r="D42" s="610"/>
       <c r="E42" s="516" t="s">
         <v>271</v>
       </c>
@@ -10151,23 +10151,23 @@
         <v>272</v>
       </c>
       <c r="G42" s="515"/>
-      <c r="H42" s="610" t="s">
+      <c r="H42" s="598" t="s">
         <v>273</v>
       </c>
-      <c r="I42" s="610"/>
-      <c r="J42" s="620"/>
-      <c r="K42" s="620"/>
-      <c r="L42" s="620"/>
+      <c r="I42" s="598"/>
+      <c r="J42" s="611"/>
+      <c r="K42" s="611"/>
+      <c r="L42" s="611"/>
       <c r="M42" s="87"/>
       <c r="W42" s="435"/>
     </row>
-    <row r="43" spans="1:23" ht="15" customHeight="1">
+    <row r="43" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A43" s="504"/>
-      <c r="B43" s="626" t="s">
+      <c r="B43" s="596" t="s">
         <v>274</v>
       </c>
-      <c r="C43" s="626"/>
-      <c r="D43" s="626"/>
+      <c r="C43" s="596"/>
+      <c r="D43" s="596"/>
       <c r="E43" s="517" t="s">
         <v>142</v>
       </c>
@@ -10175,23 +10175,23 @@
         <v>275</v>
       </c>
       <c r="G43" s="515"/>
-      <c r="H43" s="610" t="s">
+      <c r="H43" s="598" t="s">
         <v>276</v>
       </c>
-      <c r="I43" s="610"/>
-      <c r="J43" s="611"/>
-      <c r="K43" s="611"/>
-      <c r="L43" s="612"/>
+      <c r="I43" s="598"/>
+      <c r="J43" s="599"/>
+      <c r="K43" s="599"/>
+      <c r="L43" s="600"/>
       <c r="M43" s="87"/>
       <c r="W43" s="435"/>
     </row>
-    <row r="44" spans="1:23" ht="15" customHeight="1">
+    <row r="44" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A44" s="504"/>
-      <c r="B44" s="626" t="s">
+      <c r="B44" s="596" t="s">
         <v>277</v>
       </c>
-      <c r="C44" s="626"/>
-      <c r="D44" s="626"/>
+      <c r="C44" s="596"/>
+      <c r="D44" s="596"/>
       <c r="E44" s="517" t="s">
         <v>144</v>
       </c>
@@ -10199,20 +10199,20 @@
         <v>275</v>
       </c>
       <c r="G44" s="515"/>
-      <c r="H44" s="610"/>
-      <c r="I44" s="610"/>
-      <c r="J44" s="613"/>
-      <c r="K44" s="613"/>
-      <c r="L44" s="614"/>
+      <c r="H44" s="598"/>
+      <c r="I44" s="598"/>
+      <c r="J44" s="601"/>
+      <c r="K44" s="601"/>
+      <c r="L44" s="602"/>
       <c r="M44" s="87"/>
     </row>
-    <row r="45" spans="1:23" ht="15" customHeight="1">
+    <row r="45" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A45" s="504"/>
-      <c r="B45" s="622" t="s">
+      <c r="B45" s="592" t="s">
         <v>278</v>
       </c>
-      <c r="C45" s="622"/>
-      <c r="D45" s="622"/>
+      <c r="C45" s="592"/>
+      <c r="D45" s="592"/>
       <c r="E45" s="517" t="s">
         <v>146</v>
       </c>
@@ -10220,39 +10220,39 @@
         <v>275</v>
       </c>
       <c r="G45" s="515"/>
-      <c r="H45" s="610" t="s">
+      <c r="H45" s="598" t="s">
         <v>279</v>
       </c>
-      <c r="I45" s="610"/>
-      <c r="J45" s="611"/>
-      <c r="K45" s="611"/>
-      <c r="L45" s="612"/>
+      <c r="I45" s="598"/>
+      <c r="J45" s="599"/>
+      <c r="K45" s="599"/>
+      <c r="L45" s="600"/>
       <c r="M45" s="87"/>
     </row>
-    <row r="46" spans="1:23" ht="15" customHeight="1">
+    <row r="46" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A46" s="504"/>
-      <c r="B46" s="615" t="s">
+      <c r="B46" s="603" t="s">
         <v>280</v>
       </c>
-      <c r="C46" s="615"/>
-      <c r="D46" s="615"/>
-      <c r="E46" s="615"/>
-      <c r="F46" s="615"/>
+      <c r="C46" s="603"/>
+      <c r="D46" s="603"/>
+      <c r="E46" s="603"/>
+      <c r="F46" s="603"/>
       <c r="G46" s="515"/>
-      <c r="H46" s="610"/>
-      <c r="I46" s="610"/>
-      <c r="J46" s="613"/>
-      <c r="K46" s="613"/>
-      <c r="L46" s="614"/>
+      <c r="H46" s="598"/>
+      <c r="I46" s="598"/>
+      <c r="J46" s="601"/>
+      <c r="K46" s="601"/>
+      <c r="L46" s="602"/>
       <c r="M46" s="87"/>
     </row>
-    <row r="47" spans="1:23" ht="15" customHeight="1">
+    <row r="47" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A47" s="504"/>
-      <c r="B47" s="622" t="s">
+      <c r="B47" s="592" t="s">
         <v>281</v>
       </c>
-      <c r="C47" s="622"/>
-      <c r="D47" s="622"/>
+      <c r="C47" s="592"/>
+      <c r="D47" s="592"/>
       <c r="E47" s="517" t="s">
         <v>148</v>
       </c>
@@ -10260,20 +10260,20 @@
         <v>282</v>
       </c>
       <c r="G47" s="515"/>
-      <c r="H47" s="623"/>
-      <c r="I47" s="623"/>
-      <c r="J47" s="624"/>
-      <c r="K47" s="624"/>
-      <c r="L47" s="625"/>
+      <c r="H47" s="593"/>
+      <c r="I47" s="593"/>
+      <c r="J47" s="594"/>
+      <c r="K47" s="594"/>
+      <c r="L47" s="595"/>
       <c r="M47" s="87"/>
     </row>
-    <row r="48" spans="1:23" ht="15" customHeight="1">
+    <row r="48" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A48" s="504"/>
-      <c r="B48" s="626" t="s">
+      <c r="B48" s="596" t="s">
         <v>149</v>
       </c>
-      <c r="C48" s="626"/>
-      <c r="D48" s="626"/>
+      <c r="C48" s="596"/>
+      <c r="D48" s="596"/>
       <c r="E48" s="517" t="s">
         <v>146</v>
       </c>
@@ -10281,20 +10281,20 @@
         <v>282</v>
       </c>
       <c r="G48" s="515"/>
-      <c r="H48" s="623"/>
-      <c r="I48" s="623"/>
-      <c r="J48" s="624"/>
-      <c r="K48" s="624"/>
-      <c r="L48" s="625"/>
+      <c r="H48" s="593"/>
+      <c r="I48" s="593"/>
+      <c r="J48" s="594"/>
+      <c r="K48" s="594"/>
+      <c r="L48" s="595"/>
       <c r="M48" s="87"/>
     </row>
-    <row r="49" spans="1:13" ht="15" customHeight="1">
+    <row r="49" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A49" s="504"/>
-      <c r="B49" s="626" t="s">
+      <c r="B49" s="596" t="s">
         <v>151</v>
       </c>
-      <c r="C49" s="626"/>
-      <c r="D49" s="626"/>
+      <c r="C49" s="596"/>
+      <c r="D49" s="596"/>
       <c r="E49" s="517" t="s">
         <v>146</v>
       </c>
@@ -10309,7 +10309,7 @@
       <c r="L49" s="520"/>
       <c r="M49" s="87"/>
     </row>
-    <row r="50" spans="1:13" ht="18.75" customHeight="1">
+    <row r="50" spans="1:13" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A50" s="521"/>
       <c r="B50" s="522" t="s">
         <v>283</v>
@@ -10326,7 +10326,7 @@
       <c r="L50" s="528"/>
       <c r="M50" s="87"/>
     </row>
-    <row r="51" spans="1:13" ht="7.5" customHeight="1">
+    <row r="51" spans="1:13" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A51" s="529"/>
       <c r="B51" s="435"/>
       <c r="C51" s="435"/>
@@ -10341,7 +10341,7 @@
       <c r="L51" s="435"/>
       <c r="M51" s="87"/>
     </row>
-    <row r="52" spans="1:13" ht="22.5" customHeight="1">
+    <row r="52" spans="1:13" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A52" s="532" t="s">
         <v>98</v>
       </c>
@@ -10358,7 +10358,7 @@
       <c r="L52" s="526"/>
       <c r="M52" s="87"/>
     </row>
-    <row r="53" spans="1:13" ht="25.5" customHeight="1">
+    <row r="53" spans="1:13" ht="25.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A53" s="533"/>
       <c r="B53" s="527"/>
       <c r="C53" s="527"/>
@@ -10373,7 +10373,7 @@
       <c r="L53" s="526"/>
       <c r="M53" s="87"/>
     </row>
-    <row r="54" spans="1:13" ht="6.75" customHeight="1">
+    <row r="54" spans="1:13" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A54" s="534"/>
       <c r="B54" s="435"/>
       <c r="C54" s="435"/>
@@ -10388,7 +10388,7 @@
       <c r="L54" s="536"/>
       <c r="M54" s="87"/>
     </row>
-    <row r="55" spans="1:13" ht="30" customHeight="1">
+    <row r="55" spans="1:13" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A55" s="534"/>
       <c r="B55" s="435"/>
       <c r="C55" s="435"/>
@@ -10403,7 +10403,7 @@
       <c r="L55" s="435"/>
       <c r="M55" s="87"/>
     </row>
-    <row r="56" spans="1:13" ht="15.9" customHeight="1">
+    <row r="56" spans="1:13" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A56" s="537"/>
       <c r="B56" s="435"/>
       <c r="J56" s="435"/>
@@ -10411,21 +10411,21 @@
       <c r="L56" s="435"/>
       <c r="M56" s="87"/>
     </row>
-    <row r="57" spans="1:13" ht="4.5" customHeight="1">
-      <c r="B57" s="627"/>
-      <c r="C57" s="627"/>
-      <c r="D57" s="627"/>
-      <c r="E57" s="627"/>
-      <c r="F57" s="627"/>
-      <c r="G57" s="627"/>
-      <c r="H57" s="627"/>
-      <c r="I57" s="627"/>
-      <c r="J57" s="627"/>
+    <row r="57" spans="1:13" ht="4.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B57" s="597"/>
+      <c r="C57" s="597"/>
+      <c r="D57" s="597"/>
+      <c r="E57" s="597"/>
+      <c r="F57" s="597"/>
+      <c r="G57" s="597"/>
+      <c r="H57" s="597"/>
+      <c r="I57" s="597"/>
+      <c r="J57" s="597"/>
       <c r="K57" s="480"/>
       <c r="L57" s="435"/>
       <c r="M57" s="87"/>
     </row>
-    <row r="58" spans="1:13" ht="15.9" customHeight="1">
+    <row r="58" spans="1:13" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A58" s="538" t="s">
         <v>91</v>
       </c>
@@ -10442,7 +10442,7 @@
       <c r="L58" s="435"/>
       <c r="M58" s="87"/>
     </row>
-    <row r="59" spans="1:13" ht="15.9" customHeight="1">
+    <row r="59" spans="1:13" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A59" s="538" t="s">
         <v>295</v>
       </c>
@@ -10461,25 +10461,25 @@
       <c r="L59" s="435"/>
       <c r="M59" s="87"/>
     </row>
-    <row r="60" spans="1:13" ht="3.75" customHeight="1"/>
-    <row r="61" spans="1:13" ht="30.75" customHeight="1">
-      <c r="A61" s="621" t="s">
+    <row r="60" spans="1:13" ht="3.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="61" spans="1:13" ht="30.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A61" s="589" t="s">
         <v>285</v>
       </c>
-      <c r="B61" s="621"/>
-      <c r="C61" s="621"/>
-      <c r="D61" s="621"/>
-      <c r="E61" s="621"/>
-      <c r="F61" s="621"/>
-      <c r="G61" s="621"/>
-      <c r="H61" s="621"/>
-      <c r="I61" s="621"/>
-      <c r="J61" s="621"/>
-      <c r="K61" s="621"/>
-      <c r="L61" s="621"/>
-    </row>
-    <row r="62" spans="1:13" ht="15.9" customHeight="1"/>
-    <row r="63" spans="1:13" ht="15.9" customHeight="1"/>
+      <c r="B61" s="589"/>
+      <c r="C61" s="589"/>
+      <c r="D61" s="589"/>
+      <c r="E61" s="589"/>
+      <c r="F61" s="589"/>
+      <c r="G61" s="589"/>
+      <c r="H61" s="589"/>
+      <c r="I61" s="589"/>
+      <c r="J61" s="589"/>
+      <c r="K61" s="589"/>
+      <c r="L61" s="589"/>
+    </row>
+    <row r="62" spans="1:13" ht="15.95" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="63" spans="1:13" ht="15.95" customHeight="1" x14ac:dyDescent="0.2"/>
   </sheetData>
   <sheetProtection algorithmName="SHA-512" hashValue="zFaKPAn6ViOpya0rqSfRP+lf5nP0Stsd4GeHYr5E3M4pf5abxDHp7CyitZu3QfPbBPFWYk0mv07jVBjbhu2ckg==" saltValue="VTj2SwRAYFQHMWaCbVSW8A==" spinCount="100000" sheet="1" objects="1" scenarios="1"/>
   <protectedRanges>
@@ -10487,6 +10487,40 @@
     <protectedRange sqref="C57" name="Rango3_3_1_1_1_1_1_2_1"/>
   </protectedRanges>
   <mergeCells count="50">
+    <mergeCell ref="A24:D24"/>
+    <mergeCell ref="A7:L7"/>
+    <mergeCell ref="A8:L8"/>
+    <mergeCell ref="A14:L14"/>
+    <mergeCell ref="A15:L15"/>
+    <mergeCell ref="A17:I17"/>
+    <mergeCell ref="A25:D25"/>
+    <mergeCell ref="E25:F25"/>
+    <mergeCell ref="H25:J25"/>
+    <mergeCell ref="A26:D26"/>
+    <mergeCell ref="E26:F26"/>
+    <mergeCell ref="H26:I26"/>
+    <mergeCell ref="C37:G37"/>
+    <mergeCell ref="A27:D27"/>
+    <mergeCell ref="E27:F27"/>
+    <mergeCell ref="B30:G30"/>
+    <mergeCell ref="J30:K30"/>
+    <mergeCell ref="C31:G31"/>
+    <mergeCell ref="C32:G32"/>
+    <mergeCell ref="C33:G33"/>
+    <mergeCell ref="C34:G34"/>
+    <mergeCell ref="C35:G35"/>
+    <mergeCell ref="C36:G36"/>
+    <mergeCell ref="H45:I46"/>
+    <mergeCell ref="J45:L46"/>
+    <mergeCell ref="B46:F46"/>
+    <mergeCell ref="C38:G38"/>
+    <mergeCell ref="C39:G39"/>
+    <mergeCell ref="B41:F41"/>
+    <mergeCell ref="H41:I41"/>
+    <mergeCell ref="J41:L41"/>
+    <mergeCell ref="B42:D42"/>
+    <mergeCell ref="H42:I42"/>
+    <mergeCell ref="J42:L42"/>
     <mergeCell ref="A61:L61"/>
     <mergeCell ref="A28:D28"/>
     <mergeCell ref="E28:F28"/>
@@ -10503,40 +10537,6 @@
     <mergeCell ref="J43:L44"/>
     <mergeCell ref="B44:D44"/>
     <mergeCell ref="B45:D45"/>
-    <mergeCell ref="H45:I46"/>
-    <mergeCell ref="J45:L46"/>
-    <mergeCell ref="B46:F46"/>
-    <mergeCell ref="C38:G38"/>
-    <mergeCell ref="C39:G39"/>
-    <mergeCell ref="B41:F41"/>
-    <mergeCell ref="H41:I41"/>
-    <mergeCell ref="J41:L41"/>
-    <mergeCell ref="B42:D42"/>
-    <mergeCell ref="H42:I42"/>
-    <mergeCell ref="J42:L42"/>
-    <mergeCell ref="C37:G37"/>
-    <mergeCell ref="A27:D27"/>
-    <mergeCell ref="E27:F27"/>
-    <mergeCell ref="B30:G30"/>
-    <mergeCell ref="J30:K30"/>
-    <mergeCell ref="C31:G31"/>
-    <mergeCell ref="C32:G32"/>
-    <mergeCell ref="C33:G33"/>
-    <mergeCell ref="C34:G34"/>
-    <mergeCell ref="C35:G35"/>
-    <mergeCell ref="C36:G36"/>
-    <mergeCell ref="A25:D25"/>
-    <mergeCell ref="E25:F25"/>
-    <mergeCell ref="H25:J25"/>
-    <mergeCell ref="A26:D26"/>
-    <mergeCell ref="E26:F26"/>
-    <mergeCell ref="H26:I26"/>
-    <mergeCell ref="A24:D24"/>
-    <mergeCell ref="A7:L7"/>
-    <mergeCell ref="A8:L8"/>
-    <mergeCell ref="A14:L14"/>
-    <mergeCell ref="A15:L15"/>
-    <mergeCell ref="A17:I17"/>
   </mergeCells>
   <conditionalFormatting sqref="A18:A22">
     <cfRule type="cellIs" priority="1" stopIfTrue="1" operator="between">
@@ -10553,27 +10553,27 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:Q94"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="10.33203125" defaultRowHeight="13.8"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="10.28515625" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="10.44140625" style="316" customWidth="1"/>
+    <col min="1" max="1" width="10.42578125" style="316" customWidth="1"/>
     <col min="2" max="2" width="3" style="316" customWidth="1"/>
-    <col min="3" max="3" width="4.44140625" style="316" customWidth="1"/>
-    <col min="4" max="4" width="1.5546875" style="316" customWidth="1"/>
-    <col min="5" max="5" width="5.44140625" style="316" customWidth="1"/>
-    <col min="6" max="8" width="9.6640625" style="316" customWidth="1"/>
-    <col min="9" max="9" width="4.5546875" style="316" customWidth="1"/>
-    <col min="10" max="10" width="6.44140625" style="316" customWidth="1"/>
-    <col min="11" max="11" width="11.6640625" style="316" customWidth="1"/>
+    <col min="3" max="3" width="4.42578125" style="316" customWidth="1"/>
+    <col min="4" max="4" width="1.5703125" style="316" customWidth="1"/>
+    <col min="5" max="5" width="5.42578125" style="316" customWidth="1"/>
+    <col min="6" max="8" width="9.7109375" style="316" customWidth="1"/>
+    <col min="9" max="9" width="4.5703125" style="316" customWidth="1"/>
+    <col min="10" max="10" width="6.42578125" style="316" customWidth="1"/>
+    <col min="11" max="11" width="11.7109375" style="316" customWidth="1"/>
     <col min="12" max="12" width="10" style="316" customWidth="1"/>
-    <col min="13" max="13" width="1.33203125" style="316" customWidth="1"/>
-    <col min="14" max="14" width="13.5546875" style="316" customWidth="1"/>
-    <col min="15" max="15" width="6.44140625" style="316" customWidth="1"/>
+    <col min="13" max="13" width="1.28515625" style="316" customWidth="1"/>
+    <col min="14" max="14" width="13.5703125" style="316" customWidth="1"/>
+    <col min="15" max="15" width="6.42578125" style="316" customWidth="1"/>
     <col min="16" max="16" width="1" style="316" customWidth="1"/>
-    <col min="17" max="17" width="6.44140625" style="316" customWidth="1"/>
-    <col min="18" max="16384" width="10.33203125" style="316"/>
+    <col min="17" max="17" width="6.42578125" style="316" customWidth="1"/>
+    <col min="18" max="16384" width="10.28515625" style="316"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17" ht="28.5" customHeight="1">
+    <row r="1" spans="1:17" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="309"/>
       <c r="B1" s="309"/>
       <c r="C1" s="309"/>
@@ -10589,62 +10589,62 @@
       <c r="M1" s="309"/>
       <c r="N1" s="309"/>
     </row>
-    <row r="2" spans="1:17" ht="15.9" customHeight="1">
-      <c r="A2" s="544" t="s">
+    <row r="2" spans="1:17" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2" s="567" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="544"/>
-      <c r="C2" s="544"/>
-      <c r="D2" s="544"/>
-      <c r="E2" s="544"/>
-      <c r="F2" s="544"/>
-      <c r="G2" s="544"/>
-      <c r="H2" s="544"/>
-      <c r="I2" s="544"/>
-      <c r="J2" s="544"/>
-      <c r="K2" s="544"/>
-      <c r="L2" s="544"/>
-      <c r="M2" s="544"/>
-      <c r="N2" s="544"/>
-    </row>
-    <row r="3" spans="1:17" ht="15.9" customHeight="1">
-      <c r="A3" s="635">
+      <c r="B2" s="567"/>
+      <c r="C2" s="567"/>
+      <c r="D2" s="567"/>
+      <c r="E2" s="567"/>
+      <c r="F2" s="567"/>
+      <c r="G2" s="567"/>
+      <c r="H2" s="567"/>
+      <c r="I2" s="567"/>
+      <c r="J2" s="567"/>
+      <c r="K2" s="567"/>
+      <c r="L2" s="567"/>
+      <c r="M2" s="567"/>
+      <c r="N2" s="567"/>
+    </row>
+    <row r="3" spans="1:17" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A3" s="628">
         <v>0</v>
       </c>
-      <c r="B3" s="635"/>
-      <c r="C3" s="635"/>
-      <c r="D3" s="635"/>
-      <c r="E3" s="635"/>
-      <c r="F3" s="635"/>
-      <c r="G3" s="635"/>
-      <c r="H3" s="635"/>
-      <c r="I3" s="635"/>
-      <c r="J3" s="635"/>
-      <c r="K3" s="635"/>
-      <c r="L3" s="635"/>
-      <c r="M3" s="635"/>
-      <c r="N3" s="635"/>
-    </row>
-    <row r="4" spans="1:17" ht="15.9" customHeight="1"/>
-    <row r="5" spans="1:17" ht="15" customHeight="1">
+      <c r="B3" s="628"/>
+      <c r="C3" s="628"/>
+      <c r="D3" s="628"/>
+      <c r="E3" s="628"/>
+      <c r="F3" s="628"/>
+      <c r="G3" s="628"/>
+      <c r="H3" s="628"/>
+      <c r="I3" s="628"/>
+      <c r="J3" s="628"/>
+      <c r="K3" s="628"/>
+      <c r="L3" s="628"/>
+      <c r="M3" s="628"/>
+      <c r="N3" s="628"/>
+    </row>
+    <row r="4" spans="1:17" ht="15.95" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="5" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="297" t="s">
         <v>1</v>
       </c>
       <c r="B5" s="177" t="s">
         <v>2</v>
       </c>
-      <c r="C5" s="647">
+      <c r="C5" s="645">
         <f>+Resumen!P2</f>
         <v>0</v>
       </c>
-      <c r="D5" s="647"/>
-      <c r="E5" s="647"/>
-      <c r="F5" s="647"/>
-      <c r="G5" s="647"/>
-      <c r="H5" s="647"/>
-      <c r="I5" s="647"/>
-      <c r="J5" s="647"/>
-      <c r="K5" s="647"/>
+      <c r="D5" s="645"/>
+      <c r="E5" s="645"/>
+      <c r="F5" s="645"/>
+      <c r="G5" s="645"/>
+      <c r="H5" s="645"/>
+      <c r="I5" s="645"/>
+      <c r="J5" s="645"/>
+      <c r="K5" s="645"/>
       <c r="L5" s="27" t="s">
         <v>6</v>
       </c>
@@ -10656,25 +10656,25 @@
       </c>
       <c r="Q5" s="317"/>
     </row>
-    <row r="6" spans="1:17" ht="21" customHeight="1">
+    <row r="6" spans="1:17" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="297" t="s">
         <v>100</v>
       </c>
       <c r="B6" s="177" t="s">
         <v>2</v>
       </c>
-      <c r="C6" s="628">
+      <c r="C6" s="647">
         <f>+Resumen!P3</f>
         <v>0</v>
       </c>
-      <c r="D6" s="628"/>
-      <c r="E6" s="628"/>
-      <c r="F6" s="628"/>
-      <c r="G6" s="628"/>
-      <c r="H6" s="628"/>
-      <c r="I6" s="628"/>
-      <c r="J6" s="628"/>
-      <c r="K6" s="628"/>
+      <c r="D6" s="647"/>
+      <c r="E6" s="647"/>
+      <c r="F6" s="647"/>
+      <c r="G6" s="647"/>
+      <c r="H6" s="647"/>
+      <c r="I6" s="647"/>
+      <c r="J6" s="647"/>
+      <c r="K6" s="647"/>
       <c r="L6" s="458" t="s">
         <v>233</v>
       </c>
@@ -10689,25 +10689,25 @@
       <c r="P6" s="317"/>
       <c r="Q6" s="317"/>
     </row>
-    <row r="7" spans="1:17" ht="15" customHeight="1">
+    <row r="7" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="297" t="s">
         <v>8</v>
       </c>
       <c r="B7" s="177" t="s">
         <v>2</v>
       </c>
-      <c r="C7" s="647">
+      <c r="C7" s="645">
         <f>+Resumen!P4</f>
         <v>0</v>
       </c>
-      <c r="D7" s="647"/>
-      <c r="E7" s="647"/>
-      <c r="F7" s="647"/>
-      <c r="G7" s="647"/>
-      <c r="H7" s="647"/>
-      <c r="I7" s="647"/>
-      <c r="J7" s="647"/>
-      <c r="K7" s="647"/>
+      <c r="D7" s="645"/>
+      <c r="E7" s="645"/>
+      <c r="F7" s="645"/>
+      <c r="G7" s="645"/>
+      <c r="H7" s="645"/>
+      <c r="I7" s="645"/>
+      <c r="J7" s="645"/>
+      <c r="K7" s="645"/>
       <c r="L7" s="458" t="s">
         <v>297</v>
       </c>
@@ -10722,25 +10722,25 @@
       <c r="P7" s="317"/>
       <c r="Q7" s="317"/>
     </row>
-    <row r="8" spans="1:17" ht="17.399999999999999" customHeight="1">
+    <row r="8" spans="1:17" ht="17.45" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="297" t="s">
         <v>11</v>
       </c>
       <c r="B8" s="177" t="s">
         <v>2</v>
       </c>
-      <c r="C8" s="628">
+      <c r="C8" s="647">
         <f>+Resumen!P5</f>
         <v>0</v>
       </c>
-      <c r="D8" s="628"/>
-      <c r="E8" s="628"/>
-      <c r="F8" s="628"/>
-      <c r="G8" s="628"/>
-      <c r="H8" s="628"/>
-      <c r="I8" s="628"/>
-      <c r="J8" s="628"/>
-      <c r="K8" s="628"/>
+      <c r="D8" s="647"/>
+      <c r="E8" s="647"/>
+      <c r="F8" s="647"/>
+      <c r="G8" s="647"/>
+      <c r="H8" s="647"/>
+      <c r="I8" s="647"/>
+      <c r="J8" s="647"/>
+      <c r="K8" s="647"/>
       <c r="L8" s="458" t="s">
         <v>101</v>
       </c>
@@ -10748,14 +10748,14 @@
         <v>2</v>
       </c>
       <c r="N8" s="361">
-        <f>+Resumen!P8</f>
+        <f>+Resumen!P9</f>
         <v>0</v>
       </c>
       <c r="O8" s="317"/>
       <c r="P8" s="317"/>
       <c r="Q8" s="317"/>
     </row>
-    <row r="9" spans="1:17" ht="14.25" customHeight="1">
+    <row r="9" spans="1:17" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="291" t="s">
         <v>14</v>
       </c>
@@ -10776,49 +10776,49 @@
       <c r="P9" s="317"/>
       <c r="Q9" s="317"/>
     </row>
-    <row r="10" spans="1:17">
-      <c r="A10" s="636" t="s">
+    <row r="10" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A10" s="629" t="s">
         <v>102</v>
       </c>
-      <c r="B10" s="637"/>
-      <c r="C10" s="637"/>
-      <c r="D10" s="637"/>
-      <c r="E10" s="637"/>
-      <c r="F10" s="637"/>
-      <c r="G10" s="637"/>
-      <c r="H10" s="637"/>
-      <c r="I10" s="637"/>
-      <c r="J10" s="637"/>
-      <c r="K10" s="637"/>
-      <c r="L10" s="637"/>
-      <c r="M10" s="637"/>
-      <c r="N10" s="638"/>
+      <c r="B10" s="630"/>
+      <c r="C10" s="630"/>
+      <c r="D10" s="630"/>
+      <c r="E10" s="630"/>
+      <c r="F10" s="630"/>
+      <c r="G10" s="630"/>
+      <c r="H10" s="630"/>
+      <c r="I10" s="630"/>
+      <c r="J10" s="630"/>
+      <c r="K10" s="630"/>
+      <c r="L10" s="630"/>
+      <c r="M10" s="630"/>
+      <c r="N10" s="631"/>
       <c r="O10" s="317"/>
       <c r="P10" s="317"/>
       <c r="Q10" s="317"/>
     </row>
-    <row r="11" spans="1:17" ht="12" customHeight="1">
-      <c r="A11" s="639" t="s">
+    <row r="11" spans="1:17" ht="12" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A11" s="632" t="s">
         <v>103</v>
       </c>
-      <c r="B11" s="640"/>
-      <c r="C11" s="640"/>
-      <c r="D11" s="640"/>
-      <c r="E11" s="640"/>
-      <c r="F11" s="640"/>
-      <c r="G11" s="640"/>
-      <c r="H11" s="640"/>
-      <c r="I11" s="640"/>
-      <c r="J11" s="640"/>
-      <c r="K11" s="640"/>
-      <c r="L11" s="640"/>
-      <c r="M11" s="640"/>
-      <c r="N11" s="641"/>
+      <c r="B11" s="633"/>
+      <c r="C11" s="633"/>
+      <c r="D11" s="633"/>
+      <c r="E11" s="633"/>
+      <c r="F11" s="633"/>
+      <c r="G11" s="633"/>
+      <c r="H11" s="633"/>
+      <c r="I11" s="633"/>
+      <c r="J11" s="633"/>
+      <c r="K11" s="633"/>
+      <c r="L11" s="633"/>
+      <c r="M11" s="633"/>
+      <c r="N11" s="634"/>
       <c r="O11" s="317"/>
       <c r="P11" s="317"/>
       <c r="Q11" s="317"/>
     </row>
-    <row r="12" spans="1:17" ht="6" customHeight="1">
+    <row r="12" spans="1:17" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="189"/>
       <c r="B12" s="190"/>
       <c r="C12" s="190"/>
@@ -10837,7 +10837,7 @@
       <c r="P12" s="317"/>
       <c r="Q12" s="317"/>
     </row>
-    <row r="13" spans="1:17" ht="15" customHeight="1">
+    <row r="13" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" s="362" t="s">
         <v>17</v>
       </c>
@@ -10856,7 +10856,7 @@
       <c r="N13" s="182"/>
       <c r="Q13" s="317"/>
     </row>
-    <row r="14" spans="1:17" ht="15" customHeight="1">
+    <row r="14" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" s="40" t="s">
         <v>104</v>
       </c>
@@ -10886,7 +10886,7 @@
       </c>
       <c r="Q14" s="317"/>
     </row>
-    <row r="15" spans="1:17" ht="15" customHeight="1">
+    <row r="15" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" s="40" t="s">
         <v>25</v>
       </c>
@@ -10916,7 +10916,7 @@
       </c>
       <c r="Q15" s="317"/>
     </row>
-    <row r="16" spans="1:17" ht="15" customHeight="1">
+    <row r="16" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A16" s="40" t="s">
         <v>232</v>
       </c>
@@ -10949,7 +10949,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:17" ht="15" customHeight="1">
+    <row r="17" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A17" s="155" t="s">
         <v>33</v>
       </c>
@@ -10979,37 +10979,37 @@
       </c>
       <c r="Q17" s="317"/>
     </row>
-    <row r="18" spans="1:17" ht="6.75" customHeight="1">
+    <row r="18" spans="1:17" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A18" s="310"/>
       <c r="B18" s="310"/>
       <c r="C18" s="310"/>
-      <c r="D18" s="644"/>
-      <c r="E18" s="644"/>
+      <c r="D18" s="638"/>
+      <c r="E18" s="638"/>
       <c r="F18" s="310"/>
       <c r="G18" s="310"/>
       <c r="H18" s="310"/>
       <c r="I18" s="310"/>
       <c r="J18" s="310"/>
       <c r="K18" s="310"/>
-      <c r="L18" s="644"/>
-      <c r="M18" s="644"/>
+      <c r="L18" s="638"/>
+      <c r="M18" s="638"/>
       <c r="N18" s="310"/>
       <c r="O18" s="317"/>
       <c r="P18" s="317"/>
       <c r="Q18" s="317"/>
     </row>
-    <row r="19" spans="1:17" ht="18" customHeight="1">
+    <row r="19" spans="1:17" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A19" s="310"/>
       <c r="B19" s="310"/>
       <c r="C19" s="310"/>
-      <c r="D19" s="645" t="s">
+      <c r="D19" s="639" t="s">
         <v>108</v>
       </c>
-      <c r="E19" s="645"/>
-      <c r="F19" s="645"/>
-      <c r="G19" s="645"/>
-      <c r="H19" s="645"/>
-      <c r="I19" s="645"/>
+      <c r="E19" s="639"/>
+      <c r="F19" s="639"/>
+      <c r="G19" s="639"/>
+      <c r="H19" s="639"/>
+      <c r="I19" s="639"/>
       <c r="J19" s="311" t="s">
         <v>109</v>
       </c>
@@ -11023,7 +11023,7 @@
       <c r="P19" s="317"/>
       <c r="Q19" s="317"/>
     </row>
-    <row r="20" spans="1:17" ht="17.25" customHeight="1">
+    <row r="20" spans="1:17" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A20" s="188"/>
       <c r="B20" s="188"/>
       <c r="C20" s="320"/>
@@ -11042,14 +11042,14 @@
         <f>+'Datos ensayo'!G17</f>
         <v>1</v>
       </c>
-      <c r="L20" s="642"/>
-      <c r="M20" s="642"/>
+      <c r="L20" s="636"/>
+      <c r="M20" s="636"/>
       <c r="N20" s="312"/>
       <c r="O20" s="317"/>
       <c r="P20" s="317"/>
       <c r="Q20" s="317"/>
     </row>
-    <row r="21" spans="1:17" ht="17.25" customHeight="1">
+    <row r="21" spans="1:17" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A21" s="188"/>
       <c r="B21" s="188"/>
       <c r="C21" s="320"/>
@@ -11068,14 +11068,14 @@
         <f>+'Datos ensayo'!G18</f>
         <v>0</v>
       </c>
-      <c r="L21" s="642"/>
-      <c r="M21" s="642"/>
+      <c r="L21" s="636"/>
+      <c r="M21" s="636"/>
       <c r="N21" s="312"/>
       <c r="O21" s="317"/>
       <c r="P21" s="317"/>
       <c r="Q21" s="317"/>
     </row>
-    <row r="22" spans="1:17" ht="17.25" customHeight="1">
+    <row r="22" spans="1:17" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A22" s="188"/>
       <c r="B22" s="188"/>
       <c r="C22" s="320"/>
@@ -11094,14 +11094,14 @@
         <f>+'Datos ensayo'!H19</f>
         <v>0,00</v>
       </c>
-      <c r="L22" s="643"/>
-      <c r="M22" s="643"/>
+      <c r="L22" s="637"/>
+      <c r="M22" s="637"/>
       <c r="N22" s="313"/>
       <c r="O22" s="323"/>
       <c r="P22" s="323"/>
       <c r="Q22" s="317"/>
     </row>
-    <row r="23" spans="1:17" ht="17.25" customHeight="1">
+    <row r="23" spans="1:17" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A23" s="188"/>
       <c r="B23" s="188"/>
       <c r="C23" s="320"/>
@@ -11127,7 +11127,7 @@
       <c r="P23" s="317"/>
       <c r="Q23" s="317"/>
     </row>
-    <row r="24" spans="1:17" ht="17.25" customHeight="1">
+    <row r="24" spans="1:17" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A24" s="188"/>
       <c r="B24" s="188"/>
       <c r="C24" s="320"/>
@@ -11153,7 +11153,7 @@
       <c r="P24" s="317"/>
       <c r="Q24" s="317"/>
     </row>
-    <row r="25" spans="1:17" ht="17.25" customHeight="1">
+    <row r="25" spans="1:17" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A25" s="188"/>
       <c r="B25" s="188"/>
       <c r="C25" s="320"/>
@@ -11179,7 +11179,7 @@
       <c r="P25" s="317"/>
       <c r="Q25" s="317"/>
     </row>
-    <row r="26" spans="1:17" ht="17.25" customHeight="1">
+    <row r="26" spans="1:17" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A26" s="13"/>
       <c r="B26" s="13"/>
       <c r="C26" s="314"/>
@@ -11205,7 +11205,7 @@
       <c r="P26" s="317"/>
       <c r="Q26" s="317"/>
     </row>
-    <row r="27" spans="1:17" ht="17.25" customHeight="1">
+    <row r="27" spans="1:17" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A27" s="188"/>
       <c r="B27" s="188"/>
       <c r="C27" s="320"/>
@@ -11231,7 +11231,7 @@
       <c r="P27" s="317"/>
       <c r="Q27" s="317"/>
     </row>
-    <row r="28" spans="1:17" ht="4.5" customHeight="1">
+    <row r="28" spans="1:17" ht="4.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A28" s="188"/>
       <c r="B28" s="188"/>
       <c r="C28" s="188"/>
@@ -11250,7 +11250,7 @@
       <c r="P28" s="317"/>
       <c r="Q28" s="317"/>
     </row>
-    <row r="29" spans="1:17" ht="15.9" customHeight="1">
+    <row r="29" spans="1:17" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A29" s="170" t="s">
         <v>118</v>
       </c>
@@ -11271,7 +11271,7 @@
       <c r="P29" s="317"/>
       <c r="Q29" s="317"/>
     </row>
-    <row r="30" spans="1:17" ht="15.9" customHeight="1">
+    <row r="30" spans="1:17" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A30" s="356" t="s">
         <v>119</v>
       </c>
@@ -11295,7 +11295,7 @@
       <c r="P30" s="317"/>
       <c r="Q30" s="317"/>
     </row>
-    <row r="31" spans="1:17" ht="15.9" customHeight="1">
+    <row r="31" spans="1:17" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A31" s="356" t="s">
         <v>120</v>
       </c>
@@ -11319,7 +11319,7 @@
       <c r="P31" s="317"/>
       <c r="Q31" s="317"/>
     </row>
-    <row r="32" spans="1:17" ht="15.9" customHeight="1">
+    <row r="32" spans="1:17" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A32" s="356" t="s">
         <v>121</v>
       </c>
@@ -11343,7 +11343,7 @@
       <c r="P32" s="317"/>
       <c r="Q32" s="317"/>
     </row>
-    <row r="33" spans="1:17" ht="15.9" customHeight="1">
+    <row r="33" spans="1:17" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A33" s="356" t="s">
         <v>122</v>
       </c>
@@ -11367,7 +11367,7 @@
       <c r="P33" s="317"/>
       <c r="Q33" s="317"/>
     </row>
-    <row r="34" spans="1:17" ht="14.25" customHeight="1">
+    <row r="34" spans="1:17" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A34" s="356" t="s">
         <v>123</v>
       </c>
@@ -11391,7 +11391,7 @@
       <c r="P34" s="317"/>
       <c r="Q34" s="317"/>
     </row>
-    <row r="35" spans="1:17" ht="5.25" customHeight="1">
+    <row r="35" spans="1:17" ht="5.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A35" s="356"/>
       <c r="B35" s="193"/>
       <c r="C35" s="193"/>
@@ -11410,7 +11410,7 @@
       <c r="P35" s="317"/>
       <c r="Q35" s="317"/>
     </row>
-    <row r="36" spans="1:17" ht="14.25" customHeight="1">
+    <row r="36" spans="1:17" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A36" s="170" t="s">
         <v>228</v>
       </c>
@@ -11431,7 +11431,7 @@
       <c r="P36" s="317"/>
       <c r="Q36" s="317"/>
     </row>
-    <row r="37" spans="1:17" ht="14.25" customHeight="1">
+    <row r="37" spans="1:17" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A37" s="357" t="s">
         <v>230</v>
       </c>
@@ -11444,18 +11444,18 @@
       <c r="H37" s="193"/>
       <c r="I37" s="195"/>
       <c r="J37" s="195"/>
-      <c r="K37" s="648">
+      <c r="K37" s="646">
         <f>+Resumen!E27</f>
         <v>0</v>
       </c>
-      <c r="L37" s="648"/>
+      <c r="L37" s="646"/>
       <c r="M37" s="159"/>
       <c r="N37" s="159"/>
       <c r="O37" s="317"/>
       <c r="P37" s="317"/>
       <c r="Q37" s="317"/>
     </row>
-    <row r="38" spans="1:17" ht="14.25" customHeight="1">
+    <row r="38" spans="1:17" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A38" s="357" t="s">
         <v>229</v>
       </c>
@@ -11468,25 +11468,25 @@
       <c r="H38" s="193"/>
       <c r="I38" s="195"/>
       <c r="J38" s="195"/>
-      <c r="K38" s="646">
+      <c r="K38" s="640">
         <f>+Resumen!E28</f>
         <v>0</v>
       </c>
-      <c r="L38" s="646"/>
+      <c r="L38" s="640"/>
       <c r="M38" s="159"/>
       <c r="N38" s="159"/>
       <c r="O38" s="317"/>
       <c r="P38" s="317"/>
       <c r="Q38" s="317"/>
     </row>
-    <row r="39" spans="1:17" ht="6" customHeight="1">
+    <row r="39" spans="1:17" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="M39" s="159"/>
       <c r="N39" s="159"/>
       <c r="O39" s="317"/>
       <c r="P39" s="317"/>
       <c r="Q39" s="317"/>
     </row>
-    <row r="40" spans="1:17" ht="10.5" customHeight="1">
+    <row r="40" spans="1:17" ht="10.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A40" s="170" t="s">
         <v>124</v>
       </c>
@@ -11507,112 +11507,112 @@
       <c r="P40" s="317"/>
       <c r="Q40" s="317"/>
     </row>
-    <row r="41" spans="1:17" ht="15" customHeight="1">
-      <c r="A41" s="629" t="s">
+    <row r="41" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A41" s="648" t="s">
         <v>312</v>
       </c>
-      <c r="B41" s="629"/>
-      <c r="C41" s="629"/>
-      <c r="D41" s="629"/>
-      <c r="E41" s="629"/>
-      <c r="F41" s="629"/>
-      <c r="G41" s="629"/>
-      <c r="H41" s="629"/>
-      <c r="I41" s="629"/>
-      <c r="J41" s="629"/>
-      <c r="K41" s="629"/>
-      <c r="L41" s="629"/>
-      <c r="M41" s="629"/>
-      <c r="N41" s="629"/>
+      <c r="B41" s="648"/>
+      <c r="C41" s="648"/>
+      <c r="D41" s="648"/>
+      <c r="E41" s="648"/>
+      <c r="F41" s="648"/>
+      <c r="G41" s="648"/>
+      <c r="H41" s="648"/>
+      <c r="I41" s="648"/>
+      <c r="J41" s="648"/>
+      <c r="K41" s="648"/>
+      <c r="L41" s="648"/>
+      <c r="M41" s="648"/>
+      <c r="N41" s="648"/>
       <c r="O41" s="317"/>
       <c r="P41" s="317"/>
       <c r="Q41" s="317"/>
     </row>
-    <row r="42" spans="1:17" ht="33" customHeight="1">
-      <c r="A42" s="632" t="s">
+    <row r="42" spans="1:17" ht="33" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A42" s="635" t="s">
         <v>313</v>
       </c>
-      <c r="B42" s="632"/>
-      <c r="C42" s="632"/>
-      <c r="D42" s="632"/>
-      <c r="E42" s="632"/>
-      <c r="F42" s="632"/>
-      <c r="G42" s="632"/>
-      <c r="H42" s="632"/>
-      <c r="I42" s="632"/>
-      <c r="J42" s="632"/>
-      <c r="K42" s="632"/>
-      <c r="L42" s="632"/>
-      <c r="M42" s="632"/>
-      <c r="N42" s="632"/>
+      <c r="B42" s="635"/>
+      <c r="C42" s="635"/>
+      <c r="D42" s="635"/>
+      <c r="E42" s="635"/>
+      <c r="F42" s="635"/>
+      <c r="G42" s="635"/>
+      <c r="H42" s="635"/>
+      <c r="I42" s="635"/>
+      <c r="J42" s="635"/>
+      <c r="K42" s="635"/>
+      <c r="L42" s="635"/>
+      <c r="M42" s="635"/>
+      <c r="N42" s="635"/>
       <c r="O42" s="317"/>
       <c r="P42" s="317"/>
       <c r="Q42" s="317"/>
     </row>
-    <row r="43" spans="1:17" ht="18.600000000000001" customHeight="1">
-      <c r="A43" s="632" t="s">
+    <row r="43" spans="1:17" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A43" s="635" t="s">
         <v>314</v>
       </c>
-      <c r="B43" s="632"/>
-      <c r="C43" s="632"/>
-      <c r="D43" s="632"/>
-      <c r="E43" s="632"/>
-      <c r="F43" s="632"/>
-      <c r="G43" s="632"/>
-      <c r="H43" s="632"/>
-      <c r="I43" s="632"/>
-      <c r="J43" s="632"/>
-      <c r="K43" s="632"/>
-      <c r="L43" s="632"/>
-      <c r="M43" s="632"/>
-      <c r="N43" s="632"/>
+      <c r="B43" s="635"/>
+      <c r="C43" s="635"/>
+      <c r="D43" s="635"/>
+      <c r="E43" s="635"/>
+      <c r="F43" s="635"/>
+      <c r="G43" s="635"/>
+      <c r="H43" s="635"/>
+      <c r="I43" s="635"/>
+      <c r="J43" s="635"/>
+      <c r="K43" s="635"/>
+      <c r="L43" s="635"/>
+      <c r="M43" s="635"/>
+      <c r="N43" s="635"/>
       <c r="O43" s="317"/>
       <c r="P43" s="317"/>
       <c r="Q43" s="317"/>
     </row>
-    <row r="44" spans="1:17" ht="23.4" customHeight="1">
-      <c r="A44" s="632" t="s">
+    <row r="44" spans="1:17" ht="23.45" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A44" s="635" t="s">
         <v>315</v>
       </c>
-      <c r="B44" s="632"/>
-      <c r="C44" s="632"/>
-      <c r="D44" s="632"/>
-      <c r="E44" s="632"/>
-      <c r="F44" s="632"/>
-      <c r="G44" s="632"/>
-      <c r="H44" s="632"/>
-      <c r="I44" s="632"/>
-      <c r="J44" s="632"/>
-      <c r="K44" s="632"/>
-      <c r="L44" s="632"/>
-      <c r="M44" s="632"/>
-      <c r="N44" s="632"/>
+      <c r="B44" s="635"/>
+      <c r="C44" s="635"/>
+      <c r="D44" s="635"/>
+      <c r="E44" s="635"/>
+      <c r="F44" s="635"/>
+      <c r="G44" s="635"/>
+      <c r="H44" s="635"/>
+      <c r="I44" s="635"/>
+      <c r="J44" s="635"/>
+      <c r="K44" s="635"/>
+      <c r="L44" s="635"/>
+      <c r="M44" s="635"/>
+      <c r="N44" s="635"/>
       <c r="O44" s="317"/>
       <c r="P44" s="317"/>
       <c r="Q44" s="317"/>
     </row>
-    <row r="45" spans="1:17" ht="23.25" customHeight="1">
-      <c r="A45" s="634" t="s">
+    <row r="45" spans="1:17" ht="23.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A45" s="644" t="s">
         <v>316</v>
       </c>
-      <c r="B45" s="634"/>
-      <c r="C45" s="634"/>
-      <c r="D45" s="634"/>
-      <c r="E45" s="634"/>
-      <c r="F45" s="634"/>
-      <c r="G45" s="634"/>
-      <c r="H45" s="634"/>
-      <c r="I45" s="634"/>
-      <c r="J45" s="634"/>
-      <c r="K45" s="634"/>
-      <c r="L45" s="634"/>
-      <c r="M45" s="634"/>
-      <c r="N45" s="634"/>
+      <c r="B45" s="644"/>
+      <c r="C45" s="644"/>
+      <c r="D45" s="644"/>
+      <c r="E45" s="644"/>
+      <c r="F45" s="644"/>
+      <c r="G45" s="644"/>
+      <c r="H45" s="644"/>
+      <c r="I45" s="644"/>
+      <c r="J45" s="644"/>
+      <c r="K45" s="644"/>
+      <c r="L45" s="644"/>
+      <c r="M45" s="644"/>
+      <c r="N45" s="644"/>
       <c r="O45" s="317"/>
       <c r="P45" s="317"/>
       <c r="Q45" s="317"/>
     </row>
-    <row r="46" spans="1:17" ht="5.25" customHeight="1">
+    <row r="46" spans="1:17" ht="5.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A46" s="193"/>
       <c r="B46" s="196"/>
       <c r="C46" s="196"/>
@@ -11620,7 +11620,7 @@
       <c r="P46" s="317"/>
       <c r="Q46" s="317"/>
     </row>
-    <row r="47" spans="1:17" ht="19.5" customHeight="1">
+    <row r="47" spans="1:17" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A47" s="170" t="s">
         <v>98</v>
       </c>
@@ -11641,19 +11641,19 @@
       <c r="P47" s="317"/>
       <c r="Q47" s="317"/>
     </row>
-    <row r="48" spans="1:17" ht="15" customHeight="1">
+    <row r="48" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A48" s="196"/>
       <c r="B48" s="196"/>
       <c r="C48" s="196"/>
-      <c r="K48" s="633"/>
-      <c r="L48" s="633"/>
-      <c r="M48" s="633"/>
-      <c r="N48" s="633"/>
+      <c r="K48" s="643"/>
+      <c r="L48" s="643"/>
+      <c r="M48" s="643"/>
+      <c r="N48" s="643"/>
       <c r="O48" s="317"/>
       <c r="P48" s="317"/>
       <c r="Q48" s="317"/>
     </row>
-    <row r="49" spans="1:17" ht="66.75" customHeight="1">
+    <row r="49" spans="1:17" ht="66.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A49" s="196"/>
       <c r="B49" s="196"/>
       <c r="C49" s="196"/>
@@ -11666,19 +11666,19 @@
       <c r="P49" s="317"/>
       <c r="Q49" s="317"/>
     </row>
-    <row r="50" spans="1:17">
+    <row r="50" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A50" s="196"/>
       <c r="B50" s="196"/>
       <c r="C50" s="196"/>
-      <c r="K50" s="633"/>
-      <c r="L50" s="633"/>
-      <c r="M50" s="633"/>
-      <c r="N50" s="633"/>
+      <c r="K50" s="643"/>
+      <c r="L50" s="643"/>
+      <c r="M50" s="643"/>
+      <c r="N50" s="643"/>
       <c r="O50" s="317"/>
       <c r="P50" s="317"/>
       <c r="Q50" s="317"/>
     </row>
-    <row r="51" spans="1:17">
+    <row r="51" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A51" s="195" t="s">
         <v>91</v>
       </c>
@@ -11691,12 +11691,12 @@
       <c r="H51" s="324"/>
       <c r="I51" s="324"/>
       <c r="J51" s="324"/>
-      <c r="K51" s="633"/>
-      <c r="L51" s="633"/>
-      <c r="M51" s="633"/>
-      <c r="N51" s="633"/>
-    </row>
-    <row r="52" spans="1:17" ht="11.25" customHeight="1">
+      <c r="K51" s="643"/>
+      <c r="L51" s="643"/>
+      <c r="M51" s="643"/>
+      <c r="N51" s="643"/>
+    </row>
+    <row r="52" spans="1:17" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A52" s="195" t="s">
         <v>317</v>
       </c>
@@ -11709,30 +11709,30 @@
       <c r="H52" s="324"/>
       <c r="I52" s="324"/>
       <c r="J52" s="324"/>
-      <c r="K52" s="633" t="s">
+      <c r="K52" s="643" t="s">
         <v>125</v>
       </c>
-      <c r="L52" s="633"/>
-      <c r="M52" s="633"/>
-      <c r="N52" s="633"/>
-    </row>
-    <row r="53" spans="1:17" ht="15.9" customHeight="1">
+      <c r="L52" s="643"/>
+      <c r="M52" s="643"/>
+      <c r="N52" s="643"/>
+    </row>
+    <row r="53" spans="1:17" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="M53" s="185"/>
       <c r="N53" s="317"/>
     </row>
-    <row r="54" spans="1:17">
+    <row r="54" spans="1:17" x14ac:dyDescent="0.2">
       <c r="M54" s="186"/>
       <c r="N54" s="317"/>
     </row>
-    <row r="55" spans="1:17">
+    <row r="55" spans="1:17" x14ac:dyDescent="0.2">
       <c r="M55" s="317"/>
       <c r="N55" s="317"/>
     </row>
-    <row r="56" spans="1:17">
+    <row r="56" spans="1:17" x14ac:dyDescent="0.2">
       <c r="M56" s="317"/>
       <c r="N56" s="317"/>
     </row>
-    <row r="57" spans="1:17">
+    <row r="57" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A57" s="317"/>
       <c r="B57" s="317"/>
       <c r="C57" s="317"/>
@@ -11747,7 +11747,7 @@
       <c r="L57" s="317"/>
       <c r="M57" s="317"/>
     </row>
-    <row r="58" spans="1:17" ht="11.25" customHeight="1">
+    <row r="58" spans="1:17" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A58" s="187"/>
       <c r="B58" s="187"/>
       <c r="C58" s="187"/>
@@ -11763,23 +11763,23 @@
       <c r="M58" s="187"/>
       <c r="N58" s="187"/>
     </row>
-    <row r="59" spans="1:17" ht="30" customHeight="1">
-      <c r="A59" s="631"/>
-      <c r="B59" s="631"/>
-      <c r="C59" s="631"/>
-      <c r="D59" s="631"/>
-      <c r="E59" s="631"/>
-      <c r="F59" s="631"/>
-      <c r="G59" s="631"/>
-      <c r="H59" s="631"/>
-      <c r="I59" s="631"/>
-      <c r="J59" s="631"/>
-      <c r="K59" s="631"/>
-      <c r="L59" s="631"/>
-      <c r="M59" s="631"/>
-      <c r="N59" s="631"/>
-    </row>
-    <row r="60" spans="1:17" ht="30" customHeight="1">
+    <row r="59" spans="1:17" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A59" s="642"/>
+      <c r="B59" s="642"/>
+      <c r="C59" s="642"/>
+      <c r="D59" s="642"/>
+      <c r="E59" s="642"/>
+      <c r="F59" s="642"/>
+      <c r="G59" s="642"/>
+      <c r="H59" s="642"/>
+      <c r="I59" s="642"/>
+      <c r="J59" s="642"/>
+      <c r="K59" s="642"/>
+      <c r="L59" s="642"/>
+      <c r="M59" s="642"/>
+      <c r="N59" s="642"/>
+    </row>
+    <row r="60" spans="1:17" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A60" s="193"/>
       <c r="B60" s="193"/>
       <c r="C60" s="193"/>
@@ -11795,23 +11795,23 @@
       <c r="M60" s="324"/>
       <c r="N60" s="324"/>
     </row>
-    <row r="61" spans="1:17" ht="39.75" customHeight="1">
-      <c r="A61" s="631"/>
-      <c r="B61" s="631"/>
-      <c r="C61" s="631"/>
-      <c r="D61" s="631"/>
-      <c r="E61" s="631"/>
-      <c r="F61" s="631"/>
-      <c r="G61" s="631"/>
-      <c r="H61" s="631"/>
-      <c r="I61" s="631"/>
-      <c r="J61" s="631"/>
-      <c r="K61" s="631"/>
-      <c r="L61" s="631"/>
-      <c r="M61" s="631"/>
-      <c r="N61" s="631"/>
-    </row>
-    <row r="62" spans="1:17" ht="30" customHeight="1">
+    <row r="61" spans="1:17" ht="39.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A61" s="642"/>
+      <c r="B61" s="642"/>
+      <c r="C61" s="642"/>
+      <c r="D61" s="642"/>
+      <c r="E61" s="642"/>
+      <c r="F61" s="642"/>
+      <c r="G61" s="642"/>
+      <c r="H61" s="642"/>
+      <c r="I61" s="642"/>
+      <c r="J61" s="642"/>
+      <c r="K61" s="642"/>
+      <c r="L61" s="642"/>
+      <c r="M61" s="642"/>
+      <c r="N61" s="642"/>
+    </row>
+    <row r="62" spans="1:17" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A62" s="194"/>
       <c r="B62" s="194"/>
       <c r="C62" s="194"/>
@@ -11827,7 +11827,7 @@
       <c r="M62" s="307"/>
       <c r="N62" s="307"/>
     </row>
-    <row r="63" spans="1:17">
+    <row r="63" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A63" s="327"/>
       <c r="B63" s="327"/>
       <c r="C63" s="327"/>
@@ -11843,139 +11843,139 @@
       <c r="M63" s="327"/>
       <c r="N63" s="327"/>
     </row>
-    <row r="70" spans="11:14">
+    <row r="70" spans="11:14" x14ac:dyDescent="0.2">
       <c r="K70" s="317"/>
       <c r="L70" s="317"/>
       <c r="M70" s="317"/>
       <c r="N70" s="317"/>
     </row>
-    <row r="71" spans="11:14">
+    <row r="71" spans="11:14" x14ac:dyDescent="0.2">
       <c r="K71" s="317"/>
       <c r="L71" s="317"/>
       <c r="M71" s="317"/>
       <c r="N71" s="317"/>
     </row>
-    <row r="72" spans="11:14">
+    <row r="72" spans="11:14" x14ac:dyDescent="0.2">
       <c r="K72" s="317"/>
       <c r="L72" s="317"/>
       <c r="M72" s="317"/>
       <c r="N72" s="317"/>
     </row>
-    <row r="73" spans="11:14">
+    <row r="73" spans="11:14" x14ac:dyDescent="0.2">
       <c r="K73" s="317"/>
       <c r="L73" s="317"/>
       <c r="M73" s="317"/>
       <c r="N73" s="317"/>
     </row>
-    <row r="74" spans="11:14">
+    <row r="74" spans="11:14" x14ac:dyDescent="0.2">
       <c r="K74" s="317"/>
       <c r="L74" s="317"/>
       <c r="M74" s="317"/>
       <c r="N74" s="317"/>
     </row>
-    <row r="75" spans="11:14">
+    <row r="75" spans="11:14" x14ac:dyDescent="0.2">
       <c r="K75" s="317"/>
       <c r="L75" s="317"/>
       <c r="M75" s="317"/>
       <c r="N75" s="317"/>
     </row>
-    <row r="76" spans="11:14">
+    <row r="76" spans="11:14" x14ac:dyDescent="0.2">
       <c r="K76" s="317"/>
       <c r="L76" s="317"/>
       <c r="M76" s="317"/>
       <c r="N76" s="317"/>
     </row>
-    <row r="77" spans="11:14">
+    <row r="77" spans="11:14" x14ac:dyDescent="0.2">
       <c r="K77" s="317"/>
       <c r="L77" s="317"/>
       <c r="M77" s="317"/>
       <c r="N77" s="317"/>
     </row>
-    <row r="78" spans="11:14">
+    <row r="78" spans="11:14" x14ac:dyDescent="0.2">
       <c r="K78" s="328"/>
       <c r="L78" s="328"/>
       <c r="M78" s="328"/>
       <c r="N78" s="317"/>
     </row>
-    <row r="79" spans="11:14">
-      <c r="K79" s="630"/>
-      <c r="L79" s="630"/>
-      <c r="M79" s="630"/>
+    <row r="79" spans="11:14" x14ac:dyDescent="0.2">
+      <c r="K79" s="641"/>
+      <c r="L79" s="641"/>
+      <c r="M79" s="641"/>
       <c r="N79" s="317"/>
     </row>
-    <row r="80" spans="11:14">
-      <c r="K80" s="630"/>
-      <c r="L80" s="630"/>
-      <c r="M80" s="630"/>
+    <row r="80" spans="11:14" x14ac:dyDescent="0.2">
+      <c r="K80" s="641"/>
+      <c r="L80" s="641"/>
+      <c r="M80" s="641"/>
       <c r="N80" s="317"/>
     </row>
-    <row r="81" spans="1:14">
+    <row r="81" spans="1:14" x14ac:dyDescent="0.2">
       <c r="K81" s="329"/>
       <c r="L81" s="329"/>
       <c r="M81" s="329"/>
       <c r="N81" s="317"/>
     </row>
-    <row r="82" spans="1:14">
+    <row r="82" spans="1:14" x14ac:dyDescent="0.2">
       <c r="K82" s="329"/>
       <c r="L82" s="329"/>
       <c r="M82" s="329"/>
       <c r="N82" s="317"/>
     </row>
-    <row r="83" spans="1:14">
+    <row r="83" spans="1:14" x14ac:dyDescent="0.2">
       <c r="K83" s="329"/>
       <c r="L83" s="329"/>
       <c r="M83" s="329"/>
       <c r="N83" s="317"/>
     </row>
-    <row r="84" spans="1:14">
+    <row r="84" spans="1:14" x14ac:dyDescent="0.2">
       <c r="K84" s="329"/>
       <c r="L84" s="329"/>
       <c r="M84" s="329"/>
       <c r="N84" s="317"/>
     </row>
-    <row r="85" spans="1:14">
+    <row r="85" spans="1:14" x14ac:dyDescent="0.2">
       <c r="K85" s="329"/>
       <c r="L85" s="329"/>
       <c r="M85" s="329"/>
       <c r="N85" s="317"/>
     </row>
-    <row r="86" spans="1:14">
+    <row r="86" spans="1:14" x14ac:dyDescent="0.2">
       <c r="K86" s="329"/>
       <c r="L86" s="329"/>
       <c r="M86" s="329"/>
       <c r="N86" s="317"/>
     </row>
-    <row r="87" spans="1:14">
+    <row r="87" spans="1:14" x14ac:dyDescent="0.2">
       <c r="K87" s="329"/>
       <c r="L87" s="329"/>
       <c r="M87" s="329"/>
       <c r="N87" s="317"/>
     </row>
-    <row r="88" spans="1:14">
+    <row r="88" spans="1:14" x14ac:dyDescent="0.2">
       <c r="K88" s="329"/>
       <c r="L88" s="329"/>
       <c r="M88" s="329"/>
       <c r="N88" s="317"/>
     </row>
-    <row r="89" spans="1:14">
+    <row r="89" spans="1:14" x14ac:dyDescent="0.2">
       <c r="K89" s="329"/>
       <c r="L89" s="329"/>
       <c r="M89" s="329"/>
       <c r="N89" s="317"/>
     </row>
-    <row r="90" spans="1:14">
+    <row r="90" spans="1:14" x14ac:dyDescent="0.2">
       <c r="K90" s="329"/>
       <c r="L90" s="329"/>
       <c r="M90" s="329"/>
       <c r="N90" s="317"/>
     </row>
-    <row r="91" spans="1:14">
+    <row r="91" spans="1:14" x14ac:dyDescent="0.2">
       <c r="K91" s="329"/>
       <c r="L91" s="329"/>
       <c r="M91" s="329"/>
       <c r="N91" s="317"/>
     </row>
-    <row r="92" spans="1:14">
+    <row r="92" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A92" s="317"/>
       <c r="B92" s="317"/>
       <c r="C92" s="317"/>
@@ -11991,7 +11991,7 @@
       <c r="M92" s="317"/>
       <c r="N92" s="317"/>
     </row>
-    <row r="93" spans="1:14">
+    <row r="93" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A93" s="317"/>
       <c r="B93" s="317"/>
       <c r="C93" s="317"/>
@@ -12007,7 +12007,7 @@
       <c r="M93" s="317"/>
       <c r="N93" s="317"/>
     </row>
-    <row r="94" spans="1:14">
+    <row r="94" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A94" s="317"/>
       <c r="B94" s="317"/>
       <c r="C94" s="317"/>
@@ -12030,6 +12030,20 @@
     <protectedRange sqref="E5:F6" name="Rango3_3_1_1_1_1_1_2_1"/>
   </protectedRanges>
   <mergeCells count="30">
+    <mergeCell ref="C8:K8"/>
+    <mergeCell ref="A41:N41"/>
+    <mergeCell ref="M79:M80"/>
+    <mergeCell ref="A59:N59"/>
+    <mergeCell ref="A61:N61"/>
+    <mergeCell ref="A42:N42"/>
+    <mergeCell ref="A44:N44"/>
+    <mergeCell ref="K50:N50"/>
+    <mergeCell ref="K48:N48"/>
+    <mergeCell ref="A45:N45"/>
+    <mergeCell ref="K51:N51"/>
+    <mergeCell ref="K52:N52"/>
+    <mergeCell ref="K79:K80"/>
+    <mergeCell ref="L79:L80"/>
     <mergeCell ref="A2:N2"/>
     <mergeCell ref="A3:N3"/>
     <mergeCell ref="A10:N10"/>
@@ -12046,20 +12060,6 @@
     <mergeCell ref="K37:L37"/>
     <mergeCell ref="C6:K6"/>
     <mergeCell ref="C7:K7"/>
-    <mergeCell ref="C8:K8"/>
-    <mergeCell ref="A41:N41"/>
-    <mergeCell ref="M79:M80"/>
-    <mergeCell ref="A59:N59"/>
-    <mergeCell ref="A61:N61"/>
-    <mergeCell ref="A42:N42"/>
-    <mergeCell ref="A44:N44"/>
-    <mergeCell ref="K50:N50"/>
-    <mergeCell ref="K48:N48"/>
-    <mergeCell ref="A45:N45"/>
-    <mergeCell ref="K51:N51"/>
-    <mergeCell ref="K52:N52"/>
-    <mergeCell ref="K79:K80"/>
-    <mergeCell ref="L79:L80"/>
   </mergeCells>
   <conditionalFormatting sqref="A30:A38">
     <cfRule type="cellIs" priority="1" stopIfTrue="1" operator="between">
@@ -12092,23 +12092,23 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:N53"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="10.33203125" defaultRowHeight="13.2"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="10.28515625" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="4.6640625" style="317" customWidth="1"/>
-    <col min="2" max="2" width="11.33203125" style="317" customWidth="1"/>
-    <col min="3" max="3" width="12.33203125" style="317" customWidth="1"/>
-    <col min="4" max="5" width="11.33203125" style="317" customWidth="1"/>
-    <col min="6" max="6" width="13.33203125" style="317" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="12.109375" style="317" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.88671875" style="317" customWidth="1"/>
-    <col min="9" max="9" width="10.6640625" style="317" customWidth="1"/>
-    <col min="10" max="10" width="11.44140625" style="317" customWidth="1"/>
-    <col min="11" max="11" width="13.33203125" style="317" customWidth="1"/>
-    <col min="12" max="12" width="5.6640625" style="317" customWidth="1"/>
-    <col min="13" max="16384" width="10.33203125" style="317"/>
+    <col min="1" max="1" width="4.7109375" style="317" customWidth="1"/>
+    <col min="2" max="2" width="11.28515625" style="317" customWidth="1"/>
+    <col min="3" max="3" width="12.28515625" style="317" customWidth="1"/>
+    <col min="4" max="5" width="11.28515625" style="317" customWidth="1"/>
+    <col min="6" max="6" width="13.28515625" style="317" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="12.140625" style="317" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.85546875" style="317" customWidth="1"/>
+    <col min="9" max="9" width="10.7109375" style="317" customWidth="1"/>
+    <col min="10" max="10" width="11.42578125" style="317" customWidth="1"/>
+    <col min="11" max="11" width="13.28515625" style="317" customWidth="1"/>
+    <col min="12" max="12" width="5.7109375" style="317" customWidth="1"/>
+    <col min="13" max="16384" width="10.28515625" style="317"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" ht="5.4" customHeight="1">
+    <row r="1" spans="1:14" ht="5.45" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="383"/>
       <c r="B1" s="384"/>
       <c r="C1" s="384"/>
@@ -12123,41 +12123,41 @@
       <c r="L1" s="385"/>
       <c r="M1" s="386"/>
     </row>
-    <row r="2" spans="1:14" ht="15" customHeight="1">
+    <row r="2" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="387"/>
-      <c r="B2" s="649" t="s">
+      <c r="B2" s="661" t="s">
         <v>102</v>
       </c>
-      <c r="C2" s="649"/>
-      <c r="D2" s="649"/>
-      <c r="E2" s="649"/>
-      <c r="F2" s="649"/>
-      <c r="G2" s="649"/>
-      <c r="H2" s="649"/>
-      <c r="I2" s="649"/>
-      <c r="J2" s="649"/>
-      <c r="K2" s="649"/>
+      <c r="C2" s="661"/>
+      <c r="D2" s="661"/>
+      <c r="E2" s="661"/>
+      <c r="F2" s="661"/>
+      <c r="G2" s="661"/>
+      <c r="H2" s="661"/>
+      <c r="I2" s="661"/>
+      <c r="J2" s="661"/>
+      <c r="K2" s="661"/>
       <c r="L2" s="374"/>
       <c r="M2" s="386"/>
     </row>
-    <row r="3" spans="1:14" ht="15" customHeight="1">
+    <row r="3" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="387"/>
-      <c r="B3" s="649" t="s">
+      <c r="B3" s="661" t="s">
         <v>103</v>
       </c>
-      <c r="C3" s="649"/>
-      <c r="D3" s="649"/>
-      <c r="E3" s="649"/>
-      <c r="F3" s="649"/>
-      <c r="G3" s="649"/>
-      <c r="H3" s="649"/>
-      <c r="I3" s="649"/>
-      <c r="J3" s="649"/>
-      <c r="K3" s="649"/>
+      <c r="C3" s="661"/>
+      <c r="D3" s="661"/>
+      <c r="E3" s="661"/>
+      <c r="F3" s="661"/>
+      <c r="G3" s="661"/>
+      <c r="H3" s="661"/>
+      <c r="I3" s="661"/>
+      <c r="J3" s="661"/>
+      <c r="K3" s="661"/>
       <c r="L3" s="374"/>
       <c r="M3" s="386"/>
     </row>
-    <row r="4" spans="1:14" ht="6.6" customHeight="1">
+    <row r="4" spans="1:14" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="387"/>
       <c r="B4" s="375"/>
       <c r="C4" s="375"/>
@@ -12172,14 +12172,14 @@
       <c r="L4" s="374"/>
       <c r="M4" s="386"/>
     </row>
-    <row r="5" spans="1:14" ht="15" customHeight="1">
+    <row r="5" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="387"/>
-      <c r="B5" s="655" t="s">
+      <c r="B5" s="652" t="s">
         <v>126</v>
       </c>
-      <c r="C5" s="656"/>
-      <c r="D5" s="656"/>
-      <c r="E5" s="657"/>
+      <c r="C5" s="653"/>
+      <c r="D5" s="653"/>
+      <c r="E5" s="654"/>
       <c r="F5" s="331">
         <f>+Resumen!J26</f>
         <v>0</v>
@@ -12194,7 +12194,7 @@
       <c r="L5" s="374"/>
       <c r="M5" s="386"/>
     </row>
-    <row r="6" spans="1:14" ht="15" customHeight="1">
+    <row r="6" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="387"/>
       <c r="B6" s="375"/>
       <c r="C6" s="375"/>
@@ -12212,14 +12212,14 @@
       <c r="M6" s="386"/>
       <c r="N6" s="197"/>
     </row>
-    <row r="7" spans="1:14" ht="15" customHeight="1">
+    <row r="7" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="387"/>
-      <c r="B7" s="655" t="s">
+      <c r="B7" s="652" t="s">
         <v>129</v>
       </c>
-      <c r="C7" s="656"/>
-      <c r="D7" s="656"/>
-      <c r="E7" s="657"/>
+      <c r="C7" s="653"/>
+      <c r="D7" s="653"/>
+      <c r="E7" s="654"/>
       <c r="F7" s="331">
         <f>+IF(F5="A",0.1,0.01)</f>
         <v>0.01</v>
@@ -12229,7 +12229,7 @@
       <c r="M7" s="386"/>
       <c r="N7" s="197"/>
     </row>
-    <row r="8" spans="1:14" ht="15" customHeight="1">
+    <row r="8" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="387"/>
       <c r="B8" s="375"/>
       <c r="C8" s="375"/>
@@ -12254,7 +12254,7 @@
       <c r="L8" s="374"/>
       <c r="M8" s="386"/>
     </row>
-    <row r="9" spans="1:14" ht="15" customHeight="1">
+    <row r="9" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="387"/>
       <c r="B9" s="372" t="s">
         <v>246</v>
@@ -12284,7 +12284,7 @@
       <c r="L9" s="377"/>
       <c r="M9" s="386"/>
     </row>
-    <row r="10" spans="1:14" ht="15" customHeight="1">
+    <row r="10" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="387"/>
       <c r="G10" s="197"/>
       <c r="H10" s="330" t="str">
@@ -12304,7 +12304,7 @@
       </c>
       <c r="L10" s="378"/>
     </row>
-    <row r="11" spans="1:14" ht="15" customHeight="1">
+    <row r="11" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="387"/>
       <c r="B11" s="372" t="s">
         <v>238</v>
@@ -12322,12 +12322,12 @@
       <c r="K11" s="379"/>
       <c r="L11" s="380"/>
     </row>
-    <row r="12" spans="1:14" ht="8.4" customHeight="1">
+    <row r="12" spans="1:14" ht="8.4499999999999993" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="387"/>
       <c r="G12" s="197"/>
       <c r="L12" s="394"/>
     </row>
-    <row r="13" spans="1:14" ht="15" customHeight="1">
+    <row r="13" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" s="387"/>
       <c r="B13" s="372" t="s">
         <v>245</v>
@@ -12340,12 +12340,12 @@
       <c r="G13" s="197"/>
       <c r="L13" s="394"/>
     </row>
-    <row r="14" spans="1:14" ht="7.95" customHeight="1">
+    <row r="14" spans="1:14" ht="7.9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" s="387"/>
       <c r="G14" s="197"/>
       <c r="L14" s="394"/>
     </row>
-    <row r="15" spans="1:14" ht="15" customHeight="1">
+    <row r="15" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" s="387"/>
       <c r="B15" s="372" t="s">
         <v>107</v>
@@ -12361,27 +12361,27 @@
       <c r="G15" s="197"/>
       <c r="L15" s="394"/>
     </row>
-    <row r="16" spans="1:14" ht="7.95" customHeight="1">
+    <row r="16" spans="1:14" ht="7.9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A16" s="387"/>
       <c r="L16" s="394"/>
     </row>
-    <row r="17" spans="1:12" ht="15" customHeight="1">
+    <row r="17" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A17" s="396">
         <v>1</v>
       </c>
-      <c r="B17" s="658" t="s">
+      <c r="B17" s="655" t="s">
         <v>35</v>
       </c>
-      <c r="C17" s="659"/>
-      <c r="D17" s="659"/>
-      <c r="E17" s="660"/>
+      <c r="C17" s="656"/>
+      <c r="D17" s="656"/>
+      <c r="E17" s="657"/>
       <c r="F17" s="397" t="s">
         <v>36</v>
       </c>
       <c r="G17" s="426">
         <v>1</v>
       </c>
-      <c r="H17" s="651" t="s">
+      <c r="H17" s="663" t="s">
         <v>37</v>
       </c>
       <c r="J17" s="4" t="s">
@@ -12392,16 +12392,16 @@
       </c>
       <c r="L17" s="394"/>
     </row>
-    <row r="18" spans="1:12" ht="17.25" customHeight="1">
+    <row r="18" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A18" s="396">
         <v>2</v>
       </c>
-      <c r="B18" s="658" t="s">
+      <c r="B18" s="655" t="s">
         <v>111</v>
       </c>
-      <c r="C18" s="659"/>
-      <c r="D18" s="659"/>
-      <c r="E18" s="660"/>
+      <c r="C18" s="656"/>
+      <c r="D18" s="656"/>
+      <c r="E18" s="657"/>
       <c r="F18" s="397" t="s">
         <v>36</v>
       </c>
@@ -12409,7 +12409,7 @@
         <f>+Resumen!I32</f>
         <v>0</v>
       </c>
-      <c r="H18" s="651"/>
+      <c r="H18" s="663"/>
       <c r="J18" s="4" t="s">
         <v>237</v>
       </c>
@@ -12418,16 +12418,16 @@
       </c>
       <c r="L18" s="394"/>
     </row>
-    <row r="19" spans="1:12" ht="17.25" customHeight="1">
+    <row r="19" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A19" s="396">
         <v>3</v>
       </c>
-      <c r="B19" s="658" t="s">
+      <c r="B19" s="655" t="s">
         <v>112</v>
       </c>
-      <c r="C19" s="659"/>
-      <c r="D19" s="659"/>
-      <c r="E19" s="660"/>
+      <c r="C19" s="656"/>
+      <c r="D19" s="656"/>
+      <c r="E19" s="657"/>
       <c r="F19" s="397" t="s">
         <v>41</v>
       </c>
@@ -12447,16 +12447,16 @@
       </c>
       <c r="L19" s="394"/>
     </row>
-    <row r="20" spans="1:12" ht="17.25" customHeight="1">
+    <row r="20" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A20" s="396">
         <v>4</v>
       </c>
-      <c r="B20" s="658" t="s">
+      <c r="B20" s="655" t="s">
         <v>113</v>
       </c>
-      <c r="C20" s="659"/>
-      <c r="D20" s="659"/>
-      <c r="E20" s="660"/>
+      <c r="C20" s="656"/>
+      <c r="D20" s="656"/>
+      <c r="E20" s="657"/>
       <c r="F20" s="397" t="s">
         <v>41</v>
       </c>
@@ -12476,7 +12476,7 @@
       </c>
       <c r="L20" s="394"/>
     </row>
-    <row r="21" spans="1:12" ht="17.25" customHeight="1">
+    <row r="21" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A21" s="396">
         <v>5</v>
       </c>
@@ -12505,16 +12505,16 @@
       </c>
       <c r="L21" s="394"/>
     </row>
-    <row r="22" spans="1:12" ht="17.25" customHeight="1">
+    <row r="22" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A22" s="396">
         <v>6</v>
       </c>
-      <c r="B22" s="658" t="s">
+      <c r="B22" s="655" t="s">
         <v>114</v>
       </c>
-      <c r="C22" s="659"/>
-      <c r="D22" s="659"/>
-      <c r="E22" s="660"/>
+      <c r="C22" s="656"/>
+      <c r="D22" s="656"/>
+      <c r="E22" s="657"/>
       <c r="F22" s="399" t="s">
         <v>41</v>
       </c>
@@ -12534,16 +12534,16 @@
       </c>
       <c r="L22" s="394"/>
     </row>
-    <row r="23" spans="1:12" ht="17.25" customHeight="1">
+    <row r="23" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A23" s="396">
         <v>7</v>
       </c>
-      <c r="B23" s="658" t="s">
+      <c r="B23" s="655" t="s">
         <v>115</v>
       </c>
-      <c r="C23" s="659"/>
-      <c r="D23" s="659"/>
-      <c r="E23" s="660"/>
+      <c r="C23" s="656"/>
+      <c r="D23" s="656"/>
+      <c r="E23" s="657"/>
       <c r="F23" s="397" t="s">
         <v>41</v>
       </c>
@@ -12563,16 +12563,16 @@
       </c>
       <c r="L23" s="394"/>
     </row>
-    <row r="24" spans="1:12" ht="17.25" customHeight="1">
+    <row r="24" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A24" s="396">
         <v>8</v>
       </c>
-      <c r="B24" s="658" t="s">
+      <c r="B24" s="655" t="s">
         <v>116</v>
       </c>
-      <c r="C24" s="659"/>
-      <c r="D24" s="659"/>
-      <c r="E24" s="660"/>
+      <c r="C24" s="656"/>
+      <c r="D24" s="656"/>
+      <c r="E24" s="657"/>
       <c r="F24" s="399" t="s">
         <v>41</v>
       </c>
@@ -12592,16 +12592,16 @@
       </c>
       <c r="L24" s="394"/>
     </row>
-    <row r="25" spans="1:12" ht="17.25" customHeight="1">
+    <row r="25" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A25" s="396">
         <v>9</v>
       </c>
-      <c r="B25" s="661" t="s">
+      <c r="B25" s="658" t="s">
         <v>117</v>
       </c>
-      <c r="C25" s="662"/>
-      <c r="D25" s="662"/>
-      <c r="E25" s="663"/>
+      <c r="C25" s="659"/>
+      <c r="D25" s="659"/>
+      <c r="E25" s="660"/>
       <c r="F25" s="399" t="s">
         <v>56</v>
       </c>
@@ -12621,7 +12621,7 @@
       </c>
       <c r="L25" s="394"/>
     </row>
-    <row r="26" spans="1:12" ht="14.25" customHeight="1">
+    <row r="26" spans="1:12" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A26" s="387"/>
       <c r="B26" s="400"/>
       <c r="C26" s="400"/>
@@ -12642,7 +12642,7 @@
       </c>
       <c r="L26" s="394"/>
     </row>
-    <row r="27" spans="1:12" ht="17.25" customHeight="1">
+    <row r="27" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A27" s="387"/>
       <c r="B27" s="199" t="s">
         <v>134</v>
@@ -12664,7 +12664,7 @@
       </c>
       <c r="L27" s="394"/>
     </row>
-    <row r="28" spans="1:12" ht="17.25" customHeight="1">
+    <row r="28" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A28" s="387"/>
       <c r="B28" s="199" t="s">
         <v>135</v>
@@ -12686,7 +12686,7 @@
       </c>
       <c r="L28" s="394"/>
     </row>
-    <row r="29" spans="1:12" ht="15.9" customHeight="1">
+    <row r="29" spans="1:12" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A29" s="387"/>
       <c r="B29" s="199" t="s">
         <v>136</v>
@@ -12708,33 +12708,33 @@
       </c>
       <c r="L29" s="394"/>
     </row>
-    <row r="30" spans="1:12" ht="5.25" customHeight="1">
+    <row r="30" spans="1:12" ht="5.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A30" s="387"/>
       <c r="I30" s="405"/>
       <c r="J30" s="406"/>
       <c r="K30" s="406"/>
       <c r="L30" s="394"/>
     </row>
-    <row r="31" spans="1:12" ht="15.9" customHeight="1">
+    <row r="31" spans="1:12" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A31" s="387"/>
-      <c r="B31" s="650" t="s">
+      <c r="B31" s="662" t="s">
         <v>137</v>
       </c>
-      <c r="C31" s="650"/>
-      <c r="D31" s="650"/>
-      <c r="E31" s="650"/>
-      <c r="F31" s="650"/>
-      <c r="G31" s="650"/>
+      <c r="C31" s="662"/>
+      <c r="D31" s="662"/>
+      <c r="E31" s="662"/>
+      <c r="F31" s="662"/>
+      <c r="G31" s="662"/>
       <c r="L31" s="394"/>
     </row>
-    <row r="32" spans="1:12" ht="26.25" customHeight="1">
+    <row r="32" spans="1:12" ht="26.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A32" s="387"/>
-      <c r="B32" s="655" t="s">
+      <c r="B32" s="652" t="s">
         <v>138</v>
       </c>
-      <c r="C32" s="656"/>
-      <c r="D32" s="656"/>
-      <c r="E32" s="657"/>
+      <c r="C32" s="653"/>
+      <c r="D32" s="653"/>
+      <c r="E32" s="654"/>
       <c r="F32" s="369" t="s">
         <v>139</v>
       </c>
@@ -12743,14 +12743,14 @@
       </c>
       <c r="L32" s="394"/>
     </row>
-    <row r="33" spans="1:12" ht="16.5" customHeight="1">
+    <row r="33" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A33" s="387"/>
-      <c r="B33" s="652" t="s">
+      <c r="B33" s="649" t="s">
         <v>141</v>
       </c>
-      <c r="C33" s="653"/>
-      <c r="D33" s="653"/>
-      <c r="E33" s="654"/>
+      <c r="C33" s="650"/>
+      <c r="D33" s="650"/>
+      <c r="E33" s="651"/>
       <c r="F33" s="330" t="s">
         <v>142</v>
       </c>
@@ -12759,14 +12759,14 @@
       </c>
       <c r="L33" s="394"/>
     </row>
-    <row r="34" spans="1:12" ht="16.5" customHeight="1">
+    <row r="34" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A34" s="387"/>
-      <c r="B34" s="652" t="s">
+      <c r="B34" s="649" t="s">
         <v>143</v>
       </c>
-      <c r="C34" s="653"/>
-      <c r="D34" s="653"/>
-      <c r="E34" s="654"/>
+      <c r="C34" s="650"/>
+      <c r="D34" s="650"/>
+      <c r="E34" s="651"/>
       <c r="F34" s="330" t="s">
         <v>144</v>
       </c>
@@ -12775,14 +12775,14 @@
       </c>
       <c r="L34" s="394"/>
     </row>
-    <row r="35" spans="1:12" ht="16.5" customHeight="1">
+    <row r="35" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A35" s="387"/>
-      <c r="B35" s="652" t="s">
+      <c r="B35" s="649" t="s">
         <v>145</v>
       </c>
-      <c r="C35" s="653"/>
-      <c r="D35" s="653"/>
-      <c r="E35" s="654"/>
+      <c r="C35" s="650"/>
+      <c r="D35" s="650"/>
+      <c r="E35" s="651"/>
       <c r="F35" s="330" t="s">
         <v>146</v>
       </c>
@@ -12791,26 +12791,26 @@
       </c>
       <c r="L35" s="394"/>
     </row>
-    <row r="36" spans="1:12" ht="16.5" customHeight="1">
+    <row r="36" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A36" s="387"/>
-      <c r="B36" s="650" t="s">
+      <c r="B36" s="662" t="s">
         <v>147</v>
       </c>
-      <c r="C36" s="650"/>
-      <c r="D36" s="650"/>
-      <c r="E36" s="650"/>
-      <c r="F36" s="650"/>
-      <c r="G36" s="650"/>
+      <c r="C36" s="662"/>
+      <c r="D36" s="662"/>
+      <c r="E36" s="662"/>
+      <c r="F36" s="662"/>
+      <c r="G36" s="662"/>
       <c r="L36" s="394"/>
     </row>
-    <row r="37" spans="1:12" ht="16.5" customHeight="1">
+    <row r="37" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A37" s="387"/>
-      <c r="B37" s="652" t="s">
+      <c r="B37" s="649" t="s">
         <v>227</v>
       </c>
-      <c r="C37" s="653"/>
-      <c r="D37" s="653"/>
-      <c r="E37" s="654"/>
+      <c r="C37" s="650"/>
+      <c r="D37" s="650"/>
+      <c r="E37" s="651"/>
       <c r="F37" s="330" t="s">
         <v>148</v>
       </c>
@@ -12819,14 +12819,14 @@
       </c>
       <c r="L37" s="394"/>
     </row>
-    <row r="38" spans="1:12" ht="16.5" customHeight="1">
+    <row r="38" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A38" s="387"/>
-      <c r="B38" s="652" t="s">
+      <c r="B38" s="649" t="s">
         <v>149</v>
       </c>
-      <c r="C38" s="653"/>
-      <c r="D38" s="653"/>
-      <c r="E38" s="654"/>
+      <c r="C38" s="650"/>
+      <c r="D38" s="650"/>
+      <c r="E38" s="651"/>
       <c r="F38" s="330" t="s">
         <v>150</v>
       </c>
@@ -12835,14 +12835,14 @@
       </c>
       <c r="L38" s="394"/>
     </row>
-    <row r="39" spans="1:12" ht="16.5" customHeight="1">
+    <row r="39" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A39" s="387"/>
-      <c r="B39" s="652" t="s">
+      <c r="B39" s="649" t="s">
         <v>151</v>
       </c>
-      <c r="C39" s="653"/>
-      <c r="D39" s="653"/>
-      <c r="E39" s="654"/>
+      <c r="C39" s="650"/>
+      <c r="D39" s="650"/>
+      <c r="E39" s="651"/>
       <c r="F39" s="330" t="s">
         <v>152</v>
       </c>
@@ -12851,98 +12851,98 @@
       </c>
       <c r="L39" s="394"/>
     </row>
-    <row r="40" spans="1:12" ht="13.5" customHeight="1">
+    <row r="40" spans="1:12" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A40" s="387"/>
       <c r="I40" s="197"/>
       <c r="J40" s="381"/>
       <c r="K40" s="329"/>
       <c r="L40" s="394"/>
     </row>
-    <row r="41" spans="1:12" ht="13.5" customHeight="1">
+    <row r="41" spans="1:12" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A41" s="387"/>
       <c r="I41" s="197"/>
       <c r="J41" s="381"/>
       <c r="K41" s="329"/>
       <c r="L41" s="394"/>
     </row>
-    <row r="42" spans="1:12" ht="13.5" customHeight="1">
+    <row r="42" spans="1:12" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A42" s="387"/>
       <c r="I42" s="197"/>
       <c r="J42" s="381"/>
       <c r="K42" s="329"/>
       <c r="L42" s="394"/>
     </row>
-    <row r="43" spans="1:12" ht="13.5" customHeight="1">
+    <row r="43" spans="1:12" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A43" s="387"/>
       <c r="I43" s="197"/>
       <c r="J43" s="381"/>
       <c r="K43" s="329"/>
       <c r="L43" s="394"/>
     </row>
-    <row r="44" spans="1:12" ht="13.5" customHeight="1">
+    <row r="44" spans="1:12" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A44" s="387"/>
       <c r="I44" s="197"/>
       <c r="J44" s="381"/>
       <c r="K44" s="329"/>
       <c r="L44" s="394"/>
     </row>
-    <row r="45" spans="1:12" ht="13.5" customHeight="1">
+    <row r="45" spans="1:12" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A45" s="387"/>
       <c r="I45" s="197"/>
       <c r="J45" s="381"/>
       <c r="K45" s="329"/>
       <c r="L45" s="394"/>
     </row>
-    <row r="46" spans="1:12" ht="13.5" customHeight="1">
+    <row r="46" spans="1:12" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A46" s="387"/>
       <c r="I46" s="197"/>
       <c r="J46" s="381"/>
       <c r="K46" s="329"/>
       <c r="L46" s="394"/>
     </row>
-    <row r="47" spans="1:12" ht="13.5" customHeight="1">
+    <row r="47" spans="1:12" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A47" s="387"/>
       <c r="I47" s="197"/>
       <c r="J47" s="381"/>
       <c r="K47" s="329"/>
       <c r="L47" s="394"/>
     </row>
-    <row r="48" spans="1:12" ht="13.5" customHeight="1">
+    <row r="48" spans="1:12" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A48" s="387"/>
       <c r="I48" s="197"/>
       <c r="J48" s="381"/>
       <c r="K48" s="329"/>
       <c r="L48" s="394"/>
     </row>
-    <row r="49" spans="1:12" ht="13.5" customHeight="1">
+    <row r="49" spans="1:12" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A49" s="387"/>
       <c r="I49" s="197"/>
       <c r="J49" s="381"/>
       <c r="K49" s="329"/>
       <c r="L49" s="394"/>
     </row>
-    <row r="50" spans="1:12" ht="13.5" customHeight="1">
+    <row r="50" spans="1:12" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A50" s="387"/>
       <c r="I50" s="197"/>
       <c r="J50" s="381"/>
       <c r="K50" s="329"/>
       <c r="L50" s="394"/>
     </row>
-    <row r="51" spans="1:12" ht="13.5" customHeight="1">
+    <row r="51" spans="1:12" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A51" s="387"/>
       <c r="I51" s="197"/>
       <c r="J51" s="382"/>
       <c r="K51" s="329"/>
       <c r="L51" s="394"/>
     </row>
-    <row r="52" spans="1:12">
+    <row r="52" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A52" s="387"/>
       <c r="I52" s="197"/>
       <c r="J52" s="381"/>
       <c r="K52" s="329"/>
       <c r="L52" s="394"/>
     </row>
-    <row r="53" spans="1:12" ht="13.8" thickBot="1">
+    <row r="53" spans="1:12" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A53" s="407"/>
       <c r="B53" s="408"/>
       <c r="C53" s="408"/>
@@ -12959,6 +12959,15 @@
   </sheetData>
   <sheetProtection algorithmName="SHA-512" hashValue="xWWTH2ODRJvJuq26fz8BDBTKOyLp8SD8OPQSny0kNhk0w02O6G1TzYz/+8aUJNSNF0435K8vhuSYHksIa+3eMQ==" saltValue="O89M/G/p4V9ywCWV4cqXXA==" spinCount="100000" sheet="1" objects="1" scenarios="1"/>
   <mergeCells count="22">
+    <mergeCell ref="B2:K2"/>
+    <mergeCell ref="B3:K3"/>
+    <mergeCell ref="B31:G31"/>
+    <mergeCell ref="B36:G36"/>
+    <mergeCell ref="H17:H18"/>
+    <mergeCell ref="B33:E33"/>
+    <mergeCell ref="B34:E34"/>
+    <mergeCell ref="B35:E35"/>
+    <mergeCell ref="B32:E32"/>
     <mergeCell ref="B39:E39"/>
     <mergeCell ref="B5:E5"/>
     <mergeCell ref="B7:E7"/>
@@ -12972,15 +12981,6 @@
     <mergeCell ref="B25:E25"/>
     <mergeCell ref="B37:E37"/>
     <mergeCell ref="B38:E38"/>
-    <mergeCell ref="B2:K2"/>
-    <mergeCell ref="B3:K3"/>
-    <mergeCell ref="B31:G31"/>
-    <mergeCell ref="B36:G36"/>
-    <mergeCell ref="H17:H18"/>
-    <mergeCell ref="B33:E33"/>
-    <mergeCell ref="B34:E34"/>
-    <mergeCell ref="B35:E35"/>
-    <mergeCell ref="B32:E32"/>
   </mergeCells>
   <conditionalFormatting sqref="E11">
     <cfRule type="containsText" dxfId="0" priority="1" operator="containsText" text="no">
@@ -13009,32 +13009,32 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:K72"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11.44140625" defaultRowHeight="13.2"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.42578125" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="21.88671875" style="339" customWidth="1"/>
-    <col min="2" max="2" width="11.5546875" style="339" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="12.5546875" style="339" customWidth="1"/>
-    <col min="4" max="4" width="11.5546875" style="339" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="21.85546875" style="339" customWidth="1"/>
+    <col min="2" max="2" width="11.5703125" style="339" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.5703125" style="339" customWidth="1"/>
+    <col min="4" max="4" width="11.5703125" style="339" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="20" style="339" customWidth="1"/>
     <col min="6" max="6" width="14" style="339" customWidth="1"/>
-    <col min="7" max="7" width="13.6640625" style="339" customWidth="1"/>
-    <col min="8" max="8" width="15.33203125" style="339" customWidth="1"/>
-    <col min="9" max="9" width="9.88671875" style="339" customWidth="1"/>
-    <col min="10" max="10" width="14.44140625" style="339" customWidth="1"/>
-    <col min="11" max="16384" width="11.44140625" style="339"/>
+    <col min="7" max="7" width="13.7109375" style="339" customWidth="1"/>
+    <col min="8" max="8" width="15.28515625" style="339" customWidth="1"/>
+    <col min="9" max="9" width="9.85546875" style="339" customWidth="1"/>
+    <col min="10" max="10" width="14.42578125" style="339" customWidth="1"/>
+    <col min="11" max="16384" width="11.42578125" style="339"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" ht="12.75" customHeight="1">
-      <c r="A1" s="681"/>
-      <c r="B1" s="682"/>
-      <c r="C1" s="672" t="s">
+    <row r="1" spans="1:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A1" s="673"/>
+      <c r="B1" s="674"/>
+      <c r="C1" s="664" t="s">
         <v>153</v>
       </c>
-      <c r="D1" s="673"/>
-      <c r="E1" s="673"/>
-      <c r="F1" s="673"/>
-      <c r="G1" s="673"/>
-      <c r="H1" s="674"/>
+      <c r="D1" s="665"/>
+      <c r="E1" s="665"/>
+      <c r="F1" s="665"/>
+      <c r="G1" s="665"/>
+      <c r="H1" s="666"/>
       <c r="I1" s="221" t="s">
         <v>154</v>
       </c>
@@ -13042,15 +13042,15 @@
         <v>155</v>
       </c>
     </row>
-    <row r="2" spans="1:10" ht="12.75" customHeight="1">
-      <c r="A2" s="683"/>
-      <c r="B2" s="684"/>
-      <c r="C2" s="675"/>
-      <c r="D2" s="676"/>
-      <c r="E2" s="676"/>
-      <c r="F2" s="676"/>
-      <c r="G2" s="676"/>
-      <c r="H2" s="677"/>
+    <row r="2" spans="1:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2" s="675"/>
+      <c r="B2" s="676"/>
+      <c r="C2" s="667"/>
+      <c r="D2" s="668"/>
+      <c r="E2" s="668"/>
+      <c r="F2" s="668"/>
+      <c r="G2" s="668"/>
+      <c r="H2" s="669"/>
       <c r="I2" s="221" t="s">
         <v>156</v>
       </c>
@@ -13058,15 +13058,15 @@
         <v>3</v>
       </c>
     </row>
-    <row r="3" spans="1:10" ht="12.75" customHeight="1">
-      <c r="A3" s="683"/>
-      <c r="B3" s="684"/>
-      <c r="C3" s="675"/>
-      <c r="D3" s="676"/>
-      <c r="E3" s="676"/>
-      <c r="F3" s="676"/>
-      <c r="G3" s="676"/>
-      <c r="H3" s="677"/>
+    <row r="3" spans="1:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A3" s="675"/>
+      <c r="B3" s="676"/>
+      <c r="C3" s="667"/>
+      <c r="D3" s="668"/>
+      <c r="E3" s="668"/>
+      <c r="F3" s="668"/>
+      <c r="G3" s="668"/>
+      <c r="H3" s="669"/>
       <c r="I3" s="221" t="s">
         <v>157</v>
       </c>
@@ -13074,15 +13074,15 @@
         <v>46146</v>
       </c>
     </row>
-    <row r="4" spans="1:10" ht="12.75" customHeight="1">
-      <c r="A4" s="685"/>
-      <c r="B4" s="686"/>
-      <c r="C4" s="678"/>
-      <c r="D4" s="679"/>
-      <c r="E4" s="679"/>
-      <c r="F4" s="679"/>
-      <c r="G4" s="679"/>
-      <c r="H4" s="680"/>
+    <row r="4" spans="1:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A4" s="677"/>
+      <c r="B4" s="678"/>
+      <c r="C4" s="670"/>
+      <c r="D4" s="671"/>
+      <c r="E4" s="671"/>
+      <c r="F4" s="671"/>
+      <c r="G4" s="671"/>
+      <c r="H4" s="672"/>
       <c r="I4" s="221" t="s">
         <v>158</v>
       </c>
@@ -13090,7 +13090,7 @@
         <v>159</v>
       </c>
     </row>
-    <row r="6" spans="1:10" ht="18" customHeight="1">
+    <row r="6" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="223" t="s">
         <v>160</v>
       </c>
@@ -13106,7 +13106,7 @@
       <c r="I6" s="340"/>
       <c r="J6" s="341"/>
     </row>
-    <row r="7" spans="1:10" ht="18" customHeight="1">
+    <row r="7" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="223" t="s">
         <v>162</v>
       </c>
@@ -13122,7 +13122,7 @@
       <c r="I7" s="340"/>
       <c r="J7" s="341"/>
     </row>
-    <row r="8" spans="1:10" ht="18" customHeight="1">
+    <row r="8" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="223" t="s">
         <v>163</v>
       </c>
@@ -13138,7 +13138,7 @@
       <c r="I8" s="340"/>
       <c r="J8" s="341"/>
     </row>
-    <row r="9" spans="1:10" ht="18" customHeight="1">
+    <row r="9" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="224" t="s">
         <v>302</v>
       </c>
@@ -13154,13 +13154,13 @@
       <c r="I9" s="340"/>
       <c r="J9" s="341"/>
     </row>
-    <row r="11" spans="1:10" ht="12" customHeight="1">
+    <row r="11" spans="1:10" ht="12" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="351" t="s">
         <v>303</v>
       </c>
     </row>
-    <row r="12" spans="1:10" ht="12" customHeight="1"/>
-    <row r="13" spans="1:10" ht="12" customHeight="1">
+    <row r="12" spans="1:10" ht="12" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="13" spans="1:10" ht="12" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" s="353" t="s">
         <v>165</v>
       </c>
@@ -13168,81 +13168,81 @@
         <v>169</v>
       </c>
     </row>
-    <row r="14" spans="1:10" ht="12" customHeight="1"/>
-    <row r="15" spans="1:10" ht="12" customHeight="1">
+    <row r="14" spans="1:10" ht="12" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="15" spans="1:10" ht="12" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" s="352" t="s">
         <v>166</v>
       </c>
       <c r="G15" s="350"/>
     </row>
-    <row r="16" spans="1:10" ht="12" customHeight="1">
+    <row r="16" spans="1:10" ht="12" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A16" s="352" t="s">
         <v>167</v>
       </c>
     </row>
-    <row r="17" spans="1:11" ht="12" customHeight="1">
+    <row r="17" spans="1:11" ht="12" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A17" s="352" t="s">
         <v>168</v>
       </c>
       <c r="G17" s="350"/>
     </row>
-    <row r="18" spans="1:11" ht="12" customHeight="1"/>
-    <row r="19" spans="1:11" ht="12" customHeight="1">
+    <row r="18" spans="1:11" ht="12" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="19" spans="1:11" ht="12" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A19" s="353" t="s">
         <v>170</v>
       </c>
       <c r="G19" s="350"/>
     </row>
-    <row r="20" spans="1:11" ht="12" customHeight="1"/>
-    <row r="21" spans="1:11" ht="12" customHeight="1">
+    <row r="20" spans="1:11" ht="12" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="21" spans="1:11" ht="12" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A21" s="352" t="s">
         <v>171</v>
       </c>
       <c r="G21" s="350"/>
     </row>
-    <row r="22" spans="1:11" ht="17.25" customHeight="1"/>
-    <row r="23" spans="1:11" ht="12" customHeight="1">
+    <row r="22" spans="1:11" ht="17.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="23" spans="1:11" ht="12" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A23" s="351" t="s">
         <v>172</v>
       </c>
     </row>
-    <row r="24" spans="1:11" ht="12" customHeight="1"/>
-    <row r="25" spans="1:11" ht="12" customHeight="1"/>
-    <row r="26" spans="1:11" ht="12" customHeight="1"/>
-    <row r="27" spans="1:11" ht="12" customHeight="1">
+    <row r="24" spans="1:11" ht="12" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="25" spans="1:11" ht="12" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="26" spans="1:11" ht="12" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="27" spans="1:11" ht="12" customHeight="1" x14ac:dyDescent="0.2">
       <c r="K27" s="350"/>
     </row>
-    <row r="28" spans="1:11" ht="6" customHeight="1"/>
-    <row r="29" spans="1:11" ht="16.5" customHeight="1">
+    <row r="28" spans="1:11" ht="6" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="29" spans="1:11" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="F29" s="350"/>
     </row>
-    <row r="30" spans="1:11" ht="16.5" customHeight="1"/>
-    <row r="31" spans="1:11" ht="16.5" customHeight="1"/>
-    <row r="32" spans="1:11" ht="16.5" customHeight="1"/>
-    <row r="33" spans="1:10" ht="21.75" customHeight="1">
+    <row r="30" spans="1:11" ht="16.5" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="31" spans="1:11" ht="16.5" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="32" spans="1:11" ht="16.5" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="33" spans="1:10" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="I33" s="350"/>
     </row>
-    <row r="34" spans="1:10" ht="17.25" customHeight="1"/>
-    <row r="35" spans="1:10" ht="17.25" customHeight="1"/>
-    <row r="37" spans="1:10" ht="10.5" customHeight="1">
+    <row r="34" spans="1:10" ht="17.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="35" spans="1:10" ht="17.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="37" spans="1:10" ht="10.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="I37" s="337"/>
       <c r="J37" s="337"/>
     </row>
-    <row r="38" spans="1:10" ht="15.75" customHeight="1" thickBot="1">
-      <c r="A38" s="691" t="s">
+    <row r="38" spans="1:10" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A38" s="683" t="s">
         <v>304</v>
       </c>
-      <c r="B38" s="692"/>
-      <c r="C38" s="692"/>
-      <c r="D38" s="692"/>
-      <c r="E38" s="692"/>
-      <c r="F38" s="692"/>
-      <c r="G38" s="692"/>
-      <c r="H38" s="693"/>
+      <c r="B38" s="684"/>
+      <c r="C38" s="684"/>
+      <c r="D38" s="684"/>
+      <c r="E38" s="684"/>
+      <c r="F38" s="684"/>
+      <c r="G38" s="684"/>
+      <c r="H38" s="685"/>
       <c r="I38" s="337"/>
       <c r="J38" s="337"/>
     </row>
-    <row r="39" spans="1:10" ht="45" customHeight="1" thickBot="1">
+    <row r="39" spans="1:10" ht="45" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A39" s="244" t="s">
         <v>173</v>
       </c>
@@ -13273,7 +13273,7 @@
       </c>
       <c r="J39" s="337"/>
     </row>
-    <row r="40" spans="1:10" s="343" customFormat="1" ht="21.75" customHeight="1">
+    <row r="40" spans="1:10" s="343" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A40" s="234" t="s">
         <v>181</v>
       </c>
@@ -13302,7 +13302,7 @@
       <c r="I40" s="337"/>
       <c r="J40" s="342"/>
     </row>
-    <row r="41" spans="1:10" s="343" customFormat="1" ht="21.75" customHeight="1">
+    <row r="41" spans="1:10" s="343" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A41" s="268" t="s">
         <v>183</v>
       </c>
@@ -13333,7 +13333,7 @@
       </c>
       <c r="I41" s="337"/>
     </row>
-    <row r="42" spans="1:10" s="343" customFormat="1" ht="21.75" customHeight="1">
+    <row r="42" spans="1:10" s="343" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A42" s="235" t="s">
         <v>185</v>
       </c>
@@ -13360,7 +13360,7 @@
       </c>
       <c r="I42" s="337"/>
     </row>
-    <row r="43" spans="1:10" s="343" customFormat="1" ht="21.75" customHeight="1">
+    <row r="43" spans="1:10" s="343" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A43" s="235" t="s">
         <v>187</v>
       </c>
@@ -13387,7 +13387,7 @@
       </c>
       <c r="I43" s="337"/>
     </row>
-    <row r="44" spans="1:10" s="343" customFormat="1" ht="21.75" customHeight="1">
+    <row r="44" spans="1:10" s="343" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A44" s="235" t="s">
         <v>189</v>
       </c>
@@ -13414,7 +13414,7 @@
       </c>
       <c r="I44" s="337"/>
     </row>
-    <row r="45" spans="1:10" s="343" customFormat="1" ht="21.75" customHeight="1">
+    <row r="45" spans="1:10" s="343" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A45" s="268" t="s">
         <v>191</v>
       </c>
@@ -13444,7 +13444,7 @@
       <c r="I45" s="337"/>
       <c r="J45" s="337"/>
     </row>
-    <row r="46" spans="1:10" s="343" customFormat="1" ht="21.75" customHeight="1">
+    <row r="46" spans="1:10" s="343" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A46" s="235" t="s">
         <v>185</v>
       </c>
@@ -13472,7 +13472,7 @@
       <c r="I46" s="337"/>
       <c r="J46" s="337"/>
     </row>
-    <row r="47" spans="1:10" s="343" customFormat="1" ht="21.75" customHeight="1">
+    <row r="47" spans="1:10" s="343" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A47" s="235" t="s">
         <v>187</v>
       </c>
@@ -13500,7 +13500,7 @@
       <c r="I47" s="337"/>
       <c r="J47" s="337"/>
     </row>
-    <row r="48" spans="1:10" s="343" customFormat="1" ht="21.75" customHeight="1">
+    <row r="48" spans="1:10" s="343" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A48" s="235" t="s">
         <v>189</v>
       </c>
@@ -13528,7 +13528,7 @@
       <c r="I48" s="337"/>
       <c r="J48" s="337"/>
     </row>
-    <row r="49" spans="1:10" s="343" customFormat="1" ht="21.75" customHeight="1">
+    <row r="49" spans="1:10" s="343" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A49" s="268" t="s">
         <v>192</v>
       </c>
@@ -13558,7 +13558,7 @@
       <c r="I49" s="337"/>
       <c r="J49" s="337"/>
     </row>
-    <row r="50" spans="1:10" s="343" customFormat="1" ht="21.75" customHeight="1">
+    <row r="50" spans="1:10" s="343" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A50" s="235" t="s">
         <v>185</v>
       </c>
@@ -13586,7 +13586,7 @@
       <c r="I50" s="337"/>
       <c r="J50" s="337"/>
     </row>
-    <row r="51" spans="1:10" s="343" customFormat="1" ht="21.75" customHeight="1">
+    <row r="51" spans="1:10" s="343" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A51" s="235" t="s">
         <v>187</v>
       </c>
@@ -13614,7 +13614,7 @@
       <c r="I51" s="337"/>
       <c r="J51" s="337"/>
     </row>
-    <row r="52" spans="1:10" s="343" customFormat="1" ht="21.75" customHeight="1">
+    <row r="52" spans="1:10" s="343" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A52" s="235" t="s">
         <v>189</v>
       </c>
@@ -13642,7 +13642,7 @@
       <c r="I52" s="337"/>
       <c r="J52" s="337"/>
     </row>
-    <row r="53" spans="1:10" s="343" customFormat="1" ht="21.75" customHeight="1" thickBot="1">
+    <row r="53" spans="1:10" s="343" customFormat="1" ht="21.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A53" s="272" t="s">
         <v>193</v>
       </c>
@@ -13671,49 +13671,49 @@
       <c r="I53" s="337"/>
       <c r="J53" s="337"/>
     </row>
-    <row r="54" spans="1:10" s="343" customFormat="1" ht="16.5" customHeight="1">
-      <c r="A54" s="694" t="s">
+    <row r="54" spans="1:10" s="343" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A54" s="686" t="s">
         <v>195</v>
       </c>
-      <c r="B54" s="695"/>
-      <c r="C54" s="696"/>
+      <c r="B54" s="687"/>
+      <c r="C54" s="688"/>
       <c r="D54" s="280" t="s">
         <v>56</v>
       </c>
       <c r="E54" s="281"/>
-      <c r="F54" s="687" t="e">
+      <c r="F54" s="679" t="e">
         <f>SQRT((H41*H41)+(H45*H45)+(H49*H49)+(H53*H53))</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="G54" s="687"/>
-      <c r="H54" s="688"/>
+      <c r="G54" s="679"/>
+      <c r="H54" s="680"/>
       <c r="I54" s="337" t="s">
         <v>196</v>
       </c>
       <c r="J54" s="337"/>
     </row>
-    <row r="55" spans="1:10" s="343" customFormat="1" ht="18" customHeight="1" thickBot="1">
-      <c r="A55" s="697" t="s">
+    <row r="55" spans="1:10" s="343" customFormat="1" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A55" s="689" t="s">
         <v>197</v>
       </c>
-      <c r="B55" s="698"/>
-      <c r="C55" s="699"/>
+      <c r="B55" s="690"/>
+      <c r="C55" s="691"/>
       <c r="D55" s="308" t="s">
         <v>56</v>
       </c>
       <c r="E55" s="282"/>
-      <c r="F55" s="689" t="e">
+      <c r="F55" s="681" t="e">
         <f>F54*2</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="G55" s="689"/>
-      <c r="H55" s="690"/>
+      <c r="G55" s="681"/>
+      <c r="H55" s="682"/>
       <c r="I55" s="337" t="s">
         <v>198</v>
       </c>
       <c r="J55" s="337"/>
     </row>
-    <row r="56" spans="1:10" ht="15" customHeight="1">
+    <row r="56" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A56" s="337"/>
       <c r="D56" s="337"/>
       <c r="E56" s="337"/>
@@ -13723,7 +13723,7 @@
       <c r="I56" s="337"/>
       <c r="J56" s="337"/>
     </row>
-    <row r="57" spans="1:10" ht="15" customHeight="1">
+    <row r="57" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A57" s="337"/>
       <c r="D57" s="337"/>
       <c r="E57" s="337"/>
@@ -13733,7 +13733,7 @@
       <c r="I57" s="337"/>
       <c r="J57" s="337"/>
     </row>
-    <row r="58" spans="1:10" ht="15" customHeight="1">
+    <row r="58" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="E58" s="337"/>
       <c r="F58" s="337"/>
       <c r="G58" s="337"/>
@@ -13741,7 +13741,7 @@
       <c r="I58" s="337"/>
       <c r="J58" s="337"/>
     </row>
-    <row r="59" spans="1:10" ht="15" customHeight="1">
+    <row r="59" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B59" s="345" t="s">
         <v>305</v>
       </c>
@@ -13752,7 +13752,7 @@
       <c r="I59" s="337"/>
       <c r="J59" s="337"/>
     </row>
-    <row r="60" spans="1:10" ht="15" customHeight="1">
+    <row r="60" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A60" s="252"/>
       <c r="B60" s="228" t="s">
         <v>199</v>
@@ -13770,7 +13770,7 @@
       <c r="I60" s="337"/>
       <c r="J60" s="337"/>
     </row>
-    <row r="61" spans="1:10" ht="15" customHeight="1">
+    <row r="61" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A61" s="253"/>
       <c r="B61" s="346" t="str">
         <f>A41</f>
@@ -13791,7 +13791,7 @@
       <c r="I61" s="337"/>
       <c r="J61" s="337"/>
     </row>
-    <row r="62" spans="1:10" ht="15" customHeight="1">
+    <row r="62" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A62" s="253"/>
       <c r="B62" s="346" t="str">
         <f>A45</f>
@@ -13812,7 +13812,7 @@
       <c r="I62" s="337"/>
       <c r="J62" s="337"/>
     </row>
-    <row r="63" spans="1:10" ht="15" customHeight="1">
+    <row r="63" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A63" s="255"/>
       <c r="B63" s="347" t="str">
         <f>A49</f>
@@ -13833,7 +13833,7 @@
       <c r="I63" s="337"/>
       <c r="J63" s="337"/>
     </row>
-    <row r="64" spans="1:10" ht="15" customHeight="1">
+    <row r="64" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A64" s="255"/>
       <c r="B64" s="347" t="str">
         <f>A53</f>
@@ -13854,7 +13854,7 @@
       <c r="I64" s="337"/>
       <c r="J64" s="337"/>
     </row>
-    <row r="65" spans="1:10" ht="15" customHeight="1">
+    <row r="65" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A65" s="257"/>
       <c r="B65" s="258"/>
       <c r="C65" s="259" t="e">
@@ -13872,48 +13872,54 @@
       <c r="I65" s="337"/>
       <c r="J65" s="337"/>
     </row>
-    <row r="66" spans="1:10" ht="15" customHeight="1"/>
-    <row r="67" spans="1:10" ht="15" customHeight="1"/>
-    <row r="68" spans="1:10" ht="15" customHeight="1"/>
-    <row r="69" spans="1:10" ht="15" customHeight="1"/>
-    <row r="70" spans="1:10">
+    <row r="66" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="67" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="68" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="69" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="70" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A70" s="541" t="s">
         <v>306</v>
       </c>
-      <c r="B70" s="664" t="s">
+      <c r="B70" s="692" t="s">
         <v>307</v>
       </c>
-      <c r="C70" s="665"/>
+      <c r="C70" s="693"/>
       <c r="D70" s="542"/>
-      <c r="E70" s="666" t="s">
+      <c r="E70" s="694" t="s">
         <v>308</v>
       </c>
-      <c r="F70" s="666"/>
-      <c r="G70" s="667" t="s">
+      <c r="F70" s="694"/>
+      <c r="G70" s="695" t="s">
         <v>309</v>
       </c>
-      <c r="H70" s="668"/>
-    </row>
-    <row r="72" spans="1:10">
+      <c r="H70" s="696"/>
+    </row>
+    <row r="72" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A72" s="543" t="s">
         <v>310</v>
       </c>
-      <c r="B72" s="669">
+      <c r="B72" s="697">
         <v>44944</v>
       </c>
-      <c r="C72" s="670"/>
-      <c r="E72" s="671" t="s">
+      <c r="C72" s="698"/>
+      <c r="E72" s="699" t="s">
         <v>311</v>
       </c>
-      <c r="F72" s="671"/>
-      <c r="G72" s="669">
+      <c r="F72" s="699"/>
+      <c r="G72" s="697">
         <v>44944</v>
       </c>
-      <c r="H72" s="670"/>
+      <c r="H72" s="698"/>
     </row>
   </sheetData>
   <sheetProtection algorithmName="SHA-512" hashValue="iLEnVB6pm8HGxp/myiIucvHcjmqcSrUFV5EFJhRy/Wl6J20Lu8rufg9gJo4vTQR/wN6I3HZ06PN9TnsphGZBRg==" saltValue="rC1uvtCaR6F4sqhd68ayKA==" spinCount="100000" sheet="1" selectLockedCells="1" selectUnlockedCells="1"/>
   <mergeCells count="13">
+    <mergeCell ref="B70:C70"/>
+    <mergeCell ref="E70:F70"/>
+    <mergeCell ref="G70:H70"/>
+    <mergeCell ref="B72:C72"/>
+    <mergeCell ref="E72:F72"/>
+    <mergeCell ref="G72:H72"/>
     <mergeCell ref="C1:H4"/>
     <mergeCell ref="A1:B4"/>
     <mergeCell ref="F54:H54"/>
@@ -13921,12 +13927,6 @@
     <mergeCell ref="A38:H38"/>
     <mergeCell ref="A54:C54"/>
     <mergeCell ref="A55:C55"/>
-    <mergeCell ref="B70:C70"/>
-    <mergeCell ref="E70:F70"/>
-    <mergeCell ref="G70:H70"/>
-    <mergeCell ref="B72:C72"/>
-    <mergeCell ref="E72:F72"/>
-    <mergeCell ref="G72:H72"/>
   </mergeCells>
   <pageMargins left="0.70866141732283472" right="0.31496062992125984" top="0.74803149606299213" bottom="0.55118110236220474" header="0.31496062992125984" footer="0.31496062992125984"/>
   <pageSetup paperSize="9" scale="70" orientation="portrait" r:id="rId1"/>
@@ -13940,15 +13940,15 @@
             <anchor moveWithCells="1">
               <from>
                 <xdr:col>4</xdr:col>
-                <xdr:colOff>769620</xdr:colOff>
+                <xdr:colOff>771525</xdr:colOff>
                 <xdr:row>11</xdr:row>
-                <xdr:rowOff>83820</xdr:rowOff>
+                <xdr:rowOff>85725</xdr:rowOff>
               </from>
               <to>
                 <xdr:col>6</xdr:col>
-                <xdr:colOff>480060</xdr:colOff>
+                <xdr:colOff>476250</xdr:colOff>
                 <xdr:row>15</xdr:row>
-                <xdr:rowOff>60960</xdr:rowOff>
+                <xdr:rowOff>57150</xdr:rowOff>
               </to>
             </anchor>
           </objectPr>
@@ -13965,22 +13965,22 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <dimension ref="B2:O26"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11.44140625" defaultRowHeight="13.2"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.42578125" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="3" style="173" customWidth="1"/>
-    <col min="2" max="2" width="11.44140625" style="173"/>
-    <col min="3" max="3" width="10.33203125" style="173" customWidth="1"/>
+    <col min="2" max="2" width="11.42578125" style="173"/>
+    <col min="3" max="3" width="10.28515625" style="173" customWidth="1"/>
     <col min="4" max="4" width="12" style="173" customWidth="1"/>
-    <col min="5" max="7" width="11.44140625" style="173"/>
-    <col min="8" max="8" width="14.44140625" style="173" customWidth="1"/>
-    <col min="9" max="9" width="11.44140625" style="173"/>
-    <col min="10" max="10" width="11.88671875" style="173" customWidth="1"/>
-    <col min="11" max="11" width="9.88671875" style="173" customWidth="1"/>
-    <col min="12" max="15" width="12.109375" style="173" customWidth="1"/>
-    <col min="16" max="16384" width="11.44140625" style="173"/>
+    <col min="5" max="7" width="11.42578125" style="173"/>
+    <col min="8" max="8" width="14.42578125" style="173" customWidth="1"/>
+    <col min="9" max="9" width="11.42578125" style="173"/>
+    <col min="10" max="10" width="11.85546875" style="173" customWidth="1"/>
+    <col min="11" max="11" width="9.85546875" style="173" customWidth="1"/>
+    <col min="12" max="15" width="12.140625" style="173" customWidth="1"/>
+    <col min="16" max="16384" width="11.42578125" style="173"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:15">
+    <row r="2" spans="2:15" x14ac:dyDescent="0.2">
       <c r="B2" s="203" t="s">
         <v>201</v>
       </c>
@@ -13992,7 +13992,7 @@
       <c r="K2" s="204"/>
       <c r="L2" s="204"/>
     </row>
-    <row r="3" spans="2:15">
+    <row r="3" spans="2:15" x14ac:dyDescent="0.2">
       <c r="B3" s="289" t="s">
         <v>130</v>
       </c>
@@ -14007,7 +14007,7 @@
         <v>3.7900000000000001E-6</v>
       </c>
     </row>
-    <row r="4" spans="2:15">
+    <row r="4" spans="2:15" x14ac:dyDescent="0.2">
       <c r="B4" s="173" t="s">
         <v>202</v>
       </c>
@@ -14028,7 +14028,7 @@
         <v>2.3000000000000001E-10</v>
       </c>
     </row>
-    <row r="5" spans="2:15">
+    <row r="5" spans="2:15" x14ac:dyDescent="0.2">
       <c r="B5" s="173" t="s">
         <v>203</v>
       </c>
@@ -14045,7 +14045,7 @@
       </c>
       <c r="L5" s="289"/>
     </row>
-    <row r="6" spans="2:15">
+    <row r="6" spans="2:15" x14ac:dyDescent="0.2">
       <c r="B6" s="173" t="s">
         <v>204</v>
       </c>
@@ -14065,7 +14065,7 @@
       </c>
       <c r="L6" s="289"/>
     </row>
-    <row r="7" spans="2:15">
+    <row r="7" spans="2:15" x14ac:dyDescent="0.2">
       <c r="B7" s="173" t="s">
         <v>206</v>
       </c>
@@ -14081,7 +14081,7 @@
         <v>133</v>
       </c>
     </row>
-    <row r="8" spans="2:15">
+    <row r="8" spans="2:15" x14ac:dyDescent="0.2">
       <c r="B8" s="173" t="s">
         <v>300</v>
       </c>
@@ -14098,22 +14098,22 @@
         <v>46132</v>
       </c>
     </row>
-    <row r="9" spans="2:15">
+    <row r="9" spans="2:15" x14ac:dyDescent="0.2">
       <c r="B9" s="206"/>
       <c r="C9" s="205"/>
       <c r="J9" s="206"/>
     </row>
-    <row r="10" spans="2:15">
+    <row r="10" spans="2:15" x14ac:dyDescent="0.2">
       <c r="B10" s="206"/>
       <c r="C10" s="205"/>
       <c r="J10" s="206"/>
     </row>
-    <row r="11" spans="2:15">
+    <row r="11" spans="2:15" x14ac:dyDescent="0.2">
       <c r="B11" s="206"/>
       <c r="C11" s="205"/>
       <c r="J11" s="206"/>
     </row>
-    <row r="12" spans="2:15">
+    <row r="12" spans="2:15" x14ac:dyDescent="0.2">
       <c r="B12" s="209" t="s">
         <v>249</v>
       </c>
@@ -14154,7 +14154,7 @@
         <v>1000</v>
       </c>
     </row>
-    <row r="13" spans="2:15">
+    <row r="13" spans="2:15" x14ac:dyDescent="0.2">
       <c r="B13" s="359"/>
       <c r="C13" s="360"/>
       <c r="D13" s="299"/>
@@ -14169,7 +14169,7 @@
       <c r="N13" s="358"/>
       <c r="O13" s="358"/>
     </row>
-    <row r="14" spans="2:15">
+    <row r="14" spans="2:15" x14ac:dyDescent="0.2">
       <c r="B14" s="359"/>
       <c r="C14" s="360"/>
       <c r="D14" s="299"/>
@@ -14184,14 +14184,14 @@
       <c r="N14" s="358"/>
       <c r="O14" s="358"/>
     </row>
-    <row r="15" spans="2:15">
+    <row r="15" spans="2:15" x14ac:dyDescent="0.2">
       <c r="D15" s="210"/>
       <c r="E15" s="210"/>
       <c r="F15" s="210"/>
       <c r="G15" s="210"/>
       <c r="H15" s="210"/>
     </row>
-    <row r="16" spans="2:15">
+    <row r="16" spans="2:15" x14ac:dyDescent="0.2">
       <c r="B16" s="208"/>
       <c r="C16" s="207" t="s">
         <v>208</v>
@@ -14228,7 +14228,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="3:15">
+    <row r="18" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C18" s="700" t="s">
         <v>209</v>
       </c>
@@ -14246,7 +14246,7 @@
       <c r="N18" s="703"/>
       <c r="O18" s="704"/>
     </row>
-    <row r="19" spans="3:15">
+    <row r="19" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C19" s="213"/>
       <c r="D19" s="214"/>
       <c r="E19" s="214"/>
@@ -14260,7 +14260,7 @@
       <c r="N19" s="214"/>
       <c r="O19" s="215"/>
     </row>
-    <row r="20" spans="3:15" ht="15.75" customHeight="1">
+    <row r="20" spans="3:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C20" s="216"/>
       <c r="D20" s="208">
         <f>+D12</f>
@@ -14297,7 +14297,7 @@
       </c>
       <c r="O20" s="172"/>
     </row>
-    <row r="21" spans="3:15">
+    <row r="21" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C21" s="216"/>
       <c r="D21" s="211">
         <f>D16</f>
@@ -14338,7 +14338,7 @@
       </c>
       <c r="O21" s="172"/>
     </row>
-    <row r="22" spans="3:15">
+    <row r="22" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C22" s="216"/>
       <c r="G22" s="217"/>
       <c r="H22" s="215"/>
@@ -14349,7 +14349,7 @@
       <c r="N22" s="287"/>
       <c r="O22" s="172"/>
     </row>
-    <row r="23" spans="3:15">
+    <row r="23" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C23" s="216"/>
       <c r="D23" s="260"/>
       <c r="E23" s="261" t="s">
@@ -14379,7 +14379,7 @@
       </c>
       <c r="O23" s="172"/>
     </row>
-    <row r="24" spans="3:15">
+    <row r="24" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C24" s="216"/>
       <c r="D24" s="216"/>
       <c r="E24" s="262" t="s">
@@ -14409,7 +14409,7 @@
       </c>
       <c r="O24" s="172"/>
     </row>
-    <row r="25" spans="3:15">
+    <row r="25" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C25" s="216"/>
       <c r="D25" s="260"/>
       <c r="E25" s="295" t="s">
@@ -14439,7 +14439,7 @@
       </c>
       <c r="O25" s="172"/>
     </row>
-    <row r="26" spans="3:15">
+    <row r="26" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C26" s="218"/>
       <c r="D26" s="219"/>
       <c r="E26" s="219"/>
@@ -14468,28 +14468,28 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
   <dimension ref="B2:F12"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11.44140625" defaultRowHeight="13.2"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.42578125" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="6.6640625" style="201" customWidth="1"/>
-    <col min="2" max="2" width="38.88671875" style="201" customWidth="1"/>
-    <col min="3" max="5" width="11.44140625" style="201"/>
-    <col min="6" max="6" width="13.5546875" style="201" customWidth="1"/>
-    <col min="7" max="16384" width="11.44140625" style="201"/>
+    <col min="1" max="1" width="6.7109375" style="201" customWidth="1"/>
+    <col min="2" max="2" width="38.85546875" style="201" customWidth="1"/>
+    <col min="3" max="5" width="11.42578125" style="201"/>
+    <col min="6" max="6" width="13.5703125" style="201" customWidth="1"/>
+    <col min="7" max="16384" width="11.42578125" style="201"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:6">
+    <row r="2" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B2" s="285"/>
     </row>
-    <row r="3" spans="2:6">
+    <row r="3" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B3" s="284"/>
     </row>
-    <row r="4" spans="2:6">
+    <row r="4" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B4" s="285" t="s">
         <v>301</v>
       </c>
       <c r="C4" s="349"/>
     </row>
-    <row r="5" spans="2:6" ht="13.95" customHeight="1">
+    <row r="5" spans="2:6" ht="13.9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B5" s="284" t="s">
         <v>32</v>
       </c>
@@ -14497,11 +14497,11 @@
         <v>46064</v>
       </c>
     </row>
-    <row r="6" spans="2:6">
+    <row r="6" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B6" s="284"/>
       <c r="E6" s="284"/>
     </row>
-    <row r="7" spans="2:6" ht="15" customHeight="1">
+    <row r="7" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B7" s="283" t="s">
         <v>210</v>
       </c>
@@ -14512,7 +14512,7 @@
       <c r="E7" s="705"/>
       <c r="F7" s="284"/>
     </row>
-    <row r="8" spans="2:6" ht="15" customHeight="1">
+    <row r="8" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B8" s="283" t="s">
         <v>211</v>
       </c>
@@ -14523,10 +14523,10 @@
       <c r="E8" s="705"/>
       <c r="F8" s="284"/>
     </row>
-    <row r="9" spans="2:6" ht="15" customHeight="1"/>
-    <row r="10" spans="2:6" ht="15" customHeight="1"/>
-    <row r="11" spans="2:6" ht="15" customHeight="1"/>
-    <row r="12" spans="2:6" ht="15" customHeight="1"/>
+    <row r="9" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="10" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="11" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="12" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.2"/>
   </sheetData>
   <sheetProtection algorithmName="SHA-512" hashValue="fksItH3sKB6aMM9OjE11xpwc3b7QQ4B/ZgnDmR0PCCclYu+rmlI//dvWUv9w8mTKYTp/W81Rdw2DHPDsFl5ALw==" saltValue="fdRUkgooo9rZMN2n5fqfUw==" spinCount="100000" sheet="1" objects="1" scenarios="1"/>
   <mergeCells count="2">
@@ -14542,18 +14542,18 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
   <sheetPr codeName="Hoja3"/>
   <dimension ref="A2:M9"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11.44140625" defaultRowHeight="13.2"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.42578125" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="2" width="10.44140625" customWidth="1"/>
-    <col min="3" max="3" width="18.33203125" customWidth="1"/>
+    <col min="1" max="2" width="10.42578125" customWidth="1"/>
+    <col min="3" max="3" width="18.28515625" customWidth="1"/>
     <col min="4" max="4" width="20" customWidth="1"/>
-    <col min="6" max="6" width="12.44140625" customWidth="1"/>
-    <col min="11" max="11" width="17.6640625" customWidth="1"/>
-    <col min="12" max="12" width="12.44140625" customWidth="1"/>
-    <col min="13" max="13" width="15.44140625" customWidth="1"/>
+    <col min="6" max="6" width="12.42578125" customWidth="1"/>
+    <col min="11" max="11" width="17.7109375" customWidth="1"/>
+    <col min="12" max="12" width="12.42578125" customWidth="1"/>
+    <col min="13" max="13" width="15.42578125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:13" ht="18.75" customHeight="1">
+    <row r="2" spans="1:13" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="706" t="s">
         <v>212</v>
       </c>
@@ -14592,7 +14592,7 @@
         <v>223</v>
       </c>
     </row>
-    <row r="3" spans="1:13" ht="18.75" customHeight="1">
+    <row r="3" spans="1:13" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="7">
         <v>4400</v>
       </c>
@@ -14638,7 +14638,7 @@
         <v>225</v>
       </c>
     </row>
-    <row r="4" spans="1:13" ht="18.75" customHeight="1">
+    <row r="4" spans="1:13" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="1"/>
       <c r="B4" s="1"/>
       <c r="C4" s="6" t="str">
@@ -14675,7 +14675,7 @@
         <v>226</v>
       </c>
     </row>
-    <row r="5" spans="1:13" ht="18.75" customHeight="1">
+    <row r="5" spans="1:13" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="1">
         <f>+B3+1</f>
         <v>4402</v>
@@ -14718,7 +14718,7 @@
         <v>226</v>
       </c>
     </row>
-    <row r="6" spans="1:13" ht="18.75" customHeight="1">
+    <row r="6" spans="1:13" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="1"/>
       <c r="B6" s="1"/>
       <c r="C6" s="6" t="str">
@@ -14755,7 +14755,7 @@
         <v>226</v>
       </c>
     </row>
-    <row r="7" spans="1:13" ht="18.75" customHeight="1">
+    <row r="7" spans="1:13" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="1">
         <f>+B5+1</f>
         <v>4404</v>
@@ -14798,7 +14798,7 @@
         <v>226</v>
       </c>
     </row>
-    <row r="8" spans="1:13" ht="18.75" customHeight="1">
+    <row r="8" spans="1:13" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="1"/>
       <c r="B8" s="1"/>
       <c r="C8" s="6" t="str">
@@ -14835,7 +14835,7 @@
         <v>225</v>
       </c>
     </row>
-    <row r="9" spans="1:13" ht="15" customHeight="1"/>
+    <row r="9" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.2"/>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A2:B2"/>

--- a/app/templates/informes/Humedad ASTM D2216-19/1-INF.-N-000-26-SU20-HM-V07.XLSX
+++ b/app/templates/informes/Humedad ASTM D2216-19/1-INF.-N-000-26-SU20-HM-V07.XLSX
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="24332"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="27928"/>
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Mi unidad\3.0 Formatos e informes\2026\1.0 Informe de ensayo\1.1 Informe Suelo\INFORME ACREDITADO-E ISO\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Lenovo\Documents\crmnew\api-geofal-crm\app\templates\informes\Humedad ASTM D2216-19\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{83CB10A4-D8C2-4A78-8CE2-3645BCB75D3E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{727B4D86-4987-44C3-9DEE-9499B7EEE3C1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="723" firstSheet="1" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="723" firstSheet="1" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="informe NTP" sheetId="91" state="hidden" r:id="rId1"/>
@@ -1259,7 +1259,7 @@
     <numFmt numFmtId="186" formatCode="000\-\ &quot;26&quot;"/>
     <numFmt numFmtId="187" formatCode="&quot;FORMATO F-LEM-P-SU-11.01&quot;"/>
   </numFmts>
-  <fonts count="82" x14ac:knownFonts="1">
+  <fonts count="82">
     <font>
       <sz val="10"/>
       <name val="Arial"/>
@@ -4226,44 +4226,100 @@
     <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="3" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="4" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="3" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="6" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="38" fillId="8" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="38" fillId="8" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="38" fillId="8" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="38" fillId="8" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="42" fillId="8" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="42" fillId="8" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="166" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="169" fontId="20" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="176" fontId="25" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" xfId="4" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="7" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
       <protection hidden="1"/>
     </xf>
     <xf numFmtId="0" fontId="42" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="55" fillId="4" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="55" fillId="4" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="55" fillId="4" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="55" fillId="4" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="14" fontId="8" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" xfId="4" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="7" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
       <protection hidden="1"/>
     </xf>
     <xf numFmtId="0" fontId="16" fillId="9" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
@@ -4315,88 +4371,66 @@
       <alignment horizontal="left" vertical="center" wrapText="1"/>
       <protection hidden="1"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="4" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="55" fillId="4" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="55" fillId="4" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="55" fillId="4" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="55" fillId="4" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="8" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="3" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="48" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="6" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="48" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="38" fillId="8" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="25" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="187" fontId="25" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection hidden="1"/>
     </xf>
-    <xf numFmtId="0" fontId="38" fillId="8" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection hidden="1"/>
     </xf>
-    <xf numFmtId="0" fontId="38" fillId="8" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection hidden="1"/>
     </xf>
-    <xf numFmtId="0" fontId="38" fillId="8" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection hidden="1"/>
     </xf>
-    <xf numFmtId="0" fontId="42" fillId="8" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection hidden="1"/>
     </xf>
-    <xf numFmtId="0" fontId="42" fillId="8" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="166" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="3" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="169" fontId="20" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="176" fontId="25" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="2" borderId="0" xfId="9" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="16" fillId="2" borderId="1" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="1"/>
@@ -4405,28 +4439,33 @@
       <alignment horizontal="center" vertical="center"/>
       <protection hidden="1"/>
     </xf>
-    <xf numFmtId="16" fontId="16" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="2" borderId="0" xfId="2" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="29" fillId="2" borderId="10" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="2" borderId="11" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="2" borderId="12" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="2" borderId="1" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="16" fillId="2" borderId="10" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="16" fillId="2" borderId="11" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="16" fillId="2" borderId="12" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="38" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="38" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="16" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
@@ -4452,15 +4491,6 @@
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="167" fontId="16" fillId="2" borderId="10" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="167" fontId="16" fillId="2" borderId="11" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="167" fontId="16" fillId="2" borderId="12" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="38" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection hidden="1"/>
@@ -4481,61 +4511,54 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="38" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="38" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="16" fillId="2" borderId="0" xfId="9" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="29" fillId="2" borderId="10" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="2" borderId="11" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="2" borderId="12" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="2" borderId="1" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="48" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="16" fontId="16" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="2" borderId="0" xfId="2" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="4" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="48" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="187" fontId="25" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="42" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" xfId="4" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="4" quotePrefix="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="58" fillId="0" borderId="0" xfId="4" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" xfId="4" quotePrefix="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="184" fontId="25" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
@@ -4558,9 +4581,6 @@
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="4" quotePrefix="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="3" fontId="16" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -4578,19 +4598,6 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="42" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" xfId="4" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="58" fillId="0" borderId="0" xfId="4" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" xfId="4" quotePrefix="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center"/>
       <protection locked="0"/>
@@ -4599,12 +4606,14 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="4" quotePrefix="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" xfId="3" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="169" fontId="5" fillId="0" borderId="1" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="10" xfId="3" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -4642,13 +4651,28 @@
     <xf numFmtId="167" fontId="5" fillId="0" borderId="12" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" xfId="3" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="169" fontId="5" fillId="0" borderId="1" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="59" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="59" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="62" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="181" fontId="59" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="181" fontId="59" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="181" fontId="4" fillId="2" borderId="10" xfId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="181" fontId="4" fillId="2" borderId="12" xfId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="3" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="64" fillId="2" borderId="4" xfId="6" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -4735,30 +4759,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="2" fontId="16" fillId="2" borderId="40" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="59" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="59" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="62" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="181" fontId="59" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="181" fontId="59" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="181" fontId="4" fillId="2" borderId="10" xfId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="181" fontId="4" fillId="2" borderId="12" xfId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="3" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="65" fillId="2" borderId="1" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -6173,15 +6173,15 @@
       <xdr:twoCellAnchor editAs="oneCell">
         <xdr:from>
           <xdr:col>4</xdr:col>
-          <xdr:colOff>771525</xdr:colOff>
+          <xdr:colOff>769620</xdr:colOff>
           <xdr:row>11</xdr:row>
-          <xdr:rowOff>85725</xdr:rowOff>
+          <xdr:rowOff>83820</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>6</xdr:col>
-          <xdr:colOff>476250</xdr:colOff>
+          <xdr:colOff>480060</xdr:colOff>
           <xdr:row>15</xdr:row>
-          <xdr:rowOff>57150</xdr:rowOff>
+          <xdr:rowOff>60960</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
@@ -6523,7 +6523,7 @@
 </file>
 
 <file path=xl/externalLinks/externalLink1.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <sheetNames>
       <sheetName val="-------"/>
@@ -6582,7 +6582,7 @@
 </file>
 
 <file path=xl/externalLinks/externalLink2.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <sheetNames>
       <sheetName val="datos de ecuacion del anillo"/>
@@ -6701,7 +6701,7 @@
 </file>
 
 <file path=xl/externalLinks/externalLink3.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <sheetNames>
       <sheetName val="-------"/>
@@ -6752,7 +6752,7 @@
 </file>
 
 <file path=xl/externalLinks/externalLink4.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <sheetNames>
       <sheetName val="-------"/>
@@ -6804,7 +6804,7 @@
 </file>
 
 <file path=xl/externalLinks/externalLink5.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <sheetNames>
       <sheetName val="BGA"/>
@@ -6836,7 +6836,7 @@
 </file>
 
 <file path=xl/externalLinks/externalLink6.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <sheetNames>
       <sheetName val="-------"/>
@@ -7542,29 +7542,29 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr codeName="Hoja2"/>
   <dimension ref="A1:Z101"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="10.28515625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="10.33203125" defaultRowHeight="13.8"/>
   <cols>
-    <col min="1" max="1" width="16.28515625" style="15" customWidth="1"/>
+    <col min="1" max="1" width="16.33203125" style="15" customWidth="1"/>
     <col min="2" max="2" width="2" style="15" customWidth="1"/>
-    <col min="3" max="5" width="9.7109375" style="15" customWidth="1"/>
-    <col min="6" max="6" width="6.7109375" style="15" customWidth="1"/>
-    <col min="7" max="8" width="9.7109375" style="15" customWidth="1"/>
-    <col min="9" max="9" width="8.85546875" style="15" customWidth="1"/>
-    <col min="10" max="10" width="1.5703125" style="15" customWidth="1"/>
-    <col min="11" max="11" width="13.5703125" style="15" customWidth="1"/>
-    <col min="12" max="13" width="6.42578125" style="15" customWidth="1"/>
+    <col min="3" max="5" width="9.6640625" style="15" customWidth="1"/>
+    <col min="6" max="6" width="6.6640625" style="15" customWidth="1"/>
+    <col min="7" max="8" width="9.6640625" style="15" customWidth="1"/>
+    <col min="9" max="9" width="8.88671875" style="15" customWidth="1"/>
+    <col min="10" max="10" width="1.5546875" style="15" customWidth="1"/>
+    <col min="11" max="11" width="13.5546875" style="15" customWidth="1"/>
+    <col min="12" max="13" width="6.44140625" style="15" customWidth="1"/>
     <col min="14" max="14" width="8" style="15" customWidth="1"/>
-    <col min="15" max="15" width="10.28515625" style="15"/>
-    <col min="16" max="16" width="18.28515625" style="15" customWidth="1"/>
-    <col min="17" max="17" width="10.28515625" style="15"/>
+    <col min="15" max="15" width="10.33203125" style="15"/>
+    <col min="16" max="16" width="18.33203125" style="15" customWidth="1"/>
+    <col min="17" max="17" width="10.33203125" style="15"/>
     <col min="18" max="18" width="12" style="15" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="11.42578125" style="15" customWidth="1"/>
-    <col min="20" max="21" width="10.28515625" style="15"/>
-    <col min="22" max="22" width="12.42578125" style="15" customWidth="1"/>
-    <col min="23" max="16384" width="10.28515625" style="15"/>
+    <col min="19" max="19" width="11.44140625" style="15" customWidth="1"/>
+    <col min="20" max="21" width="10.33203125" style="15"/>
+    <col min="22" max="22" width="12.44140625" style="15" customWidth="1"/>
+    <col min="23" max="16384" width="10.33203125" style="15"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:18" ht="15.75" customHeight="1">
       <c r="A1" s="13"/>
       <c r="B1" s="13"/>
       <c r="C1" s="13"/>
@@ -7574,7 +7574,7 @@
       <c r="G1" s="14"/>
       <c r="H1" s="14"/>
     </row>
-    <row r="2" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:18" ht="15.75" customHeight="1">
       <c r="A2" s="13"/>
       <c r="B2" s="13"/>
       <c r="C2" s="13"/>
@@ -7584,7 +7584,7 @@
       <c r="G2" s="14"/>
       <c r="H2" s="14"/>
     </row>
-    <row r="3" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:18" ht="15.75" customHeight="1">
       <c r="A3" s="13"/>
       <c r="B3" s="13"/>
       <c r="C3" s="13"/>
@@ -7594,7 +7594,7 @@
       <c r="G3" s="14"/>
       <c r="H3" s="14"/>
     </row>
-    <row r="4" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:18" ht="15.75" customHeight="1">
       <c r="A4" s="13"/>
       <c r="B4" s="13"/>
       <c r="C4" s="13"/>
@@ -7604,7 +7604,7 @@
       <c r="G4" s="14"/>
       <c r="H4" s="14"/>
     </row>
-    <row r="5" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:18" ht="15.75" customHeight="1">
       <c r="A5" s="16"/>
       <c r="B5" s="16"/>
       <c r="C5" s="16"/>
@@ -7617,7 +7617,7 @@
       <c r="J5" s="16"/>
       <c r="K5" s="16"/>
     </row>
-    <row r="6" spans="1:18" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:18" ht="15.9" customHeight="1">
       <c r="A6" s="16"/>
       <c r="B6" s="16"/>
       <c r="C6" s="16"/>
@@ -7630,41 +7630,41 @@
       <c r="J6" s="16"/>
       <c r="K6" s="16"/>
     </row>
-    <row r="7" spans="1:18" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="567" t="s">
+    <row r="7" spans="1:18" ht="15.9" customHeight="1">
+      <c r="A7" s="544" t="s">
         <v>0</v>
       </c>
-      <c r="B7" s="567"/>
-      <c r="C7" s="567"/>
-      <c r="D7" s="567"/>
-      <c r="E7" s="567"/>
-      <c r="F7" s="567"/>
-      <c r="G7" s="567"/>
-      <c r="H7" s="567"/>
-      <c r="I7" s="567"/>
-      <c r="J7" s="567"/>
-      <c r="K7" s="567"/>
-    </row>
-    <row r="8" spans="1:18" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="587">
+      <c r="B7" s="544"/>
+      <c r="C7" s="544"/>
+      <c r="D7" s="544"/>
+      <c r="E7" s="544"/>
+      <c r="F7" s="544"/>
+      <c r="G7" s="544"/>
+      <c r="H7" s="544"/>
+      <c r="I7" s="544"/>
+      <c r="J7" s="544"/>
+      <c r="K7" s="544"/>
+    </row>
+    <row r="8" spans="1:18" ht="15.9" customHeight="1">
+      <c r="A8" s="565">
         <f>K13</f>
         <v>15</v>
       </c>
-      <c r="B8" s="587"/>
-      <c r="C8" s="587"/>
-      <c r="D8" s="587"/>
-      <c r="E8" s="587"/>
-      <c r="F8" s="587"/>
-      <c r="G8" s="587"/>
-      <c r="H8" s="587"/>
-      <c r="I8" s="587"/>
-      <c r="J8" s="587"/>
-      <c r="K8" s="587"/>
-    </row>
-    <row r="9" spans="1:18" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B8" s="565"/>
+      <c r="C8" s="565"/>
+      <c r="D8" s="565"/>
+      <c r="E8" s="565"/>
+      <c r="F8" s="565"/>
+      <c r="G8" s="565"/>
+      <c r="H8" s="565"/>
+      <c r="I8" s="565"/>
+      <c r="J8" s="565"/>
+      <c r="K8" s="565"/>
+    </row>
+    <row r="9" spans="1:18" ht="15.9" customHeight="1">
       <c r="P9" s="17"/>
     </row>
-    <row r="10" spans="1:18" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:18" ht="15.9" customHeight="1">
       <c r="A10" s="19" t="s">
         <v>1</v>
       </c>
@@ -7683,7 +7683,7 @@
       <c r="J10" s="18"/>
       <c r="K10" s="18"/>
     </row>
-    <row r="11" spans="1:18" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:18" ht="15.9" customHeight="1">
       <c r="A11" s="19" t="s">
         <v>4</v>
       </c>
@@ -7712,7 +7712,7 @@
       <c r="N11" s="25"/>
       <c r="P11" s="26"/>
     </row>
-    <row r="12" spans="1:18" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:18" ht="15.9" customHeight="1">
       <c r="A12" s="19" t="s">
         <v>8</v>
       </c>
@@ -7743,7 +7743,7 @@
       <c r="Q12" s="30"/>
       <c r="R12" s="31"/>
     </row>
-    <row r="13" spans="1:18" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:18" ht="15.9" customHeight="1">
       <c r="A13" s="19" t="s">
         <v>11</v>
       </c>
@@ -7770,10 +7770,10 @@
       <c r="L13" s="25"/>
       <c r="M13" s="25"/>
       <c r="N13" s="25"/>
-      <c r="Q13" s="578"/>
-      <c r="R13" s="578"/>
-    </row>
-    <row r="14" spans="1:18" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="Q13" s="556"/>
+      <c r="R13" s="556"/>
+    </row>
+    <row r="14" spans="1:18" ht="15.9" customHeight="1">
       <c r="A14" s="167" t="s">
         <v>14</v>
       </c>
@@ -7793,51 +7793,51 @@
       <c r="Q14" s="304"/>
       <c r="R14" s="304"/>
     </row>
-    <row r="15" spans="1:18" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="579" t="s">
+    <row r="15" spans="1:18" ht="18" customHeight="1">
+      <c r="A15" s="557" t="s">
         <v>15</v>
       </c>
-      <c r="B15" s="580"/>
-      <c r="C15" s="580"/>
-      <c r="D15" s="580"/>
-      <c r="E15" s="580"/>
-      <c r="F15" s="580"/>
-      <c r="G15" s="580"/>
-      <c r="H15" s="580"/>
-      <c r="I15" s="580"/>
-      <c r="J15" s="580"/>
-      <c r="K15" s="581"/>
+      <c r="B15" s="558"/>
+      <c r="C15" s="558"/>
+      <c r="D15" s="558"/>
+      <c r="E15" s="558"/>
+      <c r="F15" s="558"/>
+      <c r="G15" s="558"/>
+      <c r="H15" s="558"/>
+      <c r="I15" s="558"/>
+      <c r="J15" s="558"/>
+      <c r="K15" s="559"/>
       <c r="L15" s="25"/>
       <c r="M15" s="25"/>
       <c r="N15" s="25"/>
       <c r="Q15" s="304"/>
       <c r="R15" s="304"/>
     </row>
-    <row r="16" spans="1:18" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="584" t="s">
+    <row r="16" spans="1:18" ht="18" customHeight="1">
+      <c r="A16" s="562" t="s">
         <v>16</v>
       </c>
-      <c r="B16" s="585"/>
-      <c r="C16" s="585"/>
-      <c r="D16" s="585"/>
-      <c r="E16" s="585"/>
-      <c r="F16" s="585"/>
-      <c r="G16" s="585"/>
-      <c r="H16" s="585"/>
-      <c r="I16" s="585"/>
-      <c r="J16" s="585"/>
-      <c r="K16" s="586"/>
+      <c r="B16" s="563"/>
+      <c r="C16" s="563"/>
+      <c r="D16" s="563"/>
+      <c r="E16" s="563"/>
+      <c r="F16" s="563"/>
+      <c r="G16" s="563"/>
+      <c r="H16" s="563"/>
+      <c r="I16" s="563"/>
+      <c r="J16" s="563"/>
+      <c r="K16" s="564"/>
       <c r="L16" s="25"/>
       <c r="M16" s="25"/>
       <c r="N16" s="25"/>
       <c r="Q16" s="304"/>
       <c r="R16" s="304"/>
     </row>
-    <row r="17" spans="1:26" ht="11.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="568" t="s">
+    <row r="17" spans="1:26" ht="11.25" customHeight="1">
+      <c r="A17" s="545" t="s">
         <v>17</v>
       </c>
-      <c r="B17" s="569"/>
+      <c r="B17" s="546"/>
       <c r="C17" s="36"/>
       <c r="D17" s="36"/>
       <c r="E17" s="36"/>
@@ -7853,9 +7853,9 @@
       <c r="Q17" s="304"/>
       <c r="R17" s="304"/>
     </row>
-    <row r="18" spans="1:26" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="570"/>
-      <c r="B18" s="571"/>
+    <row r="18" spans="1:26" ht="15.9" customHeight="1">
+      <c r="A18" s="547"/>
+      <c r="B18" s="548"/>
       <c r="C18" s="39"/>
       <c r="D18" s="39"/>
       <c r="E18" s="39"/>
@@ -7887,7 +7887,7 @@
       <c r="Y18" s="83"/>
       <c r="Z18" s="84"/>
     </row>
-    <row r="19" spans="1:26" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:26" ht="15.9" customHeight="1">
       <c r="A19" s="40" t="s">
         <v>20</v>
       </c>
@@ -7929,7 +7929,7 @@
       <c r="Y19" s="89"/>
       <c r="Z19" s="90"/>
     </row>
-    <row r="20" spans="1:26" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:26" ht="15.9" customHeight="1">
       <c r="A20" s="40" t="s">
         <v>25</v>
       </c>
@@ -7971,7 +7971,7 @@
       <c r="Y20" s="89"/>
       <c r="Z20" s="90"/>
     </row>
-    <row r="21" spans="1:26" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:26" ht="15.9" customHeight="1">
       <c r="A21" s="40" t="s">
         <v>29</v>
       </c>
@@ -8000,10 +8000,10 @@
       <c r="P21" s="93" t="s">
         <v>32</v>
       </c>
-      <c r="Q21" s="550">
+      <c r="Q21" s="588">
         <v>44090</v>
       </c>
-      <c r="R21" s="550"/>
+      <c r="R21" s="588"/>
       <c r="S21" s="94"/>
       <c r="T21" s="95"/>
       <c r="U21" s="94"/>
@@ -8013,7 +8013,7 @@
       <c r="Y21" s="96"/>
       <c r="Z21" s="97"/>
     </row>
-    <row r="22" spans="1:26" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:26" ht="15" customHeight="1">
       <c r="A22" s="155" t="s">
         <v>33</v>
       </c>
@@ -8044,23 +8044,23 @@
       <c r="Y22"/>
       <c r="Z22"/>
     </row>
-    <row r="23" spans="1:26" ht="13.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:26" ht="13.5" customHeight="1" thickBot="1">
       <c r="A23" s="168"/>
-      <c r="B23" s="588"/>
-      <c r="C23" s="588"/>
+      <c r="B23" s="566"/>
+      <c r="C23" s="566"/>
       <c r="D23" s="306"/>
       <c r="E23" s="306"/>
       <c r="F23" s="306"/>
       <c r="G23" s="306"/>
       <c r="H23" s="306"/>
-      <c r="I23" s="588"/>
-      <c r="J23" s="588"/>
+      <c r="I23" s="566"/>
+      <c r="J23" s="566"/>
       <c r="K23" s="168"/>
       <c r="L23" s="25"/>
       <c r="M23" s="49"/>
       <c r="N23" s="49"/>
     </row>
-    <row r="24" spans="1:26" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:26" ht="17.25" customHeight="1">
       <c r="A24" s="171"/>
       <c r="B24" s="50" t="s">
         <v>35</v>
@@ -8076,8 +8076,8 @@
         <f>+R24</f>
         <v>1</v>
       </c>
-      <c r="I24" s="582"/>
-      <c r="J24" s="582"/>
+      <c r="I24" s="560"/>
+      <c r="J24" s="560"/>
       <c r="K24" s="305"/>
       <c r="L24" s="25"/>
       <c r="M24" s="54"/>
@@ -8091,23 +8091,23 @@
       <c r="R24" s="56">
         <v>1</v>
       </c>
-      <c r="S24" s="551" t="s">
+      <c r="S24" s="549" t="s">
         <v>37</v>
       </c>
       <c r="U24" s="56">
         <v>2</v>
       </c>
-      <c r="V24" s="551" t="s">
+      <c r="V24" s="549" t="s">
         <v>37</v>
       </c>
-      <c r="W24" s="546" t="s">
+      <c r="W24" s="584" t="s">
         <v>38</v>
       </c>
-      <c r="X24" s="546"/>
-      <c r="Y24" s="546"/>
-      <c r="Z24" s="547"/>
-    </row>
-    <row r="25" spans="1:26" ht="17.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="X24" s="584"/>
+      <c r="Y24" s="584"/>
+      <c r="Z24" s="585"/>
+    </row>
+    <row r="25" spans="1:26" ht="17.25" customHeight="1" thickBot="1">
       <c r="A25" s="171"/>
       <c r="B25" s="50" t="s">
         <v>39</v>
@@ -8123,8 +8123,8 @@
         <f>+R25</f>
         <v>1</v>
       </c>
-      <c r="I25" s="582"/>
-      <c r="J25" s="582"/>
+      <c r="I25" s="560"/>
+      <c r="J25" s="560"/>
       <c r="K25" s="305"/>
       <c r="L25" s="25"/>
       <c r="M25" s="54"/>
@@ -8138,17 +8138,17 @@
       <c r="R25" s="59">
         <v>1</v>
       </c>
-      <c r="S25" s="551"/>
+      <c r="S25" s="549"/>
       <c r="U25" s="59">
         <v>2</v>
       </c>
-      <c r="V25" s="551"/>
-      <c r="W25" s="548"/>
-      <c r="X25" s="548"/>
-      <c r="Y25" s="548"/>
-      <c r="Z25" s="549"/>
-    </row>
-    <row r="26" spans="1:26" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="V25" s="549"/>
+      <c r="W25" s="586"/>
+      <c r="X25" s="586"/>
+      <c r="Y25" s="586"/>
+      <c r="Z25" s="587"/>
+    </row>
+    <row r="26" spans="1:26" ht="17.25" customHeight="1">
       <c r="A26" s="171"/>
       <c r="B26" s="50" t="s">
         <v>40</v>
@@ -8164,8 +8164,8 @@
         <f>S26</f>
         <v>794.6995891401001</v>
       </c>
-      <c r="I26" s="583"/>
-      <c r="J26" s="583"/>
+      <c r="I26" s="561"/>
+      <c r="J26" s="561"/>
       <c r="K26" s="169"/>
       <c r="L26" s="60"/>
       <c r="M26" s="54"/>
@@ -8191,7 +8191,7 @@
         <v>793.69958965710009</v>
       </c>
     </row>
-    <row r="27" spans="1:26" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:26" ht="17.25" customHeight="1">
       <c r="A27" s="171"/>
       <c r="B27" s="50" t="s">
         <v>43</v>
@@ -8234,7 +8234,7 @@
         <v>775.79959891139993</v>
       </c>
     </row>
-    <row r="28" spans="1:26" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:26" ht="17.25" customHeight="1">
       <c r="A28" s="171"/>
       <c r="B28" s="50" t="s">
         <v>45</v>
@@ -8277,7 +8277,7 @@
         <v>775.79959891139993</v>
       </c>
     </row>
-    <row r="29" spans="1:26" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:26" ht="17.25" customHeight="1">
       <c r="A29" s="171"/>
       <c r="B29" s="50" t="s">
         <v>47</v>
@@ -8320,7 +8320,7 @@
         <v>775.79959891139993</v>
       </c>
     </row>
-    <row r="30" spans="1:26" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:26" ht="17.25" customHeight="1">
       <c r="A30" s="171"/>
       <c r="B30" s="50" t="s">
         <v>49</v>
@@ -8365,7 +8365,7 @@
         <v>17.899990745700165</v>
       </c>
     </row>
-    <row r="31" spans="1:26" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:26" ht="17.25" customHeight="1">
       <c r="A31" s="171"/>
       <c r="B31" s="50" t="s">
         <v>51</v>
@@ -8408,7 +8408,7 @@
         <v>163.1999156256</v>
       </c>
     </row>
-    <row r="32" spans="1:26" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:26" ht="17.25" customHeight="1">
       <c r="A32" s="62"/>
       <c r="B32" s="50" t="s">
         <v>53</v>
@@ -8453,7 +8453,7 @@
         <v>612.59968328579998</v>
       </c>
     </row>
-    <row r="33" spans="1:22" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:22" ht="17.25" customHeight="1">
       <c r="A33" s="171"/>
       <c r="B33" s="142" t="s">
         <v>55</v>
@@ -8498,7 +8498,7 @@
         <v>2.9219719229513821</v>
       </c>
     </row>
-    <row r="34" spans="1:22" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:22" ht="15.9" customHeight="1">
       <c r="B34" s="68" t="s">
         <v>58</v>
       </c>
@@ -8507,35 +8507,35 @@
       <c r="L34" s="25"/>
       <c r="M34" s="25"/>
       <c r="N34" s="25"/>
-      <c r="P34" s="572" t="s">
+      <c r="P34" s="550" t="s">
         <v>59</v>
       </c>
-      <c r="Q34" s="573"/>
-      <c r="R34" s="576" t="s">
+      <c r="Q34" s="551"/>
+      <c r="R34" s="554" t="s">
         <v>60</v>
       </c>
-      <c r="S34" s="576" t="s">
+      <c r="S34" s="554" t="s">
         <v>61</v>
       </c>
       <c r="T34" s="132"/>
       <c r="U34" s="132"/>
       <c r="V34" s="132"/>
     </row>
-    <row r="35" spans="1:22" ht="2.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:22" ht="2.25" customHeight="1">
       <c r="J35" s="61"/>
       <c r="K35" s="61"/>
       <c r="L35" s="25"/>
       <c r="M35" s="25"/>
       <c r="N35" s="25"/>
-      <c r="P35" s="574"/>
-      <c r="Q35" s="575"/>
-      <c r="R35" s="577"/>
-      <c r="S35" s="577"/>
+      <c r="P35" s="552"/>
+      <c r="Q35" s="553"/>
+      <c r="R35" s="555"/>
+      <c r="S35" s="555"/>
       <c r="T35" s="133"/>
       <c r="U35" s="132"/>
       <c r="V35" s="132"/>
     </row>
-    <row r="36" spans="1:22" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:22" ht="15.9" customHeight="1">
       <c r="A36" s="170" t="s">
         <v>62</v>
       </c>
@@ -8566,7 +8566,7 @@
       <c r="U36"/>
       <c r="V36" s="98"/>
     </row>
-    <row r="37" spans="1:22" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:22" ht="15.9" customHeight="1">
       <c r="A37" s="164" t="s">
         <v>66</v>
       </c>
@@ -8599,7 +8599,7 @@
       <c r="U37" s="135"/>
       <c r="V37" s="135"/>
     </row>
-    <row r="38" spans="1:22" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:22" ht="14.25" customHeight="1">
       <c r="A38" s="164" t="s">
         <v>71</v>
       </c>
@@ -8618,7 +8618,7 @@
       <c r="L38" s="25"/>
       <c r="M38" s="25"/>
       <c r="N38" s="25"/>
-      <c r="P38" s="554" t="s">
+      <c r="P38" s="570" t="s">
         <v>72</v>
       </c>
       <c r="Q38" s="108">
@@ -8634,17 +8634,17 @@
       <c r="U38" s="135"/>
       <c r="V38" s="135"/>
     </row>
-    <row r="39" spans="1:22" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A39" s="552" t="s">
+    <row r="39" spans="1:22" ht="14.25" customHeight="1">
+      <c r="A39" s="567" t="s">
         <v>75</v>
       </c>
-      <c r="B39" s="552"/>
-      <c r="C39" s="552"/>
-      <c r="D39" s="552"/>
-      <c r="E39" s="552"/>
-      <c r="F39" s="552"/>
-      <c r="G39" s="552"/>
-      <c r="H39" s="553"/>
+      <c r="B39" s="567"/>
+      <c r="C39" s="567"/>
+      <c r="D39" s="567"/>
+      <c r="E39" s="567"/>
+      <c r="F39" s="567"/>
+      <c r="G39" s="567"/>
+      <c r="H39" s="568"/>
       <c r="I39" s="166" t="s">
         <v>67</v>
       </c>
@@ -8653,7 +8653,7 @@
       <c r="L39" s="25"/>
       <c r="M39" s="25"/>
       <c r="N39" s="25"/>
-      <c r="P39" s="555"/>
+      <c r="P39" s="571"/>
       <c r="Q39" s="108">
         <v>0.75</v>
       </c>
@@ -8665,7 +8665,7 @@
       <c r="U39" s="135"/>
       <c r="V39" s="135"/>
     </row>
-    <row r="40" spans="1:22" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:22" ht="8.25" customHeight="1">
       <c r="A40" s="125"/>
       <c r="B40" s="126"/>
       <c r="C40" s="126"/>
@@ -8678,7 +8678,7 @@
       <c r="L40" s="25"/>
       <c r="M40" s="25"/>
       <c r="N40" s="25"/>
-      <c r="P40" s="555"/>
+      <c r="P40" s="571"/>
       <c r="Q40" s="108">
         <v>1.5</v>
       </c>
@@ -8690,7 +8690,7 @@
       <c r="U40" s="135"/>
       <c r="V40" s="135"/>
     </row>
-    <row r="41" spans="1:22" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:22" ht="15.9" customHeight="1">
       <c r="A41" s="69" t="s">
         <v>78</v>
       </c>
@@ -8705,7 +8705,7 @@
       <c r="L41" s="25"/>
       <c r="M41" s="25"/>
       <c r="N41" s="25"/>
-      <c r="P41" s="556"/>
+      <c r="P41" s="572"/>
       <c r="Q41" s="104">
         <v>3</v>
       </c>
@@ -8717,7 +8717,7 @@
       <c r="U41" s="135"/>
       <c r="V41" s="135"/>
     </row>
-    <row r="42" spans="1:22" ht="12" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:22" ht="12" customHeight="1">
       <c r="A42" s="153" t="s">
         <v>80</v>
       </c>
@@ -8746,7 +8746,7 @@
       <c r="U42" s="137"/>
       <c r="V42" s="137"/>
     </row>
-    <row r="43" spans="1:22" ht="12" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:22" ht="12" customHeight="1">
       <c r="A43" s="153" t="s">
         <v>82</v>
       </c>
@@ -8776,7 +8776,7 @@
       <c r="U43" s="99"/>
       <c r="V43" s="98"/>
     </row>
-    <row r="44" spans="1:22" ht="12" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:22" ht="12" customHeight="1">
       <c r="A44" s="153" t="s">
         <v>85</v>
       </c>
@@ -8808,7 +8808,7 @@
       <c r="U44" s="100"/>
       <c r="V44" s="101"/>
     </row>
-    <row r="45" spans="1:22" ht="12" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:22" ht="12" customHeight="1">
       <c r="A45" s="153" t="s">
         <v>87</v>
       </c>
@@ -8836,9 +8836,9 @@
       </c>
       <c r="T45" s="86"/>
       <c r="U45" s="102"/>
-      <c r="V45" s="545"/>
-    </row>
-    <row r="46" spans="1:22" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="V45" s="569"/>
+    </row>
+    <row r="46" spans="1:22" ht="15.9" customHeight="1">
       <c r="C46" s="42"/>
       <c r="D46" s="67"/>
       <c r="E46" s="67"/>
@@ -8862,9 +8862,9 @@
       </c>
       <c r="T46" s="86"/>
       <c r="U46" s="106"/>
-      <c r="V46" s="545"/>
-    </row>
-    <row r="47" spans="1:22" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="V46" s="569"/>
+    </row>
+    <row r="47" spans="1:22" ht="12.75" customHeight="1">
       <c r="A47" s="154" t="s">
         <v>91</v>
       </c>
@@ -8894,7 +8894,7 @@
       <c r="U47" s="106"/>
       <c r="V47" s="107"/>
     </row>
-    <row r="48" spans="1:22" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:22" ht="12.75" customHeight="1">
       <c r="A48" s="154" t="s">
         <v>93</v>
       </c>
@@ -8915,7 +8915,7 @@
       <c r="U48" s="109"/>
       <c r="V48" s="107"/>
     </row>
-    <row r="49" spans="1:22" ht="10.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:22" ht="10.5" customHeight="1">
       <c r="A49" s="77" t="s">
         <v>94</v>
       </c>
@@ -8932,7 +8932,7 @@
       <c r="U49" s="109"/>
       <c r="V49" s="107"/>
     </row>
-    <row r="50" spans="1:22" ht="10.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:22" ht="10.5" customHeight="1">
       <c r="A50" s="77" t="s">
         <v>95</v>
       </c>
@@ -8950,64 +8950,64 @@
       <c r="U50" s="110"/>
       <c r="V50" s="107"/>
     </row>
-    <row r="51" spans="1:22" ht="33" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A51" s="566" t="s">
+    <row r="51" spans="1:22" ht="33" customHeight="1">
+      <c r="A51" s="582" t="s">
         <v>96</v>
       </c>
-      <c r="B51" s="566"/>
-      <c r="C51" s="566"/>
-      <c r="D51" s="566"/>
-      <c r="E51" s="566"/>
-      <c r="F51" s="566"/>
-      <c r="G51" s="566"/>
-      <c r="H51" s="566"/>
-      <c r="I51" s="566"/>
-      <c r="J51" s="566"/>
-      <c r="K51" s="566"/>
+      <c r="B51" s="582"/>
+      <c r="C51" s="582"/>
+      <c r="D51" s="582"/>
+      <c r="E51" s="582"/>
+      <c r="F51" s="582"/>
+      <c r="G51" s="582"/>
+      <c r="H51" s="582"/>
+      <c r="I51" s="582"/>
+      <c r="J51" s="582"/>
+      <c r="K51" s="582"/>
       <c r="T51" s="86"/>
       <c r="U51" s="109"/>
       <c r="V51" s="107"/>
     </row>
-    <row r="52" spans="1:22" ht="11.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="H52" s="565" t="s">
+    <row r="52" spans="1:22" ht="11.25" customHeight="1">
+      <c r="H52" s="581" t="s">
         <v>97</v>
       </c>
-      <c r="I52" s="565"/>
-      <c r="J52" s="565"/>
-      <c r="K52" s="565"/>
+      <c r="I52" s="581"/>
+      <c r="J52" s="581"/>
+      <c r="K52" s="581"/>
       <c r="T52" s="86"/>
       <c r="U52" s="109"/>
       <c r="V52" s="107"/>
     </row>
-    <row r="53" spans="1:22" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:22" ht="15.9" customHeight="1">
       <c r="J53" s="70"/>
       <c r="K53" s="71"/>
       <c r="T53" s="117"/>
       <c r="U53" s="109"/>
       <c r="V53" s="107"/>
     </row>
-    <row r="54" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:22">
       <c r="J54" s="72"/>
       <c r="K54" s="71"/>
-      <c r="T54" s="544"/>
+      <c r="T54" s="583"/>
       <c r="U54" s="109"/>
       <c r="V54" s="107"/>
     </row>
-    <row r="55" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:22">
       <c r="J55"/>
       <c r="K55" s="71"/>
-      <c r="T55" s="544"/>
+      <c r="T55" s="583"/>
       <c r="U55" s="109"/>
       <c r="V55" s="107"/>
     </row>
-    <row r="56" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:22">
       <c r="J56"/>
       <c r="K56" s="71"/>
       <c r="T56" s="122"/>
       <c r="U56" s="109"/>
       <c r="V56" s="107"/>
     </row>
-    <row r="57" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:22">
       <c r="A57"/>
       <c r="B57"/>
       <c r="C57"/>
@@ -9022,7 +9022,7 @@
       <c r="U57" s="109"/>
       <c r="V57" s="107"/>
     </row>
-    <row r="58" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:22">
       <c r="A58" s="73"/>
       <c r="B58" s="73"/>
       <c r="C58" s="73"/>
@@ -9035,61 +9035,61 @@
       <c r="J58" s="73"/>
       <c r="K58" s="73"/>
     </row>
-    <row r="59" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A59" s="557" t="s">
+    <row r="59" spans="1:22">
+      <c r="A59" s="573" t="s">
         <v>98</v>
       </c>
-      <c r="B59" s="559"/>
-      <c r="C59" s="559"/>
-      <c r="D59" s="559"/>
-      <c r="E59" s="559"/>
-      <c r="F59" s="559"/>
-      <c r="G59" s="559"/>
-      <c r="H59" s="559"/>
-      <c r="I59" s="559"/>
-      <c r="J59" s="559"/>
-      <c r="K59" s="560"/>
-    </row>
-    <row r="60" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A60" s="558"/>
-      <c r="B60" s="561"/>
-      <c r="C60" s="561"/>
-      <c r="D60" s="561"/>
-      <c r="E60" s="561"/>
-      <c r="F60" s="561"/>
-      <c r="G60" s="561"/>
-      <c r="H60" s="561"/>
-      <c r="I60" s="561"/>
-      <c r="J60" s="561"/>
-      <c r="K60" s="562"/>
-    </row>
-    <row r="61" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="B59" s="575"/>
+      <c r="C59" s="575"/>
+      <c r="D59" s="575"/>
+      <c r="E59" s="575"/>
+      <c r="F59" s="575"/>
+      <c r="G59" s="575"/>
+      <c r="H59" s="575"/>
+      <c r="I59" s="575"/>
+      <c r="J59" s="575"/>
+      <c r="K59" s="576"/>
+    </row>
+    <row r="60" spans="1:22">
+      <c r="A60" s="574"/>
+      <c r="B60" s="577"/>
+      <c r="C60" s="577"/>
+      <c r="D60" s="577"/>
+      <c r="E60" s="577"/>
+      <c r="F60" s="577"/>
+      <c r="G60" s="577"/>
+      <c r="H60" s="577"/>
+      <c r="I60" s="577"/>
+      <c r="J60" s="577"/>
+      <c r="K60" s="578"/>
+    </row>
+    <row r="61" spans="1:22">
       <c r="A61" s="74"/>
-      <c r="B61" s="561"/>
-      <c r="C61" s="561"/>
-      <c r="D61" s="561"/>
-      <c r="E61" s="561"/>
-      <c r="F61" s="561"/>
-      <c r="G61" s="561"/>
-      <c r="H61" s="561"/>
-      <c r="I61" s="561"/>
-      <c r="J61" s="561"/>
-      <c r="K61" s="562"/>
-    </row>
-    <row r="62" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="B61" s="577"/>
+      <c r="C61" s="577"/>
+      <c r="D61" s="577"/>
+      <c r="E61" s="577"/>
+      <c r="F61" s="577"/>
+      <c r="G61" s="577"/>
+      <c r="H61" s="577"/>
+      <c r="I61" s="577"/>
+      <c r="J61" s="577"/>
+      <c r="K61" s="578"/>
+    </row>
+    <row r="62" spans="1:22">
       <c r="A62" s="75"/>
-      <c r="B62" s="563"/>
-      <c r="C62" s="563"/>
-      <c r="D62" s="563"/>
-      <c r="E62" s="563"/>
-      <c r="F62" s="563"/>
-      <c r="G62" s="563"/>
-      <c r="H62" s="563"/>
-      <c r="I62" s="563"/>
-      <c r="J62" s="563"/>
-      <c r="K62" s="564"/>
-    </row>
-    <row r="63" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="B62" s="579"/>
+      <c r="C62" s="579"/>
+      <c r="D62" s="579"/>
+      <c r="E62" s="579"/>
+      <c r="F62" s="579"/>
+      <c r="G62" s="579"/>
+      <c r="H62" s="579"/>
+      <c r="I62" s="579"/>
+      <c r="J62" s="579"/>
+      <c r="K62" s="580"/>
+    </row>
+    <row r="63" spans="1:22">
       <c r="A63" s="76"/>
       <c r="B63" s="76"/>
       <c r="C63" s="76"/>
@@ -9102,7 +9102,7 @@
       <c r="J63" s="76"/>
       <c r="K63" s="76"/>
     </row>
-    <row r="68" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:11">
       <c r="A68"/>
       <c r="B68"/>
       <c r="C68"/>
@@ -9115,7 +9115,7 @@
       <c r="J68"/>
       <c r="K68"/>
     </row>
-    <row r="69" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:11">
       <c r="A69"/>
       <c r="B69"/>
       <c r="C69"/>
@@ -9128,139 +9128,139 @@
       <c r="J69"/>
       <c r="K69"/>
     </row>
-    <row r="77" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:11">
       <c r="H77" s="98"/>
       <c r="I77" s="98"/>
       <c r="J77" s="98"/>
       <c r="K77"/>
     </row>
-    <row r="78" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:11">
       <c r="H78"/>
       <c r="I78"/>
       <c r="J78"/>
       <c r="K78"/>
     </row>
-    <row r="79" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:11">
       <c r="H79"/>
       <c r="I79"/>
       <c r="J79"/>
       <c r="K79"/>
     </row>
-    <row r="80" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:11">
       <c r="H80"/>
       <c r="I80"/>
       <c r="J80"/>
       <c r="K80"/>
     </row>
-    <row r="81" spans="8:11" x14ac:dyDescent="0.25">
+    <row r="81" spans="8:11">
       <c r="H81"/>
       <c r="I81"/>
       <c r="J81"/>
       <c r="K81"/>
     </row>
-    <row r="82" spans="8:11" x14ac:dyDescent="0.25">
+    <row r="82" spans="8:11">
       <c r="H82" s="98"/>
       <c r="I82" s="98"/>
       <c r="J82" s="98"/>
       <c r="K82"/>
     </row>
-    <row r="83" spans="8:11" x14ac:dyDescent="0.25">
+    <row r="83" spans="8:11">
       <c r="H83" s="98"/>
       <c r="I83" s="98"/>
       <c r="J83" s="98"/>
       <c r="K83"/>
     </row>
-    <row r="84" spans="8:11" x14ac:dyDescent="0.25">
+    <row r="84" spans="8:11">
       <c r="H84" s="98"/>
       <c r="I84" s="98"/>
       <c r="J84" s="98"/>
       <c r="K84"/>
     </row>
-    <row r="85" spans="8:11" x14ac:dyDescent="0.25">
+    <row r="85" spans="8:11">
       <c r="H85" s="101"/>
       <c r="I85" s="101"/>
       <c r="J85" s="101"/>
       <c r="K85"/>
     </row>
-    <row r="86" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H86" s="545"/>
-      <c r="I86" s="545"/>
-      <c r="J86" s="545"/>
+    <row r="86" spans="8:11">
+      <c r="H86" s="569"/>
+      <c r="I86" s="569"/>
+      <c r="J86" s="569"/>
       <c r="K86"/>
     </row>
-    <row r="87" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H87" s="545"/>
-      <c r="I87" s="545"/>
-      <c r="J87" s="545"/>
+    <row r="87" spans="8:11">
+      <c r="H87" s="569"/>
+      <c r="I87" s="569"/>
+      <c r="J87" s="569"/>
       <c r="K87"/>
     </row>
-    <row r="88" spans="8:11" x14ac:dyDescent="0.25">
+    <row r="88" spans="8:11">
       <c r="H88" s="107"/>
       <c r="I88" s="107"/>
       <c r="J88" s="107"/>
       <c r="K88"/>
     </row>
-    <row r="89" spans="8:11" x14ac:dyDescent="0.25">
+    <row r="89" spans="8:11">
       <c r="H89" s="107"/>
       <c r="I89" s="107"/>
       <c r="J89" s="107"/>
       <c r="K89"/>
     </row>
-    <row r="90" spans="8:11" x14ac:dyDescent="0.25">
+    <row r="90" spans="8:11">
       <c r="H90" s="107"/>
       <c r="I90" s="107"/>
       <c r="J90" s="107"/>
       <c r="K90"/>
     </row>
-    <row r="91" spans="8:11" x14ac:dyDescent="0.25">
+    <row r="91" spans="8:11">
       <c r="H91" s="107"/>
       <c r="I91" s="107"/>
       <c r="J91" s="107"/>
       <c r="K91"/>
     </row>
-    <row r="92" spans="8:11" x14ac:dyDescent="0.25">
+    <row r="92" spans="8:11">
       <c r="H92" s="107"/>
       <c r="I92" s="107"/>
       <c r="J92" s="107"/>
       <c r="K92"/>
     </row>
-    <row r="93" spans="8:11" x14ac:dyDescent="0.25">
+    <row r="93" spans="8:11">
       <c r="H93" s="107"/>
       <c r="I93" s="107"/>
       <c r="J93" s="107"/>
       <c r="K93"/>
     </row>
-    <row r="94" spans="8:11" x14ac:dyDescent="0.25">
+    <row r="94" spans="8:11">
       <c r="H94" s="107"/>
       <c r="I94" s="107"/>
       <c r="J94" s="107"/>
       <c r="K94"/>
     </row>
-    <row r="95" spans="8:11" x14ac:dyDescent="0.25">
+    <row r="95" spans="8:11">
       <c r="H95" s="107"/>
       <c r="I95" s="107"/>
       <c r="J95" s="107"/>
       <c r="K95"/>
     </row>
-    <row r="96" spans="8:11" x14ac:dyDescent="0.25">
+    <row r="96" spans="8:11">
       <c r="H96" s="107"/>
       <c r="I96" s="107"/>
       <c r="J96" s="107"/>
       <c r="K96"/>
     </row>
-    <row r="97" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:11">
       <c r="H97" s="107"/>
       <c r="I97" s="107"/>
       <c r="J97" s="107"/>
       <c r="K97"/>
     </row>
-    <row r="98" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:11">
       <c r="H98" s="107"/>
       <c r="I98" s="107"/>
       <c r="J98" s="107"/>
       <c r="K98"/>
     </row>
-    <row r="99" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:11">
       <c r="A99"/>
       <c r="B99"/>
       <c r="C99"/>
@@ -9273,7 +9273,7 @@
       <c r="J99"/>
       <c r="K99"/>
     </row>
-    <row r="100" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:11">
       <c r="A100"/>
       <c r="B100"/>
       <c r="C100"/>
@@ -9286,7 +9286,7 @@
       <c r="J100"/>
       <c r="K100"/>
     </row>
-    <row r="101" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:11">
       <c r="A101"/>
       <c r="B101"/>
       <c r="C101"/>
@@ -9305,6 +9305,20 @@
     <protectedRange sqref="C10:C11" name="Rango3_3_1_1_1_1_1_2_1"/>
   </protectedRanges>
   <mergeCells count="29">
+    <mergeCell ref="T54:T55"/>
+    <mergeCell ref="V45:V46"/>
+    <mergeCell ref="W24:Z25"/>
+    <mergeCell ref="Q21:R21"/>
+    <mergeCell ref="S24:S25"/>
+    <mergeCell ref="A39:H39"/>
+    <mergeCell ref="H86:H87"/>
+    <mergeCell ref="I86:I87"/>
+    <mergeCell ref="J86:J87"/>
+    <mergeCell ref="P38:P41"/>
+    <mergeCell ref="A59:A60"/>
+    <mergeCell ref="B59:K62"/>
+    <mergeCell ref="H52:K52"/>
+    <mergeCell ref="A51:K51"/>
     <mergeCell ref="A7:K7"/>
     <mergeCell ref="A17:B18"/>
     <mergeCell ref="V24:V25"/>
@@ -9320,20 +9334,6 @@
     <mergeCell ref="B23:C23"/>
     <mergeCell ref="I23:J23"/>
     <mergeCell ref="I24:J24"/>
-    <mergeCell ref="A39:H39"/>
-    <mergeCell ref="H86:H87"/>
-    <mergeCell ref="I86:I87"/>
-    <mergeCell ref="J86:J87"/>
-    <mergeCell ref="P38:P41"/>
-    <mergeCell ref="A59:A60"/>
-    <mergeCell ref="B59:K62"/>
-    <mergeCell ref="H52:K52"/>
-    <mergeCell ref="A51:K51"/>
-    <mergeCell ref="T54:T55"/>
-    <mergeCell ref="V45:V46"/>
-    <mergeCell ref="W24:Z25"/>
-    <mergeCell ref="Q21:R21"/>
-    <mergeCell ref="S24:S25"/>
   </mergeCells>
   <conditionalFormatting sqref="A39">
     <cfRule type="cellIs" priority="1" stopIfTrue="1" operator="between">
@@ -9355,27 +9355,27 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B701DF6C-5F27-49B6-872C-8C68C4082771}">
   <dimension ref="A1:W63"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="10.28515625" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="10.33203125" defaultRowHeight="13.8"/>
   <cols>
-    <col min="1" max="1" width="8.7109375" style="430" customWidth="1"/>
-    <col min="2" max="2" width="3.140625" style="430" customWidth="1"/>
-    <col min="3" max="3" width="10.85546875" style="430" customWidth="1"/>
-    <col min="4" max="4" width="14.42578125" style="430" customWidth="1"/>
-    <col min="5" max="5" width="10.85546875" style="430" customWidth="1"/>
-    <col min="6" max="6" width="11.28515625" style="430" customWidth="1"/>
+    <col min="1" max="1" width="8.6640625" style="430" customWidth="1"/>
+    <col min="2" max="2" width="3.109375" style="430" customWidth="1"/>
+    <col min="3" max="3" width="10.88671875" style="430" customWidth="1"/>
+    <col min="4" max="4" width="14.44140625" style="430" customWidth="1"/>
+    <col min="5" max="5" width="10.88671875" style="430" customWidth="1"/>
+    <col min="6" max="6" width="11.33203125" style="430" customWidth="1"/>
     <col min="7" max="7" width="3" style="430" customWidth="1"/>
-    <col min="8" max="8" width="9.28515625" style="430" customWidth="1"/>
-    <col min="9" max="9" width="16.85546875" style="430" customWidth="1"/>
-    <col min="10" max="10" width="6.7109375" style="430" customWidth="1"/>
-    <col min="11" max="11" width="8.42578125" style="430" customWidth="1"/>
-    <col min="12" max="12" width="2.140625" style="430" customWidth="1"/>
-    <col min="13" max="13" width="6.42578125" style="430" customWidth="1"/>
-    <col min="14" max="14" width="9.28515625" style="430" customWidth="1"/>
-    <col min="15" max="15" width="12.42578125" style="430" customWidth="1"/>
-    <col min="16" max="16384" width="10.28515625" style="430"/>
+    <col min="8" max="8" width="9.33203125" style="430" customWidth="1"/>
+    <col min="9" max="9" width="16.88671875" style="430" customWidth="1"/>
+    <col min="10" max="10" width="6.6640625" style="430" customWidth="1"/>
+    <col min="11" max="11" width="8.44140625" style="430" customWidth="1"/>
+    <col min="12" max="12" width="2.109375" style="430" customWidth="1"/>
+    <col min="13" max="13" width="6.44140625" style="430" customWidth="1"/>
+    <col min="14" max="14" width="9.33203125" style="430" customWidth="1"/>
+    <col min="15" max="15" width="12.44140625" style="430" customWidth="1"/>
+    <col min="16" max="16384" width="10.33203125" style="430"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16" ht="12.75" customHeight="1" thickTop="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:16" ht="12.75" customHeight="1" thickTop="1">
       <c r="A1" s="461"/>
       <c r="B1" s="462"/>
       <c r="C1" s="462"/>
@@ -9389,7 +9389,7 @@
       <c r="K1" s="464"/>
       <c r="L1" s="465"/>
     </row>
-    <row r="2" spans="1:16" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:16" ht="12.75" customHeight="1">
       <c r="A2" s="466"/>
       <c r="B2" s="467"/>
       <c r="C2" s="467"/>
@@ -9405,7 +9405,7 @@
       </c>
       <c r="P2" s="451"/>
     </row>
-    <row r="3" spans="1:16" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:16" ht="12.75" customHeight="1">
       <c r="A3" s="466"/>
       <c r="B3" s="467"/>
       <c r="C3" s="467"/>
@@ -9421,7 +9421,7 @@
       </c>
       <c r="P3" s="452"/>
     </row>
-    <row r="4" spans="1:16" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:16" ht="12.75" customHeight="1">
       <c r="A4" s="466"/>
       <c r="B4" s="467"/>
       <c r="C4" s="467"/>
@@ -9437,7 +9437,7 @@
       </c>
       <c r="P4" s="452"/>
     </row>
-    <row r="5" spans="1:16" ht="12.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:16" ht="12.75" customHeight="1" thickBot="1">
       <c r="A5" s="470"/>
       <c r="B5" s="471"/>
       <c r="C5" s="471"/>
@@ -9455,7 +9455,7 @@
       </c>
       <c r="P5" s="452"/>
     </row>
-    <row r="6" spans="1:16" ht="6.75" customHeight="1" thickTop="1" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:16" ht="6.75" customHeight="1" thickTop="1">
       <c r="A6" s="473"/>
       <c r="B6" s="473"/>
       <c r="C6" s="473"/>
@@ -9471,47 +9471,47 @@
       <c r="O6" s="453"/>
       <c r="P6" s="454"/>
     </row>
-    <row r="7" spans="1:16" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A7" s="620" t="s">
+    <row r="7" spans="1:16" ht="15.9" customHeight="1">
+      <c r="A7" s="591" t="s">
         <v>0</v>
       </c>
-      <c r="B7" s="620"/>
-      <c r="C7" s="620"/>
-      <c r="D7" s="620"/>
-      <c r="E7" s="620"/>
-      <c r="F7" s="620"/>
-      <c r="G7" s="620"/>
-      <c r="H7" s="620"/>
-      <c r="I7" s="620"/>
-      <c r="J7" s="620"/>
-      <c r="K7" s="620"/>
-      <c r="L7" s="620"/>
+      <c r="B7" s="591"/>
+      <c r="C7" s="591"/>
+      <c r="D7" s="591"/>
+      <c r="E7" s="591"/>
+      <c r="F7" s="591"/>
+      <c r="G7" s="591"/>
+      <c r="H7" s="591"/>
+      <c r="I7" s="591"/>
+      <c r="J7" s="591"/>
+      <c r="K7" s="591"/>
+      <c r="L7" s="591"/>
       <c r="O7" s="450" t="s">
         <v>233</v>
       </c>
       <c r="P7" s="454"/>
     </row>
-    <row r="8" spans="1:16" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="621" t="s">
+    <row r="8" spans="1:16" ht="15.9" customHeight="1">
+      <c r="A8" s="592" t="s">
         <v>250</v>
       </c>
-      <c r="B8" s="621"/>
-      <c r="C8" s="621"/>
-      <c r="D8" s="621"/>
-      <c r="E8" s="621"/>
-      <c r="F8" s="621"/>
-      <c r="G8" s="621"/>
-      <c r="H8" s="621"/>
-      <c r="I8" s="621"/>
-      <c r="J8" s="621"/>
-      <c r="K8" s="621"/>
-      <c r="L8" s="621"/>
+      <c r="B8" s="592"/>
+      <c r="C8" s="592"/>
+      <c r="D8" s="592"/>
+      <c r="E8" s="592"/>
+      <c r="F8" s="592"/>
+      <c r="G8" s="592"/>
+      <c r="H8" s="592"/>
+      <c r="I8" s="592"/>
+      <c r="J8" s="592"/>
+      <c r="K8" s="592"/>
+      <c r="L8" s="592"/>
       <c r="O8" s="450" t="s">
         <v>296</v>
       </c>
       <c r="P8" s="455"/>
     </row>
-    <row r="9" spans="1:16" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:16" ht="8.25" customHeight="1">
       <c r="A9" s="474"/>
       <c r="B9" s="474"/>
       <c r="C9" s="474"/>
@@ -9529,7 +9529,7 @@
       </c>
       <c r="P9" s="454"/>
     </row>
-    <row r="10" spans="1:16" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:16" ht="15.9" customHeight="1">
       <c r="A10" s="474"/>
       <c r="B10" s="474"/>
       <c r="D10" s="475" t="s">
@@ -9552,7 +9552,7 @@
       <c r="O10" s="453"/>
       <c r="P10" s="454"/>
     </row>
-    <row r="11" spans="1:16" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:16" ht="15.9" customHeight="1">
       <c r="A11" s="474"/>
       <c r="B11" s="474"/>
       <c r="C11" s="474"/>
@@ -9570,7 +9570,7 @@
       </c>
       <c r="P11" s="454"/>
     </row>
-    <row r="12" spans="1:16" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:16" ht="15.9" customHeight="1">
       <c r="A12" s="474"/>
       <c r="B12" s="474"/>
       <c r="C12" s="474"/>
@@ -9584,7 +9584,7 @@
       </c>
       <c r="P12" s="455"/>
     </row>
-    <row r="13" spans="1:16" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:16" ht="7.5" customHeight="1">
       <c r="A13" s="479"/>
       <c r="B13" s="480"/>
       <c r="C13" s="481"/>
@@ -9603,47 +9603,47 @@
       </c>
       <c r="P13" s="455"/>
     </row>
-    <row r="14" spans="1:16" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A14" s="622" t="s">
+    <row r="14" spans="1:16" ht="17.25" customHeight="1">
+      <c r="A14" s="593" t="s">
         <v>102</v>
       </c>
-      <c r="B14" s="623"/>
-      <c r="C14" s="623"/>
-      <c r="D14" s="623"/>
-      <c r="E14" s="623"/>
-      <c r="F14" s="623"/>
-      <c r="G14" s="623"/>
-      <c r="H14" s="623"/>
-      <c r="I14" s="623"/>
-      <c r="J14" s="623"/>
-      <c r="K14" s="623"/>
-      <c r="L14" s="624"/>
+      <c r="B14" s="594"/>
+      <c r="C14" s="594"/>
+      <c r="D14" s="594"/>
+      <c r="E14" s="594"/>
+      <c r="F14" s="594"/>
+      <c r="G14" s="594"/>
+      <c r="H14" s="594"/>
+      <c r="I14" s="594"/>
+      <c r="J14" s="594"/>
+      <c r="K14" s="594"/>
+      <c r="L14" s="595"/>
       <c r="M14" s="87"/>
       <c r="O14" s="453"/>
       <c r="P14" s="454"/>
     </row>
-    <row r="15" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A15" s="625" t="s">
+    <row r="15" spans="1:16" ht="15" customHeight="1">
+      <c r="A15" s="596" t="s">
         <v>103</v>
       </c>
-      <c r="B15" s="626"/>
-      <c r="C15" s="626"/>
-      <c r="D15" s="626"/>
-      <c r="E15" s="626"/>
-      <c r="F15" s="626"/>
-      <c r="G15" s="626"/>
-      <c r="H15" s="626"/>
-      <c r="I15" s="626"/>
-      <c r="J15" s="626"/>
-      <c r="K15" s="626"/>
-      <c r="L15" s="627"/>
+      <c r="B15" s="597"/>
+      <c r="C15" s="597"/>
+      <c r="D15" s="597"/>
+      <c r="E15" s="597"/>
+      <c r="F15" s="597"/>
+      <c r="G15" s="597"/>
+      <c r="H15" s="597"/>
+      <c r="I15" s="597"/>
+      <c r="J15" s="597"/>
+      <c r="K15" s="597"/>
+      <c r="L15" s="598"/>
       <c r="M15" s="87"/>
       <c r="O15" s="450" t="s">
         <v>104</v>
       </c>
       <c r="P15" s="456"/>
     </row>
-    <row r="16" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:16" ht="18" customHeight="1">
       <c r="A16" s="483"/>
       <c r="B16" s="484"/>
       <c r="C16" s="485"/>
@@ -9662,18 +9662,18 @@
       </c>
       <c r="P16" s="456"/>
     </row>
-    <row r="17" spans="1:19" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A17" s="618" t="s">
+    <row r="17" spans="1:19" ht="15.9" customHeight="1">
+      <c r="A17" s="589" t="s">
         <v>254</v>
       </c>
-      <c r="B17" s="619"/>
-      <c r="C17" s="619"/>
-      <c r="D17" s="619"/>
-      <c r="E17" s="619"/>
-      <c r="F17" s="619"/>
-      <c r="G17" s="619"/>
-      <c r="H17" s="619"/>
-      <c r="I17" s="619"/>
+      <c r="B17" s="590"/>
+      <c r="C17" s="590"/>
+      <c r="D17" s="590"/>
+      <c r="E17" s="590"/>
+      <c r="F17" s="590"/>
+      <c r="G17" s="590"/>
+      <c r="H17" s="590"/>
+      <c r="I17" s="590"/>
       <c r="J17" s="431"/>
       <c r="K17" s="431"/>
       <c r="L17" s="487"/>
@@ -9682,7 +9682,7 @@
       </c>
       <c r="P17" s="457"/>
     </row>
-    <row r="18" spans="1:19" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:19" ht="18" customHeight="1">
       <c r="A18" s="488" t="s">
         <v>120</v>
       </c>
@@ -9698,7 +9698,7 @@
       <c r="K18" s="431"/>
       <c r="L18" s="487"/>
     </row>
-    <row r="19" spans="1:19" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:19" ht="18" customHeight="1">
       <c r="A19" s="488" t="s">
         <v>255</v>
       </c>
@@ -9714,7 +9714,7 @@
       <c r="K19" s="431"/>
       <c r="L19" s="487"/>
     </row>
-    <row r="20" spans="1:19" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:19" ht="18" customHeight="1">
       <c r="A20" s="488" t="s">
         <v>122</v>
       </c>
@@ -9730,7 +9730,7 @@
       <c r="K20" s="431"/>
       <c r="L20" s="487"/>
     </row>
-    <row r="21" spans="1:19" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:19" ht="18" customHeight="1">
       <c r="A21" s="488" t="s">
         <v>123</v>
       </c>
@@ -9746,7 +9746,7 @@
       <c r="K21" s="431"/>
       <c r="L21" s="487"/>
     </row>
-    <row r="22" spans="1:19" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:19" ht="18" customHeight="1">
       <c r="A22" s="491" t="s">
         <v>293</v>
       </c>
@@ -9762,7 +9762,7 @@
       <c r="K22" s="431"/>
       <c r="L22" s="487"/>
     </row>
-    <row r="23" spans="1:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:19" ht="14.4" customHeight="1">
       <c r="A23" s="492"/>
       <c r="B23" s="432"/>
       <c r="C23" s="432"/>
@@ -9776,13 +9776,13 @@
       <c r="K23" s="431"/>
       <c r="L23" s="487"/>
     </row>
-    <row r="24" spans="1:19" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A24" s="618" t="s">
+    <row r="24" spans="1:19" ht="15.9" customHeight="1">
+      <c r="A24" s="589" t="s">
         <v>256</v>
       </c>
-      <c r="B24" s="619"/>
-      <c r="C24" s="619"/>
-      <c r="D24" s="619"/>
+      <c r="B24" s="590"/>
+      <c r="C24" s="590"/>
+      <c r="D24" s="590"/>
       <c r="E24" s="432"/>
       <c r="F24" s="432"/>
       <c r="G24" s="432"/>
@@ -9792,51 +9792,51 @@
       <c r="K24" s="431"/>
       <c r="L24" s="487"/>
     </row>
-    <row r="25" spans="1:19" ht="19.149999999999999" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A25" s="590" t="s">
+    <row r="25" spans="1:19" ht="19.2" customHeight="1">
+      <c r="A25" s="599" t="s">
         <v>257</v>
       </c>
-      <c r="B25" s="590"/>
-      <c r="C25" s="590"/>
-      <c r="D25" s="590"/>
-      <c r="E25" s="591"/>
-      <c r="F25" s="591"/>
+      <c r="B25" s="599"/>
+      <c r="C25" s="599"/>
+      <c r="D25" s="599"/>
+      <c r="E25" s="600"/>
+      <c r="F25" s="600"/>
       <c r="G25" s="433"/>
-      <c r="H25" s="614" t="s">
+      <c r="H25" s="601" t="s">
         <v>286</v>
       </c>
-      <c r="I25" s="615"/>
-      <c r="J25" s="616"/>
+      <c r="I25" s="602"/>
+      <c r="J25" s="603"/>
       <c r="K25" s="493"/>
       <c r="L25" s="487"/>
     </row>
-    <row r="26" spans="1:19" ht="19.149999999999999" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A26" s="590" t="s">
+    <row r="26" spans="1:19" ht="19.2" customHeight="1">
+      <c r="A26" s="599" t="s">
         <v>258</v>
       </c>
-      <c r="B26" s="590"/>
-      <c r="C26" s="590"/>
-      <c r="D26" s="590"/>
-      <c r="E26" s="591"/>
-      <c r="F26" s="591"/>
+      <c r="B26" s="599"/>
+      <c r="C26" s="599"/>
+      <c r="D26" s="599"/>
+      <c r="E26" s="600"/>
+      <c r="F26" s="600"/>
       <c r="G26" s="433"/>
-      <c r="H26" s="617" t="s">
+      <c r="H26" s="604" t="s">
         <v>287</v>
       </c>
-      <c r="I26" s="617"/>
+      <c r="I26" s="604"/>
       <c r="J26" s="434"/>
       <c r="K26" s="494"/>
       <c r="L26" s="487"/>
     </row>
-    <row r="27" spans="1:19" ht="19.149999999999999" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A27" s="590" t="s">
+    <row r="27" spans="1:19" ht="19.2" customHeight="1">
+      <c r="A27" s="599" t="s">
         <v>259</v>
       </c>
-      <c r="B27" s="590"/>
-      <c r="C27" s="590"/>
-      <c r="D27" s="590"/>
-      <c r="E27" s="591"/>
-      <c r="F27" s="591"/>
+      <c r="B27" s="599"/>
+      <c r="C27" s="599"/>
+      <c r="D27" s="599"/>
+      <c r="E27" s="600"/>
+      <c r="F27" s="600"/>
       <c r="G27" s="433"/>
       <c r="H27" s="446"/>
       <c r="I27" s="447"/>
@@ -9845,19 +9845,19 @@
       <c r="L27" s="487"/>
       <c r="M27" s="87"/>
     </row>
-    <row r="28" spans="1:19" ht="19.149999999999999" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A28" s="590" t="s">
+    <row r="28" spans="1:19" ht="19.2" customHeight="1">
+      <c r="A28" s="599" t="s">
         <v>288</v>
       </c>
-      <c r="B28" s="590"/>
-      <c r="C28" s="590"/>
-      <c r="D28" s="590"/>
-      <c r="E28" s="591"/>
-      <c r="F28" s="591"/>
+      <c r="B28" s="599"/>
+      <c r="C28" s="599"/>
+      <c r="D28" s="599"/>
+      <c r="E28" s="600"/>
+      <c r="F28" s="600"/>
       <c r="L28" s="495"/>
       <c r="M28" s="87"/>
     </row>
-    <row r="29" spans="1:19" ht="22.15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:19" ht="22.2" customHeight="1">
       <c r="A29" s="496"/>
       <c r="B29" s="497"/>
       <c r="C29" s="497"/>
@@ -9872,39 +9872,39 @@
       <c r="L29" s="500"/>
       <c r="M29" s="87"/>
     </row>
-    <row r="30" spans="1:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:19" ht="15.75" customHeight="1">
       <c r="A30" s="501"/>
-      <c r="B30" s="612" t="s">
+      <c r="B30" s="608" t="s">
         <v>261</v>
       </c>
-      <c r="C30" s="612"/>
-      <c r="D30" s="612"/>
-      <c r="E30" s="612"/>
-      <c r="F30" s="612"/>
-      <c r="G30" s="612"/>
+      <c r="C30" s="608"/>
+      <c r="D30" s="608"/>
+      <c r="E30" s="608"/>
+      <c r="F30" s="608"/>
+      <c r="G30" s="608"/>
       <c r="H30" s="502" t="s">
         <v>262</v>
       </c>
       <c r="I30" s="502" t="s">
         <v>263</v>
       </c>
-      <c r="J30" s="613"/>
-      <c r="K30" s="613"/>
+      <c r="J30" s="609"/>
+      <c r="K30" s="609"/>
       <c r="L30" s="503"/>
       <c r="M30" s="87"/>
     </row>
-    <row r="31" spans="1:19" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:19" ht="21.75" customHeight="1">
       <c r="A31" s="504"/>
       <c r="B31" s="505">
         <v>1</v>
       </c>
-      <c r="C31" s="604" t="s">
+      <c r="C31" s="605" t="s">
         <v>35</v>
       </c>
-      <c r="D31" s="605"/>
-      <c r="E31" s="605"/>
-      <c r="F31" s="605"/>
-      <c r="G31" s="606"/>
+      <c r="D31" s="606"/>
+      <c r="E31" s="606"/>
+      <c r="F31" s="606"/>
+      <c r="G31" s="607"/>
       <c r="H31" s="506" t="s">
         <v>36</v>
       </c>
@@ -9914,18 +9914,18 @@
       <c r="L31" s="509"/>
       <c r="M31" s="87"/>
     </row>
-    <row r="32" spans="1:19" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:19" ht="21.75" customHeight="1">
       <c r="A32" s="504"/>
       <c r="B32" s="510">
         <v>2</v>
       </c>
-      <c r="C32" s="604" t="s">
+      <c r="C32" s="605" t="s">
         <v>111</v>
       </c>
-      <c r="D32" s="605"/>
-      <c r="E32" s="605"/>
-      <c r="F32" s="605"/>
-      <c r="G32" s="606"/>
+      <c r="D32" s="606"/>
+      <c r="E32" s="606"/>
+      <c r="F32" s="606"/>
+      <c r="G32" s="607"/>
       <c r="H32" s="506" t="s">
         <v>36</v>
       </c>
@@ -9936,18 +9936,18 @@
       <c r="M32" s="87"/>
       <c r="S32" s="435"/>
     </row>
-    <row r="33" spans="1:23" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:23" ht="21.75" customHeight="1">
       <c r="A33" s="504"/>
       <c r="B33" s="510">
         <v>3</v>
       </c>
-      <c r="C33" s="604" t="s">
+      <c r="C33" s="605" t="s">
         <v>112</v>
       </c>
-      <c r="D33" s="605"/>
-      <c r="E33" s="605"/>
-      <c r="F33" s="605"/>
-      <c r="G33" s="606"/>
+      <c r="D33" s="606"/>
+      <c r="E33" s="606"/>
+      <c r="F33" s="606"/>
+      <c r="G33" s="607"/>
       <c r="H33" s="506" t="s">
         <v>184</v>
       </c>
@@ -9958,18 +9958,18 @@
       <c r="M33" s="436"/>
       <c r="W33" s="435"/>
     </row>
-    <row r="34" spans="1:23" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:23" ht="21.75" customHeight="1">
       <c r="A34" s="504"/>
       <c r="B34" s="505">
         <v>4</v>
       </c>
-      <c r="C34" s="604" t="s">
+      <c r="C34" s="605" t="s">
         <v>113</v>
       </c>
-      <c r="D34" s="605"/>
-      <c r="E34" s="605"/>
-      <c r="F34" s="605"/>
-      <c r="G34" s="606"/>
+      <c r="D34" s="606"/>
+      <c r="E34" s="606"/>
+      <c r="F34" s="606"/>
+      <c r="G34" s="607"/>
       <c r="H34" s="506" t="s">
         <v>184</v>
       </c>
@@ -9982,18 +9982,18 @@
       <c r="P34" s="437"/>
       <c r="W34" s="435"/>
     </row>
-    <row r="35" spans="1:23" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:23" ht="21.75" customHeight="1">
       <c r="A35" s="504"/>
       <c r="B35" s="510">
         <v>5</v>
       </c>
-      <c r="C35" s="604" t="s">
+      <c r="C35" s="605" t="s">
         <v>265</v>
       </c>
-      <c r="D35" s="605"/>
-      <c r="E35" s="605"/>
-      <c r="F35" s="605"/>
-      <c r="G35" s="606"/>
+      <c r="D35" s="606"/>
+      <c r="E35" s="606"/>
+      <c r="F35" s="606"/>
+      <c r="G35" s="607"/>
       <c r="H35" s="506" t="s">
         <v>184</v>
       </c>
@@ -10006,18 +10006,18 @@
       <c r="P35" s="437"/>
       <c r="W35" s="435"/>
     </row>
-    <row r="36" spans="1:23" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:23" ht="21.75" customHeight="1">
       <c r="A36" s="504"/>
       <c r="B36" s="505">
         <v>6</v>
       </c>
-      <c r="C36" s="604" t="s">
+      <c r="C36" s="605" t="s">
         <v>114</v>
       </c>
-      <c r="D36" s="605"/>
-      <c r="E36" s="605"/>
-      <c r="F36" s="605"/>
-      <c r="G36" s="606"/>
+      <c r="D36" s="606"/>
+      <c r="E36" s="606"/>
+      <c r="F36" s="606"/>
+      <c r="G36" s="607"/>
       <c r="H36" s="506" t="s">
         <v>184</v>
       </c>
@@ -10030,18 +10030,18 @@
       <c r="P36" s="437"/>
       <c r="W36" s="435"/>
     </row>
-    <row r="37" spans="1:23" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:23" ht="21.75" customHeight="1">
       <c r="A37" s="504"/>
       <c r="B37" s="510">
         <v>7</v>
       </c>
-      <c r="C37" s="604" t="s">
+      <c r="C37" s="605" t="s">
         <v>294</v>
       </c>
-      <c r="D37" s="605"/>
-      <c r="E37" s="605"/>
-      <c r="F37" s="605"/>
-      <c r="G37" s="606"/>
+      <c r="D37" s="606"/>
+      <c r="E37" s="606"/>
+      <c r="F37" s="606"/>
+      <c r="G37" s="607"/>
       <c r="H37" s="506" t="s">
         <v>184</v>
       </c>
@@ -10054,18 +10054,18 @@
       <c r="O37" s="437"/>
       <c r="P37" s="437"/>
     </row>
-    <row r="38" spans="1:23" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:23" ht="21.75" customHeight="1">
       <c r="A38" s="504"/>
       <c r="B38" s="510">
         <v>8</v>
       </c>
-      <c r="C38" s="604" t="s">
+      <c r="C38" s="605" t="s">
         <v>266</v>
       </c>
-      <c r="D38" s="605"/>
-      <c r="E38" s="605"/>
-      <c r="F38" s="605"/>
-      <c r="G38" s="606"/>
+      <c r="D38" s="606"/>
+      <c r="E38" s="606"/>
+      <c r="F38" s="606"/>
+      <c r="G38" s="607"/>
       <c r="H38" s="506" t="s">
         <v>184</v>
       </c>
@@ -10078,18 +10078,18 @@
       <c r="O38" s="440"/>
       <c r="P38" s="440"/>
     </row>
-    <row r="39" spans="1:23" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:23" ht="21.75" customHeight="1">
       <c r="A39" s="504"/>
       <c r="B39" s="505">
         <v>9</v>
       </c>
-      <c r="C39" s="604" t="s">
+      <c r="C39" s="605" t="s">
         <v>267</v>
       </c>
-      <c r="D39" s="605"/>
-      <c r="E39" s="605"/>
-      <c r="F39" s="605"/>
-      <c r="G39" s="606"/>
+      <c r="D39" s="606"/>
+      <c r="E39" s="606"/>
+      <c r="F39" s="606"/>
+      <c r="G39" s="607"/>
       <c r="H39" s="506" t="s">
         <v>56</v>
       </c>
@@ -10101,7 +10101,7 @@
       <c r="N39" s="441"/>
       <c r="O39" s="201"/>
     </row>
-    <row r="40" spans="1:23" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:23" ht="6.75" customHeight="1">
       <c r="A40" s="504"/>
       <c r="B40" s="498"/>
       <c r="C40" s="498"/>
@@ -10117,33 +10117,33 @@
       <c r="O40" s="201"/>
       <c r="W40" s="435"/>
     </row>
-    <row r="41" spans="1:23" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:23" ht="17.25" customHeight="1">
       <c r="A41" s="504"/>
-      <c r="B41" s="603" t="s">
+      <c r="B41" s="615" t="s">
         <v>268</v>
       </c>
-      <c r="C41" s="603"/>
-      <c r="D41" s="603"/>
-      <c r="E41" s="603"/>
-      <c r="F41" s="603"/>
+      <c r="C41" s="615"/>
+      <c r="D41" s="615"/>
+      <c r="E41" s="615"/>
+      <c r="F41" s="615"/>
       <c r="G41" s="515"/>
-      <c r="H41" s="607" t="s">
+      <c r="H41" s="616" t="s">
         <v>269</v>
       </c>
-      <c r="I41" s="608"/>
-      <c r="J41" s="609"/>
-      <c r="K41" s="609"/>
-      <c r="L41" s="608"/>
+      <c r="I41" s="617"/>
+      <c r="J41" s="618"/>
+      <c r="K41" s="618"/>
+      <c r="L41" s="617"/>
       <c r="M41" s="87"/>
       <c r="W41" s="435"/>
     </row>
-    <row r="42" spans="1:23" ht="26.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:23" ht="26.25" customHeight="1">
       <c r="A42" s="504"/>
-      <c r="B42" s="610" t="s">
+      <c r="B42" s="619" t="s">
         <v>270</v>
       </c>
-      <c r="C42" s="610"/>
-      <c r="D42" s="610"/>
+      <c r="C42" s="619"/>
+      <c r="D42" s="619"/>
       <c r="E42" s="516" t="s">
         <v>271</v>
       </c>
@@ -10151,23 +10151,23 @@
         <v>272</v>
       </c>
       <c r="G42" s="515"/>
-      <c r="H42" s="598" t="s">
+      <c r="H42" s="610" t="s">
         <v>273</v>
       </c>
-      <c r="I42" s="598"/>
-      <c r="J42" s="611"/>
-      <c r="K42" s="611"/>
-      <c r="L42" s="611"/>
+      <c r="I42" s="610"/>
+      <c r="J42" s="620"/>
+      <c r="K42" s="620"/>
+      <c r="L42" s="620"/>
       <c r="M42" s="87"/>
       <c r="W42" s="435"/>
     </row>
-    <row r="43" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:23" ht="15" customHeight="1">
       <c r="A43" s="504"/>
-      <c r="B43" s="596" t="s">
+      <c r="B43" s="626" t="s">
         <v>274</v>
       </c>
-      <c r="C43" s="596"/>
-      <c r="D43" s="596"/>
+      <c r="C43" s="626"/>
+      <c r="D43" s="626"/>
       <c r="E43" s="517" t="s">
         <v>142</v>
       </c>
@@ -10175,23 +10175,23 @@
         <v>275</v>
       </c>
       <c r="G43" s="515"/>
-      <c r="H43" s="598" t="s">
+      <c r="H43" s="610" t="s">
         <v>276</v>
       </c>
-      <c r="I43" s="598"/>
-      <c r="J43" s="599"/>
-      <c r="K43" s="599"/>
-      <c r="L43" s="600"/>
+      <c r="I43" s="610"/>
+      <c r="J43" s="611"/>
+      <c r="K43" s="611"/>
+      <c r="L43" s="612"/>
       <c r="M43" s="87"/>
       <c r="W43" s="435"/>
     </row>
-    <row r="44" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="44" spans="1:23" ht="15" customHeight="1">
       <c r="A44" s="504"/>
-      <c r="B44" s="596" t="s">
+      <c r="B44" s="626" t="s">
         <v>277</v>
       </c>
-      <c r="C44" s="596"/>
-      <c r="D44" s="596"/>
+      <c r="C44" s="626"/>
+      <c r="D44" s="626"/>
       <c r="E44" s="517" t="s">
         <v>144</v>
       </c>
@@ -10199,20 +10199,20 @@
         <v>275</v>
       </c>
       <c r="G44" s="515"/>
-      <c r="H44" s="598"/>
-      <c r="I44" s="598"/>
-      <c r="J44" s="601"/>
-      <c r="K44" s="601"/>
-      <c r="L44" s="602"/>
+      <c r="H44" s="610"/>
+      <c r="I44" s="610"/>
+      <c r="J44" s="613"/>
+      <c r="K44" s="613"/>
+      <c r="L44" s="614"/>
       <c r="M44" s="87"/>
     </row>
-    <row r="45" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="45" spans="1:23" ht="15" customHeight="1">
       <c r="A45" s="504"/>
-      <c r="B45" s="592" t="s">
+      <c r="B45" s="622" t="s">
         <v>278</v>
       </c>
-      <c r="C45" s="592"/>
-      <c r="D45" s="592"/>
+      <c r="C45" s="622"/>
+      <c r="D45" s="622"/>
       <c r="E45" s="517" t="s">
         <v>146</v>
       </c>
@@ -10220,39 +10220,39 @@
         <v>275</v>
       </c>
       <c r="G45" s="515"/>
-      <c r="H45" s="598" t="s">
+      <c r="H45" s="610" t="s">
         <v>279</v>
       </c>
-      <c r="I45" s="598"/>
-      <c r="J45" s="599"/>
-      <c r="K45" s="599"/>
-      <c r="L45" s="600"/>
+      <c r="I45" s="610"/>
+      <c r="J45" s="611"/>
+      <c r="K45" s="611"/>
+      <c r="L45" s="612"/>
       <c r="M45" s="87"/>
     </row>
-    <row r="46" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="46" spans="1:23" ht="15" customHeight="1">
       <c r="A46" s="504"/>
-      <c r="B46" s="603" t="s">
+      <c r="B46" s="615" t="s">
         <v>280</v>
       </c>
-      <c r="C46" s="603"/>
-      <c r="D46" s="603"/>
-      <c r="E46" s="603"/>
-      <c r="F46" s="603"/>
+      <c r="C46" s="615"/>
+      <c r="D46" s="615"/>
+      <c r="E46" s="615"/>
+      <c r="F46" s="615"/>
       <c r="G46" s="515"/>
-      <c r="H46" s="598"/>
-      <c r="I46" s="598"/>
-      <c r="J46" s="601"/>
-      <c r="K46" s="601"/>
-      <c r="L46" s="602"/>
+      <c r="H46" s="610"/>
+      <c r="I46" s="610"/>
+      <c r="J46" s="613"/>
+      <c r="K46" s="613"/>
+      <c r="L46" s="614"/>
       <c r="M46" s="87"/>
     </row>
-    <row r="47" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="47" spans="1:23" ht="15" customHeight="1">
       <c r="A47" s="504"/>
-      <c r="B47" s="592" t="s">
+      <c r="B47" s="622" t="s">
         <v>281</v>
       </c>
-      <c r="C47" s="592"/>
-      <c r="D47" s="592"/>
+      <c r="C47" s="622"/>
+      <c r="D47" s="622"/>
       <c r="E47" s="517" t="s">
         <v>148</v>
       </c>
@@ -10260,20 +10260,20 @@
         <v>282</v>
       </c>
       <c r="G47" s="515"/>
-      <c r="H47" s="593"/>
-      <c r="I47" s="593"/>
-      <c r="J47" s="594"/>
-      <c r="K47" s="594"/>
-      <c r="L47" s="595"/>
+      <c r="H47" s="623"/>
+      <c r="I47" s="623"/>
+      <c r="J47" s="624"/>
+      <c r="K47" s="624"/>
+      <c r="L47" s="625"/>
       <c r="M47" s="87"/>
     </row>
-    <row r="48" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="48" spans="1:23" ht="15" customHeight="1">
       <c r="A48" s="504"/>
-      <c r="B48" s="596" t="s">
+      <c r="B48" s="626" t="s">
         <v>149</v>
       </c>
-      <c r="C48" s="596"/>
-      <c r="D48" s="596"/>
+      <c r="C48" s="626"/>
+      <c r="D48" s="626"/>
       <c r="E48" s="517" t="s">
         <v>146</v>
       </c>
@@ -10281,20 +10281,20 @@
         <v>282</v>
       </c>
       <c r="G48" s="515"/>
-      <c r="H48" s="593"/>
-      <c r="I48" s="593"/>
-      <c r="J48" s="594"/>
-      <c r="K48" s="594"/>
-      <c r="L48" s="595"/>
+      <c r="H48" s="623"/>
+      <c r="I48" s="623"/>
+      <c r="J48" s="624"/>
+      <c r="K48" s="624"/>
+      <c r="L48" s="625"/>
       <c r="M48" s="87"/>
     </row>
-    <row r="49" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="49" spans="1:13" ht="15" customHeight="1">
       <c r="A49" s="504"/>
-      <c r="B49" s="596" t="s">
+      <c r="B49" s="626" t="s">
         <v>151</v>
       </c>
-      <c r="C49" s="596"/>
-      <c r="D49" s="596"/>
+      <c r="C49" s="626"/>
+      <c r="D49" s="626"/>
       <c r="E49" s="517" t="s">
         <v>146</v>
       </c>
@@ -10309,7 +10309,7 @@
       <c r="L49" s="520"/>
       <c r="M49" s="87"/>
     </row>
-    <row r="50" spans="1:13" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="50" spans="1:13" ht="18.75" customHeight="1">
       <c r="A50" s="521"/>
       <c r="B50" s="522" t="s">
         <v>283</v>
@@ -10326,7 +10326,7 @@
       <c r="L50" s="528"/>
       <c r="M50" s="87"/>
     </row>
-    <row r="51" spans="1:13" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="51" spans="1:13" ht="7.5" customHeight="1">
       <c r="A51" s="529"/>
       <c r="B51" s="435"/>
       <c r="C51" s="435"/>
@@ -10341,7 +10341,7 @@
       <c r="L51" s="435"/>
       <c r="M51" s="87"/>
     </row>
-    <row r="52" spans="1:13" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="52" spans="1:13" ht="22.5" customHeight="1">
       <c r="A52" s="532" t="s">
         <v>98</v>
       </c>
@@ -10358,7 +10358,7 @@
       <c r="L52" s="526"/>
       <c r="M52" s="87"/>
     </row>
-    <row r="53" spans="1:13" ht="25.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="53" spans="1:13" ht="25.5" customHeight="1">
       <c r="A53" s="533"/>
       <c r="B53" s="527"/>
       <c r="C53" s="527"/>
@@ -10373,7 +10373,7 @@
       <c r="L53" s="526"/>
       <c r="M53" s="87"/>
     </row>
-    <row r="54" spans="1:13" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="54" spans="1:13" ht="6.75" customHeight="1">
       <c r="A54" s="534"/>
       <c r="B54" s="435"/>
       <c r="C54" s="435"/>
@@ -10388,7 +10388,7 @@
       <c r="L54" s="536"/>
       <c r="M54" s="87"/>
     </row>
-    <row r="55" spans="1:13" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="55" spans="1:13" ht="30" customHeight="1">
       <c r="A55" s="534"/>
       <c r="B55" s="435"/>
       <c r="C55" s="435"/>
@@ -10403,7 +10403,7 @@
       <c r="L55" s="435"/>
       <c r="M55" s="87"/>
     </row>
-    <row r="56" spans="1:13" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="56" spans="1:13" ht="15.9" customHeight="1">
       <c r="A56" s="537"/>
       <c r="B56" s="435"/>
       <c r="J56" s="435"/>
@@ -10411,21 +10411,21 @@
       <c r="L56" s="435"/>
       <c r="M56" s="87"/>
     </row>
-    <row r="57" spans="1:13" ht="4.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B57" s="597"/>
-      <c r="C57" s="597"/>
-      <c r="D57" s="597"/>
-      <c r="E57" s="597"/>
-      <c r="F57" s="597"/>
-      <c r="G57" s="597"/>
-      <c r="H57" s="597"/>
-      <c r="I57" s="597"/>
-      <c r="J57" s="597"/>
+    <row r="57" spans="1:13" ht="4.5" customHeight="1">
+      <c r="B57" s="627"/>
+      <c r="C57" s="627"/>
+      <c r="D57" s="627"/>
+      <c r="E57" s="627"/>
+      <c r="F57" s="627"/>
+      <c r="G57" s="627"/>
+      <c r="H57" s="627"/>
+      <c r="I57" s="627"/>
+      <c r="J57" s="627"/>
       <c r="K57" s="480"/>
       <c r="L57" s="435"/>
       <c r="M57" s="87"/>
     </row>
-    <row r="58" spans="1:13" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="58" spans="1:13" ht="15.9" customHeight="1">
       <c r="A58" s="538" t="s">
         <v>91</v>
       </c>
@@ -10442,7 +10442,7 @@
       <c r="L58" s="435"/>
       <c r="M58" s="87"/>
     </row>
-    <row r="59" spans="1:13" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="59" spans="1:13" ht="15.9" customHeight="1">
       <c r="A59" s="538" t="s">
         <v>295</v>
       </c>
@@ -10461,25 +10461,25 @@
       <c r="L59" s="435"/>
       <c r="M59" s="87"/>
     </row>
-    <row r="60" spans="1:13" ht="3.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="61" spans="1:13" ht="30.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A61" s="589" t="s">
+    <row r="60" spans="1:13" ht="3.75" customHeight="1"/>
+    <row r="61" spans="1:13" ht="30.75" customHeight="1">
+      <c r="A61" s="621" t="s">
         <v>285</v>
       </c>
-      <c r="B61" s="589"/>
-      <c r="C61" s="589"/>
-      <c r="D61" s="589"/>
-      <c r="E61" s="589"/>
-      <c r="F61" s="589"/>
-      <c r="G61" s="589"/>
-      <c r="H61" s="589"/>
-      <c r="I61" s="589"/>
-      <c r="J61" s="589"/>
-      <c r="K61" s="589"/>
-      <c r="L61" s="589"/>
-    </row>
-    <row r="62" spans="1:13" ht="15.95" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="63" spans="1:13" ht="15.95" customHeight="1" x14ac:dyDescent="0.2"/>
+      <c r="B61" s="621"/>
+      <c r="C61" s="621"/>
+      <c r="D61" s="621"/>
+      <c r="E61" s="621"/>
+      <c r="F61" s="621"/>
+      <c r="G61" s="621"/>
+      <c r="H61" s="621"/>
+      <c r="I61" s="621"/>
+      <c r="J61" s="621"/>
+      <c r="K61" s="621"/>
+      <c r="L61" s="621"/>
+    </row>
+    <row r="62" spans="1:13" ht="15.9" customHeight="1"/>
+    <row r="63" spans="1:13" ht="15.9" customHeight="1"/>
   </sheetData>
   <sheetProtection algorithmName="SHA-512" hashValue="zFaKPAn6ViOpya0rqSfRP+lf5nP0Stsd4GeHYr5E3M4pf5abxDHp7CyitZu3QfPbBPFWYk0mv07jVBjbhu2ckg==" saltValue="VTj2SwRAYFQHMWaCbVSW8A==" spinCount="100000" sheet="1" objects="1" scenarios="1"/>
   <protectedRanges>
@@ -10487,40 +10487,6 @@
     <protectedRange sqref="C57" name="Rango3_3_1_1_1_1_1_2_1"/>
   </protectedRanges>
   <mergeCells count="50">
-    <mergeCell ref="A24:D24"/>
-    <mergeCell ref="A7:L7"/>
-    <mergeCell ref="A8:L8"/>
-    <mergeCell ref="A14:L14"/>
-    <mergeCell ref="A15:L15"/>
-    <mergeCell ref="A17:I17"/>
-    <mergeCell ref="A25:D25"/>
-    <mergeCell ref="E25:F25"/>
-    <mergeCell ref="H25:J25"/>
-    <mergeCell ref="A26:D26"/>
-    <mergeCell ref="E26:F26"/>
-    <mergeCell ref="H26:I26"/>
-    <mergeCell ref="C37:G37"/>
-    <mergeCell ref="A27:D27"/>
-    <mergeCell ref="E27:F27"/>
-    <mergeCell ref="B30:G30"/>
-    <mergeCell ref="J30:K30"/>
-    <mergeCell ref="C31:G31"/>
-    <mergeCell ref="C32:G32"/>
-    <mergeCell ref="C33:G33"/>
-    <mergeCell ref="C34:G34"/>
-    <mergeCell ref="C35:G35"/>
-    <mergeCell ref="C36:G36"/>
-    <mergeCell ref="H45:I46"/>
-    <mergeCell ref="J45:L46"/>
-    <mergeCell ref="B46:F46"/>
-    <mergeCell ref="C38:G38"/>
-    <mergeCell ref="C39:G39"/>
-    <mergeCell ref="B41:F41"/>
-    <mergeCell ref="H41:I41"/>
-    <mergeCell ref="J41:L41"/>
-    <mergeCell ref="B42:D42"/>
-    <mergeCell ref="H42:I42"/>
-    <mergeCell ref="J42:L42"/>
     <mergeCell ref="A61:L61"/>
     <mergeCell ref="A28:D28"/>
     <mergeCell ref="E28:F28"/>
@@ -10537,6 +10503,40 @@
     <mergeCell ref="J43:L44"/>
     <mergeCell ref="B44:D44"/>
     <mergeCell ref="B45:D45"/>
+    <mergeCell ref="H45:I46"/>
+    <mergeCell ref="J45:L46"/>
+    <mergeCell ref="B46:F46"/>
+    <mergeCell ref="C38:G38"/>
+    <mergeCell ref="C39:G39"/>
+    <mergeCell ref="B41:F41"/>
+    <mergeCell ref="H41:I41"/>
+    <mergeCell ref="J41:L41"/>
+    <mergeCell ref="B42:D42"/>
+    <mergeCell ref="H42:I42"/>
+    <mergeCell ref="J42:L42"/>
+    <mergeCell ref="C37:G37"/>
+    <mergeCell ref="A27:D27"/>
+    <mergeCell ref="E27:F27"/>
+    <mergeCell ref="B30:G30"/>
+    <mergeCell ref="J30:K30"/>
+    <mergeCell ref="C31:G31"/>
+    <mergeCell ref="C32:G32"/>
+    <mergeCell ref="C33:G33"/>
+    <mergeCell ref="C34:G34"/>
+    <mergeCell ref="C35:G35"/>
+    <mergeCell ref="C36:G36"/>
+    <mergeCell ref="A25:D25"/>
+    <mergeCell ref="E25:F25"/>
+    <mergeCell ref="H25:J25"/>
+    <mergeCell ref="A26:D26"/>
+    <mergeCell ref="E26:F26"/>
+    <mergeCell ref="H26:I26"/>
+    <mergeCell ref="A24:D24"/>
+    <mergeCell ref="A7:L7"/>
+    <mergeCell ref="A8:L8"/>
+    <mergeCell ref="A14:L14"/>
+    <mergeCell ref="A15:L15"/>
+    <mergeCell ref="A17:I17"/>
   </mergeCells>
   <conditionalFormatting sqref="A18:A22">
     <cfRule type="cellIs" priority="1" stopIfTrue="1" operator="between">
@@ -10553,27 +10553,27 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:Q94"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="10.28515625" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="10.33203125" defaultRowHeight="13.8"/>
   <cols>
-    <col min="1" max="1" width="10.42578125" style="316" customWidth="1"/>
+    <col min="1" max="1" width="10.44140625" style="316" customWidth="1"/>
     <col min="2" max="2" width="3" style="316" customWidth="1"/>
-    <col min="3" max="3" width="4.42578125" style="316" customWidth="1"/>
-    <col min="4" max="4" width="1.5703125" style="316" customWidth="1"/>
-    <col min="5" max="5" width="5.42578125" style="316" customWidth="1"/>
-    <col min="6" max="8" width="9.7109375" style="316" customWidth="1"/>
-    <col min="9" max="9" width="4.5703125" style="316" customWidth="1"/>
-    <col min="10" max="10" width="6.42578125" style="316" customWidth="1"/>
-    <col min="11" max="11" width="11.7109375" style="316" customWidth="1"/>
+    <col min="3" max="3" width="4.44140625" style="316" customWidth="1"/>
+    <col min="4" max="4" width="1.5546875" style="316" customWidth="1"/>
+    <col min="5" max="5" width="5.44140625" style="316" customWidth="1"/>
+    <col min="6" max="8" width="9.6640625" style="316" customWidth="1"/>
+    <col min="9" max="9" width="4.5546875" style="316" customWidth="1"/>
+    <col min="10" max="10" width="6.44140625" style="316" customWidth="1"/>
+    <col min="11" max="11" width="11.6640625" style="316" customWidth="1"/>
     <col min="12" max="12" width="10" style="316" customWidth="1"/>
-    <col min="13" max="13" width="1.28515625" style="316" customWidth="1"/>
-    <col min="14" max="14" width="13.5703125" style="316" customWidth="1"/>
-    <col min="15" max="15" width="6.42578125" style="316" customWidth="1"/>
+    <col min="13" max="13" width="1.33203125" style="316" customWidth="1"/>
+    <col min="14" max="14" width="13.5546875" style="316" customWidth="1"/>
+    <col min="15" max="15" width="6.44140625" style="316" customWidth="1"/>
     <col min="16" max="16" width="1" style="316" customWidth="1"/>
-    <col min="17" max="17" width="6.42578125" style="316" customWidth="1"/>
-    <col min="18" max="16384" width="10.28515625" style="316"/>
+    <col min="17" max="17" width="6.44140625" style="316" customWidth="1"/>
+    <col min="18" max="16384" width="10.33203125" style="316"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:17" ht="28.5" customHeight="1">
       <c r="A1" s="309"/>
       <c r="B1" s="309"/>
       <c r="C1" s="309"/>
@@ -10589,62 +10589,62 @@
       <c r="M1" s="309"/>
       <c r="N1" s="309"/>
     </row>
-    <row r="2" spans="1:17" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="567" t="s">
+    <row r="2" spans="1:17" ht="15.9" customHeight="1">
+      <c r="A2" s="544" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="567"/>
-      <c r="C2" s="567"/>
-      <c r="D2" s="567"/>
-      <c r="E2" s="567"/>
-      <c r="F2" s="567"/>
-      <c r="G2" s="567"/>
-      <c r="H2" s="567"/>
-      <c r="I2" s="567"/>
-      <c r="J2" s="567"/>
-      <c r="K2" s="567"/>
-      <c r="L2" s="567"/>
-      <c r="M2" s="567"/>
-      <c r="N2" s="567"/>
-    </row>
-    <row r="3" spans="1:17" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="628">
+      <c r="B2" s="544"/>
+      <c r="C2" s="544"/>
+      <c r="D2" s="544"/>
+      <c r="E2" s="544"/>
+      <c r="F2" s="544"/>
+      <c r="G2" s="544"/>
+      <c r="H2" s="544"/>
+      <c r="I2" s="544"/>
+      <c r="J2" s="544"/>
+      <c r="K2" s="544"/>
+      <c r="L2" s="544"/>
+      <c r="M2" s="544"/>
+      <c r="N2" s="544"/>
+    </row>
+    <row r="3" spans="1:17" ht="15.9" customHeight="1">
+      <c r="A3" s="635">
         <v>0</v>
       </c>
-      <c r="B3" s="628"/>
-      <c r="C3" s="628"/>
-      <c r="D3" s="628"/>
-      <c r="E3" s="628"/>
-      <c r="F3" s="628"/>
-      <c r="G3" s="628"/>
-      <c r="H3" s="628"/>
-      <c r="I3" s="628"/>
-      <c r="J3" s="628"/>
-      <c r="K3" s="628"/>
-      <c r="L3" s="628"/>
-      <c r="M3" s="628"/>
-      <c r="N3" s="628"/>
-    </row>
-    <row r="4" spans="1:17" ht="15.95" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="5" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B3" s="635"/>
+      <c r="C3" s="635"/>
+      <c r="D3" s="635"/>
+      <c r="E3" s="635"/>
+      <c r="F3" s="635"/>
+      <c r="G3" s="635"/>
+      <c r="H3" s="635"/>
+      <c r="I3" s="635"/>
+      <c r="J3" s="635"/>
+      <c r="K3" s="635"/>
+      <c r="L3" s="635"/>
+      <c r="M3" s="635"/>
+      <c r="N3" s="635"/>
+    </row>
+    <row r="4" spans="1:17" ht="15.9" customHeight="1"/>
+    <row r="5" spans="1:17" ht="15" customHeight="1">
       <c r="A5" s="297" t="s">
         <v>1</v>
       </c>
       <c r="B5" s="177" t="s">
         <v>2</v>
       </c>
-      <c r="C5" s="645">
+      <c r="C5" s="647">
         <f>+Resumen!P2</f>
         <v>0</v>
       </c>
-      <c r="D5" s="645"/>
-      <c r="E5" s="645"/>
-      <c r="F5" s="645"/>
-      <c r="G5" s="645"/>
-      <c r="H5" s="645"/>
-      <c r="I5" s="645"/>
-      <c r="J5" s="645"/>
-      <c r="K5" s="645"/>
+      <c r="D5" s="647"/>
+      <c r="E5" s="647"/>
+      <c r="F5" s="647"/>
+      <c r="G5" s="647"/>
+      <c r="H5" s="647"/>
+      <c r="I5" s="647"/>
+      <c r="J5" s="647"/>
+      <c r="K5" s="647"/>
       <c r="L5" s="27" t="s">
         <v>6</v>
       </c>
@@ -10656,25 +10656,25 @@
       </c>
       <c r="Q5" s="317"/>
     </row>
-    <row r="6" spans="1:17" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:17" ht="21" customHeight="1">
       <c r="A6" s="297" t="s">
         <v>100</v>
       </c>
       <c r="B6" s="177" t="s">
         <v>2</v>
       </c>
-      <c r="C6" s="647">
+      <c r="C6" s="628">
         <f>+Resumen!P3</f>
         <v>0</v>
       </c>
-      <c r="D6" s="647"/>
-      <c r="E6" s="647"/>
-      <c r="F6" s="647"/>
-      <c r="G6" s="647"/>
-      <c r="H6" s="647"/>
-      <c r="I6" s="647"/>
-      <c r="J6" s="647"/>
-      <c r="K6" s="647"/>
+      <c r="D6" s="628"/>
+      <c r="E6" s="628"/>
+      <c r="F6" s="628"/>
+      <c r="G6" s="628"/>
+      <c r="H6" s="628"/>
+      <c r="I6" s="628"/>
+      <c r="J6" s="628"/>
+      <c r="K6" s="628"/>
       <c r="L6" s="458" t="s">
         <v>233</v>
       </c>
@@ -10689,25 +10689,25 @@
       <c r="P6" s="317"/>
       <c r="Q6" s="317"/>
     </row>
-    <row r="7" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:17" ht="15" customHeight="1">
       <c r="A7" s="297" t="s">
         <v>8</v>
       </c>
       <c r="B7" s="177" t="s">
         <v>2</v>
       </c>
-      <c r="C7" s="645">
+      <c r="C7" s="647">
         <f>+Resumen!P4</f>
         <v>0</v>
       </c>
-      <c r="D7" s="645"/>
-      <c r="E7" s="645"/>
-      <c r="F7" s="645"/>
-      <c r="G7" s="645"/>
-      <c r="H7" s="645"/>
-      <c r="I7" s="645"/>
-      <c r="J7" s="645"/>
-      <c r="K7" s="645"/>
+      <c r="D7" s="647"/>
+      <c r="E7" s="647"/>
+      <c r="F7" s="647"/>
+      <c r="G7" s="647"/>
+      <c r="H7" s="647"/>
+      <c r="I7" s="647"/>
+      <c r="J7" s="647"/>
+      <c r="K7" s="647"/>
       <c r="L7" s="458" t="s">
         <v>297</v>
       </c>
@@ -10722,25 +10722,25 @@
       <c r="P7" s="317"/>
       <c r="Q7" s="317"/>
     </row>
-    <row r="8" spans="1:17" ht="17.45" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:17" ht="17.399999999999999" customHeight="1">
       <c r="A8" s="297" t="s">
         <v>11</v>
       </c>
       <c r="B8" s="177" t="s">
         <v>2</v>
       </c>
-      <c r="C8" s="647">
+      <c r="C8" s="628">
         <f>+Resumen!P5</f>
         <v>0</v>
       </c>
-      <c r="D8" s="647"/>
-      <c r="E8" s="647"/>
-      <c r="F8" s="647"/>
-      <c r="G8" s="647"/>
-      <c r="H8" s="647"/>
-      <c r="I8" s="647"/>
-      <c r="J8" s="647"/>
-      <c r="K8" s="647"/>
+      <c r="D8" s="628"/>
+      <c r="E8" s="628"/>
+      <c r="F8" s="628"/>
+      <c r="G8" s="628"/>
+      <c r="H8" s="628"/>
+      <c r="I8" s="628"/>
+      <c r="J8" s="628"/>
+      <c r="K8" s="628"/>
       <c r="L8" s="458" t="s">
         <v>101</v>
       </c>
@@ -10748,14 +10748,14 @@
         <v>2</v>
       </c>
       <c r="N8" s="361">
-        <f>+Resumen!P9</f>
+        <f>+Resumen!P8</f>
         <v>0</v>
       </c>
       <c r="O8" s="317"/>
       <c r="P8" s="317"/>
       <c r="Q8" s="317"/>
     </row>
-    <row r="9" spans="1:17" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:17" ht="14.25" customHeight="1">
       <c r="A9" s="291" t="s">
         <v>14</v>
       </c>
@@ -10776,49 +10776,49 @@
       <c r="P9" s="317"/>
       <c r="Q9" s="317"/>
     </row>
-    <row r="10" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="A10" s="629" t="s">
+    <row r="10" spans="1:17">
+      <c r="A10" s="636" t="s">
         <v>102</v>
       </c>
-      <c r="B10" s="630"/>
-      <c r="C10" s="630"/>
-      <c r="D10" s="630"/>
-      <c r="E10" s="630"/>
-      <c r="F10" s="630"/>
-      <c r="G10" s="630"/>
-      <c r="H10" s="630"/>
-      <c r="I10" s="630"/>
-      <c r="J10" s="630"/>
-      <c r="K10" s="630"/>
-      <c r="L10" s="630"/>
-      <c r="M10" s="630"/>
-      <c r="N10" s="631"/>
+      <c r="B10" s="637"/>
+      <c r="C10" s="637"/>
+      <c r="D10" s="637"/>
+      <c r="E10" s="637"/>
+      <c r="F10" s="637"/>
+      <c r="G10" s="637"/>
+      <c r="H10" s="637"/>
+      <c r="I10" s="637"/>
+      <c r="J10" s="637"/>
+      <c r="K10" s="637"/>
+      <c r="L10" s="637"/>
+      <c r="M10" s="637"/>
+      <c r="N10" s="638"/>
       <c r="O10" s="317"/>
       <c r="P10" s="317"/>
       <c r="Q10" s="317"/>
     </row>
-    <row r="11" spans="1:17" ht="12" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A11" s="632" t="s">
+    <row r="11" spans="1:17" ht="12" customHeight="1">
+      <c r="A11" s="639" t="s">
         <v>103</v>
       </c>
-      <c r="B11" s="633"/>
-      <c r="C11" s="633"/>
-      <c r="D11" s="633"/>
-      <c r="E11" s="633"/>
-      <c r="F11" s="633"/>
-      <c r="G11" s="633"/>
-      <c r="H11" s="633"/>
-      <c r="I11" s="633"/>
-      <c r="J11" s="633"/>
-      <c r="K11" s="633"/>
-      <c r="L11" s="633"/>
-      <c r="M11" s="633"/>
-      <c r="N11" s="634"/>
+      <c r="B11" s="640"/>
+      <c r="C11" s="640"/>
+      <c r="D11" s="640"/>
+      <c r="E11" s="640"/>
+      <c r="F11" s="640"/>
+      <c r="G11" s="640"/>
+      <c r="H11" s="640"/>
+      <c r="I11" s="640"/>
+      <c r="J11" s="640"/>
+      <c r="K11" s="640"/>
+      <c r="L11" s="640"/>
+      <c r="M11" s="640"/>
+      <c r="N11" s="641"/>
       <c r="O11" s="317"/>
       <c r="P11" s="317"/>
       <c r="Q11" s="317"/>
     </row>
-    <row r="12" spans="1:17" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:17" ht="6" customHeight="1">
       <c r="A12" s="189"/>
       <c r="B12" s="190"/>
       <c r="C12" s="190"/>
@@ -10837,7 +10837,7 @@
       <c r="P12" s="317"/>
       <c r="Q12" s="317"/>
     </row>
-    <row r="13" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:17" ht="15" customHeight="1">
       <c r="A13" s="362" t="s">
         <v>17</v>
       </c>
@@ -10856,7 +10856,7 @@
       <c r="N13" s="182"/>
       <c r="Q13" s="317"/>
     </row>
-    <row r="14" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:17" ht="15" customHeight="1">
       <c r="A14" s="40" t="s">
         <v>104</v>
       </c>
@@ -10886,7 +10886,7 @@
       </c>
       <c r="Q14" s="317"/>
     </row>
-    <row r="15" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:17" ht="15" customHeight="1">
       <c r="A15" s="40" t="s">
         <v>25</v>
       </c>
@@ -10916,7 +10916,7 @@
       </c>
       <c r="Q15" s="317"/>
     </row>
-    <row r="16" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:17" ht="15" customHeight="1">
       <c r="A16" s="40" t="s">
         <v>232</v>
       </c>
@@ -10949,7 +10949,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:17" ht="15" customHeight="1">
       <c r="A17" s="155" t="s">
         <v>33</v>
       </c>
@@ -10979,37 +10979,37 @@
       </c>
       <c r="Q17" s="317"/>
     </row>
-    <row r="18" spans="1:17" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:17" ht="6.75" customHeight="1">
       <c r="A18" s="310"/>
       <c r="B18" s="310"/>
       <c r="C18" s="310"/>
-      <c r="D18" s="638"/>
-      <c r="E18" s="638"/>
+      <c r="D18" s="644"/>
+      <c r="E18" s="644"/>
       <c r="F18" s="310"/>
       <c r="G18" s="310"/>
       <c r="H18" s="310"/>
       <c r="I18" s="310"/>
       <c r="J18" s="310"/>
       <c r="K18" s="310"/>
-      <c r="L18" s="638"/>
-      <c r="M18" s="638"/>
+      <c r="L18" s="644"/>
+      <c r="M18" s="644"/>
       <c r="N18" s="310"/>
       <c r="O18" s="317"/>
       <c r="P18" s="317"/>
       <c r="Q18" s="317"/>
     </row>
-    <row r="19" spans="1:17" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:17" ht="18" customHeight="1">
       <c r="A19" s="310"/>
       <c r="B19" s="310"/>
       <c r="C19" s="310"/>
-      <c r="D19" s="639" t="s">
+      <c r="D19" s="645" t="s">
         <v>108</v>
       </c>
-      <c r="E19" s="639"/>
-      <c r="F19" s="639"/>
-      <c r="G19" s="639"/>
-      <c r="H19" s="639"/>
-      <c r="I19" s="639"/>
+      <c r="E19" s="645"/>
+      <c r="F19" s="645"/>
+      <c r="G19" s="645"/>
+      <c r="H19" s="645"/>
+      <c r="I19" s="645"/>
       <c r="J19" s="311" t="s">
         <v>109</v>
       </c>
@@ -11023,7 +11023,7 @@
       <c r="P19" s="317"/>
       <c r="Q19" s="317"/>
     </row>
-    <row r="20" spans="1:17" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:17" ht="17.25" customHeight="1">
       <c r="A20" s="188"/>
       <c r="B20" s="188"/>
       <c r="C20" s="320"/>
@@ -11042,14 +11042,14 @@
         <f>+'Datos ensayo'!G17</f>
         <v>1</v>
       </c>
-      <c r="L20" s="636"/>
-      <c r="M20" s="636"/>
+      <c r="L20" s="642"/>
+      <c r="M20" s="642"/>
       <c r="N20" s="312"/>
       <c r="O20" s="317"/>
       <c r="P20" s="317"/>
       <c r="Q20" s="317"/>
     </row>
-    <row r="21" spans="1:17" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:17" ht="17.25" customHeight="1">
       <c r="A21" s="188"/>
       <c r="B21" s="188"/>
       <c r="C21" s="320"/>
@@ -11068,14 +11068,14 @@
         <f>+'Datos ensayo'!G18</f>
         <v>0</v>
       </c>
-      <c r="L21" s="636"/>
-      <c r="M21" s="636"/>
+      <c r="L21" s="642"/>
+      <c r="M21" s="642"/>
       <c r="N21" s="312"/>
       <c r="O21" s="317"/>
       <c r="P21" s="317"/>
       <c r="Q21" s="317"/>
     </row>
-    <row r="22" spans="1:17" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:17" ht="17.25" customHeight="1">
       <c r="A22" s="188"/>
       <c r="B22" s="188"/>
       <c r="C22" s="320"/>
@@ -11094,14 +11094,14 @@
         <f>+'Datos ensayo'!H19</f>
         <v>0,00</v>
       </c>
-      <c r="L22" s="637"/>
-      <c r="M22" s="637"/>
+      <c r="L22" s="643"/>
+      <c r="M22" s="643"/>
       <c r="N22" s="313"/>
       <c r="O22" s="323"/>
       <c r="P22" s="323"/>
       <c r="Q22" s="317"/>
     </row>
-    <row r="23" spans="1:17" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:17" ht="17.25" customHeight="1">
       <c r="A23" s="188"/>
       <c r="B23" s="188"/>
       <c r="C23" s="320"/>
@@ -11127,7 +11127,7 @@
       <c r="P23" s="317"/>
       <c r="Q23" s="317"/>
     </row>
-    <row r="24" spans="1:17" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:17" ht="17.25" customHeight="1">
       <c r="A24" s="188"/>
       <c r="B24" s="188"/>
       <c r="C24" s="320"/>
@@ -11153,7 +11153,7 @@
       <c r="P24" s="317"/>
       <c r="Q24" s="317"/>
     </row>
-    <row r="25" spans="1:17" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:17" ht="17.25" customHeight="1">
       <c r="A25" s="188"/>
       <c r="B25" s="188"/>
       <c r="C25" s="320"/>
@@ -11179,7 +11179,7 @@
       <c r="P25" s="317"/>
       <c r="Q25" s="317"/>
     </row>
-    <row r="26" spans="1:17" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:17" ht="17.25" customHeight="1">
       <c r="A26" s="13"/>
       <c r="B26" s="13"/>
       <c r="C26" s="314"/>
@@ -11205,7 +11205,7 @@
       <c r="P26" s="317"/>
       <c r="Q26" s="317"/>
     </row>
-    <row r="27" spans="1:17" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:17" ht="17.25" customHeight="1">
       <c r="A27" s="188"/>
       <c r="B27" s="188"/>
       <c r="C27" s="320"/>
@@ -11231,7 +11231,7 @@
       <c r="P27" s="317"/>
       <c r="Q27" s="317"/>
     </row>
-    <row r="28" spans="1:17" ht="4.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:17" ht="4.5" customHeight="1">
       <c r="A28" s="188"/>
       <c r="B28" s="188"/>
       <c r="C28" s="188"/>
@@ -11250,7 +11250,7 @@
       <c r="P28" s="317"/>
       <c r="Q28" s="317"/>
     </row>
-    <row r="29" spans="1:17" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:17" ht="15.9" customHeight="1">
       <c r="A29" s="170" t="s">
         <v>118</v>
       </c>
@@ -11271,7 +11271,7 @@
       <c r="P29" s="317"/>
       <c r="Q29" s="317"/>
     </row>
-    <row r="30" spans="1:17" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:17" ht="15.9" customHeight="1">
       <c r="A30" s="356" t="s">
         <v>119</v>
       </c>
@@ -11295,7 +11295,7 @@
       <c r="P30" s="317"/>
       <c r="Q30" s="317"/>
     </row>
-    <row r="31" spans="1:17" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:17" ht="15.9" customHeight="1">
       <c r="A31" s="356" t="s">
         <v>120</v>
       </c>
@@ -11319,7 +11319,7 @@
       <c r="P31" s="317"/>
       <c r="Q31" s="317"/>
     </row>
-    <row r="32" spans="1:17" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:17" ht="15.9" customHeight="1">
       <c r="A32" s="356" t="s">
         <v>121</v>
       </c>
@@ -11343,7 +11343,7 @@
       <c r="P32" s="317"/>
       <c r="Q32" s="317"/>
     </row>
-    <row r="33" spans="1:17" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:17" ht="15.9" customHeight="1">
       <c r="A33" s="356" t="s">
         <v>122</v>
       </c>
@@ -11367,7 +11367,7 @@
       <c r="P33" s="317"/>
       <c r="Q33" s="317"/>
     </row>
-    <row r="34" spans="1:17" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:17" ht="14.25" customHeight="1">
       <c r="A34" s="356" t="s">
         <v>123</v>
       </c>
@@ -11391,7 +11391,7 @@
       <c r="P34" s="317"/>
       <c r="Q34" s="317"/>
     </row>
-    <row r="35" spans="1:17" ht="5.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:17" ht="5.25" customHeight="1">
       <c r="A35" s="356"/>
       <c r="B35" s="193"/>
       <c r="C35" s="193"/>
@@ -11410,7 +11410,7 @@
       <c r="P35" s="317"/>
       <c r="Q35" s="317"/>
     </row>
-    <row r="36" spans="1:17" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:17" ht="14.25" customHeight="1">
       <c r="A36" s="170" t="s">
         <v>228</v>
       </c>
@@ -11431,7 +11431,7 @@
       <c r="P36" s="317"/>
       <c r="Q36" s="317"/>
     </row>
-    <row r="37" spans="1:17" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:17" ht="14.25" customHeight="1">
       <c r="A37" s="357" t="s">
         <v>230</v>
       </c>
@@ -11444,18 +11444,18 @@
       <c r="H37" s="193"/>
       <c r="I37" s="195"/>
       <c r="J37" s="195"/>
-      <c r="K37" s="646">
+      <c r="K37" s="648">
         <f>+Resumen!E27</f>
         <v>0</v>
       </c>
-      <c r="L37" s="646"/>
+      <c r="L37" s="648"/>
       <c r="M37" s="159"/>
       <c r="N37" s="159"/>
       <c r="O37" s="317"/>
       <c r="P37" s="317"/>
       <c r="Q37" s="317"/>
     </row>
-    <row r="38" spans="1:17" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:17" ht="14.25" customHeight="1">
       <c r="A38" s="357" t="s">
         <v>229</v>
       </c>
@@ -11468,25 +11468,25 @@
       <c r="H38" s="193"/>
       <c r="I38" s="195"/>
       <c r="J38" s="195"/>
-      <c r="K38" s="640">
+      <c r="K38" s="646">
         <f>+Resumen!E28</f>
         <v>0</v>
       </c>
-      <c r="L38" s="640"/>
+      <c r="L38" s="646"/>
       <c r="M38" s="159"/>
       <c r="N38" s="159"/>
       <c r="O38" s="317"/>
       <c r="P38" s="317"/>
       <c r="Q38" s="317"/>
     </row>
-    <row r="39" spans="1:17" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:17" ht="6" customHeight="1">
       <c r="M39" s="159"/>
       <c r="N39" s="159"/>
       <c r="O39" s="317"/>
       <c r="P39" s="317"/>
       <c r="Q39" s="317"/>
     </row>
-    <row r="40" spans="1:17" ht="10.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:17" ht="10.5" customHeight="1">
       <c r="A40" s="170" t="s">
         <v>124</v>
       </c>
@@ -11507,112 +11507,112 @@
       <c r="P40" s="317"/>
       <c r="Q40" s="317"/>
     </row>
-    <row r="41" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A41" s="648" t="s">
+    <row r="41" spans="1:17" ht="15" customHeight="1">
+      <c r="A41" s="629" t="s">
         <v>312</v>
       </c>
-      <c r="B41" s="648"/>
-      <c r="C41" s="648"/>
-      <c r="D41" s="648"/>
-      <c r="E41" s="648"/>
-      <c r="F41" s="648"/>
-      <c r="G41" s="648"/>
-      <c r="H41" s="648"/>
-      <c r="I41" s="648"/>
-      <c r="J41" s="648"/>
-      <c r="K41" s="648"/>
-      <c r="L41" s="648"/>
-      <c r="M41" s="648"/>
-      <c r="N41" s="648"/>
+      <c r="B41" s="629"/>
+      <c r="C41" s="629"/>
+      <c r="D41" s="629"/>
+      <c r="E41" s="629"/>
+      <c r="F41" s="629"/>
+      <c r="G41" s="629"/>
+      <c r="H41" s="629"/>
+      <c r="I41" s="629"/>
+      <c r="J41" s="629"/>
+      <c r="K41" s="629"/>
+      <c r="L41" s="629"/>
+      <c r="M41" s="629"/>
+      <c r="N41" s="629"/>
       <c r="O41" s="317"/>
       <c r="P41" s="317"/>
       <c r="Q41" s="317"/>
     </row>
-    <row r="42" spans="1:17" ht="33" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A42" s="635" t="s">
+    <row r="42" spans="1:17" ht="33" customHeight="1">
+      <c r="A42" s="632" t="s">
         <v>313</v>
       </c>
-      <c r="B42" s="635"/>
-      <c r="C42" s="635"/>
-      <c r="D42" s="635"/>
-      <c r="E42" s="635"/>
-      <c r="F42" s="635"/>
-      <c r="G42" s="635"/>
-      <c r="H42" s="635"/>
-      <c r="I42" s="635"/>
-      <c r="J42" s="635"/>
-      <c r="K42" s="635"/>
-      <c r="L42" s="635"/>
-      <c r="M42" s="635"/>
-      <c r="N42" s="635"/>
+      <c r="B42" s="632"/>
+      <c r="C42" s="632"/>
+      <c r="D42" s="632"/>
+      <c r="E42" s="632"/>
+      <c r="F42" s="632"/>
+      <c r="G42" s="632"/>
+      <c r="H42" s="632"/>
+      <c r="I42" s="632"/>
+      <c r="J42" s="632"/>
+      <c r="K42" s="632"/>
+      <c r="L42" s="632"/>
+      <c r="M42" s="632"/>
+      <c r="N42" s="632"/>
       <c r="O42" s="317"/>
       <c r="P42" s="317"/>
       <c r="Q42" s="317"/>
     </row>
-    <row r="43" spans="1:17" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A43" s="635" t="s">
+    <row r="43" spans="1:17" ht="18.600000000000001" customHeight="1">
+      <c r="A43" s="632" t="s">
         <v>314</v>
       </c>
-      <c r="B43" s="635"/>
-      <c r="C43" s="635"/>
-      <c r="D43" s="635"/>
-      <c r="E43" s="635"/>
-      <c r="F43" s="635"/>
-      <c r="G43" s="635"/>
-      <c r="H43" s="635"/>
-      <c r="I43" s="635"/>
-      <c r="J43" s="635"/>
-      <c r="K43" s="635"/>
-      <c r="L43" s="635"/>
-      <c r="M43" s="635"/>
-      <c r="N43" s="635"/>
+      <c r="B43" s="632"/>
+      <c r="C43" s="632"/>
+      <c r="D43" s="632"/>
+      <c r="E43" s="632"/>
+      <c r="F43" s="632"/>
+      <c r="G43" s="632"/>
+      <c r="H43" s="632"/>
+      <c r="I43" s="632"/>
+      <c r="J43" s="632"/>
+      <c r="K43" s="632"/>
+      <c r="L43" s="632"/>
+      <c r="M43" s="632"/>
+      <c r="N43" s="632"/>
       <c r="O43" s="317"/>
       <c r="P43" s="317"/>
       <c r="Q43" s="317"/>
     </row>
-    <row r="44" spans="1:17" ht="23.45" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A44" s="635" t="s">
+    <row r="44" spans="1:17" ht="23.4" customHeight="1">
+      <c r="A44" s="632" t="s">
         <v>315</v>
       </c>
-      <c r="B44" s="635"/>
-      <c r="C44" s="635"/>
-      <c r="D44" s="635"/>
-      <c r="E44" s="635"/>
-      <c r="F44" s="635"/>
-      <c r="G44" s="635"/>
-      <c r="H44" s="635"/>
-      <c r="I44" s="635"/>
-      <c r="J44" s="635"/>
-      <c r="K44" s="635"/>
-      <c r="L44" s="635"/>
-      <c r="M44" s="635"/>
-      <c r="N44" s="635"/>
+      <c r="B44" s="632"/>
+      <c r="C44" s="632"/>
+      <c r="D44" s="632"/>
+      <c r="E44" s="632"/>
+      <c r="F44" s="632"/>
+      <c r="G44" s="632"/>
+      <c r="H44" s="632"/>
+      <c r="I44" s="632"/>
+      <c r="J44" s="632"/>
+      <c r="K44" s="632"/>
+      <c r="L44" s="632"/>
+      <c r="M44" s="632"/>
+      <c r="N44" s="632"/>
       <c r="O44" s="317"/>
       <c r="P44" s="317"/>
       <c r="Q44" s="317"/>
     </row>
-    <row r="45" spans="1:17" ht="23.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A45" s="644" t="s">
+    <row r="45" spans="1:17" ht="23.25" customHeight="1">
+      <c r="A45" s="634" t="s">
         <v>316</v>
       </c>
-      <c r="B45" s="644"/>
-      <c r="C45" s="644"/>
-      <c r="D45" s="644"/>
-      <c r="E45" s="644"/>
-      <c r="F45" s="644"/>
-      <c r="G45" s="644"/>
-      <c r="H45" s="644"/>
-      <c r="I45" s="644"/>
-      <c r="J45" s="644"/>
-      <c r="K45" s="644"/>
-      <c r="L45" s="644"/>
-      <c r="M45" s="644"/>
-      <c r="N45" s="644"/>
+      <c r="B45" s="634"/>
+      <c r="C45" s="634"/>
+      <c r="D45" s="634"/>
+      <c r="E45" s="634"/>
+      <c r="F45" s="634"/>
+      <c r="G45" s="634"/>
+      <c r="H45" s="634"/>
+      <c r="I45" s="634"/>
+      <c r="J45" s="634"/>
+      <c r="K45" s="634"/>
+      <c r="L45" s="634"/>
+      <c r="M45" s="634"/>
+      <c r="N45" s="634"/>
       <c r="O45" s="317"/>
       <c r="P45" s="317"/>
       <c r="Q45" s="317"/>
     </row>
-    <row r="46" spans="1:17" ht="5.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="46" spans="1:17" ht="5.25" customHeight="1">
       <c r="A46" s="193"/>
       <c r="B46" s="196"/>
       <c r="C46" s="196"/>
@@ -11620,7 +11620,7 @@
       <c r="P46" s="317"/>
       <c r="Q46" s="317"/>
     </row>
-    <row r="47" spans="1:17" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="47" spans="1:17" ht="19.5" customHeight="1">
       <c r="A47" s="170" t="s">
         <v>98</v>
       </c>
@@ -11641,19 +11641,19 @@
       <c r="P47" s="317"/>
       <c r="Q47" s="317"/>
     </row>
-    <row r="48" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="48" spans="1:17" ht="15" customHeight="1">
       <c r="A48" s="196"/>
       <c r="B48" s="196"/>
       <c r="C48" s="196"/>
-      <c r="K48" s="643"/>
-      <c r="L48" s="643"/>
-      <c r="M48" s="643"/>
-      <c r="N48" s="643"/>
+      <c r="K48" s="633"/>
+      <c r="L48" s="633"/>
+      <c r="M48" s="633"/>
+      <c r="N48" s="633"/>
       <c r="O48" s="317"/>
       <c r="P48" s="317"/>
       <c r="Q48" s="317"/>
     </row>
-    <row r="49" spans="1:17" ht="66.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="49" spans="1:17" ht="66.75" customHeight="1">
       <c r="A49" s="196"/>
       <c r="B49" s="196"/>
       <c r="C49" s="196"/>
@@ -11666,19 +11666,19 @@
       <c r="P49" s="317"/>
       <c r="Q49" s="317"/>
     </row>
-    <row r="50" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="50" spans="1:17">
       <c r="A50" s="196"/>
       <c r="B50" s="196"/>
       <c r="C50" s="196"/>
-      <c r="K50" s="643"/>
-      <c r="L50" s="643"/>
-      <c r="M50" s="643"/>
-      <c r="N50" s="643"/>
+      <c r="K50" s="633"/>
+      <c r="L50" s="633"/>
+      <c r="M50" s="633"/>
+      <c r="N50" s="633"/>
       <c r="O50" s="317"/>
       <c r="P50" s="317"/>
       <c r="Q50" s="317"/>
     </row>
-    <row r="51" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="51" spans="1:17">
       <c r="A51" s="195" t="s">
         <v>91</v>
       </c>
@@ -11691,12 +11691,12 @@
       <c r="H51" s="324"/>
       <c r="I51" s="324"/>
       <c r="J51" s="324"/>
-      <c r="K51" s="643"/>
-      <c r="L51" s="643"/>
-      <c r="M51" s="643"/>
-      <c r="N51" s="643"/>
-    </row>
-    <row r="52" spans="1:17" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="K51" s="633"/>
+      <c r="L51" s="633"/>
+      <c r="M51" s="633"/>
+      <c r="N51" s="633"/>
+    </row>
+    <row r="52" spans="1:17" ht="11.25" customHeight="1">
       <c r="A52" s="195" t="s">
         <v>317</v>
       </c>
@@ -11709,30 +11709,30 @@
       <c r="H52" s="324"/>
       <c r="I52" s="324"/>
       <c r="J52" s="324"/>
-      <c r="K52" s="643" t="s">
+      <c r="K52" s="633" t="s">
         <v>125</v>
       </c>
-      <c r="L52" s="643"/>
-      <c r="M52" s="643"/>
-      <c r="N52" s="643"/>
-    </row>
-    <row r="53" spans="1:17" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="L52" s="633"/>
+      <c r="M52" s="633"/>
+      <c r="N52" s="633"/>
+    </row>
+    <row r="53" spans="1:17" ht="15.9" customHeight="1">
       <c r="M53" s="185"/>
       <c r="N53" s="317"/>
     </row>
-    <row r="54" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="54" spans="1:17">
       <c r="M54" s="186"/>
       <c r="N54" s="317"/>
     </row>
-    <row r="55" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="55" spans="1:17">
       <c r="M55" s="317"/>
       <c r="N55" s="317"/>
     </row>
-    <row r="56" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="56" spans="1:17">
       <c r="M56" s="317"/>
       <c r="N56" s="317"/>
     </row>
-    <row r="57" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="57" spans="1:17">
       <c r="A57" s="317"/>
       <c r="B57" s="317"/>
       <c r="C57" s="317"/>
@@ -11747,7 +11747,7 @@
       <c r="L57" s="317"/>
       <c r="M57" s="317"/>
     </row>
-    <row r="58" spans="1:17" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="58" spans="1:17" ht="11.25" customHeight="1">
       <c r="A58" s="187"/>
       <c r="B58" s="187"/>
       <c r="C58" s="187"/>
@@ -11763,23 +11763,23 @@
       <c r="M58" s="187"/>
       <c r="N58" s="187"/>
     </row>
-    <row r="59" spans="1:17" ht="30" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A59" s="642"/>
-      <c r="B59" s="642"/>
-      <c r="C59" s="642"/>
-      <c r="D59" s="642"/>
-      <c r="E59" s="642"/>
-      <c r="F59" s="642"/>
-      <c r="G59" s="642"/>
-      <c r="H59" s="642"/>
-      <c r="I59" s="642"/>
-      <c r="J59" s="642"/>
-      <c r="K59" s="642"/>
-      <c r="L59" s="642"/>
-      <c r="M59" s="642"/>
-      <c r="N59" s="642"/>
-    </row>
-    <row r="60" spans="1:17" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="59" spans="1:17" ht="30" customHeight="1">
+      <c r="A59" s="631"/>
+      <c r="B59" s="631"/>
+      <c r="C59" s="631"/>
+      <c r="D59" s="631"/>
+      <c r="E59" s="631"/>
+      <c r="F59" s="631"/>
+      <c r="G59" s="631"/>
+      <c r="H59" s="631"/>
+      <c r="I59" s="631"/>
+      <c r="J59" s="631"/>
+      <c r="K59" s="631"/>
+      <c r="L59" s="631"/>
+      <c r="M59" s="631"/>
+      <c r="N59" s="631"/>
+    </row>
+    <row r="60" spans="1:17" ht="30" customHeight="1">
       <c r="A60" s="193"/>
       <c r="B60" s="193"/>
       <c r="C60" s="193"/>
@@ -11795,23 +11795,23 @@
       <c r="M60" s="324"/>
       <c r="N60" s="324"/>
     </row>
-    <row r="61" spans="1:17" ht="39.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A61" s="642"/>
-      <c r="B61" s="642"/>
-      <c r="C61" s="642"/>
-      <c r="D61" s="642"/>
-      <c r="E61" s="642"/>
-      <c r="F61" s="642"/>
-      <c r="G61" s="642"/>
-      <c r="H61" s="642"/>
-      <c r="I61" s="642"/>
-      <c r="J61" s="642"/>
-      <c r="K61" s="642"/>
-      <c r="L61" s="642"/>
-      <c r="M61" s="642"/>
-      <c r="N61" s="642"/>
-    </row>
-    <row r="62" spans="1:17" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="61" spans="1:17" ht="39.75" customHeight="1">
+      <c r="A61" s="631"/>
+      <c r="B61" s="631"/>
+      <c r="C61" s="631"/>
+      <c r="D61" s="631"/>
+      <c r="E61" s="631"/>
+      <c r="F61" s="631"/>
+      <c r="G61" s="631"/>
+      <c r="H61" s="631"/>
+      <c r="I61" s="631"/>
+      <c r="J61" s="631"/>
+      <c r="K61" s="631"/>
+      <c r="L61" s="631"/>
+      <c r="M61" s="631"/>
+      <c r="N61" s="631"/>
+    </row>
+    <row r="62" spans="1:17" ht="30" customHeight="1">
       <c r="A62" s="194"/>
       <c r="B62" s="194"/>
       <c r="C62" s="194"/>
@@ -11827,7 +11827,7 @@
       <c r="M62" s="307"/>
       <c r="N62" s="307"/>
     </row>
-    <row r="63" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="63" spans="1:17">
       <c r="A63" s="327"/>
       <c r="B63" s="327"/>
       <c r="C63" s="327"/>
@@ -11843,139 +11843,139 @@
       <c r="M63" s="327"/>
       <c r="N63" s="327"/>
     </row>
-    <row r="70" spans="11:14" x14ac:dyDescent="0.2">
+    <row r="70" spans="11:14">
       <c r="K70" s="317"/>
       <c r="L70" s="317"/>
       <c r="M70" s="317"/>
       <c r="N70" s="317"/>
     </row>
-    <row r="71" spans="11:14" x14ac:dyDescent="0.2">
+    <row r="71" spans="11:14">
       <c r="K71" s="317"/>
       <c r="L71" s="317"/>
       <c r="M71" s="317"/>
       <c r="N71" s="317"/>
     </row>
-    <row r="72" spans="11:14" x14ac:dyDescent="0.2">
+    <row r="72" spans="11:14">
       <c r="K72" s="317"/>
       <c r="L72" s="317"/>
       <c r="M72" s="317"/>
       <c r="N72" s="317"/>
     </row>
-    <row r="73" spans="11:14" x14ac:dyDescent="0.2">
+    <row r="73" spans="11:14">
       <c r="K73" s="317"/>
       <c r="L73" s="317"/>
       <c r="M73" s="317"/>
       <c r="N73" s="317"/>
     </row>
-    <row r="74" spans="11:14" x14ac:dyDescent="0.2">
+    <row r="74" spans="11:14">
       <c r="K74" s="317"/>
       <c r="L74" s="317"/>
       <c r="M74" s="317"/>
       <c r="N74" s="317"/>
     </row>
-    <row r="75" spans="11:14" x14ac:dyDescent="0.2">
+    <row r="75" spans="11:14">
       <c r="K75" s="317"/>
       <c r="L75" s="317"/>
       <c r="M75" s="317"/>
       <c r="N75" s="317"/>
     </row>
-    <row r="76" spans="11:14" x14ac:dyDescent="0.2">
+    <row r="76" spans="11:14">
       <c r="K76" s="317"/>
       <c r="L76" s="317"/>
       <c r="M76" s="317"/>
       <c r="N76" s="317"/>
     </row>
-    <row r="77" spans="11:14" x14ac:dyDescent="0.2">
+    <row r="77" spans="11:14">
       <c r="K77" s="317"/>
       <c r="L77" s="317"/>
       <c r="M77" s="317"/>
       <c r="N77" s="317"/>
     </row>
-    <row r="78" spans="11:14" x14ac:dyDescent="0.2">
+    <row r="78" spans="11:14">
       <c r="K78" s="328"/>
       <c r="L78" s="328"/>
       <c r="M78" s="328"/>
       <c r="N78" s="317"/>
     </row>
-    <row r="79" spans="11:14" x14ac:dyDescent="0.2">
-      <c r="K79" s="641"/>
-      <c r="L79" s="641"/>
-      <c r="M79" s="641"/>
+    <row r="79" spans="11:14">
+      <c r="K79" s="630"/>
+      <c r="L79" s="630"/>
+      <c r="M79" s="630"/>
       <c r="N79" s="317"/>
     </row>
-    <row r="80" spans="11:14" x14ac:dyDescent="0.2">
-      <c r="K80" s="641"/>
-      <c r="L80" s="641"/>
-      <c r="M80" s="641"/>
+    <row r="80" spans="11:14">
+      <c r="K80" s="630"/>
+      <c r="L80" s="630"/>
+      <c r="M80" s="630"/>
       <c r="N80" s="317"/>
     </row>
-    <row r="81" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="81" spans="1:14">
       <c r="K81" s="329"/>
       <c r="L81" s="329"/>
       <c r="M81" s="329"/>
       <c r="N81" s="317"/>
     </row>
-    <row r="82" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="82" spans="1:14">
       <c r="K82" s="329"/>
       <c r="L82" s="329"/>
       <c r="M82" s="329"/>
       <c r="N82" s="317"/>
     </row>
-    <row r="83" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="83" spans="1:14">
       <c r="K83" s="329"/>
       <c r="L83" s="329"/>
       <c r="M83" s="329"/>
       <c r="N83" s="317"/>
     </row>
-    <row r="84" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="84" spans="1:14">
       <c r="K84" s="329"/>
       <c r="L84" s="329"/>
       <c r="M84" s="329"/>
       <c r="N84" s="317"/>
     </row>
-    <row r="85" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="85" spans="1:14">
       <c r="K85" s="329"/>
       <c r="L85" s="329"/>
       <c r="M85" s="329"/>
       <c r="N85" s="317"/>
     </row>
-    <row r="86" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="86" spans="1:14">
       <c r="K86" s="329"/>
       <c r="L86" s="329"/>
       <c r="M86" s="329"/>
       <c r="N86" s="317"/>
     </row>
-    <row r="87" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="87" spans="1:14">
       <c r="K87" s="329"/>
       <c r="L87" s="329"/>
       <c r="M87" s="329"/>
       <c r="N87" s="317"/>
     </row>
-    <row r="88" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="88" spans="1:14">
       <c r="K88" s="329"/>
       <c r="L88" s="329"/>
       <c r="M88" s="329"/>
       <c r="N88" s="317"/>
     </row>
-    <row r="89" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="89" spans="1:14">
       <c r="K89" s="329"/>
       <c r="L89" s="329"/>
       <c r="M89" s="329"/>
       <c r="N89" s="317"/>
     </row>
-    <row r="90" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="90" spans="1:14">
       <c r="K90" s="329"/>
       <c r="L90" s="329"/>
       <c r="M90" s="329"/>
       <c r="N90" s="317"/>
     </row>
-    <row r="91" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="91" spans="1:14">
       <c r="K91" s="329"/>
       <c r="L91" s="329"/>
       <c r="M91" s="329"/>
       <c r="N91" s="317"/>
     </row>
-    <row r="92" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="92" spans="1:14">
       <c r="A92" s="317"/>
       <c r="B92" s="317"/>
       <c r="C92" s="317"/>
@@ -11991,7 +11991,7 @@
       <c r="M92" s="317"/>
       <c r="N92" s="317"/>
     </row>
-    <row r="93" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="93" spans="1:14">
       <c r="A93" s="317"/>
       <c r="B93" s="317"/>
       <c r="C93" s="317"/>
@@ -12007,7 +12007,7 @@
       <c r="M93" s="317"/>
       <c r="N93" s="317"/>
     </row>
-    <row r="94" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="94" spans="1:14">
       <c r="A94" s="317"/>
       <c r="B94" s="317"/>
       <c r="C94" s="317"/>
@@ -12030,20 +12030,6 @@
     <protectedRange sqref="E5:F6" name="Rango3_3_1_1_1_1_1_2_1"/>
   </protectedRanges>
   <mergeCells count="30">
-    <mergeCell ref="C8:K8"/>
-    <mergeCell ref="A41:N41"/>
-    <mergeCell ref="M79:M80"/>
-    <mergeCell ref="A59:N59"/>
-    <mergeCell ref="A61:N61"/>
-    <mergeCell ref="A42:N42"/>
-    <mergeCell ref="A44:N44"/>
-    <mergeCell ref="K50:N50"/>
-    <mergeCell ref="K48:N48"/>
-    <mergeCell ref="A45:N45"/>
-    <mergeCell ref="K51:N51"/>
-    <mergeCell ref="K52:N52"/>
-    <mergeCell ref="K79:K80"/>
-    <mergeCell ref="L79:L80"/>
     <mergeCell ref="A2:N2"/>
     <mergeCell ref="A3:N3"/>
     <mergeCell ref="A10:N10"/>
@@ -12060,6 +12046,20 @@
     <mergeCell ref="K37:L37"/>
     <mergeCell ref="C6:K6"/>
     <mergeCell ref="C7:K7"/>
+    <mergeCell ref="C8:K8"/>
+    <mergeCell ref="A41:N41"/>
+    <mergeCell ref="M79:M80"/>
+    <mergeCell ref="A59:N59"/>
+    <mergeCell ref="A61:N61"/>
+    <mergeCell ref="A42:N42"/>
+    <mergeCell ref="A44:N44"/>
+    <mergeCell ref="K50:N50"/>
+    <mergeCell ref="K48:N48"/>
+    <mergeCell ref="A45:N45"/>
+    <mergeCell ref="K51:N51"/>
+    <mergeCell ref="K52:N52"/>
+    <mergeCell ref="K79:K80"/>
+    <mergeCell ref="L79:L80"/>
   </mergeCells>
   <conditionalFormatting sqref="A30:A38">
     <cfRule type="cellIs" priority="1" stopIfTrue="1" operator="between">
@@ -12092,23 +12092,23 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:N53"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="10.28515625" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="10.33203125" defaultRowHeight="13.2"/>
   <cols>
-    <col min="1" max="1" width="4.7109375" style="317" customWidth="1"/>
-    <col min="2" max="2" width="11.28515625" style="317" customWidth="1"/>
-    <col min="3" max="3" width="12.28515625" style="317" customWidth="1"/>
-    <col min="4" max="5" width="11.28515625" style="317" customWidth="1"/>
-    <col min="6" max="6" width="13.28515625" style="317" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="12.140625" style="317" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.85546875" style="317" customWidth="1"/>
-    <col min="9" max="9" width="10.7109375" style="317" customWidth="1"/>
-    <col min="10" max="10" width="11.42578125" style="317" customWidth="1"/>
-    <col min="11" max="11" width="13.28515625" style="317" customWidth="1"/>
-    <col min="12" max="12" width="5.7109375" style="317" customWidth="1"/>
-    <col min="13" max="16384" width="10.28515625" style="317"/>
+    <col min="1" max="1" width="4.6640625" style="317" customWidth="1"/>
+    <col min="2" max="2" width="11.33203125" style="317" customWidth="1"/>
+    <col min="3" max="3" width="12.33203125" style="317" customWidth="1"/>
+    <col min="4" max="5" width="11.33203125" style="317" customWidth="1"/>
+    <col min="6" max="6" width="13.33203125" style="317" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="12.109375" style="317" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.88671875" style="317" customWidth="1"/>
+    <col min="9" max="9" width="10.6640625" style="317" customWidth="1"/>
+    <col min="10" max="10" width="11.44140625" style="317" customWidth="1"/>
+    <col min="11" max="11" width="13.33203125" style="317" customWidth="1"/>
+    <col min="12" max="12" width="5.6640625" style="317" customWidth="1"/>
+    <col min="13" max="16384" width="10.33203125" style="317"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" ht="5.45" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:14" ht="5.4" customHeight="1">
       <c r="A1" s="383"/>
       <c r="B1" s="384"/>
       <c r="C1" s="384"/>
@@ -12123,41 +12123,41 @@
       <c r="L1" s="385"/>
       <c r="M1" s="386"/>
     </row>
-    <row r="2" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:14" ht="15" customHeight="1">
       <c r="A2" s="387"/>
-      <c r="B2" s="661" t="s">
+      <c r="B2" s="649" t="s">
         <v>102</v>
       </c>
-      <c r="C2" s="661"/>
-      <c r="D2" s="661"/>
-      <c r="E2" s="661"/>
-      <c r="F2" s="661"/>
-      <c r="G2" s="661"/>
-      <c r="H2" s="661"/>
-      <c r="I2" s="661"/>
-      <c r="J2" s="661"/>
-      <c r="K2" s="661"/>
+      <c r="C2" s="649"/>
+      <c r="D2" s="649"/>
+      <c r="E2" s="649"/>
+      <c r="F2" s="649"/>
+      <c r="G2" s="649"/>
+      <c r="H2" s="649"/>
+      <c r="I2" s="649"/>
+      <c r="J2" s="649"/>
+      <c r="K2" s="649"/>
       <c r="L2" s="374"/>
       <c r="M2" s="386"/>
     </row>
-    <row r="3" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:14" ht="15" customHeight="1">
       <c r="A3" s="387"/>
-      <c r="B3" s="661" t="s">
+      <c r="B3" s="649" t="s">
         <v>103</v>
       </c>
-      <c r="C3" s="661"/>
-      <c r="D3" s="661"/>
-      <c r="E3" s="661"/>
-      <c r="F3" s="661"/>
-      <c r="G3" s="661"/>
-      <c r="H3" s="661"/>
-      <c r="I3" s="661"/>
-      <c r="J3" s="661"/>
-      <c r="K3" s="661"/>
+      <c r="C3" s="649"/>
+      <c r="D3" s="649"/>
+      <c r="E3" s="649"/>
+      <c r="F3" s="649"/>
+      <c r="G3" s="649"/>
+      <c r="H3" s="649"/>
+      <c r="I3" s="649"/>
+      <c r="J3" s="649"/>
+      <c r="K3" s="649"/>
       <c r="L3" s="374"/>
       <c r="M3" s="386"/>
     </row>
-    <row r="4" spans="1:14" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:14" ht="6.6" customHeight="1">
       <c r="A4" s="387"/>
       <c r="B4" s="375"/>
       <c r="C4" s="375"/>
@@ -12172,14 +12172,14 @@
       <c r="L4" s="374"/>
       <c r="M4" s="386"/>
     </row>
-    <row r="5" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:14" ht="15" customHeight="1">
       <c r="A5" s="387"/>
-      <c r="B5" s="652" t="s">
+      <c r="B5" s="655" t="s">
         <v>126</v>
       </c>
-      <c r="C5" s="653"/>
-      <c r="D5" s="653"/>
-      <c r="E5" s="654"/>
+      <c r="C5" s="656"/>
+      <c r="D5" s="656"/>
+      <c r="E5" s="657"/>
       <c r="F5" s="331">
         <f>+Resumen!J26</f>
         <v>0</v>
@@ -12194,7 +12194,7 @@
       <c r="L5" s="374"/>
       <c r="M5" s="386"/>
     </row>
-    <row r="6" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:14" ht="15" customHeight="1">
       <c r="A6" s="387"/>
       <c r="B6" s="375"/>
       <c r="C6" s="375"/>
@@ -12212,14 +12212,14 @@
       <c r="M6" s="386"/>
       <c r="N6" s="197"/>
     </row>
-    <row r="7" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:14" ht="15" customHeight="1">
       <c r="A7" s="387"/>
-      <c r="B7" s="652" t="s">
+      <c r="B7" s="655" t="s">
         <v>129</v>
       </c>
-      <c r="C7" s="653"/>
-      <c r="D7" s="653"/>
-      <c r="E7" s="654"/>
+      <c r="C7" s="656"/>
+      <c r="D7" s="656"/>
+      <c r="E7" s="657"/>
       <c r="F7" s="331">
         <f>+IF(F5="A",0.1,0.01)</f>
         <v>0.01</v>
@@ -12229,7 +12229,7 @@
       <c r="M7" s="386"/>
       <c r="N7" s="197"/>
     </row>
-    <row r="8" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:14" ht="15" customHeight="1">
       <c r="A8" s="387"/>
       <c r="B8" s="375"/>
       <c r="C8" s="375"/>
@@ -12254,7 +12254,7 @@
       <c r="L8" s="374"/>
       <c r="M8" s="386"/>
     </row>
-    <row r="9" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:14" ht="15" customHeight="1">
       <c r="A9" s="387"/>
       <c r="B9" s="372" t="s">
         <v>246</v>
@@ -12284,7 +12284,7 @@
       <c r="L9" s="377"/>
       <c r="M9" s="386"/>
     </row>
-    <row r="10" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:14" ht="15" customHeight="1">
       <c r="A10" s="387"/>
       <c r="G10" s="197"/>
       <c r="H10" s="330" t="str">
@@ -12304,7 +12304,7 @@
       </c>
       <c r="L10" s="378"/>
     </row>
-    <row r="11" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:14" ht="15" customHeight="1">
       <c r="A11" s="387"/>
       <c r="B11" s="372" t="s">
         <v>238</v>
@@ -12322,12 +12322,12 @@
       <c r="K11" s="379"/>
       <c r="L11" s="380"/>
     </row>
-    <row r="12" spans="1:14" ht="8.4499999999999993" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:14" ht="8.4" customHeight="1">
       <c r="A12" s="387"/>
       <c r="G12" s="197"/>
       <c r="L12" s="394"/>
     </row>
-    <row r="13" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:14" ht="15" customHeight="1">
       <c r="A13" s="387"/>
       <c r="B13" s="372" t="s">
         <v>245</v>
@@ -12340,12 +12340,12 @@
       <c r="G13" s="197"/>
       <c r="L13" s="394"/>
     </row>
-    <row r="14" spans="1:14" ht="7.9" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:14" ht="7.95" customHeight="1">
       <c r="A14" s="387"/>
       <c r="G14" s="197"/>
       <c r="L14" s="394"/>
     </row>
-    <row r="15" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:14" ht="15" customHeight="1">
       <c r="A15" s="387"/>
       <c r="B15" s="372" t="s">
         <v>107</v>
@@ -12361,27 +12361,27 @@
       <c r="G15" s="197"/>
       <c r="L15" s="394"/>
     </row>
-    <row r="16" spans="1:14" ht="7.9" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:14" ht="7.95" customHeight="1">
       <c r="A16" s="387"/>
       <c r="L16" s="394"/>
     </row>
-    <row r="17" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:12" ht="15" customHeight="1">
       <c r="A17" s="396">
         <v>1</v>
       </c>
-      <c r="B17" s="655" t="s">
+      <c r="B17" s="658" t="s">
         <v>35</v>
       </c>
-      <c r="C17" s="656"/>
-      <c r="D17" s="656"/>
-      <c r="E17" s="657"/>
+      <c r="C17" s="659"/>
+      <c r="D17" s="659"/>
+      <c r="E17" s="660"/>
       <c r="F17" s="397" t="s">
         <v>36</v>
       </c>
       <c r="G17" s="426">
         <v>1</v>
       </c>
-      <c r="H17" s="663" t="s">
+      <c r="H17" s="651" t="s">
         <v>37</v>
       </c>
       <c r="J17" s="4" t="s">
@@ -12392,16 +12392,16 @@
       </c>
       <c r="L17" s="394"/>
     </row>
-    <row r="18" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:12" ht="17.25" customHeight="1">
       <c r="A18" s="396">
         <v>2</v>
       </c>
-      <c r="B18" s="655" t="s">
+      <c r="B18" s="658" t="s">
         <v>111</v>
       </c>
-      <c r="C18" s="656"/>
-      <c r="D18" s="656"/>
-      <c r="E18" s="657"/>
+      <c r="C18" s="659"/>
+      <c r="D18" s="659"/>
+      <c r="E18" s="660"/>
       <c r="F18" s="397" t="s">
         <v>36</v>
       </c>
@@ -12409,7 +12409,7 @@
         <f>+Resumen!I32</f>
         <v>0</v>
       </c>
-      <c r="H18" s="663"/>
+      <c r="H18" s="651"/>
       <c r="J18" s="4" t="s">
         <v>237</v>
       </c>
@@ -12418,16 +12418,16 @@
       </c>
       <c r="L18" s="394"/>
     </row>
-    <row r="19" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:12" ht="17.25" customHeight="1">
       <c r="A19" s="396">
         <v>3</v>
       </c>
-      <c r="B19" s="655" t="s">
+      <c r="B19" s="658" t="s">
         <v>112</v>
       </c>
-      <c r="C19" s="656"/>
-      <c r="D19" s="656"/>
-      <c r="E19" s="657"/>
+      <c r="C19" s="659"/>
+      <c r="D19" s="659"/>
+      <c r="E19" s="660"/>
       <c r="F19" s="397" t="s">
         <v>41</v>
       </c>
@@ -12447,16 +12447,16 @@
       </c>
       <c r="L19" s="394"/>
     </row>
-    <row r="20" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:12" ht="17.25" customHeight="1">
       <c r="A20" s="396">
         <v>4</v>
       </c>
-      <c r="B20" s="655" t="s">
+      <c r="B20" s="658" t="s">
         <v>113</v>
       </c>
-      <c r="C20" s="656"/>
-      <c r="D20" s="656"/>
-      <c r="E20" s="657"/>
+      <c r="C20" s="659"/>
+      <c r="D20" s="659"/>
+      <c r="E20" s="660"/>
       <c r="F20" s="397" t="s">
         <v>41</v>
       </c>
@@ -12476,7 +12476,7 @@
       </c>
       <c r="L20" s="394"/>
     </row>
-    <row r="21" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:12" ht="17.25" customHeight="1">
       <c r="A21" s="396">
         <v>5</v>
       </c>
@@ -12505,16 +12505,16 @@
       </c>
       <c r="L21" s="394"/>
     </row>
-    <row r="22" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:12" ht="17.25" customHeight="1">
       <c r="A22" s="396">
         <v>6</v>
       </c>
-      <c r="B22" s="655" t="s">
+      <c r="B22" s="658" t="s">
         <v>114</v>
       </c>
-      <c r="C22" s="656"/>
-      <c r="D22" s="656"/>
-      <c r="E22" s="657"/>
+      <c r="C22" s="659"/>
+      <c r="D22" s="659"/>
+      <c r="E22" s="660"/>
       <c r="F22" s="399" t="s">
         <v>41</v>
       </c>
@@ -12534,16 +12534,16 @@
       </c>
       <c r="L22" s="394"/>
     </row>
-    <row r="23" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:12" ht="17.25" customHeight="1">
       <c r="A23" s="396">
         <v>7</v>
       </c>
-      <c r="B23" s="655" t="s">
+      <c r="B23" s="658" t="s">
         <v>115</v>
       </c>
-      <c r="C23" s="656"/>
-      <c r="D23" s="656"/>
-      <c r="E23" s="657"/>
+      <c r="C23" s="659"/>
+      <c r="D23" s="659"/>
+      <c r="E23" s="660"/>
       <c r="F23" s="397" t="s">
         <v>41</v>
       </c>
@@ -12563,16 +12563,16 @@
       </c>
       <c r="L23" s="394"/>
     </row>
-    <row r="24" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:12" ht="17.25" customHeight="1">
       <c r="A24" s="396">
         <v>8</v>
       </c>
-      <c r="B24" s="655" t="s">
+      <c r="B24" s="658" t="s">
         <v>116</v>
       </c>
-      <c r="C24" s="656"/>
-      <c r="D24" s="656"/>
-      <c r="E24" s="657"/>
+      <c r="C24" s="659"/>
+      <c r="D24" s="659"/>
+      <c r="E24" s="660"/>
       <c r="F24" s="399" t="s">
         <v>41</v>
       </c>
@@ -12592,16 +12592,16 @@
       </c>
       <c r="L24" s="394"/>
     </row>
-    <row r="25" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:12" ht="17.25" customHeight="1">
       <c r="A25" s="396">
         <v>9</v>
       </c>
-      <c r="B25" s="658" t="s">
+      <c r="B25" s="661" t="s">
         <v>117</v>
       </c>
-      <c r="C25" s="659"/>
-      <c r="D25" s="659"/>
-      <c r="E25" s="660"/>
+      <c r="C25" s="662"/>
+      <c r="D25" s="662"/>
+      <c r="E25" s="663"/>
       <c r="F25" s="399" t="s">
         <v>56</v>
       </c>
@@ -12621,7 +12621,7 @@
       </c>
       <c r="L25" s="394"/>
     </row>
-    <row r="26" spans="1:12" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:12" ht="14.25" customHeight="1">
       <c r="A26" s="387"/>
       <c r="B26" s="400"/>
       <c r="C26" s="400"/>
@@ -12642,7 +12642,7 @@
       </c>
       <c r="L26" s="394"/>
     </row>
-    <row r="27" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:12" ht="17.25" customHeight="1">
       <c r="A27" s="387"/>
       <c r="B27" s="199" t="s">
         <v>134</v>
@@ -12664,7 +12664,7 @@
       </c>
       <c r="L27" s="394"/>
     </row>
-    <row r="28" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:12" ht="17.25" customHeight="1">
       <c r="A28" s="387"/>
       <c r="B28" s="199" t="s">
         <v>135</v>
@@ -12686,7 +12686,7 @@
       </c>
       <c r="L28" s="394"/>
     </row>
-    <row r="29" spans="1:12" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:12" ht="15.9" customHeight="1">
       <c r="A29" s="387"/>
       <c r="B29" s="199" t="s">
         <v>136</v>
@@ -12708,33 +12708,33 @@
       </c>
       <c r="L29" s="394"/>
     </row>
-    <row r="30" spans="1:12" ht="5.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:12" ht="5.25" customHeight="1">
       <c r="A30" s="387"/>
       <c r="I30" s="405"/>
       <c r="J30" s="406"/>
       <c r="K30" s="406"/>
       <c r="L30" s="394"/>
     </row>
-    <row r="31" spans="1:12" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:12" ht="15.9" customHeight="1">
       <c r="A31" s="387"/>
-      <c r="B31" s="662" t="s">
+      <c r="B31" s="650" t="s">
         <v>137</v>
       </c>
-      <c r="C31" s="662"/>
-      <c r="D31" s="662"/>
-      <c r="E31" s="662"/>
-      <c r="F31" s="662"/>
-      <c r="G31" s="662"/>
+      <c r="C31" s="650"/>
+      <c r="D31" s="650"/>
+      <c r="E31" s="650"/>
+      <c r="F31" s="650"/>
+      <c r="G31" s="650"/>
       <c r="L31" s="394"/>
     </row>
-    <row r="32" spans="1:12" ht="26.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:12" ht="26.25" customHeight="1">
       <c r="A32" s="387"/>
-      <c r="B32" s="652" t="s">
+      <c r="B32" s="655" t="s">
         <v>138</v>
       </c>
-      <c r="C32" s="653"/>
-      <c r="D32" s="653"/>
-      <c r="E32" s="654"/>
+      <c r="C32" s="656"/>
+      <c r="D32" s="656"/>
+      <c r="E32" s="657"/>
       <c r="F32" s="369" t="s">
         <v>139</v>
       </c>
@@ -12743,14 +12743,14 @@
       </c>
       <c r="L32" s="394"/>
     </row>
-    <row r="33" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:12" ht="16.5" customHeight="1">
       <c r="A33" s="387"/>
-      <c r="B33" s="649" t="s">
+      <c r="B33" s="652" t="s">
         <v>141</v>
       </c>
-      <c r="C33" s="650"/>
-      <c r="D33" s="650"/>
-      <c r="E33" s="651"/>
+      <c r="C33" s="653"/>
+      <c r="D33" s="653"/>
+      <c r="E33" s="654"/>
       <c r="F33" s="330" t="s">
         <v>142</v>
       </c>
@@ -12759,14 +12759,14 @@
       </c>
       <c r="L33" s="394"/>
     </row>
-    <row r="34" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:12" ht="16.5" customHeight="1">
       <c r="A34" s="387"/>
-      <c r="B34" s="649" t="s">
+      <c r="B34" s="652" t="s">
         <v>143</v>
       </c>
-      <c r="C34" s="650"/>
-      <c r="D34" s="650"/>
-      <c r="E34" s="651"/>
+      <c r="C34" s="653"/>
+      <c r="D34" s="653"/>
+      <c r="E34" s="654"/>
       <c r="F34" s="330" t="s">
         <v>144</v>
       </c>
@@ -12775,14 +12775,14 @@
       </c>
       <c r="L34" s="394"/>
     </row>
-    <row r="35" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:12" ht="16.5" customHeight="1">
       <c r="A35" s="387"/>
-      <c r="B35" s="649" t="s">
+      <c r="B35" s="652" t="s">
         <v>145</v>
       </c>
-      <c r="C35" s="650"/>
-      <c r="D35" s="650"/>
-      <c r="E35" s="651"/>
+      <c r="C35" s="653"/>
+      <c r="D35" s="653"/>
+      <c r="E35" s="654"/>
       <c r="F35" s="330" t="s">
         <v>146</v>
       </c>
@@ -12791,26 +12791,26 @@
       </c>
       <c r="L35" s="394"/>
     </row>
-    <row r="36" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:12" ht="16.5" customHeight="1">
       <c r="A36" s="387"/>
-      <c r="B36" s="662" t="s">
+      <c r="B36" s="650" t="s">
         <v>147</v>
       </c>
-      <c r="C36" s="662"/>
-      <c r="D36" s="662"/>
-      <c r="E36" s="662"/>
-      <c r="F36" s="662"/>
-      <c r="G36" s="662"/>
+      <c r="C36" s="650"/>
+      <c r="D36" s="650"/>
+      <c r="E36" s="650"/>
+      <c r="F36" s="650"/>
+      <c r="G36" s="650"/>
       <c r="L36" s="394"/>
     </row>
-    <row r="37" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:12" ht="16.5" customHeight="1">
       <c r="A37" s="387"/>
-      <c r="B37" s="649" t="s">
+      <c r="B37" s="652" t="s">
         <v>227</v>
       </c>
-      <c r="C37" s="650"/>
-      <c r="D37" s="650"/>
-      <c r="E37" s="651"/>
+      <c r="C37" s="653"/>
+      <c r="D37" s="653"/>
+      <c r="E37" s="654"/>
       <c r="F37" s="330" t="s">
         <v>148</v>
       </c>
@@ -12819,14 +12819,14 @@
       </c>
       <c r="L37" s="394"/>
     </row>
-    <row r="38" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:12" ht="16.5" customHeight="1">
       <c r="A38" s="387"/>
-      <c r="B38" s="649" t="s">
+      <c r="B38" s="652" t="s">
         <v>149</v>
       </c>
-      <c r="C38" s="650"/>
-      <c r="D38" s="650"/>
-      <c r="E38" s="651"/>
+      <c r="C38" s="653"/>
+      <c r="D38" s="653"/>
+      <c r="E38" s="654"/>
       <c r="F38" s="330" t="s">
         <v>150</v>
       </c>
@@ -12835,14 +12835,14 @@
       </c>
       <c r="L38" s="394"/>
     </row>
-    <row r="39" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:12" ht="16.5" customHeight="1">
       <c r="A39" s="387"/>
-      <c r="B39" s="649" t="s">
+      <c r="B39" s="652" t="s">
         <v>151</v>
       </c>
-      <c r="C39" s="650"/>
-      <c r="D39" s="650"/>
-      <c r="E39" s="651"/>
+      <c r="C39" s="653"/>
+      <c r="D39" s="653"/>
+      <c r="E39" s="654"/>
       <c r="F39" s="330" t="s">
         <v>152</v>
       </c>
@@ -12851,98 +12851,98 @@
       </c>
       <c r="L39" s="394"/>
     </row>
-    <row r="40" spans="1:12" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:12" ht="13.5" customHeight="1">
       <c r="A40" s="387"/>
       <c r="I40" s="197"/>
       <c r="J40" s="381"/>
       <c r="K40" s="329"/>
       <c r="L40" s="394"/>
     </row>
-    <row r="41" spans="1:12" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:12" ht="13.5" customHeight="1">
       <c r="A41" s="387"/>
       <c r="I41" s="197"/>
       <c r="J41" s="381"/>
       <c r="K41" s="329"/>
       <c r="L41" s="394"/>
     </row>
-    <row r="42" spans="1:12" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:12" ht="13.5" customHeight="1">
       <c r="A42" s="387"/>
       <c r="I42" s="197"/>
       <c r="J42" s="381"/>
       <c r="K42" s="329"/>
       <c r="L42" s="394"/>
     </row>
-    <row r="43" spans="1:12" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:12" ht="13.5" customHeight="1">
       <c r="A43" s="387"/>
       <c r="I43" s="197"/>
       <c r="J43" s="381"/>
       <c r="K43" s="329"/>
       <c r="L43" s="394"/>
     </row>
-    <row r="44" spans="1:12" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="44" spans="1:12" ht="13.5" customHeight="1">
       <c r="A44" s="387"/>
       <c r="I44" s="197"/>
       <c r="J44" s="381"/>
       <c r="K44" s="329"/>
       <c r="L44" s="394"/>
     </row>
-    <row r="45" spans="1:12" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="45" spans="1:12" ht="13.5" customHeight="1">
       <c r="A45" s="387"/>
       <c r="I45" s="197"/>
       <c r="J45" s="381"/>
       <c r="K45" s="329"/>
       <c r="L45" s="394"/>
     </row>
-    <row r="46" spans="1:12" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="46" spans="1:12" ht="13.5" customHeight="1">
       <c r="A46" s="387"/>
       <c r="I46" s="197"/>
       <c r="J46" s="381"/>
       <c r="K46" s="329"/>
       <c r="L46" s="394"/>
     </row>
-    <row r="47" spans="1:12" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="47" spans="1:12" ht="13.5" customHeight="1">
       <c r="A47" s="387"/>
       <c r="I47" s="197"/>
       <c r="J47" s="381"/>
       <c r="K47" s="329"/>
       <c r="L47" s="394"/>
     </row>
-    <row r="48" spans="1:12" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="48" spans="1:12" ht="13.5" customHeight="1">
       <c r="A48" s="387"/>
       <c r="I48" s="197"/>
       <c r="J48" s="381"/>
       <c r="K48" s="329"/>
       <c r="L48" s="394"/>
     </row>
-    <row r="49" spans="1:12" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="49" spans="1:12" ht="13.5" customHeight="1">
       <c r="A49" s="387"/>
       <c r="I49" s="197"/>
       <c r="J49" s="381"/>
       <c r="K49" s="329"/>
       <c r="L49" s="394"/>
     </row>
-    <row r="50" spans="1:12" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="50" spans="1:12" ht="13.5" customHeight="1">
       <c r="A50" s="387"/>
       <c r="I50" s="197"/>
       <c r="J50" s="381"/>
       <c r="K50" s="329"/>
       <c r="L50" s="394"/>
     </row>
-    <row r="51" spans="1:12" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="51" spans="1:12" ht="13.5" customHeight="1">
       <c r="A51" s="387"/>
       <c r="I51" s="197"/>
       <c r="J51" s="382"/>
       <c r="K51" s="329"/>
       <c r="L51" s="394"/>
     </row>
-    <row r="52" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="52" spans="1:12">
       <c r="A52" s="387"/>
       <c r="I52" s="197"/>
       <c r="J52" s="381"/>
       <c r="K52" s="329"/>
       <c r="L52" s="394"/>
     </row>
-    <row r="53" spans="1:12" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:12" ht="13.8" thickBot="1">
       <c r="A53" s="407"/>
       <c r="B53" s="408"/>
       <c r="C53" s="408"/>
@@ -12959,15 +12959,6 @@
   </sheetData>
   <sheetProtection algorithmName="SHA-512" hashValue="xWWTH2ODRJvJuq26fz8BDBTKOyLp8SD8OPQSny0kNhk0w02O6G1TzYz/+8aUJNSNF0435K8vhuSYHksIa+3eMQ==" saltValue="O89M/G/p4V9ywCWV4cqXXA==" spinCount="100000" sheet="1" objects="1" scenarios="1"/>
   <mergeCells count="22">
-    <mergeCell ref="B2:K2"/>
-    <mergeCell ref="B3:K3"/>
-    <mergeCell ref="B31:G31"/>
-    <mergeCell ref="B36:G36"/>
-    <mergeCell ref="H17:H18"/>
-    <mergeCell ref="B33:E33"/>
-    <mergeCell ref="B34:E34"/>
-    <mergeCell ref="B35:E35"/>
-    <mergeCell ref="B32:E32"/>
     <mergeCell ref="B39:E39"/>
     <mergeCell ref="B5:E5"/>
     <mergeCell ref="B7:E7"/>
@@ -12981,6 +12972,15 @@
     <mergeCell ref="B25:E25"/>
     <mergeCell ref="B37:E37"/>
     <mergeCell ref="B38:E38"/>
+    <mergeCell ref="B2:K2"/>
+    <mergeCell ref="B3:K3"/>
+    <mergeCell ref="B31:G31"/>
+    <mergeCell ref="B36:G36"/>
+    <mergeCell ref="H17:H18"/>
+    <mergeCell ref="B33:E33"/>
+    <mergeCell ref="B34:E34"/>
+    <mergeCell ref="B35:E35"/>
+    <mergeCell ref="B32:E32"/>
   </mergeCells>
   <conditionalFormatting sqref="E11">
     <cfRule type="containsText" dxfId="0" priority="1" operator="containsText" text="no">
@@ -13009,32 +13009,32 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:K72"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11.42578125" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.44140625" defaultRowHeight="13.2"/>
   <cols>
-    <col min="1" max="1" width="21.85546875" style="339" customWidth="1"/>
-    <col min="2" max="2" width="11.5703125" style="339" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="12.5703125" style="339" customWidth="1"/>
-    <col min="4" max="4" width="11.5703125" style="339" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="21.88671875" style="339" customWidth="1"/>
+    <col min="2" max="2" width="11.5546875" style="339" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.5546875" style="339" customWidth="1"/>
+    <col min="4" max="4" width="11.5546875" style="339" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="20" style="339" customWidth="1"/>
     <col min="6" max="6" width="14" style="339" customWidth="1"/>
-    <col min="7" max="7" width="13.7109375" style="339" customWidth="1"/>
-    <col min="8" max="8" width="15.28515625" style="339" customWidth="1"/>
-    <col min="9" max="9" width="9.85546875" style="339" customWidth="1"/>
-    <col min="10" max="10" width="14.42578125" style="339" customWidth="1"/>
-    <col min="11" max="16384" width="11.42578125" style="339"/>
+    <col min="7" max="7" width="13.6640625" style="339" customWidth="1"/>
+    <col min="8" max="8" width="15.33203125" style="339" customWidth="1"/>
+    <col min="9" max="9" width="9.88671875" style="339" customWidth="1"/>
+    <col min="10" max="10" width="14.44140625" style="339" customWidth="1"/>
+    <col min="11" max="16384" width="11.44140625" style="339"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="673"/>
-      <c r="B1" s="674"/>
-      <c r="C1" s="664" t="s">
+    <row r="1" spans="1:10" ht="12.75" customHeight="1">
+      <c r="A1" s="681"/>
+      <c r="B1" s="682"/>
+      <c r="C1" s="672" t="s">
         <v>153</v>
       </c>
-      <c r="D1" s="665"/>
-      <c r="E1" s="665"/>
-      <c r="F1" s="665"/>
-      <c r="G1" s="665"/>
-      <c r="H1" s="666"/>
+      <c r="D1" s="673"/>
+      <c r="E1" s="673"/>
+      <c r="F1" s="673"/>
+      <c r="G1" s="673"/>
+      <c r="H1" s="674"/>
       <c r="I1" s="221" t="s">
         <v>154</v>
       </c>
@@ -13042,15 +13042,15 @@
         <v>155</v>
       </c>
     </row>
-    <row r="2" spans="1:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="675"/>
-      <c r="B2" s="676"/>
-      <c r="C2" s="667"/>
-      <c r="D2" s="668"/>
-      <c r="E2" s="668"/>
-      <c r="F2" s="668"/>
-      <c r="G2" s="668"/>
-      <c r="H2" s="669"/>
+    <row r="2" spans="1:10" ht="12.75" customHeight="1">
+      <c r="A2" s="683"/>
+      <c r="B2" s="684"/>
+      <c r="C2" s="675"/>
+      <c r="D2" s="676"/>
+      <c r="E2" s="676"/>
+      <c r="F2" s="676"/>
+      <c r="G2" s="676"/>
+      <c r="H2" s="677"/>
       <c r="I2" s="221" t="s">
         <v>156</v>
       </c>
@@ -13058,15 +13058,15 @@
         <v>3</v>
       </c>
     </row>
-    <row r="3" spans="1:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="675"/>
-      <c r="B3" s="676"/>
-      <c r="C3" s="667"/>
-      <c r="D3" s="668"/>
-      <c r="E3" s="668"/>
-      <c r="F3" s="668"/>
-      <c r="G3" s="668"/>
-      <c r="H3" s="669"/>
+    <row r="3" spans="1:10" ht="12.75" customHeight="1">
+      <c r="A3" s="683"/>
+      <c r="B3" s="684"/>
+      <c r="C3" s="675"/>
+      <c r="D3" s="676"/>
+      <c r="E3" s="676"/>
+      <c r="F3" s="676"/>
+      <c r="G3" s="676"/>
+      <c r="H3" s="677"/>
       <c r="I3" s="221" t="s">
         <v>157</v>
       </c>
@@ -13074,15 +13074,15 @@
         <v>46146</v>
       </c>
     </row>
-    <row r="4" spans="1:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A4" s="677"/>
-      <c r="B4" s="678"/>
-      <c r="C4" s="670"/>
-      <c r="D4" s="671"/>
-      <c r="E4" s="671"/>
-      <c r="F4" s="671"/>
-      <c r="G4" s="671"/>
-      <c r="H4" s="672"/>
+    <row r="4" spans="1:10" ht="12.75" customHeight="1">
+      <c r="A4" s="685"/>
+      <c r="B4" s="686"/>
+      <c r="C4" s="678"/>
+      <c r="D4" s="679"/>
+      <c r="E4" s="679"/>
+      <c r="F4" s="679"/>
+      <c r="G4" s="679"/>
+      <c r="H4" s="680"/>
       <c r="I4" s="221" t="s">
         <v>158</v>
       </c>
@@ -13090,7 +13090,7 @@
         <v>159</v>
       </c>
     </row>
-    <row r="6" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:10" ht="18" customHeight="1">
       <c r="A6" s="223" t="s">
         <v>160</v>
       </c>
@@ -13106,7 +13106,7 @@
       <c r="I6" s="340"/>
       <c r="J6" s="341"/>
     </row>
-    <row r="7" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:10" ht="18" customHeight="1">
       <c r="A7" s="223" t="s">
         <v>162</v>
       </c>
@@ -13122,7 +13122,7 @@
       <c r="I7" s="340"/>
       <c r="J7" s="341"/>
     </row>
-    <row r="8" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:10" ht="18" customHeight="1">
       <c r="A8" s="223" t="s">
         <v>163</v>
       </c>
@@ -13138,7 +13138,7 @@
       <c r="I8" s="340"/>
       <c r="J8" s="341"/>
     </row>
-    <row r="9" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:10" ht="18" customHeight="1">
       <c r="A9" s="224" t="s">
         <v>302</v>
       </c>
@@ -13154,13 +13154,13 @@
       <c r="I9" s="340"/>
       <c r="J9" s="341"/>
     </row>
-    <row r="11" spans="1:10" ht="12" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:10" ht="12" customHeight="1">
       <c r="A11" s="351" t="s">
         <v>303</v>
       </c>
     </row>
-    <row r="12" spans="1:10" ht="12" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="13" spans="1:10" ht="12" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:10" ht="12" customHeight="1"/>
+    <row r="13" spans="1:10" ht="12" customHeight="1">
       <c r="A13" s="353" t="s">
         <v>165</v>
       </c>
@@ -13168,81 +13168,81 @@
         <v>169</v>
       </c>
     </row>
-    <row r="14" spans="1:10" ht="12" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="15" spans="1:10" ht="12" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:10" ht="12" customHeight="1"/>
+    <row r="15" spans="1:10" ht="12" customHeight="1">
       <c r="A15" s="352" t="s">
         <v>166</v>
       </c>
       <c r="G15" s="350"/>
     </row>
-    <row r="16" spans="1:10" ht="12" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:10" ht="12" customHeight="1">
       <c r="A16" s="352" t="s">
         <v>167</v>
       </c>
     </row>
-    <row r="17" spans="1:11" ht="12" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:11" ht="12" customHeight="1">
       <c r="A17" s="352" t="s">
         <v>168</v>
       </c>
       <c r="G17" s="350"/>
     </row>
-    <row r="18" spans="1:11" ht="12" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="19" spans="1:11" ht="12" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:11" ht="12" customHeight="1"/>
+    <row r="19" spans="1:11" ht="12" customHeight="1">
       <c r="A19" s="353" t="s">
         <v>170</v>
       </c>
       <c r="G19" s="350"/>
     </row>
-    <row r="20" spans="1:11" ht="12" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="21" spans="1:11" ht="12" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:11" ht="12" customHeight="1"/>
+    <row r="21" spans="1:11" ht="12" customHeight="1">
       <c r="A21" s="352" t="s">
         <v>171</v>
       </c>
       <c r="G21" s="350"/>
     </row>
-    <row r="22" spans="1:11" ht="17.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="23" spans="1:11" ht="12" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:11" ht="17.25" customHeight="1"/>
+    <row r="23" spans="1:11" ht="12" customHeight="1">
       <c r="A23" s="351" t="s">
         <v>172</v>
       </c>
     </row>
-    <row r="24" spans="1:11" ht="12" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="25" spans="1:11" ht="12" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="26" spans="1:11" ht="12" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="27" spans="1:11" ht="12" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:11" ht="12" customHeight="1"/>
+    <row r="25" spans="1:11" ht="12" customHeight="1"/>
+    <row r="26" spans="1:11" ht="12" customHeight="1"/>
+    <row r="27" spans="1:11" ht="12" customHeight="1">
       <c r="K27" s="350"/>
     </row>
-    <row r="28" spans="1:11" ht="6" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="29" spans="1:11" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:11" ht="6" customHeight="1"/>
+    <row r="29" spans="1:11" ht="16.5" customHeight="1">
       <c r="F29" s="350"/>
     </row>
-    <row r="30" spans="1:11" ht="16.5" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="31" spans="1:11" ht="16.5" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="32" spans="1:11" ht="16.5" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="33" spans="1:10" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:11" ht="16.5" customHeight="1"/>
+    <row r="31" spans="1:11" ht="16.5" customHeight="1"/>
+    <row r="32" spans="1:11" ht="16.5" customHeight="1"/>
+    <row r="33" spans="1:10" ht="21.75" customHeight="1">
       <c r="I33" s="350"/>
     </row>
-    <row r="34" spans="1:10" ht="17.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="35" spans="1:10" ht="17.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="37" spans="1:10" ht="10.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:10" ht="17.25" customHeight="1"/>
+    <row r="35" spans="1:10" ht="17.25" customHeight="1"/>
+    <row r="37" spans="1:10" ht="10.5" customHeight="1">
       <c r="I37" s="337"/>
       <c r="J37" s="337"/>
     </row>
-    <row r="38" spans="1:10" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A38" s="683" t="s">
+    <row r="38" spans="1:10" ht="15.75" customHeight="1" thickBot="1">
+      <c r="A38" s="691" t="s">
         <v>304</v>
       </c>
-      <c r="B38" s="684"/>
-      <c r="C38" s="684"/>
-      <c r="D38" s="684"/>
-      <c r="E38" s="684"/>
-      <c r="F38" s="684"/>
-      <c r="G38" s="684"/>
-      <c r="H38" s="685"/>
+      <c r="B38" s="692"/>
+      <c r="C38" s="692"/>
+      <c r="D38" s="692"/>
+      <c r="E38" s="692"/>
+      <c r="F38" s="692"/>
+      <c r="G38" s="692"/>
+      <c r="H38" s="693"/>
       <c r="I38" s="337"/>
       <c r="J38" s="337"/>
     </row>
-    <row r="39" spans="1:10" ht="45" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:10" ht="45" customHeight="1" thickBot="1">
       <c r="A39" s="244" t="s">
         <v>173</v>
       </c>
@@ -13273,7 +13273,7 @@
       </c>
       <c r="J39" s="337"/>
     </row>
-    <row r="40" spans="1:10" s="343" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:10" s="343" customFormat="1" ht="21.75" customHeight="1">
       <c r="A40" s="234" t="s">
         <v>181</v>
       </c>
@@ -13302,7 +13302,7 @@
       <c r="I40" s="337"/>
       <c r="J40" s="342"/>
     </row>
-    <row r="41" spans="1:10" s="343" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:10" s="343" customFormat="1" ht="21.75" customHeight="1">
       <c r="A41" s="268" t="s">
         <v>183</v>
       </c>
@@ -13333,7 +13333,7 @@
       </c>
       <c r="I41" s="337"/>
     </row>
-    <row r="42" spans="1:10" s="343" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:10" s="343" customFormat="1" ht="21.75" customHeight="1">
       <c r="A42" s="235" t="s">
         <v>185</v>
       </c>
@@ -13360,7 +13360,7 @@
       </c>
       <c r="I42" s="337"/>
     </row>
-    <row r="43" spans="1:10" s="343" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:10" s="343" customFormat="1" ht="21.75" customHeight="1">
       <c r="A43" s="235" t="s">
         <v>187</v>
       </c>
@@ -13387,7 +13387,7 @@
       </c>
       <c r="I43" s="337"/>
     </row>
-    <row r="44" spans="1:10" s="343" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="44" spans="1:10" s="343" customFormat="1" ht="21.75" customHeight="1">
       <c r="A44" s="235" t="s">
         <v>189</v>
       </c>
@@ -13414,7 +13414,7 @@
       </c>
       <c r="I44" s="337"/>
     </row>
-    <row r="45" spans="1:10" s="343" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="45" spans="1:10" s="343" customFormat="1" ht="21.75" customHeight="1">
       <c r="A45" s="268" t="s">
         <v>191</v>
       </c>
@@ -13444,7 +13444,7 @@
       <c r="I45" s="337"/>
       <c r="J45" s="337"/>
     </row>
-    <row r="46" spans="1:10" s="343" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="46" spans="1:10" s="343" customFormat="1" ht="21.75" customHeight="1">
       <c r="A46" s="235" t="s">
         <v>185</v>
       </c>
@@ -13472,7 +13472,7 @@
       <c r="I46" s="337"/>
       <c r="J46" s="337"/>
     </row>
-    <row r="47" spans="1:10" s="343" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="47" spans="1:10" s="343" customFormat="1" ht="21.75" customHeight="1">
       <c r="A47" s="235" t="s">
         <v>187</v>
       </c>
@@ -13500,7 +13500,7 @@
       <c r="I47" s="337"/>
       <c r="J47" s="337"/>
     </row>
-    <row r="48" spans="1:10" s="343" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="48" spans="1:10" s="343" customFormat="1" ht="21.75" customHeight="1">
       <c r="A48" s="235" t="s">
         <v>189</v>
       </c>
@@ -13528,7 +13528,7 @@
       <c r="I48" s="337"/>
       <c r="J48" s="337"/>
     </row>
-    <row r="49" spans="1:10" s="343" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="49" spans="1:10" s="343" customFormat="1" ht="21.75" customHeight="1">
       <c r="A49" s="268" t="s">
         <v>192</v>
       </c>
@@ -13558,7 +13558,7 @@
       <c r="I49" s="337"/>
       <c r="J49" s="337"/>
     </row>
-    <row r="50" spans="1:10" s="343" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="50" spans="1:10" s="343" customFormat="1" ht="21.75" customHeight="1">
       <c r="A50" s="235" t="s">
         <v>185</v>
       </c>
@@ -13586,7 +13586,7 @@
       <c r="I50" s="337"/>
       <c r="J50" s="337"/>
     </row>
-    <row r="51" spans="1:10" s="343" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="51" spans="1:10" s="343" customFormat="1" ht="21.75" customHeight="1">
       <c r="A51" s="235" t="s">
         <v>187</v>
       </c>
@@ -13614,7 +13614,7 @@
       <c r="I51" s="337"/>
       <c r="J51" s="337"/>
     </row>
-    <row r="52" spans="1:10" s="343" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="52" spans="1:10" s="343" customFormat="1" ht="21.75" customHeight="1">
       <c r="A52" s="235" t="s">
         <v>189</v>
       </c>
@@ -13642,7 +13642,7 @@
       <c r="I52" s="337"/>
       <c r="J52" s="337"/>
     </row>
-    <row r="53" spans="1:10" s="343" customFormat="1" ht="21.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:10" s="343" customFormat="1" ht="21.75" customHeight="1" thickBot="1">
       <c r="A53" s="272" t="s">
         <v>193</v>
       </c>
@@ -13671,49 +13671,49 @@
       <c r="I53" s="337"/>
       <c r="J53" s="337"/>
     </row>
-    <row r="54" spans="1:10" s="343" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A54" s="686" t="s">
+    <row r="54" spans="1:10" s="343" customFormat="1" ht="16.5" customHeight="1">
+      <c r="A54" s="694" t="s">
         <v>195</v>
       </c>
-      <c r="B54" s="687"/>
-      <c r="C54" s="688"/>
+      <c r="B54" s="695"/>
+      <c r="C54" s="696"/>
       <c r="D54" s="280" t="s">
         <v>56</v>
       </c>
       <c r="E54" s="281"/>
-      <c r="F54" s="679" t="e">
+      <c r="F54" s="687" t="e">
         <f>SQRT((H41*H41)+(H45*H45)+(H49*H49)+(H53*H53))</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="G54" s="679"/>
-      <c r="H54" s="680"/>
+      <c r="G54" s="687"/>
+      <c r="H54" s="688"/>
       <c r="I54" s="337" t="s">
         <v>196</v>
       </c>
       <c r="J54" s="337"/>
     </row>
-    <row r="55" spans="1:10" s="343" customFormat="1" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A55" s="689" t="s">
+    <row r="55" spans="1:10" s="343" customFormat="1" ht="18" customHeight="1" thickBot="1">
+      <c r="A55" s="697" t="s">
         <v>197</v>
       </c>
-      <c r="B55" s="690"/>
-      <c r="C55" s="691"/>
+      <c r="B55" s="698"/>
+      <c r="C55" s="699"/>
       <c r="D55" s="308" t="s">
         <v>56</v>
       </c>
       <c r="E55" s="282"/>
-      <c r="F55" s="681" t="e">
+      <c r="F55" s="689" t="e">
         <f>F54*2</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="G55" s="681"/>
-      <c r="H55" s="682"/>
+      <c r="G55" s="689"/>
+      <c r="H55" s="690"/>
       <c r="I55" s="337" t="s">
         <v>198</v>
       </c>
       <c r="J55" s="337"/>
     </row>
-    <row r="56" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="56" spans="1:10" ht="15" customHeight="1">
       <c r="A56" s="337"/>
       <c r="D56" s="337"/>
       <c r="E56" s="337"/>
@@ -13723,7 +13723,7 @@
       <c r="I56" s="337"/>
       <c r="J56" s="337"/>
     </row>
-    <row r="57" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="57" spans="1:10" ht="15" customHeight="1">
       <c r="A57" s="337"/>
       <c r="D57" s="337"/>
       <c r="E57" s="337"/>
@@ -13733,7 +13733,7 @@
       <c r="I57" s="337"/>
       <c r="J57" s="337"/>
     </row>
-    <row r="58" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="58" spans="1:10" ht="15" customHeight="1">
       <c r="E58" s="337"/>
       <c r="F58" s="337"/>
       <c r="G58" s="337"/>
@@ -13741,7 +13741,7 @@
       <c r="I58" s="337"/>
       <c r="J58" s="337"/>
     </row>
-    <row r="59" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="59" spans="1:10" ht="15" customHeight="1">
       <c r="B59" s="345" t="s">
         <v>305</v>
       </c>
@@ -13752,7 +13752,7 @@
       <c r="I59" s="337"/>
       <c r="J59" s="337"/>
     </row>
-    <row r="60" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="60" spans="1:10" ht="15" customHeight="1">
       <c r="A60" s="252"/>
       <c r="B60" s="228" t="s">
         <v>199</v>
@@ -13770,7 +13770,7 @@
       <c r="I60" s="337"/>
       <c r="J60" s="337"/>
     </row>
-    <row r="61" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="61" spans="1:10" ht="15" customHeight="1">
       <c r="A61" s="253"/>
       <c r="B61" s="346" t="str">
         <f>A41</f>
@@ -13791,7 +13791,7 @@
       <c r="I61" s="337"/>
       <c r="J61" s="337"/>
     </row>
-    <row r="62" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="62" spans="1:10" ht="15" customHeight="1">
       <c r="A62" s="253"/>
       <c r="B62" s="346" t="str">
         <f>A45</f>
@@ -13812,7 +13812,7 @@
       <c r="I62" s="337"/>
       <c r="J62" s="337"/>
     </row>
-    <row r="63" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="63" spans="1:10" ht="15" customHeight="1">
       <c r="A63" s="255"/>
       <c r="B63" s="347" t="str">
         <f>A49</f>
@@ -13833,7 +13833,7 @@
       <c r="I63" s="337"/>
       <c r="J63" s="337"/>
     </row>
-    <row r="64" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="64" spans="1:10" ht="15" customHeight="1">
       <c r="A64" s="255"/>
       <c r="B64" s="347" t="str">
         <f>A53</f>
@@ -13854,7 +13854,7 @@
       <c r="I64" s="337"/>
       <c r="J64" s="337"/>
     </row>
-    <row r="65" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="65" spans="1:10" ht="15" customHeight="1">
       <c r="A65" s="257"/>
       <c r="B65" s="258"/>
       <c r="C65" s="259" t="e">
@@ -13872,54 +13872,48 @@
       <c r="I65" s="337"/>
       <c r="J65" s="337"/>
     </row>
-    <row r="66" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="67" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="68" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="69" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="70" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="66" spans="1:10" ht="15" customHeight="1"/>
+    <row r="67" spans="1:10" ht="15" customHeight="1"/>
+    <row r="68" spans="1:10" ht="15" customHeight="1"/>
+    <row r="69" spans="1:10" ht="15" customHeight="1"/>
+    <row r="70" spans="1:10">
       <c r="A70" s="541" t="s">
         <v>306</v>
       </c>
-      <c r="B70" s="692" t="s">
+      <c r="B70" s="664" t="s">
         <v>307</v>
       </c>
-      <c r="C70" s="693"/>
+      <c r="C70" s="665"/>
       <c r="D70" s="542"/>
-      <c r="E70" s="694" t="s">
+      <c r="E70" s="666" t="s">
         <v>308</v>
       </c>
-      <c r="F70" s="694"/>
-      <c r="G70" s="695" t="s">
+      <c r="F70" s="666"/>
+      <c r="G70" s="667" t="s">
         <v>309</v>
       </c>
-      <c r="H70" s="696"/>
-    </row>
-    <row r="72" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="H70" s="668"/>
+    </row>
+    <row r="72" spans="1:10">
       <c r="A72" s="543" t="s">
         <v>310</v>
       </c>
-      <c r="B72" s="697">
+      <c r="B72" s="669">
         <v>44944</v>
       </c>
-      <c r="C72" s="698"/>
-      <c r="E72" s="699" t="s">
+      <c r="C72" s="670"/>
+      <c r="E72" s="671" t="s">
         <v>311</v>
       </c>
-      <c r="F72" s="699"/>
-      <c r="G72" s="697">
+      <c r="F72" s="671"/>
+      <c r="G72" s="669">
         <v>44944</v>
       </c>
-      <c r="H72" s="698"/>
+      <c r="H72" s="670"/>
     </row>
   </sheetData>
   <sheetProtection algorithmName="SHA-512" hashValue="iLEnVB6pm8HGxp/myiIucvHcjmqcSrUFV5EFJhRy/Wl6J20Lu8rufg9gJo4vTQR/wN6I3HZ06PN9TnsphGZBRg==" saltValue="rC1uvtCaR6F4sqhd68ayKA==" spinCount="100000" sheet="1" selectLockedCells="1" selectUnlockedCells="1"/>
   <mergeCells count="13">
-    <mergeCell ref="B70:C70"/>
-    <mergeCell ref="E70:F70"/>
-    <mergeCell ref="G70:H70"/>
-    <mergeCell ref="B72:C72"/>
-    <mergeCell ref="E72:F72"/>
-    <mergeCell ref="G72:H72"/>
     <mergeCell ref="C1:H4"/>
     <mergeCell ref="A1:B4"/>
     <mergeCell ref="F54:H54"/>
@@ -13927,6 +13921,12 @@
     <mergeCell ref="A38:H38"/>
     <mergeCell ref="A54:C54"/>
     <mergeCell ref="A55:C55"/>
+    <mergeCell ref="B70:C70"/>
+    <mergeCell ref="E70:F70"/>
+    <mergeCell ref="G70:H70"/>
+    <mergeCell ref="B72:C72"/>
+    <mergeCell ref="E72:F72"/>
+    <mergeCell ref="G72:H72"/>
   </mergeCells>
   <pageMargins left="0.70866141732283472" right="0.31496062992125984" top="0.74803149606299213" bottom="0.55118110236220474" header="0.31496062992125984" footer="0.31496062992125984"/>
   <pageSetup paperSize="9" scale="70" orientation="portrait" r:id="rId1"/>
@@ -13940,15 +13940,15 @@
             <anchor moveWithCells="1">
               <from>
                 <xdr:col>4</xdr:col>
-                <xdr:colOff>771525</xdr:colOff>
+                <xdr:colOff>769620</xdr:colOff>
                 <xdr:row>11</xdr:row>
-                <xdr:rowOff>85725</xdr:rowOff>
+                <xdr:rowOff>83820</xdr:rowOff>
               </from>
               <to>
                 <xdr:col>6</xdr:col>
-                <xdr:colOff>476250</xdr:colOff>
+                <xdr:colOff>480060</xdr:colOff>
                 <xdr:row>15</xdr:row>
-                <xdr:rowOff>57150</xdr:rowOff>
+                <xdr:rowOff>60960</xdr:rowOff>
               </to>
             </anchor>
           </objectPr>
@@ -13965,22 +13965,22 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <dimension ref="B2:O26"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11.42578125" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.44140625" defaultRowHeight="13.2"/>
   <cols>
     <col min="1" max="1" width="3" style="173" customWidth="1"/>
-    <col min="2" max="2" width="11.42578125" style="173"/>
-    <col min="3" max="3" width="10.28515625" style="173" customWidth="1"/>
+    <col min="2" max="2" width="11.44140625" style="173"/>
+    <col min="3" max="3" width="10.33203125" style="173" customWidth="1"/>
     <col min="4" max="4" width="12" style="173" customWidth="1"/>
-    <col min="5" max="7" width="11.42578125" style="173"/>
-    <col min="8" max="8" width="14.42578125" style="173" customWidth="1"/>
-    <col min="9" max="9" width="11.42578125" style="173"/>
-    <col min="10" max="10" width="11.85546875" style="173" customWidth="1"/>
-    <col min="11" max="11" width="9.85546875" style="173" customWidth="1"/>
-    <col min="12" max="15" width="12.140625" style="173" customWidth="1"/>
-    <col min="16" max="16384" width="11.42578125" style="173"/>
+    <col min="5" max="7" width="11.44140625" style="173"/>
+    <col min="8" max="8" width="14.44140625" style="173" customWidth="1"/>
+    <col min="9" max="9" width="11.44140625" style="173"/>
+    <col min="10" max="10" width="11.88671875" style="173" customWidth="1"/>
+    <col min="11" max="11" width="9.88671875" style="173" customWidth="1"/>
+    <col min="12" max="15" width="12.109375" style="173" customWidth="1"/>
+    <col min="16" max="16384" width="11.44140625" style="173"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="2" spans="2:15">
       <c r="B2" s="203" t="s">
         <v>201</v>
       </c>
@@ -13992,7 +13992,7 @@
       <c r="K2" s="204"/>
       <c r="L2" s="204"/>
     </row>
-    <row r="3" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="3" spans="2:15">
       <c r="B3" s="289" t="s">
         <v>130</v>
       </c>
@@ -14007,7 +14007,7 @@
         <v>3.7900000000000001E-6</v>
       </c>
     </row>
-    <row r="4" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="4" spans="2:15">
       <c r="B4" s="173" t="s">
         <v>202</v>
       </c>
@@ -14028,7 +14028,7 @@
         <v>2.3000000000000001E-10</v>
       </c>
     </row>
-    <row r="5" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="5" spans="2:15">
       <c r="B5" s="173" t="s">
         <v>203</v>
       </c>
@@ -14045,7 +14045,7 @@
       </c>
       <c r="L5" s="289"/>
     </row>
-    <row r="6" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="6" spans="2:15">
       <c r="B6" s="173" t="s">
         <v>204</v>
       </c>
@@ -14065,7 +14065,7 @@
       </c>
       <c r="L6" s="289"/>
     </row>
-    <row r="7" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="7" spans="2:15">
       <c r="B7" s="173" t="s">
         <v>206</v>
       </c>
@@ -14081,7 +14081,7 @@
         <v>133</v>
       </c>
     </row>
-    <row r="8" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="8" spans="2:15">
       <c r="B8" s="173" t="s">
         <v>300</v>
       </c>
@@ -14098,22 +14098,22 @@
         <v>46132</v>
       </c>
     </row>
-    <row r="9" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="9" spans="2:15">
       <c r="B9" s="206"/>
       <c r="C9" s="205"/>
       <c r="J9" s="206"/>
     </row>
-    <row r="10" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="10" spans="2:15">
       <c r="B10" s="206"/>
       <c r="C10" s="205"/>
       <c r="J10" s="206"/>
     </row>
-    <row r="11" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="11" spans="2:15">
       <c r="B11" s="206"/>
       <c r="C11" s="205"/>
       <c r="J11" s="206"/>
     </row>
-    <row r="12" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="12" spans="2:15">
       <c r="B12" s="209" t="s">
         <v>249</v>
       </c>
@@ -14154,7 +14154,7 @@
         <v>1000</v>
       </c>
     </row>
-    <row r="13" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="13" spans="2:15">
       <c r="B13" s="359"/>
       <c r="C13" s="360"/>
       <c r="D13" s="299"/>
@@ -14169,7 +14169,7 @@
       <c r="N13" s="358"/>
       <c r="O13" s="358"/>
     </row>
-    <row r="14" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="14" spans="2:15">
       <c r="B14" s="359"/>
       <c r="C14" s="360"/>
       <c r="D14" s="299"/>
@@ -14184,14 +14184,14 @@
       <c r="N14" s="358"/>
       <c r="O14" s="358"/>
     </row>
-    <row r="15" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="15" spans="2:15">
       <c r="D15" s="210"/>
       <c r="E15" s="210"/>
       <c r="F15" s="210"/>
       <c r="G15" s="210"/>
       <c r="H15" s="210"/>
     </row>
-    <row r="16" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="16" spans="2:15">
       <c r="B16" s="208"/>
       <c r="C16" s="207" t="s">
         <v>208</v>
@@ -14228,7 +14228,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:15">
       <c r="C18" s="700" t="s">
         <v>209</v>
       </c>
@@ -14246,7 +14246,7 @@
       <c r="N18" s="703"/>
       <c r="O18" s="704"/>
     </row>
-    <row r="19" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:15">
       <c r="C19" s="213"/>
       <c r="D19" s="214"/>
       <c r="E19" s="214"/>
@@ -14260,7 +14260,7 @@
       <c r="N19" s="214"/>
       <c r="O19" s="215"/>
     </row>
-    <row r="20" spans="3:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="20" spans="3:15" ht="15.75" customHeight="1">
       <c r="C20" s="216"/>
       <c r="D20" s="208">
         <f>+D12</f>
@@ -14297,7 +14297,7 @@
       </c>
       <c r="O20" s="172"/>
     </row>
-    <row r="21" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:15">
       <c r="C21" s="216"/>
       <c r="D21" s="211">
         <f>D16</f>
@@ -14338,7 +14338,7 @@
       </c>
       <c r="O21" s="172"/>
     </row>
-    <row r="22" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:15">
       <c r="C22" s="216"/>
       <c r="G22" s="217"/>
       <c r="H22" s="215"/>
@@ -14349,7 +14349,7 @@
       <c r="N22" s="287"/>
       <c r="O22" s="172"/>
     </row>
-    <row r="23" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:15">
       <c r="C23" s="216"/>
       <c r="D23" s="260"/>
       <c r="E23" s="261" t="s">
@@ -14379,7 +14379,7 @@
       </c>
       <c r="O23" s="172"/>
     </row>
-    <row r="24" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:15">
       <c r="C24" s="216"/>
       <c r="D24" s="216"/>
       <c r="E24" s="262" t="s">
@@ -14409,7 +14409,7 @@
       </c>
       <c r="O24" s="172"/>
     </row>
-    <row r="25" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:15">
       <c r="C25" s="216"/>
       <c r="D25" s="260"/>
       <c r="E25" s="295" t="s">
@@ -14439,7 +14439,7 @@
       </c>
       <c r="O25" s="172"/>
     </row>
-    <row r="26" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="26" spans="3:15">
       <c r="C26" s="218"/>
       <c r="D26" s="219"/>
       <c r="E26" s="219"/>
@@ -14468,28 +14468,28 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
   <dimension ref="B2:F12"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11.42578125" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.44140625" defaultRowHeight="13.2"/>
   <cols>
-    <col min="1" max="1" width="6.7109375" style="201" customWidth="1"/>
-    <col min="2" max="2" width="38.85546875" style="201" customWidth="1"/>
-    <col min="3" max="5" width="11.42578125" style="201"/>
-    <col min="6" max="6" width="13.5703125" style="201" customWidth="1"/>
-    <col min="7" max="16384" width="11.42578125" style="201"/>
+    <col min="1" max="1" width="6.6640625" style="201" customWidth="1"/>
+    <col min="2" max="2" width="38.88671875" style="201" customWidth="1"/>
+    <col min="3" max="5" width="11.44140625" style="201"/>
+    <col min="6" max="6" width="13.5546875" style="201" customWidth="1"/>
+    <col min="7" max="16384" width="11.44140625" style="201"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:6" x14ac:dyDescent="0.2">
+    <row r="2" spans="2:6">
       <c r="B2" s="285"/>
     </row>
-    <row r="3" spans="2:6" x14ac:dyDescent="0.2">
+    <row r="3" spans="2:6">
       <c r="B3" s="284"/>
     </row>
-    <row r="4" spans="2:6" x14ac:dyDescent="0.2">
+    <row r="4" spans="2:6">
       <c r="B4" s="285" t="s">
         <v>301</v>
       </c>
       <c r="C4" s="349"/>
     </row>
-    <row r="5" spans="2:6" ht="13.9" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="5" spans="2:6" ht="13.95" customHeight="1">
       <c r="B5" s="284" t="s">
         <v>32</v>
       </c>
@@ -14497,11 +14497,11 @@
         <v>46064</v>
       </c>
     </row>
-    <row r="6" spans="2:6" x14ac:dyDescent="0.2">
+    <row r="6" spans="2:6">
       <c r="B6" s="284"/>
       <c r="E6" s="284"/>
     </row>
-    <row r="7" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="7" spans="2:6" ht="15" customHeight="1">
       <c r="B7" s="283" t="s">
         <v>210</v>
       </c>
@@ -14512,7 +14512,7 @@
       <c r="E7" s="705"/>
       <c r="F7" s="284"/>
     </row>
-    <row r="8" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="8" spans="2:6" ht="15" customHeight="1">
       <c r="B8" s="283" t="s">
         <v>211</v>
       </c>
@@ -14523,10 +14523,10 @@
       <c r="E8" s="705"/>
       <c r="F8" s="284"/>
     </row>
-    <row r="9" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="10" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="11" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="12" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="9" spans="2:6" ht="15" customHeight="1"/>
+    <row r="10" spans="2:6" ht="15" customHeight="1"/>
+    <row r="11" spans="2:6" ht="15" customHeight="1"/>
+    <row r="12" spans="2:6" ht="15" customHeight="1"/>
   </sheetData>
   <sheetProtection algorithmName="SHA-512" hashValue="fksItH3sKB6aMM9OjE11xpwc3b7QQ4B/ZgnDmR0PCCclYu+rmlI//dvWUv9w8mTKYTp/W81Rdw2DHPDsFl5ALw==" saltValue="fdRUkgooo9rZMN2n5fqfUw==" spinCount="100000" sheet="1" objects="1" scenarios="1"/>
   <mergeCells count="2">
@@ -14542,18 +14542,18 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
   <sheetPr codeName="Hoja3"/>
   <dimension ref="A2:M9"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11.42578125" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.44140625" defaultRowHeight="13.2"/>
   <cols>
-    <col min="1" max="2" width="10.42578125" customWidth="1"/>
-    <col min="3" max="3" width="18.28515625" customWidth="1"/>
+    <col min="1" max="2" width="10.44140625" customWidth="1"/>
+    <col min="3" max="3" width="18.33203125" customWidth="1"/>
     <col min="4" max="4" width="20" customWidth="1"/>
-    <col min="6" max="6" width="12.42578125" customWidth="1"/>
-    <col min="11" max="11" width="17.7109375" customWidth="1"/>
-    <col min="12" max="12" width="12.42578125" customWidth="1"/>
-    <col min="13" max="13" width="15.42578125" customWidth="1"/>
+    <col min="6" max="6" width="12.44140625" customWidth="1"/>
+    <col min="11" max="11" width="17.6640625" customWidth="1"/>
+    <col min="12" max="12" width="12.44140625" customWidth="1"/>
+    <col min="13" max="13" width="15.44140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:13" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:13" ht="18.75" customHeight="1">
       <c r="A2" s="706" t="s">
         <v>212</v>
       </c>
@@ -14592,7 +14592,7 @@
         <v>223</v>
       </c>
     </row>
-    <row r="3" spans="1:13" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:13" ht="18.75" customHeight="1">
       <c r="A3" s="7">
         <v>4400</v>
       </c>
@@ -14638,7 +14638,7 @@
         <v>225</v>
       </c>
     </row>
-    <row r="4" spans="1:13" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:13" ht="18.75" customHeight="1">
       <c r="A4" s="1"/>
       <c r="B4" s="1"/>
       <c r="C4" s="6" t="str">
@@ -14675,7 +14675,7 @@
         <v>226</v>
       </c>
     </row>
-    <row r="5" spans="1:13" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:13" ht="18.75" customHeight="1">
       <c r="A5" s="1">
         <f>+B3+1</f>
         <v>4402</v>
@@ -14718,7 +14718,7 @@
         <v>226</v>
       </c>
     </row>
-    <row r="6" spans="1:13" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:13" ht="18.75" customHeight="1">
       <c r="A6" s="1"/>
       <c r="B6" s="1"/>
       <c r="C6" s="6" t="str">
@@ -14755,7 +14755,7 @@
         <v>226</v>
       </c>
     </row>
-    <row r="7" spans="1:13" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:13" ht="18.75" customHeight="1">
       <c r="A7" s="1">
         <f>+B5+1</f>
         <v>4404</v>
@@ -14798,7 +14798,7 @@
         <v>226</v>
       </c>
     </row>
-    <row r="8" spans="1:13" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:13" ht="18.75" customHeight="1">
       <c r="A8" s="1"/>
       <c r="B8" s="1"/>
       <c r="C8" s="6" t="str">
@@ -14835,7 +14835,7 @@
         <v>225</v>
       </c>
     </row>
-    <row r="9" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="9" spans="1:13" ht="15" customHeight="1"/>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A2:B2"/>
